--- a/Results/Hydrogen/hydrogen climate change results.xlsx
+++ b/Results/Hydrogen/hydrogen climate change results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40.22958543765144</v>
+        <v>40.22943082527107</v>
       </c>
       <c r="C2" t="n">
-        <v>20.01272008613253</v>
+        <v>20.01211523602478</v>
       </c>
       <c r="D2" t="n">
-        <v>52.3671240162839</v>
+        <v>52.36685348707277</v>
       </c>
       <c r="E2" t="n">
-        <v>20.01272008613253</v>
+        <v>20.01211523602478</v>
       </c>
       <c r="F2" t="n">
-        <v>20.01272008613253</v>
+        <v>20.01211523602478</v>
       </c>
       <c r="G2" t="n">
-        <v>42.12715979200377</v>
+        <v>42.12306327559133</v>
       </c>
       <c r="H2" t="n">
-        <v>88.21923467961895</v>
+        <v>88.21900273035907</v>
       </c>
       <c r="I2" t="n">
-        <v>20.01272008613253</v>
+        <v>20.01211523602478</v>
       </c>
       <c r="J2" t="n">
-        <v>50.65049127510855</v>
+        <v>50.64972013614585</v>
       </c>
       <c r="K2" t="n">
-        <v>33.58886261389245</v>
+        <v>33.58862766647781</v>
       </c>
       <c r="L2" t="n">
-        <v>71.29974186302012</v>
+        <v>27.68889892543006</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7381813863761013</v>
+        <v>0.7381432294219801</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7015930425348215</v>
+        <v>0.7015614001163967</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7381813863761013</v>
+        <v>0.7381432294219801</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7093660098179743</v>
+        <v>0.7093338263272406</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7093660098179742</v>
+        <v>0.7093338263272402</v>
       </c>
       <c r="G3" t="n">
-        <v>0.735942394563884</v>
+        <v>0.7359043517474942</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7381813863761013</v>
+        <v>0.7381432294219801</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7235033885670705</v>
+        <v>0.7234659359229074</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7381813863761013</v>
+        <v>0.7381432294219801</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7381813863761013</v>
+        <v>0.7381432294219801</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7381813863761013</v>
+        <v>0.7381432294219801</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.433094011613418</v>
+        <v>0.9077397083255937</v>
       </c>
       <c r="C4" t="n">
-        <v>0.858291128735036</v>
+        <v>0.8582292416063464</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9468572807893519</v>
+        <v>0.9467880818218793</v>
       </c>
       <c r="E4" t="n">
-        <v>0.842151360180221</v>
+        <v>0.8420907556342103</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8921121151929634</v>
+        <v>0.8920447771991344</v>
       </c>
       <c r="G4" t="n">
-        <v>1.430855019801202</v>
+        <v>1.43064750062835</v>
       </c>
       <c r="H4" t="n">
-        <v>1.498532479416511</v>
+        <v>1.498361259798883</v>
       </c>
       <c r="I4" t="n">
-        <v>1.418416013804388</v>
+        <v>0.8930624148265223</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9396479172259441</v>
+        <v>0.939577189619581</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9090633636078622</v>
+        <v>0.9090005927729489</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9243852031916484</v>
+        <v>0.9243167086149436</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.37343841233924</v>
+        <v>1.373358444053232</v>
       </c>
       <c r="C5" t="n">
-        <v>1.358760414530211</v>
+        <v>1.358681150554159</v>
       </c>
       <c r="D5" t="n">
-        <v>1.371259806450149</v>
+        <v>1.371179838558332</v>
       </c>
       <c r="E5" t="n">
-        <v>1.357800482200736</v>
+        <v>1.357721348883492</v>
       </c>
       <c r="F5" t="n">
-        <v>1.357800482200736</v>
+        <v>1.357721348883492</v>
       </c>
       <c r="G5" t="n">
-        <v>1.371199420527023</v>
+        <v>1.371119566378746</v>
       </c>
       <c r="H5" t="n">
-        <v>1.37343841233924</v>
+        <v>1.373358444053232</v>
       </c>
       <c r="I5" t="n">
-        <v>1.358760414530211</v>
+        <v>1.358681150554159</v>
       </c>
       <c r="J5" t="n">
-        <v>1.37343841233924</v>
+        <v>1.373358444053232</v>
       </c>
       <c r="K5" t="n">
-        <v>1.37343841233924</v>
+        <v>1.373358444053232</v>
       </c>
       <c r="L5" t="n">
-        <v>1.37343841233924</v>
+        <v>1.373358444053232</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.677110698620093</v>
+        <v>1.677001272327971</v>
       </c>
       <c r="C6" t="n">
-        <v>2.408810517279402</v>
+        <v>2.408650453817536</v>
       </c>
       <c r="D6" t="n">
-        <v>2.575860542191447</v>
+        <v>2.575688990408214</v>
       </c>
       <c r="E6" t="n">
-        <v>2.204414828919411</v>
+        <v>2.204268826132764</v>
       </c>
       <c r="F6" t="n">
-        <v>1.686755863035126</v>
+        <v>1.686645587692821</v>
       </c>
       <c r="G6" t="n">
-        <v>2.419266450941651</v>
+        <v>2.419105682990746</v>
       </c>
       <c r="H6" t="n">
-        <v>2.421505442754104</v>
+        <v>2.421344560665485</v>
       </c>
       <c r="I6" t="n">
-        <v>2.406827444944841</v>
+        <v>2.406667267166171</v>
       </c>
       <c r="J6" t="n">
-        <v>2.421651737094063</v>
+        <v>2.421490844892905</v>
       </c>
       <c r="K6" t="n">
-        <v>1.663283184120873</v>
+        <v>1.663174713646578</v>
       </c>
       <c r="L6" t="n">
-        <v>3.199087997762805</v>
+        <v>3.198873365792074</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.283726877014324</v>
+        <v>3.283321765233496</v>
       </c>
       <c r="C7" t="n">
-        <v>4.037367072302779</v>
+        <v>4.036858495136696</v>
       </c>
       <c r="D7" t="n">
-        <v>4.052045197839467</v>
+        <v>4.051535916417158</v>
       </c>
       <c r="E7" t="n">
-        <v>4.923988594084919</v>
+        <v>4.923359807591758</v>
       </c>
       <c r="F7" t="n">
-        <v>4.037365874272147</v>
+        <v>4.036857297301143</v>
       </c>
       <c r="G7" t="n">
-        <v>4.049806078299592</v>
+        <v>4.049296910961288</v>
       </c>
       <c r="H7" t="n">
-        <v>4.052045070111801</v>
+        <v>4.051535788635767</v>
       </c>
       <c r="I7" t="n">
-        <v>4.037367072302779</v>
+        <v>4.036858495136696</v>
       </c>
       <c r="J7" t="n">
-        <v>4.052045070111801</v>
+        <v>4.051535788635767</v>
       </c>
       <c r="K7" t="n">
-        <v>3.084595287585431</v>
+        <v>3.606429620211598</v>
       </c>
       <c r="L7" t="n">
-        <v>4.052045070111801</v>
+        <v>4.051535788635767</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.21927153545571</v>
+        <v>10.21921019805806</v>
       </c>
       <c r="C8" t="n">
-        <v>10.85262606156983</v>
+        <v>10.85258812779364</v>
       </c>
       <c r="D8" t="n">
-        <v>9.984889231682782</v>
+        <v>9.984830458942817</v>
       </c>
       <c r="E8" t="n">
-        <v>10.85262606156983</v>
+        <v>10.85258812779364</v>
       </c>
       <c r="F8" t="n">
-        <v>10.85262606156983</v>
+        <v>10.85258812779364</v>
       </c>
       <c r="G8" t="n">
-        <v>10.221630933523</v>
+        <v>10.22165460521644</v>
       </c>
       <c r="H8" t="n">
-        <v>9.42994396181191</v>
+        <v>9.429883858664754</v>
       </c>
       <c r="I8" t="n">
-        <v>10.85262606156983</v>
+        <v>10.85258812779364</v>
       </c>
       <c r="J8" t="n">
-        <v>10.07925155478542</v>
+        <v>10.0792027200084</v>
       </c>
       <c r="K8" t="n">
-        <v>10.38763371062389</v>
+        <v>10.38757417387575</v>
       </c>
       <c r="L8" t="n">
-        <v>10.57307954921173</v>
+        <v>10.57324074301768</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.393129156096915</v>
+        <v>4.39306701126648</v>
       </c>
       <c r="C9" t="n">
-        <v>4.755806877385885</v>
+        <v>4.75576220858407</v>
       </c>
       <c r="D9" t="n">
-        <v>4.297696141727433</v>
+        <v>4.297635041338408</v>
       </c>
       <c r="E9" t="n">
-        <v>4.755806877385885</v>
+        <v>4.75576220858407</v>
       </c>
       <c r="F9" t="n">
-        <v>4.755806877385885</v>
+        <v>4.75576220858407</v>
       </c>
       <c r="G9" t="n">
-        <v>4.392153872306542</v>
+        <v>4.392127753066371</v>
       </c>
       <c r="H9" t="n">
-        <v>4.073189386223137</v>
+        <v>4.073127740868743</v>
       </c>
       <c r="I9" t="n">
-        <v>4.755806877385885</v>
+        <v>4.75576220858407</v>
       </c>
       <c r="J9" t="n">
-        <v>4.33648669056095</v>
+        <v>4.336429632347117</v>
       </c>
       <c r="K9" t="n">
-        <v>4.461739323221927</v>
+        <v>4.461677911571195</v>
       </c>
       <c r="L9" t="n">
-        <v>4.537621003908569</v>
+        <v>4.537649326855785</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.961674625987635</v>
+        <v>-1.96183733215084</v>
       </c>
       <c r="C2" t="n">
-        <v>1.014680347248169</v>
+        <v>1.014153330034924</v>
       </c>
       <c r="D2" t="n">
-        <v>1.204458203062676</v>
+        <v>1.204256942798034</v>
       </c>
       <c r="E2" t="n">
-        <v>1.014680347248169</v>
+        <v>1.014153330034924</v>
       </c>
       <c r="F2" t="n">
-        <v>1.014680347248169</v>
+        <v>1.014153330034924</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.794832256959931</v>
+        <v>-1.798178327686546</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.713723929323262</v>
+        <v>-1.714023194227144</v>
       </c>
       <c r="I2" t="n">
-        <v>1.014680347248169</v>
+        <v>1.014153330034924</v>
       </c>
       <c r="J2" t="n">
-        <v>6.716408162573991</v>
+        <v>6.715696749679182</v>
       </c>
       <c r="K2" t="n">
-        <v>4.720307402256603</v>
+        <v>4.720142873404019</v>
       </c>
       <c r="L2" t="n">
-        <v>1.598113839716564</v>
+        <v>2.243526176321574</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4787460466000201</v>
+        <v>0.4787082468514982</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4474992488907974</v>
+        <v>0.4474674213607949</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4787460466000201</v>
+        <v>0.4787082468514982</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4508243736059226</v>
+        <v>0.4507919998532299</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4508243736059226</v>
+        <v>0.4507919998532303</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4773250961060379</v>
+        <v>0.4772874095841866</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4787460466000201</v>
+        <v>0.4787082468514982</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4692550759884505</v>
+        <v>0.4692179720486337</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4787460466000201</v>
+        <v>0.4787082468514982</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4787460466000201</v>
+        <v>0.4787082468514982</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4787460466000201</v>
+        <v>0.4787082468514982</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6859469825349106</v>
+        <v>0.6857635779552169</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4788455823432832</v>
+        <v>0.4787871816138128</v>
       </c>
       <c r="D4" t="n">
-        <v>0.493484649605041</v>
+        <v>0.6997852588784139</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4747620715035064</v>
+        <v>0.474704790219538</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4813659712147369</v>
+        <v>0.4813029405089077</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6845260320409263</v>
+        <v>0.4893242011690294</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7268904058841479</v>
+        <v>0.7267362590427908</v>
       </c>
       <c r="I4" t="n">
-        <v>0.481318964139442</v>
+        <v>0.4812547636334759</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7094348040027783</v>
+        <v>0.7092476781529895</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5032733021963234</v>
+        <v>0.5032141755973907</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4931623995928691</v>
+        <v>0.4930981269636981</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.808986934650604</v>
+        <v>0.808912763933918</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7994959640390361</v>
+        <v>0.799422489131052</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8070948411506028</v>
+        <v>0.8070206707477998</v>
       </c>
       <c r="E5" t="n">
-        <v>0.793382428443953</v>
+        <v>0.7933090961223647</v>
       </c>
       <c r="F5" t="n">
-        <v>0.793382428443953</v>
+        <v>0.7933090961223647</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8075659841566228</v>
+        <v>0.8074919266666067</v>
       </c>
       <c r="H5" t="n">
-        <v>0.808986934650604</v>
+        <v>0.808912763933918</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7994959640390361</v>
+        <v>0.799422489131052</v>
       </c>
       <c r="J5" t="n">
-        <v>0.808986934650604</v>
+        <v>0.808912763933918</v>
       </c>
       <c r="K5" t="n">
-        <v>0.808986934650604</v>
+        <v>0.808912763933918</v>
       </c>
       <c r="L5" t="n">
-        <v>0.808986934650604</v>
+        <v>0.808912763933918</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8769855700390282</v>
+        <v>0.8768849321154724</v>
       </c>
       <c r="C6" t="n">
-        <v>1.187125555612979</v>
+        <v>1.186980034014433</v>
       </c>
       <c r="D6" t="n">
-        <v>1.266988309533339</v>
+        <v>1.26683248765833</v>
       </c>
       <c r="E6" t="n">
-        <v>1.098621446208692</v>
+        <v>1.098488411534104</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8752156035334624</v>
+        <v>0.8751142974679166</v>
       </c>
       <c r="G6" t="n">
-        <v>1.198586639010772</v>
+        <v>1.19844040788766</v>
       </c>
       <c r="H6" t="n">
-        <v>1.200007589506007</v>
+        <v>1.199861245156225</v>
       </c>
       <c r="I6" t="n">
-        <v>1.190516618893183</v>
+        <v>1.19037097035211</v>
       </c>
       <c r="J6" t="n">
-        <v>1.200071072606962</v>
+        <v>1.199924719274573</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8709852701805263</v>
+        <v>0.8708854812772938</v>
       </c>
       <c r="L6" t="n">
-        <v>1.537431099529563</v>
+        <v>1.537237010995717</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.333967375942274</v>
+        <v>1.333689911760626</v>
       </c>
       <c r="C7" t="n">
-        <v>1.591453540306652</v>
+        <v>1.59110797590606</v>
       </c>
       <c r="D7" t="n">
-        <v>1.600944497390244</v>
+        <v>1.600598237124632</v>
       </c>
       <c r="E7" t="n">
-        <v>1.899539390979714</v>
+        <v>1.899114437453354</v>
       </c>
       <c r="F7" t="n">
-        <v>1.591453468282268</v>
+        <v>1.591107903947547</v>
       </c>
       <c r="G7" t="n">
-        <v>1.599523560424229</v>
+        <v>1.599177413441611</v>
       </c>
       <c r="H7" t="n">
-        <v>1.60094451091821</v>
+        <v>1.600598250708926</v>
       </c>
       <c r="I7" t="n">
-        <v>1.591453540306652</v>
+        <v>1.59110797590606</v>
       </c>
       <c r="J7" t="n">
-        <v>1.60094451091821</v>
+        <v>1.600598250708926</v>
       </c>
       <c r="K7" t="n">
-        <v>1.446256904723223</v>
+        <v>1.44595050517885</v>
       </c>
       <c r="L7" t="n">
-        <v>1.60094451091821</v>
+        <v>1.600598250708926</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.88758966312978</v>
+        <v>10.88752795114851</v>
       </c>
       <c r="C8" t="n">
-        <v>11.00567980277276</v>
+        <v>11.00564099185411</v>
       </c>
       <c r="D8" t="n">
-        <v>10.80592031777833</v>
+        <v>10.80585940566278</v>
       </c>
       <c r="E8" t="n">
-        <v>11.00567980277276</v>
+        <v>11.00564099185411</v>
       </c>
       <c r="F8" t="n">
-        <v>11.00567980277276</v>
+        <v>11.00564099185411</v>
       </c>
       <c r="G8" t="n">
-        <v>10.88329502201343</v>
+        <v>10.88331703981609</v>
       </c>
       <c r="H8" t="n">
-        <v>10.87615043559091</v>
+        <v>10.87609139141626</v>
       </c>
       <c r="I8" t="n">
-        <v>11.00567980277276</v>
+        <v>11.00564099185411</v>
       </c>
       <c r="J8" t="n">
-        <v>10.67738527835352</v>
+        <v>10.67733635943306</v>
       </c>
       <c r="K8" t="n">
-        <v>10.70781265024044</v>
+        <v>10.70775088511601</v>
       </c>
       <c r="L8" t="n">
-        <v>10.7984035645366</v>
+        <v>10.78594077318138</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.508802256735694</v>
+        <v>4.50873938467036</v>
       </c>
       <c r="C9" t="n">
-        <v>4.669300943380462</v>
+        <v>4.669255246524884</v>
       </c>
       <c r="D9" t="n">
-        <v>4.475539331037316</v>
+        <v>4.475476784655234</v>
       </c>
       <c r="E9" t="n">
-        <v>4.669300943380462</v>
+        <v>4.669255246524884</v>
       </c>
       <c r="F9" t="n">
-        <v>4.669300943380462</v>
+        <v>4.669255246524884</v>
       </c>
       <c r="G9" t="n">
-        <v>4.507170626654109</v>
+        <v>4.50714325724325</v>
       </c>
       <c r="H9" t="n">
-        <v>4.504094485030696</v>
+        <v>4.504032694408256</v>
       </c>
       <c r="I9" t="n">
-        <v>4.669300943380462</v>
+        <v>4.669255246524884</v>
       </c>
       <c r="J9" t="n">
-        <v>4.423243243780966</v>
+        <v>4.423185576279483</v>
       </c>
       <c r="K9" t="n">
-        <v>4.435586365629272</v>
+        <v>4.435523471770972</v>
       </c>
       <c r="L9" t="n">
-        <v>4.472496355777478</v>
+        <v>4.472448466641765</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.17093170365084</v>
+        <v>11.16862161484197</v>
       </c>
       <c r="C2" t="n">
-        <v>14.85142216425942</v>
+        <v>14.85015747556377</v>
       </c>
       <c r="D2" t="n">
-        <v>28.68168221450503</v>
+        <v>28.68145304389607</v>
       </c>
       <c r="E2" t="n">
-        <v>12.077234097223</v>
+        <v>12.07683485092544</v>
       </c>
       <c r="F2" t="n">
-        <v>12.077234097223</v>
+        <v>12.07683485092544</v>
       </c>
       <c r="G2" t="n">
-        <v>23.08411476385364</v>
+        <v>23.08017417920552</v>
       </c>
       <c r="H2" t="n">
-        <v>40.53056426824227</v>
+        <v>40.53026496011675</v>
       </c>
       <c r="I2" t="n">
-        <v>12.077234097223</v>
+        <v>12.07683485092544</v>
       </c>
       <c r="J2" t="n">
-        <v>34.86525859893749</v>
+        <v>34.86459160164421</v>
       </c>
       <c r="K2" t="n">
-        <v>18.09475987251558</v>
+        <v>18.09455420485605</v>
       </c>
       <c r="L2" t="n">
-        <v>21.50801473980471</v>
+        <v>21.50378474938267</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6830596953494673</v>
+        <v>0.6830200871918478</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6615205008079863</v>
+        <v>0.6614875667884768</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6830596953494673</v>
+        <v>0.6830200871918479</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6556126317392043</v>
+        <v>0.6555791087662948</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6556126317392044</v>
+        <v>0.6555791087662949</v>
       </c>
       <c r="G3" t="n">
-        <v>0.680755958308205</v>
+        <v>0.680716493213085</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6830596953494673</v>
+        <v>0.6830200871918479</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6678719757882936</v>
+        <v>0.6678332525278001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6830596953494678</v>
+        <v>0.6830200871918479</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6830596953494673</v>
+        <v>0.6830200871918479</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6830596953494673</v>
+        <v>0.6830200871918479</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.192010310156808</v>
+        <v>0.7939614127031336</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7762757306236194</v>
+        <v>0.7762131020077584</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8140840883588503</v>
+        <v>0.8140144308050518</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7445237314627102</v>
+        <v>0.7444636667260008</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7774665246346333</v>
+        <v>0.777399299254218</v>
       </c>
       <c r="G4" t="n">
-        <v>1.189706573115544</v>
+        <v>1.18949650764997</v>
       </c>
       <c r="H4" t="n">
-        <v>1.271585925692368</v>
+        <v>1.271418163201664</v>
       </c>
       <c r="I4" t="n">
-        <v>1.17682259059563</v>
+        <v>1.176613266964687</v>
       </c>
       <c r="J4" t="n">
-        <v>1.226027179440581</v>
+        <v>1.225826774445845</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7934633192069213</v>
+        <v>0.793400548139188</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7967967172426621</v>
+        <v>0.7967268685299091</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.207055207586202</v>
+        <v>1.206975213139003</v>
       </c>
       <c r="C5" t="n">
-        <v>1.206135331785245</v>
+        <v>1.20605654761994</v>
       </c>
       <c r="D5" t="n">
-        <v>1.205053793180108</v>
+        <v>1.204973798836385</v>
       </c>
       <c r="E5" t="n">
-        <v>1.190500334751852</v>
+        <v>1.190421352885985</v>
       </c>
       <c r="F5" t="n">
-        <v>1.190500334751852</v>
+        <v>1.190421352885985</v>
       </c>
       <c r="G5" t="n">
-        <v>1.204751470544938</v>
+        <v>1.204671619160239</v>
       </c>
       <c r="H5" t="n">
-        <v>1.207055207586202</v>
+        <v>1.206975213139003</v>
       </c>
       <c r="I5" t="n">
-        <v>1.191867488025028</v>
+        <v>1.191788378474955</v>
       </c>
       <c r="J5" t="n">
-        <v>1.207055207586202</v>
+        <v>1.206975213139003</v>
       </c>
       <c r="K5" t="n">
-        <v>1.207055207586202</v>
+        <v>1.206975213139003</v>
       </c>
       <c r="L5" t="n">
-        <v>1.207055207586202</v>
+        <v>1.206975213139003</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.443668816261058</v>
+        <v>1.443556703736947</v>
       </c>
       <c r="C6" t="n">
-        <v>2.056804413947482</v>
+        <v>2.056641243560789</v>
       </c>
       <c r="D6" t="n">
-        <v>2.18342892375199</v>
+        <v>2.183253570203951</v>
       </c>
       <c r="E6" t="n">
-        <v>1.874270785406125</v>
+        <v>1.874121603262554</v>
       </c>
       <c r="F6" t="n">
-        <v>1.448281443800871</v>
+        <v>1.448168631925004</v>
       </c>
       <c r="G6" t="n">
-        <v>2.054075657002862</v>
+        <v>2.053911307798263</v>
       </c>
       <c r="H6" t="n">
-        <v>2.056379394046696</v>
+        <v>2.056214901779585</v>
       </c>
       <c r="I6" t="n">
-        <v>2.041191674482952</v>
+        <v>2.041028067112978</v>
       </c>
       <c r="J6" t="n">
-        <v>2.056499808675386</v>
+        <v>2.056335306114171</v>
       </c>
       <c r="K6" t="n">
-        <v>1.432287402758361</v>
+        <v>1.432176263214863</v>
       </c>
       <c r="L6" t="n">
-        <v>2.696406826058026</v>
+        <v>2.696187618769439</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.368629206433552</v>
+        <v>2.368282665040455</v>
       </c>
       <c r="C7" t="n">
-        <v>2.89019607819221</v>
+        <v>2.889763116156041</v>
       </c>
       <c r="D7" t="n">
-        <v>2.891116156608886</v>
+        <v>2.890681984252476</v>
       </c>
       <c r="E7" t="n">
-        <v>3.47886631035287</v>
+        <v>3.478331898791555</v>
       </c>
       <c r="F7" t="n">
-        <v>2.875927646100232</v>
+        <v>2.875494358778193</v>
       </c>
       <c r="G7" t="n">
-        <v>2.888812216951911</v>
+        <v>2.88837818769634</v>
       </c>
       <c r="H7" t="n">
-        <v>2.891115953993171</v>
+        <v>2.890681781675096</v>
       </c>
       <c r="I7" t="n">
-        <v>2.875928234431986</v>
+        <v>2.875494947011051</v>
       </c>
       <c r="J7" t="n">
-        <v>2.891115953993171</v>
+        <v>2.890681781675096</v>
       </c>
       <c r="K7" t="n">
-        <v>2.233211822747414</v>
+        <v>2.588001767080614</v>
       </c>
       <c r="L7" t="n">
-        <v>2.891115953993171</v>
+        <v>2.890681781675096</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.557913070481796</v>
+        <v>9.557912949204468</v>
       </c>
       <c r="C8" t="n">
-        <v>9.532909660162167</v>
+        <v>9.532880464207972</v>
       </c>
       <c r="D8" t="n">
-        <v>11.48421108984153</v>
+        <v>11.48416085874909</v>
       </c>
       <c r="E8" t="n">
-        <v>10.47973434047148</v>
+        <v>10.47968966896888</v>
       </c>
       <c r="F8" t="n">
-        <v>10.47973434047148</v>
+        <v>10.47968966896888</v>
       </c>
       <c r="G8" t="n">
-        <v>10.39850173255961</v>
+        <v>10.39850986057385</v>
       </c>
       <c r="H8" t="n">
-        <v>11.31954159663727</v>
+        <v>11.31949227162202</v>
       </c>
       <c r="I8" t="n">
-        <v>10.47973434047148</v>
+        <v>10.47968966896888</v>
       </c>
       <c r="J8" t="n">
-        <v>11.20693085455111</v>
+        <v>11.20683121478856</v>
       </c>
       <c r="K8" t="n">
-        <v>10.9908489884813</v>
+        <v>10.99078130923746</v>
       </c>
       <c r="L8" t="n">
-        <v>11.91900518225137</v>
+        <v>11.91904421694413</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.373436826735341</v>
+        <v>3.373406861037892</v>
       </c>
       <c r="C9" t="n">
-        <v>3.397552333374298</v>
+        <v>3.397507265447509</v>
       </c>
       <c r="D9" t="n">
-        <v>5.507932165075729</v>
+        <v>5.507879778800826</v>
       </c>
       <c r="E9" t="n">
-        <v>4.296280315521487</v>
+        <v>4.296231276119087</v>
       </c>
       <c r="F9" t="n">
-        <v>4.296280315521487</v>
+        <v>4.296231276119088</v>
       </c>
       <c r="G9" t="n">
-        <v>4.355815465261922</v>
+        <v>4.355772569509432</v>
       </c>
       <c r="H9" t="n">
-        <v>5.441604955927708</v>
+        <v>5.441552933998084</v>
       </c>
       <c r="I9" t="n">
-        <v>4.296280315521487</v>
+        <v>4.296231276119088</v>
       </c>
       <c r="J9" t="n">
-        <v>5.294557095923524</v>
+        <v>5.294450655387709</v>
       </c>
       <c r="K9" t="n">
-        <v>4.880128038944124</v>
+        <v>4.880058800424239</v>
       </c>
       <c r="L9" t="n">
-        <v>5.802647017362043</v>
+        <v>5.802636658332404</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.727568735107624</v>
+        <v>5.725402184150423</v>
       </c>
       <c r="C2" t="n">
-        <v>10.1206495995628</v>
+        <v>10.11956972254828</v>
       </c>
       <c r="D2" t="n">
-        <v>19.15447785813963</v>
+        <v>19.15427538737585</v>
       </c>
       <c r="E2" t="n">
-        <v>6.544276915740832</v>
+        <v>6.543925335290116</v>
       </c>
       <c r="F2" t="n">
-        <v>6.544276915740832</v>
+        <v>6.543925335290116</v>
       </c>
       <c r="G2" t="n">
-        <v>14.54941980066918</v>
+        <v>14.54621765440987</v>
       </c>
       <c r="H2" t="n">
-        <v>21.22775701205097</v>
+        <v>21.22749112229006</v>
       </c>
       <c r="I2" t="n">
-        <v>6.544276915740832</v>
+        <v>6.543925335290116</v>
       </c>
       <c r="J2" t="n">
-        <v>25.64179855316642</v>
+        <v>25.64129144854703</v>
       </c>
       <c r="K2" t="n">
-        <v>8.46346866072016</v>
+        <v>8.463300067447701</v>
       </c>
       <c r="L2" t="n">
-        <v>11.01346568929463</v>
+        <v>11.01056531930908</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6331564137232566</v>
+        <v>0.6331176455458581</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6078124017534011</v>
+        <v>0.6077803457366661</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6331564137232566</v>
+        <v>0.6331176455458581</v>
       </c>
       <c r="E3" t="n">
-        <v>0.605259790861056</v>
+        <v>0.6052265850847027</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6052597908610561</v>
+        <v>0.6052265850847034</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6309310653388807</v>
+        <v>0.6308924173826543</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6331564137232566</v>
+        <v>0.6331176455458581</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6184647676375565</v>
+        <v>0.6184267365316616</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6331564137232566</v>
+        <v>0.6331176455458583</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6331564137232566</v>
+        <v>0.6331176455458581</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6331564137232566</v>
+        <v>0.6331176455458581</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.057471248382502</v>
+        <v>1.057275620535298</v>
       </c>
       <c r="C4" t="n">
-        <v>0.708384547585744</v>
+        <v>0.7083248187481807</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7370448154911866</v>
+        <v>1.083877475540682</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6771726554455323</v>
+        <v>0.6771147583209458</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7048865791079875</v>
+        <v>0.7048225481486767</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7185289163858789</v>
+        <v>0.7184630913026872</v>
       </c>
       <c r="H4" t="n">
-        <v>1.134971288786942</v>
+        <v>1.134813964890856</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7060626186845533</v>
+        <v>0.7059974104516964</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7415110195524616</v>
+        <v>0.7414438773717484</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7167209983629691</v>
+        <v>0.7166607160868141</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7219848467700448</v>
+        <v>0.7219188356574172</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.086909440312395</v>
+        <v>1.08683383016833</v>
       </c>
       <c r="C5" t="n">
-        <v>1.086153939722672</v>
+        <v>1.086079765407646</v>
       </c>
       <c r="D5" t="n">
-        <v>1.085015898240535</v>
+        <v>1.084940288099583</v>
       </c>
       <c r="E5" t="n">
-        <v>1.070155643072593</v>
+        <v>1.070080932490938</v>
       </c>
       <c r="F5" t="n">
-        <v>1.070155643072593</v>
+        <v>1.070080932490938</v>
       </c>
       <c r="G5" t="n">
-        <v>1.084684091928015</v>
+        <v>1.084608602005126</v>
       </c>
       <c r="H5" t="n">
-        <v>1.086909440312395</v>
+        <v>1.08683383016833</v>
       </c>
       <c r="I5" t="n">
-        <v>1.072217794226697</v>
+        <v>1.072142921154129</v>
       </c>
       <c r="J5" t="n">
-        <v>1.086909440312395</v>
+        <v>1.08683383016833</v>
       </c>
       <c r="K5" t="n">
-        <v>1.086909440312395</v>
+        <v>1.08683383016833</v>
       </c>
       <c r="L5" t="n">
-        <v>1.086909440312395</v>
+        <v>1.08683383016833</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.283194833177269</v>
+        <v>1.283090888019865</v>
       </c>
       <c r="C6" t="n">
-        <v>1.812055385638163</v>
+        <v>1.811905592677845</v>
       </c>
       <c r="D6" t="n">
-        <v>1.921994184042143</v>
+        <v>1.921832974455325</v>
       </c>
       <c r="E6" t="n">
-        <v>1.652840243082843</v>
+        <v>1.652702707516627</v>
       </c>
       <c r="F6" t="n">
-        <v>1.285173916138096</v>
+        <v>1.28506930153916</v>
       </c>
       <c r="G6" t="n">
-        <v>1.810058733316171</v>
+        <v>1.80990747878584</v>
       </c>
       <c r="H6" t="n">
-        <v>1.812284081704425</v>
+        <v>1.81213270695292</v>
       </c>
       <c r="I6" t="n">
-        <v>1.79759243561485</v>
+        <v>1.797441797934844</v>
       </c>
       <c r="J6" t="n">
-        <v>1.812388062318411</v>
+        <v>1.812236678245655</v>
       </c>
       <c r="K6" t="n">
-        <v>1.273366728800457</v>
+        <v>1.273263664672113</v>
       </c>
       <c r="L6" t="n">
-        <v>2.364962042972526</v>
+        <v>2.364761124043973</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.926720115307043</v>
+        <v>1.926427535451644</v>
       </c>
       <c r="C7" t="n">
-        <v>2.334222568400682</v>
+        <v>2.333858612668688</v>
       </c>
       <c r="D7" t="n">
-        <v>2.334978276557969</v>
+        <v>2.334612884919641</v>
       </c>
       <c r="E7" t="n">
-        <v>2.791407174942466</v>
+        <v>2.790958497264107</v>
       </c>
       <c r="F7" t="n">
-        <v>2.320286056758592</v>
+        <v>2.319921402305454</v>
       </c>
       <c r="G7" t="n">
-        <v>2.332752720606034</v>
+        <v>2.332387449266164</v>
       </c>
       <c r="H7" t="n">
-        <v>2.334978068990404</v>
+        <v>2.33461267742937</v>
       </c>
       <c r="I7" t="n">
-        <v>2.320286422904705</v>
+        <v>2.319921768415169</v>
       </c>
       <c r="J7" t="n">
-        <v>2.334978068990404</v>
+        <v>2.33461267742937</v>
       </c>
       <c r="K7" t="n">
-        <v>2.098431894575686</v>
+        <v>2.098108690370339</v>
       </c>
       <c r="L7" t="n">
-        <v>2.334978068990404</v>
+        <v>2.33461267742937</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.643507410352743</v>
+        <v>9.643507869509245</v>
       </c>
       <c r="C8" t="n">
-        <v>9.601008656586675</v>
+        <v>9.600979300699038</v>
       </c>
       <c r="D8" t="n">
-        <v>11.63272890523311</v>
+        <v>11.63267890141216</v>
       </c>
       <c r="E8" t="n">
-        <v>10.56585998651859</v>
+        <v>10.56581570387053</v>
       </c>
       <c r="F8" t="n">
-        <v>10.56585998651859</v>
+        <v>10.56581570387053</v>
       </c>
       <c r="G8" t="n">
-        <v>10.54347252858141</v>
+        <v>10.54347538417608</v>
       </c>
       <c r="H8" t="n">
-        <v>11.64187613333856</v>
+        <v>11.64182701432832</v>
       </c>
       <c r="I8" t="n">
-        <v>10.56585998651859</v>
+        <v>10.56581570387053</v>
       </c>
       <c r="J8" t="n">
-        <v>11.34276750660105</v>
+        <v>11.34266555168731</v>
       </c>
       <c r="K8" t="n">
-        <v>11.15749656673671</v>
+        <v>11.15743443581558</v>
       </c>
       <c r="L8" t="n">
-        <v>12.08670304403798</v>
+        <v>12.08671982455647</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.391390288619492</v>
+        <v>3.39136121218457</v>
       </c>
       <c r="C9" t="n">
-        <v>3.41048784073038</v>
+        <v>3.410444237495148</v>
       </c>
       <c r="D9" t="n">
-        <v>5.541287499515763</v>
+        <v>5.541235550644327</v>
       </c>
       <c r="E9" t="n">
-        <v>4.312824852582914</v>
+        <v>4.312776571935561</v>
       </c>
       <c r="F9" t="n">
-        <v>4.312824852582914</v>
+        <v>4.312776571935561</v>
       </c>
       <c r="G9" t="n">
-        <v>4.398484347824367</v>
+        <v>4.398443518981107</v>
       </c>
       <c r="H9" t="n">
-        <v>5.545415845676234</v>
+        <v>5.545364252828231</v>
       </c>
       <c r="I9" t="n">
-        <v>4.312824852582914</v>
+        <v>4.312776571935561</v>
       </c>
       <c r="J9" t="n">
-        <v>5.32949897464471</v>
+        <v>5.329391930462106</v>
       </c>
       <c r="K9" t="n">
-        <v>4.922496552693675</v>
+        <v>4.922433151325711</v>
       </c>
       <c r="L9" t="n">
-        <v>5.853620535070393</v>
+        <v>5.853601759330855</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.696302659603114</v>
+        <v>2.694164972919921</v>
       </c>
       <c r="C2" t="n">
-        <v>6.67833199530023</v>
+        <v>6.677343233682686</v>
       </c>
       <c r="D2" t="n">
-        <v>12.99073130049813</v>
+        <v>12.99054857639739</v>
       </c>
       <c r="E2" t="n">
-        <v>2.707176657026964</v>
+        <v>2.70686003693972</v>
       </c>
       <c r="F2" t="n">
-        <v>2.707176657026964</v>
+        <v>2.70686003693972</v>
       </c>
       <c r="G2" t="n">
-        <v>9.384566643365263</v>
+        <v>9.381665715046347</v>
       </c>
       <c r="H2" t="n">
-        <v>12.07082660253882</v>
+        <v>12.07058222176496</v>
       </c>
       <c r="I2" t="n">
-        <v>2.707176657026964</v>
+        <v>2.70686003693972</v>
       </c>
       <c r="J2" t="n">
-        <v>18.28478835931139</v>
+        <v>18.28433997394301</v>
       </c>
       <c r="K2" t="n">
-        <v>3.735026695320227</v>
+        <v>3.734877182359631</v>
       </c>
       <c r="L2" t="n">
-        <v>5.607363001373893</v>
+        <v>5.605198848675525</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6065234031768616</v>
+        <v>0.6064845129489483</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5763690738208095</v>
+        <v>0.5763372423789577</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6065234031768616</v>
+        <v>0.6064845129489482</v>
       </c>
       <c r="E3" t="n">
-        <v>0.578633550819897</v>
+        <v>0.5786002103829384</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5786335508198971</v>
+        <v>0.5786002103829384</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6043422050252271</v>
+        <v>0.6043034225674454</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6065234031768616</v>
+        <v>0.6064845129489482</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5921080377139791</v>
+        <v>0.592069804028391</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6065234031768616</v>
+        <v>0.6064845129489483</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6065234031768616</v>
+        <v>0.6064845129489482</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6065234031768616</v>
+        <v>0.6064845129489482</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9936074894368671</v>
+        <v>0.6821620497750679</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6714872461631538</v>
+        <v>0.671427766145578</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6959105223933348</v>
+        <v>0.6958500204527868</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6404756824833271</v>
+        <v>0.6404177909026338</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6664616703920273</v>
+        <v>0.6663979427641633</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6800463870552299</v>
+        <v>0.9912327209166329</v>
       </c>
       <c r="H4" t="n">
-        <v>1.062995565397966</v>
+        <v>1.062839475144986</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6678122197439827</v>
+        <v>0.9789991023775779</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7011164365597643</v>
+        <v>1.026128297417414</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6782573973549703</v>
+        <v>0.6781971923369454</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6826254324575096</v>
+        <v>0.6825600587061705</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.031344433772498</v>
+        <v>1.031269507657255</v>
       </c>
       <c r="C5" t="n">
-        <v>1.030691798048841</v>
+        <v>1.030618341438423</v>
       </c>
       <c r="D5" t="n">
-        <v>1.02945164249892</v>
+        <v>1.029376716309631</v>
       </c>
       <c r="E5" t="n">
-        <v>1.014555446329699</v>
+        <v>1.014481390510506</v>
       </c>
       <c r="F5" t="n">
-        <v>1.014555446329699</v>
+        <v>1.014481390510506</v>
       </c>
       <c r="G5" t="n">
-        <v>1.029163235620871</v>
+        <v>1.029088417275753</v>
       </c>
       <c r="H5" t="n">
-        <v>1.031344433772498</v>
+        <v>1.031269507657255</v>
       </c>
       <c r="I5" t="n">
-        <v>1.016929068309626</v>
+        <v>1.016854798736699</v>
       </c>
       <c r="J5" t="n">
-        <v>1.031344433772498</v>
+        <v>1.031269507657255</v>
       </c>
       <c r="K5" t="n">
-        <v>1.031344433772498</v>
+        <v>1.031269507657255</v>
       </c>
       <c r="L5" t="n">
-        <v>1.031344433772498</v>
+        <v>1.031269507657255</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.206429353677458</v>
+        <v>1.206326739208676</v>
       </c>
       <c r="C6" t="n">
-        <v>1.700326762641762</v>
+        <v>1.700179130553469</v>
       </c>
       <c r="D6" t="n">
-        <v>1.803261145635565</v>
+        <v>1.803102168973559</v>
       </c>
       <c r="E6" t="n">
-        <v>1.550824689365938</v>
+        <v>1.550688990882107</v>
       </c>
       <c r="F6" t="n">
-        <v>1.207396627670023</v>
+        <v>1.207293317545004</v>
       </c>
       <c r="G6" t="n">
-        <v>1.698577531218281</v>
+        <v>1.698428342207857</v>
       </c>
       <c r="H6" t="n">
-        <v>1.700758729372572</v>
+        <v>1.700609432592022</v>
       </c>
       <c r="I6" t="n">
-        <v>1.68634336390703</v>
+        <v>1.686194723668803</v>
       </c>
       <c r="J6" t="n">
-        <v>1.700855878584201</v>
+        <v>1.70070657262927</v>
       </c>
       <c r="K6" t="n">
-        <v>1.197246931794842</v>
+        <v>1.197145184473975</v>
       </c>
       <c r="L6" t="n">
-        <v>2.217127096803379</v>
+        <v>2.216929036444688</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.700787437492209</v>
+        <v>1.700520035657846</v>
       </c>
       <c r="C7" t="n">
-        <v>2.052010479708136</v>
+        <v>2.051678656058915</v>
       </c>
       <c r="D7" t="n">
-        <v>2.052663294457993</v>
+        <v>2.052330001198833</v>
       </c>
       <c r="E7" t="n">
-        <v>2.444304638635955</v>
+        <v>2.443895964743185</v>
       </c>
       <c r="F7" t="n">
-        <v>2.03824747433564</v>
+        <v>2.037914837723731</v>
       </c>
       <c r="G7" t="n">
-        <v>2.050481917280169</v>
+        <v>2.050148731896246</v>
       </c>
       <c r="H7" t="n">
-        <v>2.052663115431797</v>
+        <v>2.052329822277746</v>
       </c>
       <c r="I7" t="n">
-        <v>2.03824774996892</v>
+        <v>2.03791511335719</v>
       </c>
       <c r="J7" t="n">
-        <v>2.052663115431797</v>
+        <v>2.052329822277746</v>
       </c>
       <c r="K7" t="n">
-        <v>1.840513442729677</v>
+        <v>1.609338456726018</v>
       </c>
       <c r="L7" t="n">
-        <v>2.052663115431797</v>
+        <v>2.052329822277746</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.699075608901975</v>
+        <v>9.699076599788713</v>
       </c>
       <c r="C8" t="n">
-        <v>9.667558915800022</v>
+        <v>9.667529985016492</v>
       </c>
       <c r="D8" t="n">
-        <v>11.75119153702577</v>
+        <v>11.75114117614617</v>
       </c>
       <c r="E8" t="n">
-        <v>10.64478859205635</v>
+        <v>10.64474614956722</v>
       </c>
       <c r="F8" t="n">
-        <v>10.64478859205635</v>
+        <v>10.64474614956722</v>
       </c>
       <c r="G8" t="n">
-        <v>10.65525259859408</v>
+        <v>10.65525535066931</v>
       </c>
       <c r="H8" t="n">
-        <v>11.80705674463482</v>
+        <v>11.80700728614756</v>
       </c>
       <c r="I8" t="n">
-        <v>10.64478859205635</v>
+        <v>10.64474614956722</v>
       </c>
       <c r="J8" t="n">
-        <v>11.48895916608101</v>
+        <v>11.48885561920161</v>
       </c>
       <c r="K8" t="n">
-        <v>11.28345507055921</v>
+        <v>11.28340525466689</v>
       </c>
       <c r="L8" t="n">
-        <v>12.18276894713182</v>
+        <v>12.18277066638165</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.40495052260494</v>
+        <v>3.404922365723294</v>
       </c>
       <c r="C9" t="n">
-        <v>3.42908826451591</v>
+        <v>3.429046321268924</v>
       </c>
       <c r="D9" t="n">
-        <v>5.571374958074241</v>
+        <v>5.571322929358455</v>
       </c>
       <c r="E9" t="n">
-        <v>4.337304286740129</v>
+        <v>4.337258297497233</v>
       </c>
       <c r="F9" t="n">
-        <v>4.337304286740129</v>
+        <v>4.337258297497233</v>
       </c>
       <c r="G9" t="n">
-        <v>4.438161941812076</v>
+        <v>4.438125122521449</v>
       </c>
       <c r="H9" t="n">
-        <v>5.594351939834</v>
+        <v>5.5943002747052</v>
       </c>
       <c r="I9" t="n">
-        <v>4.337304286740129</v>
+        <v>4.337258297497233</v>
       </c>
       <c r="J9" t="n">
-        <v>5.375243281772499</v>
+        <v>5.375135449897454</v>
       </c>
       <c r="K9" t="n">
-        <v>4.980446787486707</v>
+        <v>4.98039576952393</v>
       </c>
       <c r="L9" t="n">
-        <v>5.882512415924138</v>
+        <v>5.882487782085904</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.285823018722167</v>
+        <v>3.283489406358719</v>
       </c>
       <c r="C2" t="n">
-        <v>2.490824114964925</v>
+        <v>2.489352998656965</v>
       </c>
       <c r="D2" t="n">
-        <v>16.15236283406258</v>
+        <v>16.15214528957522</v>
       </c>
       <c r="E2" t="n">
-        <v>4.812938456847659</v>
+        <v>4.812520923821572</v>
       </c>
       <c r="F2" t="n">
-        <v>4.812938456847659</v>
+        <v>4.812520923821572</v>
       </c>
       <c r="G2" t="n">
-        <v>14.65586323379191</v>
+        <v>14.6520813629752</v>
       </c>
       <c r="H2" t="n">
-        <v>31.28648999082456</v>
+        <v>31.28619312081163</v>
       </c>
       <c r="I2" t="n">
-        <v>4.812938456847659</v>
+        <v>4.812520923821572</v>
       </c>
       <c r="J2" t="n">
-        <v>31.66475938301397</v>
+        <v>31.66406713194777</v>
       </c>
       <c r="K2" t="n">
-        <v>11.84254157182077</v>
+        <v>11.8423479351516</v>
       </c>
       <c r="L2" t="n">
-        <v>16.71311929628079</v>
+        <v>16.70869772565927</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6220618704219186</v>
+        <v>0.6220222949904478</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6007295084828737</v>
+        <v>0.6006962681346218</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6220618704219186</v>
+        <v>0.6220222949904478</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5962642341719616</v>
+        <v>0.596230512844647</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5962642341719614</v>
+        <v>0.5962305128446471</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6198192677359426</v>
+        <v>0.6197798323603083</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6220618704219186</v>
+        <v>0.6220222949904478</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6072588057564156</v>
+        <v>0.6072200978222674</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6220618704219186</v>
+        <v>0.6220222949904478</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6220618704219186</v>
+        <v>0.6220222949904478</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6220618704219186</v>
+        <v>0.6220222949904478</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.036035487358863</v>
+        <v>0.6924165088131247</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6672182497753306</v>
+        <v>0.6671550559060033</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7034103398988425</v>
+        <v>0.7033472061698364</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6478798443801196</v>
+        <v>0.6478195797887175</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6766680121745352</v>
+        <v>0.6766008511572527</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6902432131944646</v>
+        <v>0.6901740461829845</v>
       </c>
       <c r="H4" t="n">
-        <v>1.107718819788871</v>
+        <v>1.10755194725838</v>
       </c>
       <c r="I4" t="n">
-        <v>1.021232422693358</v>
+        <v>0.6776143116449446</v>
       </c>
       <c r="J4" t="n">
-        <v>1.066312939282351</v>
+        <v>1.066113384300777</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6943247074355561</v>
+        <v>0.6942618608297907</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6964858880993592</v>
+        <v>0.6964161051639111</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.096296585786722</v>
+        <v>1.096217447109786</v>
       </c>
       <c r="C5" t="n">
-        <v>1.095354948967028</v>
+        <v>1.095277006391512</v>
       </c>
       <c r="D5" t="n">
-        <v>1.094295140127153</v>
+        <v>1.09421600156776</v>
       </c>
       <c r="E5" t="n">
-        <v>1.080344575504127</v>
+        <v>1.080266401716333</v>
       </c>
       <c r="F5" t="n">
-        <v>1.080344575504127</v>
+        <v>1.080266401716333</v>
       </c>
       <c r="G5" t="n">
-        <v>1.094053983100745</v>
+        <v>1.093974984479646</v>
       </c>
       <c r="H5" t="n">
-        <v>1.096296585786722</v>
+        <v>1.096217447109786</v>
       </c>
       <c r="I5" t="n">
-        <v>1.081493521121219</v>
+        <v>1.081415249941606</v>
       </c>
       <c r="J5" t="n">
-        <v>1.096296585786722</v>
+        <v>1.096217447109786</v>
       </c>
       <c r="K5" t="n">
-        <v>1.096296585786722</v>
+        <v>1.096217447109786</v>
       </c>
       <c r="L5" t="n">
-        <v>1.096296585786722</v>
+        <v>1.096217447109786</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.295307202678561</v>
+        <v>1.295197090281328</v>
       </c>
       <c r="C6" t="n">
-        <v>1.840714122339424</v>
+        <v>1.840554309664967</v>
       </c>
       <c r="D6" t="n">
-        <v>1.953084849469698</v>
+        <v>1.952913186920493</v>
       </c>
       <c r="E6" t="n">
-        <v>1.677136688206011</v>
+        <v>1.67699048058798</v>
       </c>
       <c r="F6" t="n">
-        <v>1.298282272480135</v>
+        <v>1.298171469644949</v>
       </c>
       <c r="G6" t="n">
-        <v>1.837872731623975</v>
+        <v>1.837711780014038</v>
       </c>
       <c r="H6" t="n">
-        <v>1.840115334312058</v>
+        <v>1.839954242646282</v>
       </c>
       <c r="I6" t="n">
-        <v>1.82531226964445</v>
+        <v>1.825152045475999</v>
       </c>
       <c r="J6" t="n">
-        <v>1.840222404238024</v>
+        <v>1.840061302553376</v>
       </c>
       <c r="K6" t="n">
-        <v>1.285187111968505</v>
+        <v>1.285077946537356</v>
       </c>
       <c r="L6" t="n">
-        <v>2.409212983475258</v>
+        <v>2.408998639700684</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.05726167979338</v>
+        <v>2.05691874592333</v>
       </c>
       <c r="C7" t="n">
-        <v>2.504171980011707</v>
+        <v>2.503743665425499</v>
       </c>
       <c r="D7" t="n">
-        <v>2.505113735948365</v>
+        <v>2.504684225210058</v>
       </c>
       <c r="E7" t="n">
-        <v>3.007121691636176</v>
+        <v>3.006593140689759</v>
       </c>
       <c r="F7" t="n">
-        <v>2.490310066121217</v>
+        <v>2.489881423012076</v>
       </c>
       <c r="G7" t="n">
-        <v>2.502871014145419</v>
+        <v>2.50244164351363</v>
       </c>
       <c r="H7" t="n">
-        <v>2.505113616831399</v>
+        <v>2.50468410614377</v>
       </c>
       <c r="I7" t="n">
-        <v>2.490310552165895</v>
+        <v>2.489881908975589</v>
       </c>
       <c r="J7" t="n">
-        <v>2.505113616831399</v>
+        <v>2.50468410614377</v>
       </c>
       <c r="K7" t="n">
-        <v>1.941188055939986</v>
+        <v>1.94086756093273</v>
       </c>
       <c r="L7" t="n">
-        <v>2.505113616831399</v>
+        <v>2.50468410614377</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.415457250838475</v>
+        <v>9.415358651613179</v>
       </c>
       <c r="C8" t="n">
-        <v>9.744495736805071</v>
+        <v>9.744470421474201</v>
       </c>
       <c r="D8" t="n">
-        <v>11.69819334619795</v>
+        <v>11.6981430801781</v>
       </c>
       <c r="E8" t="n">
-        <v>10.58204963038736</v>
+        <v>10.58200472701762</v>
       </c>
       <c r="F8" t="n">
-        <v>10.58204963038735</v>
+        <v>10.58200472701762</v>
       </c>
       <c r="G8" t="n">
-        <v>10.51304084059855</v>
+        <v>10.51303766485157</v>
       </c>
       <c r="H8" t="n">
-        <v>11.43249923226437</v>
+        <v>11.43245009091116</v>
       </c>
       <c r="I8" t="n">
-        <v>10.58204963038735</v>
+        <v>10.58200472701762</v>
       </c>
       <c r="J8" t="n">
-        <v>11.21792631098272</v>
+        <v>11.2178277160418</v>
       </c>
       <c r="K8" t="n">
-        <v>11.05323328167622</v>
+        <v>11.05316198211361</v>
       </c>
       <c r="L8" t="n">
-        <v>11.96907968238661</v>
+        <v>11.96912277428018</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.131692658033262</v>
+        <v>3.13156545715674</v>
       </c>
       <c r="C9" t="n">
-        <v>3.445876476585908</v>
+        <v>3.445832547208004</v>
       </c>
       <c r="D9" t="n">
-        <v>5.55192177900174</v>
+        <v>5.551869510377162</v>
       </c>
       <c r="E9" t="n">
-        <v>4.301539993758047</v>
+        <v>4.301490480501799</v>
       </c>
       <c r="F9" t="n">
-        <v>4.301539993758047</v>
+        <v>4.301490480501799</v>
       </c>
       <c r="G9" t="n">
-        <v>4.359859154205206</v>
+        <v>4.359807183591137</v>
       </c>
       <c r="H9" t="n">
-        <v>5.444280361430319</v>
+        <v>5.444228546210851</v>
       </c>
       <c r="I9" t="n">
-        <v>4.301539993758047</v>
+        <v>4.301490480501799</v>
       </c>
       <c r="J9" t="n">
-        <v>5.265254147869482</v>
+        <v>5.265148412926903</v>
       </c>
       <c r="K9" t="n">
-        <v>4.858950390403233</v>
+        <v>4.858877745008726</v>
       </c>
       <c r="L9" t="n">
-        <v>5.796954724312496</v>
+        <v>5.796946144559209</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.546327191415968</v>
+        <v>1.544415551581109</v>
       </c>
       <c r="C2" t="n">
-        <v>1.350457148476505</v>
+        <v>1.349334518963903</v>
       </c>
       <c r="D2" t="n">
-        <v>2.096069622373691</v>
+        <v>2.095895988108304</v>
       </c>
       <c r="E2" t="n">
-        <v>2.035408574493538</v>
+        <v>2.035066062995643</v>
       </c>
       <c r="F2" t="n">
-        <v>2.035408574493538</v>
+        <v>2.035066062995643</v>
       </c>
       <c r="G2" t="n">
-        <v>3.317857889629903</v>
+        <v>3.315109124841486</v>
       </c>
       <c r="H2" t="n">
-        <v>3.117723055890171</v>
+        <v>3.117470067594295</v>
       </c>
       <c r="I2" t="n">
-        <v>2.035408574493538</v>
+        <v>2.035066062995643</v>
       </c>
       <c r="J2" t="n">
-        <v>11.61326041559099</v>
+        <v>11.61269080155997</v>
       </c>
       <c r="K2" t="n">
-        <v>2.289831007856864</v>
+        <v>2.289676999837645</v>
       </c>
       <c r="L2" t="n">
-        <v>3.990125348503126</v>
+        <v>3.98772604407775</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5609606882820629</v>
+        <v>0.5609227247993389</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5467748985911177</v>
+        <v>0.5467430748485927</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5609606882820629</v>
+        <v>0.5609227247993389</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5412030859978326</v>
+        <v>0.5411702573882989</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5412030859978275</v>
+        <v>0.5411702573882989</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5590186737527811</v>
+        <v>0.5589808193591581</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5609606882820629</v>
+        <v>0.5609227247993389</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5480640896843326</v>
+        <v>0.548026794878682</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5609606882820629</v>
+        <v>0.5609227247993389</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5609606882820629</v>
+        <v>0.5609227247993389</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5609606882820629</v>
+        <v>0.5609227247993389</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5995599730916965</v>
+        <v>0.5994958077036362</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5904685849100167</v>
+        <v>0.5904097244409913</v>
       </c>
       <c r="D4" t="n">
-        <v>0.879906979876254</v>
+        <v>0.5988984640317022</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5720223130132458</v>
+        <v>0.5719653251713026</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5864524872443519</v>
+        <v>0.5863900123802914</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5976179585624145</v>
+        <v>0.860681424745722</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9174038147075926</v>
+        <v>0.917250934429521</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5866633744939661</v>
+        <v>0.849727400265246</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6123584560697997</v>
+        <v>0.612293075580589</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5984201015494389</v>
+        <v>0.5983609604646277</v>
       </c>
       <c r="L4" t="n">
-        <v>0.600453826974185</v>
+        <v>0.6003896563492739</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9431011795099316</v>
+        <v>0.9430283366797841</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9426173533938391</v>
+        <v>0.9425459225152223</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9412063640224069</v>
+        <v>0.9411335212142512</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9287531384405819</v>
+        <v>0.9286810921700264</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9287531384405819</v>
+        <v>0.9286810921700264</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9411591649806498</v>
+        <v>0.9410864312396043</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9431011795099316</v>
+        <v>0.9430283366797841</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9302045809121944</v>
+        <v>0.9301324067591282</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9431011795099316</v>
+        <v>0.9430283366797841</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9431011795099316</v>
+        <v>0.9430283366797841</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9431011795099316</v>
+        <v>0.9430283366797841</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.077649111794887</v>
+        <v>1.077550283995456</v>
       </c>
       <c r="C6" t="n">
-        <v>1.501029728421944</v>
+        <v>1.500888141818625</v>
       </c>
       <c r="D6" t="n">
-        <v>1.588086324597905</v>
+        <v>1.587934030005306</v>
       </c>
       <c r="E6" t="n">
-        <v>1.37235394701857</v>
+        <v>1.372223716542372</v>
       </c>
       <c r="F6" t="n">
-        <v>1.07841824451705</v>
+        <v>1.078318757929564</v>
       </c>
       <c r="G6" t="n">
-        <v>1.498479664225498</v>
+        <v>1.498336661335202</v>
       </c>
       <c r="H6" t="n">
-        <v>1.500421678756312</v>
+        <v>1.500278566776912</v>
       </c>
       <c r="I6" t="n">
-        <v>1.487525080157049</v>
+        <v>1.487382636854726</v>
       </c>
       <c r="J6" t="n">
-        <v>1.500504765291564</v>
+        <v>1.500361644609072</v>
       </c>
       <c r="K6" t="n">
-        <v>1.069795894345592</v>
+        <v>1.069697889147536</v>
       </c>
       <c r="L6" t="n">
-        <v>1.942042976256619</v>
+        <v>1.941853605748272</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.57283220355452</v>
+        <v>1.572549738442008</v>
       </c>
       <c r="C7" t="n">
-        <v>1.893306938336592</v>
+        <v>1.892955824586127</v>
       </c>
       <c r="D7" t="n">
-        <v>1.893790865136179</v>
+        <v>1.893438339345597</v>
       </c>
       <c r="E7" t="n">
-        <v>2.251273437188461</v>
+        <v>2.250840731661946</v>
       </c>
       <c r="F7" t="n">
-        <v>1.880894011024606</v>
+        <v>1.880542154010266</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8918487499234</v>
+        <v>1.891496333310505</v>
       </c>
       <c r="H7" t="n">
-        <v>1.893790764452685</v>
+        <v>1.893438238750689</v>
       </c>
       <c r="I7" t="n">
-        <v>1.880894165854955</v>
+        <v>1.880542308830031</v>
       </c>
       <c r="J7" t="n">
-        <v>1.893790764452685</v>
+        <v>1.893438238750689</v>
       </c>
       <c r="K7" t="n">
-        <v>1.707826156113839</v>
+        <v>1.489382312395333</v>
       </c>
       <c r="L7" t="n">
-        <v>1.893790764452685</v>
+        <v>1.893438238750689</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.313396067949148</v>
+        <v>9.313256428790996</v>
       </c>
       <c r="C8" t="n">
-        <v>9.735057159847567</v>
+        <v>9.735028899785878</v>
       </c>
       <c r="D8" t="n">
-        <v>11.95918589333168</v>
+        <v>11.95913646191887</v>
       </c>
       <c r="E8" t="n">
-        <v>10.58866950778068</v>
+        <v>10.58862406529054</v>
       </c>
       <c r="F8" t="n">
-        <v>10.58866950778068</v>
+        <v>10.58862406529054</v>
       </c>
       <c r="G8" t="n">
-        <v>10.70214739498326</v>
+        <v>10.70212849525408</v>
       </c>
       <c r="H8" t="n">
-        <v>11.9419416823503</v>
+        <v>11.94189355948828</v>
       </c>
       <c r="I8" t="n">
-        <v>10.58866950778068</v>
+        <v>10.58862406529054</v>
       </c>
       <c r="J8" t="n">
-        <v>11.55949624197497</v>
+        <v>11.55939743495506</v>
       </c>
       <c r="K8" t="n">
-        <v>11.18313663267063</v>
+        <v>11.18306696203656</v>
       </c>
       <c r="L8" t="n">
-        <v>12.16916365442733</v>
+        <v>12.16917126140677</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.009679852945079</v>
+        <v>3.009516353230762</v>
       </c>
       <c r="C9" t="n">
-        <v>3.422699477536149</v>
+        <v>3.422656359047376</v>
       </c>
       <c r="D9" t="n">
-        <v>5.62287222311064</v>
+        <v>5.622821234887043</v>
       </c>
       <c r="E9" t="n">
-        <v>4.272881344002927</v>
+        <v>4.272832036651034</v>
       </c>
       <c r="F9" t="n">
-        <v>4.272881344002927</v>
+        <v>4.272832036651034</v>
       </c>
       <c r="G9" t="n">
-        <v>4.401543922948894</v>
+        <v>4.401487868320756</v>
       </c>
       <c r="H9" t="n">
-        <v>5.615899707920135</v>
+        <v>5.615849248519665</v>
       </c>
       <c r="I9" t="n">
-        <v>4.272881344002927</v>
+        <v>4.272832036651034</v>
       </c>
       <c r="J9" t="n">
-        <v>5.355581865154423</v>
+        <v>5.355477075186704</v>
       </c>
       <c r="K9" t="n">
-        <v>4.861591409697876</v>
+        <v>4.861520782373881</v>
       </c>
       <c r="L9" t="n">
-        <v>5.849527410578676</v>
+        <v>5.849505704407509</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.330184735587249</v>
+        <v>1.328585633237907</v>
       </c>
       <c r="C2" t="n">
-        <v>1.213963754057905</v>
+        <v>1.213134573041391</v>
       </c>
       <c r="D2" t="n">
-        <v>1.485559575542415</v>
+        <v>1.485402409203228</v>
       </c>
       <c r="E2" t="n">
-        <v>1.593351779636264</v>
+        <v>1.593082915254614</v>
       </c>
       <c r="F2" t="n">
-        <v>1.593351779636264</v>
+        <v>1.593082915254614</v>
       </c>
       <c r="G2" t="n">
-        <v>1.645037624634559</v>
+        <v>1.643046172034849</v>
       </c>
       <c r="H2" t="n">
-        <v>1.706988401610911</v>
+        <v>1.706764681381889</v>
       </c>
       <c r="I2" t="n">
-        <v>1.593351779636264</v>
+        <v>1.593082915254614</v>
       </c>
       <c r="J2" t="n">
-        <v>2.909682944606671</v>
+        <v>2.909157641823925</v>
       </c>
       <c r="K2" t="n">
-        <v>1.069735660768225</v>
+        <v>1.069598964270017</v>
       </c>
       <c r="L2" t="n">
-        <v>1.528888589713349</v>
+        <v>1.5276494654872</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5231214652021557</v>
+        <v>0.5230830220505008</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5121805662925444</v>
+        <v>0.5121485860857391</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5231214652021557</v>
+        <v>0.5230830220505008</v>
       </c>
       <c r="E3" t="n">
-        <v>0.50150425260884</v>
+        <v>0.5014711594869062</v>
       </c>
       <c r="F3" t="n">
-        <v>0.50150425260884</v>
+        <v>0.5014711594869062</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5212268436772345</v>
+        <v>0.5211884862033443</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5231214652021557</v>
+        <v>0.5230830220505008</v>
       </c>
       <c r="I3" t="n">
-        <v>0.510512949737577</v>
+        <v>0.5104750252323185</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5231214652021557</v>
+        <v>0.5230830220505008</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5231214652021557</v>
+        <v>0.5230830220505008</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5231214652021557</v>
+        <v>0.5230830220505008</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7802682109702721</v>
+        <v>0.7800813143812575</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5394985687290739</v>
+        <v>0.5394400855615091</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5465025072264403</v>
+        <v>0.5464430449411312</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5226015778179464</v>
+        <v>0.5225444561092062</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5327593570001705</v>
+        <v>0.5326974481292748</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7783735894453498</v>
+        <v>0.7781867785340778</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8228587640748662</v>
+        <v>0.8227089947530728</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5330727856086421</v>
+        <v>0.5330099910231519</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8016360480030643</v>
+        <v>0.8014553687814602</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5436963102807315</v>
+        <v>0.5436371352497931</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5461740289959615</v>
+        <v>0.5461109581068947</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8753176642527688</v>
+        <v>0.8752459852203907</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8749377576239116</v>
+        <v>0.8748675116075567</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8734226186927346</v>
+        <v>0.87335093954272</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8602669027784055</v>
+        <v>0.8601960617405148</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8602669027784055</v>
+        <v>0.8601960617405148</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8734230427278469</v>
+        <v>0.8733514493732117</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8753176642527688</v>
+        <v>0.8752459852203907</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8627091487881897</v>
+        <v>0.8626379884021738</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8753176642527688</v>
+        <v>0.8752459852203907</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8753176642527688</v>
+        <v>0.8752459852203907</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8753176642527688</v>
+        <v>0.8752459852203907</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9808694823814795</v>
+        <v>0.9807730796919855</v>
       </c>
       <c r="C6" t="n">
-        <v>1.351633174862464</v>
+        <v>1.351495580830154</v>
       </c>
       <c r="D6" t="n">
-        <v>1.428809924095291</v>
+        <v>1.428661700195845</v>
       </c>
       <c r="E6" t="n">
-        <v>1.237400065365584</v>
+        <v>1.237273264193274</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9796949559153894</v>
+        <v>0.9795979019127951</v>
       </c>
       <c r="G6" t="n">
-        <v>1.349984116516613</v>
+        <v>1.349844878288684</v>
       </c>
       <c r="H6" t="n">
-        <v>1.351878738042401</v>
+        <v>1.351739414136731</v>
       </c>
       <c r="I6" t="n">
-        <v>1.339270222576957</v>
+        <v>1.33913141731765</v>
       </c>
       <c r="J6" t="n">
-        <v>1.351951651820973</v>
+        <v>1.35181231948009</v>
       </c>
       <c r="K6" t="n">
-        <v>0.973977794995827</v>
+        <v>0.9738821895899572</v>
       </c>
       <c r="L6" t="n">
-        <v>1.739428928712335</v>
+        <v>1.739244770007389</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.423158714080477</v>
+        <v>1.422907953209126</v>
       </c>
       <c r="C7" t="n">
-        <v>1.706579189564648</v>
+        <v>1.706268491666324</v>
       </c>
       <c r="D7" t="n">
-        <v>1.706959144776913</v>
+        <v>1.706647013754719</v>
       </c>
       <c r="E7" t="n">
-        <v>2.021850070753595</v>
+        <v>2.021467638621251</v>
       </c>
       <c r="F7" t="n">
-        <v>1.694350438879319</v>
+        <v>1.694038826580537</v>
       </c>
       <c r="G7" t="n">
-        <v>1.705064474668585</v>
+        <v>1.704752429431985</v>
       </c>
       <c r="H7" t="n">
-        <v>1.706959096193507</v>
+        <v>1.706646965279162</v>
       </c>
       <c r="I7" t="n">
-        <v>1.694350580728927</v>
+        <v>1.694038968460946</v>
       </c>
       <c r="J7" t="n">
-        <v>1.706959096193507</v>
+        <v>1.706646965279162</v>
       </c>
       <c r="K7" t="n">
-        <v>1.542524060661105</v>
+        <v>1.535577591307431</v>
       </c>
       <c r="L7" t="n">
-        <v>1.706959096193507</v>
+        <v>1.706646965279162</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.117948799001619</v>
+        <v>9.117739263788831</v>
       </c>
       <c r="C8" t="n">
-        <v>9.721434014405526</v>
+        <v>9.721402388781435</v>
       </c>
       <c r="D8" t="n">
-        <v>11.9350724063796</v>
+        <v>11.93502268638526</v>
       </c>
       <c r="E8" t="n">
-        <v>10.56823238620288</v>
+        <v>10.56818808988023</v>
       </c>
       <c r="F8" t="n">
-        <v>10.56823238620288</v>
+        <v>10.56818808988023</v>
       </c>
       <c r="G8" t="n">
-        <v>10.70949340971923</v>
+        <v>10.70945930866263</v>
       </c>
       <c r="H8" t="n">
-        <v>11.93334194111607</v>
+        <v>11.9332932993448</v>
       </c>
       <c r="I8" t="n">
-        <v>10.56823238620288</v>
+        <v>10.56818808988023</v>
       </c>
       <c r="J8" t="n">
-        <v>11.6953352186194</v>
+        <v>11.69523450016747</v>
       </c>
       <c r="K8" t="n">
-        <v>11.22169667595289</v>
+        <v>11.22164253920973</v>
       </c>
       <c r="L8" t="n">
-        <v>12.18962593804908</v>
+        <v>12.18960999308456</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.81446837614016</v>
+        <v>2.81424034436657</v>
       </c>
       <c r="C9" t="n">
-        <v>3.407563813433131</v>
+        <v>3.407521394569886</v>
       </c>
       <c r="D9" t="n">
-        <v>5.590702940438439</v>
+        <v>5.59065189282189</v>
       </c>
       <c r="E9" t="n">
-        <v>4.24676972552315</v>
+        <v>4.246722562742716</v>
       </c>
       <c r="F9" t="n">
-        <v>4.24676972552315</v>
+        <v>4.246722562742716</v>
       </c>
       <c r="G9" t="n">
-        <v>4.386063110040032</v>
+        <v>4.386002437418029</v>
       </c>
       <c r="H9" t="n">
-        <v>5.590021609159638</v>
+        <v>5.589970997104285</v>
       </c>
       <c r="I9" t="n">
-        <v>4.24676972552315</v>
+        <v>4.246722562742716</v>
       </c>
       <c r="J9" t="n">
-        <v>5.373025291082534</v>
+        <v>5.372919205680152</v>
       </c>
       <c r="K9" t="n">
-        <v>4.882601838117949</v>
+        <v>4.882546737102684</v>
       </c>
       <c r="L9" t="n">
-        <v>5.83979991054366</v>
+        <v>5.839769155537748</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.075141648602247</v>
+        <v>2.072838665037255</v>
       </c>
       <c r="C2" t="n">
-        <v>1.518194267254731</v>
+        <v>1.516735966769699</v>
       </c>
       <c r="D2" t="n">
-        <v>4.598866983086515</v>
+        <v>4.598660153693683</v>
       </c>
       <c r="E2" t="n">
-        <v>2.594898314909829</v>
+        <v>2.594477377966216</v>
       </c>
       <c r="F2" t="n">
-        <v>2.594898314909829</v>
+        <v>2.594477377966216</v>
       </c>
       <c r="G2" t="n">
-        <v>7.297768276515453</v>
+        <v>7.293791374317287</v>
       </c>
       <c r="H2" t="n">
-        <v>25.80605122983052</v>
+        <v>25.80574636082396</v>
       </c>
       <c r="I2" t="n">
-        <v>2.594898314909829</v>
+        <v>2.594477377966216</v>
       </c>
       <c r="J2" t="n">
-        <v>11.45207929942206</v>
+        <v>11.4512428150026</v>
       </c>
       <c r="K2" t="n">
-        <v>4.576481670174517</v>
+        <v>4.576293297191821</v>
       </c>
       <c r="L2" t="n">
-        <v>13.28626210408291</v>
+        <v>13.28160122662345</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5949944852326099</v>
+        <v>0.5949540427459349</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5786956689309949</v>
+        <v>0.57866210444773</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5949944852326099</v>
+        <v>0.5949540427459349</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5731727443768013</v>
+        <v>0.5731386293888648</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5731727443768012</v>
+        <v>0.5731386293888647</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5929402728882656</v>
+        <v>0.5928999802864204</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5949944852326099</v>
+        <v>0.5949540427459349</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5813902685304335</v>
+        <v>0.5813507565814716</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5949944852326099</v>
+        <v>0.5949540427459349</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5949944852326099</v>
+        <v>0.5949540427459349</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5949944852326099</v>
+        <v>0.5949540427459349</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9501894205484194</v>
+        <v>0.6407211991527283</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6256415386291792</v>
+        <v>0.6255773833110584</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6395060410961848</v>
+        <v>0.6394418534001357</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6063099451428152</v>
+        <v>0.6062487589283749</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6265575883953948</v>
+        <v>0.6264891847551274</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9481352082040723</v>
+        <v>0.9479237239797165</v>
       </c>
       <c r="H4" t="n">
-        <v>1.02058727819129</v>
+        <v>1.020417623823136</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6271876288737857</v>
+        <v>0.9363745002747754</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9787395438685207</v>
+        <v>0.9785369372231526</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6387071137314075</v>
+        <v>0.6386432205813591</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6442168407898108</v>
+        <v>0.6441456519592268</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.030344559879434</v>
+        <v>1.03026350894049</v>
       </c>
       <c r="C5" t="n">
-        <v>1.029690200859618</v>
+        <v>1.029610356821719</v>
       </c>
       <c r="D5" t="n">
-        <v>1.028343350042419</v>
+        <v>1.028262299134999</v>
       </c>
       <c r="E5" t="n">
-        <v>1.015562541534057</v>
+        <v>1.015482596042529</v>
       </c>
       <c r="F5" t="n">
-        <v>1.015562541534057</v>
+        <v>1.015482596042529</v>
       </c>
       <c r="G5" t="n">
-        <v>1.028290347535088</v>
+        <v>1.028209446480963</v>
       </c>
       <c r="H5" t="n">
-        <v>1.030344559879434</v>
+        <v>1.03026350894049</v>
       </c>
       <c r="I5" t="n">
-        <v>1.016740343177258</v>
+        <v>1.01666022277602</v>
       </c>
       <c r="J5" t="n">
-        <v>1.030344559879434</v>
+        <v>1.03026350894049</v>
       </c>
       <c r="K5" t="n">
-        <v>1.030344559879434</v>
+        <v>1.03026350894049</v>
       </c>
       <c r="L5" t="n">
-        <v>1.030344559879434</v>
+        <v>1.03026350894049</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.200164548900923</v>
+        <v>1.200051369038309</v>
       </c>
       <c r="C6" t="n">
-        <v>1.694234192514212</v>
+        <v>1.694069572902544</v>
       </c>
       <c r="D6" t="n">
-        <v>1.795658717060928</v>
+        <v>1.795481784642919</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5456807742725</v>
+        <v>1.545530302978643</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2026858947814</v>
+        <v>1.202572075992872</v>
       </c>
       <c r="G6" t="n">
-        <v>1.691331817608509</v>
+        <v>1.691165984208838</v>
       </c>
       <c r="H6" t="n">
-        <v>1.69338602995514</v>
+        <v>1.693220046670648</v>
       </c>
       <c r="I6" t="n">
-        <v>1.679781813250677</v>
+        <v>1.679616760503892</v>
       </c>
       <c r="J6" t="n">
-        <v>1.693482961653842</v>
+        <v>1.693316967991981</v>
       </c>
       <c r="K6" t="n">
-        <v>1.191002706707549</v>
+        <v>1.19089050769561</v>
       </c>
       <c r="L6" t="n">
-        <v>2.208597109008558</v>
+        <v>2.208375968134572</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.842188328094738</v>
+        <v>1.841839890844177</v>
       </c>
       <c r="C7" t="n">
-        <v>2.233765369698195</v>
+        <v>2.233330094905554</v>
       </c>
       <c r="D7" t="n">
-        <v>2.234419667715012</v>
+        <v>2.233983185962272</v>
       </c>
       <c r="E7" t="n">
-        <v>2.673441608391212</v>
+        <v>2.672904455860508</v>
       </c>
       <c r="F7" t="n">
-        <v>2.220815057496345</v>
+        <v>2.220379506419716</v>
       </c>
       <c r="G7" t="n">
-        <v>2.232365516373665</v>
+        <v>2.231929184564799</v>
       </c>
       <c r="H7" t="n">
-        <v>2.23441972871801</v>
+        <v>2.233983247024321</v>
       </c>
       <c r="I7" t="n">
-        <v>2.220815512015837</v>
+        <v>2.220379960859854</v>
       </c>
       <c r="J7" t="n">
-        <v>2.23441972871801</v>
+        <v>2.233983247024321</v>
       </c>
       <c r="K7" t="n">
-        <v>1.997939048495567</v>
+        <v>2.006773820705303</v>
       </c>
       <c r="L7" t="n">
-        <v>2.23441972871801</v>
+        <v>2.233983247024321</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.327227009361279</v>
+        <v>9.327093418119526</v>
       </c>
       <c r="C8" t="n">
-        <v>9.713563256757853</v>
+        <v>9.713526391142072</v>
       </c>
       <c r="D8" t="n">
-        <v>11.93060426241939</v>
+        <v>11.93055282611551</v>
       </c>
       <c r="E8" t="n">
-        <v>10.59934652088513</v>
+        <v>10.59929993697645</v>
       </c>
       <c r="F8" t="n">
-        <v>10.59934652088513</v>
+        <v>10.59929993697645</v>
       </c>
       <c r="G8" t="n">
-        <v>10.63314926899434</v>
+        <v>10.63314437056992</v>
       </c>
       <c r="H8" t="n">
-        <v>11.50965247979312</v>
+        <v>11.5096025796872</v>
       </c>
       <c r="I8" t="n">
-        <v>10.59934652088513</v>
+        <v>10.59929993697645</v>
       </c>
       <c r="J8" t="n">
-        <v>11.60831114241835</v>
+        <v>11.60821405185529</v>
       </c>
       <c r="K8" t="n">
-        <v>11.14484252459689</v>
+        <v>11.14476464302984</v>
       </c>
       <c r="L8" t="n">
-        <v>12.01186674300463</v>
+        <v>12.01191381315388</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.029239202483904</v>
+        <v>3.029077951623913</v>
       </c>
       <c r="C9" t="n">
-        <v>3.402925693813814</v>
+        <v>3.402870561835814</v>
       </c>
       <c r="D9" t="n">
-        <v>5.626746108020733</v>
+        <v>5.626692831259729</v>
       </c>
       <c r="E9" t="n">
-        <v>4.289439885690626</v>
+        <v>4.289388674953996</v>
       </c>
       <c r="F9" t="n">
-        <v>4.289439885690626</v>
+        <v>4.289388674953996</v>
       </c>
       <c r="G9" t="n">
-        <v>4.382943180395377</v>
+        <v>4.382886989749878</v>
       </c>
       <c r="H9" t="n">
-        <v>5.455772037868434</v>
+        <v>5.455719381977469</v>
       </c>
       <c r="I9" t="n">
-        <v>4.289439885690626</v>
+        <v>4.289388674953996</v>
       </c>
       <c r="J9" t="n">
-        <v>5.39356808325702</v>
+        <v>5.393462002509447</v>
       </c>
       <c r="K9" t="n">
-        <v>4.852758019831075</v>
+        <v>4.852678966282517</v>
       </c>
       <c r="L9" t="n">
-        <v>5.799613334401295</v>
+        <v>5.79960590841696</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8864428206399222</v>
+        <v>0.8846392486171316</v>
       </c>
       <c r="C2" t="n">
-        <v>1.128052501984745</v>
+        <v>1.126980630660797</v>
       </c>
       <c r="D2" t="n">
-        <v>1.52695335759361</v>
+        <v>1.526783282120132</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7726471573722048</v>
+        <v>0.7723152492784564</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7726471573722048</v>
+        <v>0.7723152492784564</v>
       </c>
       <c r="G2" t="n">
-        <v>1.284575049022824</v>
+        <v>1.281832481942582</v>
       </c>
       <c r="H2" t="n">
-        <v>1.690085715112631</v>
+        <v>1.689832324420631</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7726471573722048</v>
+        <v>0.7723152492784564</v>
       </c>
       <c r="J2" t="n">
-        <v>1.302146340313712</v>
+        <v>1.301479047730188</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001152996535126016</v>
+        <v>0.0009846219054792105</v>
       </c>
       <c r="L2" t="n">
-        <v>1.827016653314843</v>
+        <v>1.824435277143759</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5265148434613018</v>
+        <v>0.5264766484105482</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5146968229393171</v>
+        <v>0.5146650248247291</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5265148434613018</v>
+        <v>0.5264766484105482</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5067057016373796</v>
+        <v>0.5066728221170728</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5067057016373796</v>
+        <v>0.5066728221170728</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5246377852261769</v>
+        <v>0.5245997156756578</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5265148434613018</v>
+        <v>0.5264766484105482</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5140295756711816</v>
+        <v>0.5139921585208668</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5265148434613018</v>
+        <v>0.5264766484105482</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5265148434613018</v>
+        <v>0.5264766484105482</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5265148434613018</v>
+        <v>0.5264766484105482</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7834879459884748</v>
+        <v>0.5465624348644937</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5408812192508087</v>
+        <v>0.5408221140616813</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5480684046637078</v>
+        <v>0.5480019661889506</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5229257153527774</v>
+        <v>0.52286851093883</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5337622896839783</v>
+        <v>0.5336995449917011</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5447498942626784</v>
+        <v>0.5446855021296027</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8380737255877355</v>
+        <v>0.8379202325887957</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5341416847076835</v>
+        <v>0.7708126000025952</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5544882391525112</v>
+        <v>0.8067658231303124</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5425030205800893</v>
+        <v>0.5424434644266032</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5474005865841094</v>
+        <v>0.5473359798718966</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8799724192747677</v>
+        <v>0.8798991385947816</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8795977035856862</v>
+        <v>0.879525838599868</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8780778272585024</v>
+        <v>0.8780045465301179</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8656644988701491</v>
+        <v>0.8655921438428713</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8656644988701491</v>
+        <v>0.8655921438428713</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8780953610396343</v>
+        <v>0.8780222058598907</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8799724192747677</v>
+        <v>0.8798991385947816</v>
       </c>
       <c r="I5" t="n">
-        <v>0.867487151484641</v>
+        <v>0.8674146487051011</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8799724192747677</v>
+        <v>0.8798991385947816</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8799724192747677</v>
+        <v>0.8798991385947816</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8799724192747677</v>
+        <v>0.8798991385947816</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9872452728801805</v>
+        <v>0.987145833491884</v>
       </c>
       <c r="C6" t="n">
-        <v>1.363245311756344</v>
+        <v>1.363102769251462</v>
       </c>
       <c r="D6" t="n">
-        <v>1.440786075729412</v>
+        <v>1.440632726296814</v>
       </c>
       <c r="E6" t="n">
-        <v>1.247799079772966</v>
+        <v>1.247668097191188</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9867103753818173</v>
+        <v>0.9866103866867907</v>
       </c>
       <c r="G6" t="n">
-        <v>1.361016001735808</v>
+        <v>1.360872036542468</v>
       </c>
       <c r="H6" t="n">
-        <v>1.362893059973903</v>
+        <v>1.362748969280327</v>
       </c>
       <c r="I6" t="n">
-        <v>1.350407792180813</v>
+        <v>1.35026447938768</v>
       </c>
       <c r="J6" t="n">
-        <v>1.362966885298102</v>
+        <v>1.362822785829289</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9802674223982114</v>
+        <v>0.9801688124308381</v>
       </c>
       <c r="L6" t="n">
-        <v>1.755288584536694</v>
+        <v>1.755097851821101</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.470151736301206</v>
+        <v>1.469868654579495</v>
       </c>
       <c r="C7" t="n">
-        <v>1.766829249628671</v>
+        <v>1.766477361829943</v>
       </c>
       <c r="D7" t="n">
-        <v>1.767204005931341</v>
+        <v>1.766850702350566</v>
       </c>
       <c r="E7" t="n">
-        <v>2.097510520502399</v>
+        <v>2.097076960409746</v>
       </c>
       <c r="F7" t="n">
-        <v>1.754718547528059</v>
+        <v>1.754366021947001</v>
       </c>
       <c r="G7" t="n">
-        <v>1.76532690708262</v>
+        <v>1.764973729089966</v>
       </c>
       <c r="H7" t="n">
-        <v>1.767203965317749</v>
+        <v>1.766850661824857</v>
       </c>
       <c r="I7" t="n">
-        <v>1.754718697527624</v>
+        <v>1.754366171935173</v>
       </c>
       <c r="J7" t="n">
-        <v>1.767203965317749</v>
+        <v>1.766850661824857</v>
       </c>
       <c r="K7" t="n">
-        <v>1.393162174824442</v>
+        <v>1.594778137533506</v>
       </c>
       <c r="L7" t="n">
-        <v>1.767203965317749</v>
+        <v>1.766850661824857</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.360667530408595</v>
+        <v>8.360187143693743</v>
       </c>
       <c r="C8" t="n">
-        <v>9.659650554278416</v>
+        <v>9.65960112896949</v>
       </c>
       <c r="D8" t="n">
-        <v>11.93537995221041</v>
+        <v>11.93533026483683</v>
       </c>
       <c r="E8" t="n">
-        <v>10.55750153300831</v>
+        <v>10.55744799986867</v>
       </c>
       <c r="F8" t="n">
-        <v>10.55750153300831</v>
+        <v>10.55744799986867</v>
       </c>
       <c r="G8" t="n">
-        <v>10.63971145842176</v>
+        <v>10.63965573583552</v>
       </c>
       <c r="H8" t="n">
-        <v>11.93502510585872</v>
+        <v>11.93497682270472</v>
       </c>
       <c r="I8" t="n">
-        <v>10.55750153300831</v>
+        <v>10.55744799986867</v>
       </c>
       <c r="J8" t="n">
-        <v>11.74051021928907</v>
+        <v>11.74041298661161</v>
       </c>
       <c r="K8" t="n">
-        <v>11.08827035139196</v>
+        <v>11.08817056203325</v>
       </c>
       <c r="L8" t="n">
-        <v>12.18696421127076</v>
+        <v>12.18697546605256</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.063005140680076</v>
+        <v>2.062507701175011</v>
       </c>
       <c r="C9" t="n">
-        <v>3.345587000585036</v>
+        <v>3.345523743845546</v>
       </c>
       <c r="D9" t="n">
-        <v>5.591611381432228</v>
+        <v>5.59156019165014</v>
       </c>
       <c r="E9" t="n">
-        <v>4.224784935690664</v>
+        <v>4.224727810984626</v>
       </c>
       <c r="F9" t="n">
-        <v>4.224784935690664</v>
+        <v>4.224727810984626</v>
       </c>
       <c r="G9" t="n">
-        <v>4.31246616262744</v>
+        <v>4.31237394635549</v>
       </c>
       <c r="H9" t="n">
-        <v>5.591489974825764</v>
+        <v>5.591439352823842</v>
       </c>
       <c r="I9" t="n">
-        <v>4.224784935690665</v>
+        <v>4.224727810984626</v>
       </c>
       <c r="J9" t="n">
-        <v>5.396013318128126</v>
+        <v>5.395908771559211</v>
       </c>
       <c r="K9" t="n">
-        <v>4.736303815999942</v>
+        <v>4.736203340265073</v>
       </c>
       <c r="L9" t="n">
-        <v>5.840834972787342</v>
+        <v>5.840814638419017</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.836405011988627</v>
+        <v>0.8347735266085944</v>
       </c>
       <c r="C2" t="n">
-        <v>1.041716831332786</v>
+        <v>1.040845744581319</v>
       </c>
       <c r="D2" t="n">
-        <v>1.141514943110355</v>
+        <v>1.141360518298043</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6005367781674905</v>
+        <v>0.6002645685876786</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6005367781674905</v>
+        <v>0.6002645685876786</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9525451325032189</v>
+        <v>0.9504488351782739</v>
       </c>
       <c r="H2" t="n">
-        <v>1.31774689056416</v>
+        <v>1.317520996370702</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6005367781674905</v>
+        <v>0.6002645685876786</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7515341932879935</v>
+        <v>0.7509912921048398</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.02335021237807611</v>
+        <v>-0.02350249314089015</v>
       </c>
       <c r="L2" t="n">
-        <v>1.435545699958772</v>
+        <v>1.434093050303632</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4769926849846055</v>
+        <v>0.4769542231695197</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4694805997307915</v>
+        <v>0.4694483883570268</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4769926849846055</v>
+        <v>0.4769542231695197</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4623188173922372</v>
+        <v>0.4622857743034977</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4623188173922368</v>
+        <v>0.4622857743034977</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4752877960193095</v>
+        <v>0.4752494897960297</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4769926849846055</v>
+        <v>0.4769542231695197</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4656273742003083</v>
+        <v>0.4655898967005409</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4769926849846055</v>
+        <v>0.4769542231695197</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4769926849846055</v>
+        <v>0.4769542231695197</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4769926849846055</v>
+        <v>0.4769542231695197</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6795903101796216</v>
+        <v>0.4794716901271714</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4749315169513633</v>
+        <v>0.4748726519214197</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4796818943092531</v>
+        <v>0.4796221046627311</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4616329100216022</v>
+        <v>0.4615759196742273</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4679860382414645</v>
+        <v>0.467924186271943</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6778854212143264</v>
+        <v>0.677698690284144</v>
       </c>
       <c r="H4" t="n">
-        <v>0.723241837786692</v>
+        <v>0.7230913873013062</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4681701015838157</v>
+        <v>0.6680390971886545</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6988713552563371</v>
+        <v>0.4843374840068089</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4751185886139405</v>
+        <v>0.4750590210580151</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4803774099843613</v>
+        <v>0.4803138333164609</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8015379688929314</v>
+        <v>0.8014661387407324</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8012431321891186</v>
+        <v>0.8011727426211557</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7996421665553645</v>
+        <v>0.7995703363028084</v>
       </c>
       <c r="E5" t="n">
-        <v>0.789257890372426</v>
+        <v>0.7891872514120233</v>
       </c>
       <c r="F5" t="n">
-        <v>0.789257890372426</v>
+        <v>0.7891872514120233</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7998330799276366</v>
+        <v>0.7997614053672426</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8015379688929314</v>
+        <v>0.8014661387407324</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7901726581086349</v>
+        <v>0.7901018122717537</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8015379688929314</v>
+        <v>0.8014661387407324</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8015379688929314</v>
+        <v>0.8014661387407324</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8015379688929314</v>
+        <v>0.8014661387407324</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8743919470157315</v>
+        <v>0.8742956084858892</v>
       </c>
       <c r="C6" t="n">
-        <v>1.191033646211603</v>
+        <v>1.190896344676747</v>
       </c>
       <c r="D6" t="n">
-        <v>1.255134479696729</v>
+        <v>1.254986716160888</v>
       </c>
       <c r="E6" t="n">
-        <v>1.093026889019083</v>
+        <v>1.092900759990253</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8736080486922012</v>
+        <v>0.8735114678152194</v>
       </c>
       <c r="G6" t="n">
-        <v>1.188039257777662</v>
+        <v>1.187900481781661</v>
       </c>
       <c r="H6" t="n">
-        <v>1.189744146745817</v>
+        <v>1.189605215158011</v>
       </c>
       <c r="I6" t="n">
-        <v>1.17837883595866</v>
+        <v>1.178240888686171</v>
       </c>
       <c r="J6" t="n">
-        <v>1.189806122640993</v>
+        <v>1.189667182682458</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8685341179895888</v>
+        <v>0.8684385706476636</v>
       </c>
       <c r="L6" t="n">
-        <v>1.519155888829512</v>
+        <v>1.518972465231112</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.331202402689084</v>
+        <v>1.33094862606394</v>
       </c>
       <c r="C7" t="n">
-        <v>1.594498973703378</v>
+        <v>1.59418455867934</v>
       </c>
       <c r="D7" t="n">
-        <v>1.594793820045734</v>
+        <v>1.594477964336075</v>
       </c>
       <c r="E7" t="n">
-        <v>1.887607221338501</v>
+        <v>1.887220712096993</v>
       </c>
       <c r="F7" t="n">
-        <v>1.583428353652121</v>
+        <v>1.583113482337841</v>
       </c>
       <c r="G7" t="n">
-        <v>1.593088921441897</v>
+        <v>1.592773221425427</v>
       </c>
       <c r="H7" t="n">
-        <v>1.594793810407192</v>
+        <v>1.594477954798915</v>
       </c>
       <c r="I7" t="n">
-        <v>1.583428499622896</v>
+        <v>1.583113628329936</v>
       </c>
       <c r="J7" t="n">
-        <v>1.594793810407192</v>
+        <v>1.594477954798915</v>
       </c>
       <c r="K7" t="n">
-        <v>1.43587163484304</v>
+        <v>1.435593207301055</v>
       </c>
       <c r="L7" t="n">
-        <v>1.594793810407192</v>
+        <v>1.594477954798915</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.738299019695191</v>
+        <v>5.736890351929001</v>
       </c>
       <c r="C8" t="n">
-        <v>9.614750565315193</v>
+        <v>9.614692053106555</v>
       </c>
       <c r="D8" t="n">
-        <v>11.89578089847245</v>
+        <v>11.89573146807448</v>
       </c>
       <c r="E8" t="n">
-        <v>10.53235649536093</v>
+        <v>10.53230905651378</v>
       </c>
       <c r="F8" t="n">
-        <v>10.53235649536093</v>
+        <v>10.53230905651378</v>
       </c>
       <c r="G8" t="n">
-        <v>10.44330888679954</v>
+        <v>10.44316236140265</v>
       </c>
       <c r="H8" t="n">
-        <v>11.89409556507967</v>
+        <v>11.89404732828366</v>
       </c>
       <c r="I8" t="n">
-        <v>10.53235649536093</v>
+        <v>10.53230905651378</v>
       </c>
       <c r="J8" t="n">
-        <v>11.67362997848688</v>
+        <v>11.67352992393274</v>
       </c>
       <c r="K8" t="n">
-        <v>11.13229749717298</v>
+        <v>11.13222464091971</v>
       </c>
       <c r="L8" t="n">
-        <v>12.15764506456387</v>
+        <v>12.15763360949985</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.829954183608419</v>
+        <v>0.8285453530828796</v>
       </c>
       <c r="C9" t="n">
-        <v>3.300391870516012</v>
+        <v>3.300322420004482</v>
       </c>
       <c r="D9" t="n">
-        <v>5.547411375016065</v>
+        <v>5.547360658962461</v>
       </c>
       <c r="E9" t="n">
-        <v>4.197826531784773</v>
+        <v>4.197776231006854</v>
       </c>
       <c r="F9" t="n">
-        <v>4.197826531784773</v>
+        <v>4.197776231006854</v>
       </c>
       <c r="G9" t="n">
-        <v>4.114793991504823</v>
+        <v>4.114621227939415</v>
       </c>
       <c r="H9" t="n">
-        <v>5.546741333485842</v>
+        <v>5.546691099956089</v>
       </c>
       <c r="I9" t="n">
-        <v>4.197826531784773</v>
+        <v>4.197776231006854</v>
       </c>
       <c r="J9" t="n">
-        <v>5.323005769725837</v>
+        <v>5.322900109914911</v>
       </c>
       <c r="K9" t="n">
-        <v>4.779503221610839</v>
+        <v>4.779429483463959</v>
       </c>
       <c r="L9" t="n">
-        <v>5.807369490484105</v>
+        <v>5.807340559462879</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.44185011846803</v>
+        <v>30.44171062636335</v>
       </c>
       <c r="C2" t="n">
-        <v>12.52350980286635</v>
+        <v>12.52290970921389</v>
       </c>
       <c r="D2" t="n">
-        <v>46.88476019712459</v>
+        <v>46.88450307453918</v>
       </c>
       <c r="E2" t="n">
-        <v>12.52350980286635</v>
+        <v>12.52290970921389</v>
       </c>
       <c r="F2" t="n">
-        <v>12.52350980286635</v>
+        <v>12.52290970921389</v>
       </c>
       <c r="G2" t="n">
-        <v>37.48499693816535</v>
+        <v>37.48092762597145</v>
       </c>
       <c r="H2" t="n">
-        <v>76.1687554968785</v>
+        <v>76.16851182359288</v>
       </c>
       <c r="I2" t="n">
-        <v>12.52350980286635</v>
+        <v>12.52290970921389</v>
       </c>
       <c r="J2" t="n">
-        <v>47.83703463482118</v>
+        <v>47.83635972355363</v>
       </c>
       <c r="K2" t="n">
-        <v>25.91236433959359</v>
+        <v>25.91214323707197</v>
       </c>
       <c r="L2" t="n">
-        <v>26.68507150997574</v>
+        <v>26.67837620155558</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6850350462919023</v>
+        <v>0.6849966485917566</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6469289852263701</v>
+        <v>0.6468970433018389</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6850350462919023</v>
+        <v>0.6849966485917566</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6537303356411687</v>
+        <v>0.6536978419145378</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6537303356411688</v>
+        <v>0.6536978419145378</v>
       </c>
       <c r="G3" t="n">
-        <v>0.682648420469731</v>
+        <v>0.6826101458250303</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6850350462919023</v>
+        <v>0.6849966485917566</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6694102883792651</v>
+        <v>0.6693726492656903</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6850350462919023</v>
+        <v>0.6849966485917566</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6850350462919023</v>
+        <v>0.6849966485917566</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6850350462919023</v>
+        <v>0.6849966485917566</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.301936153482135</v>
+        <v>1.301736632306952</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7728907108211464</v>
+        <v>0.7728300325536938</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8648155526789791</v>
+        <v>0.8647536299839809</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7589885595062711</v>
+        <v>0.7589290824268263</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8099863294724263</v>
+        <v>0.8099202401647138</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8267070160700081</v>
+        <v>1.299350129540222</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8485720497275289</v>
+        <v>1.360186609858338</v>
       </c>
       <c r="I4" t="n">
-        <v>1.286311395569497</v>
+        <v>1.286112632980886</v>
       </c>
       <c r="J4" t="n">
-        <v>1.330360056071633</v>
+        <v>1.330159926660563</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8243234650655736</v>
+        <v>0.8242619021380546</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8442663694430367</v>
+        <v>0.8441990787272682</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.252074807704806</v>
+        <v>1.251995958523708</v>
       </c>
       <c r="C5" t="n">
-        <v>1.236450049792168</v>
+        <v>1.236371959197644</v>
       </c>
       <c r="D5" t="n">
-        <v>1.250037207187539</v>
+        <v>1.249958358381538</v>
       </c>
       <c r="E5" t="n">
-        <v>1.235728849494246</v>
+        <v>1.23565089945782</v>
       </c>
       <c r="F5" t="n">
-        <v>1.235728849494246</v>
+        <v>1.23565089945782</v>
       </c>
       <c r="G5" t="n">
-        <v>1.249688181882634</v>
+        <v>1.249609455756984</v>
       </c>
       <c r="H5" t="n">
-        <v>1.252074807704806</v>
+        <v>1.251995958523708</v>
       </c>
       <c r="I5" t="n">
-        <v>1.236450049792168</v>
+        <v>1.236371959197644</v>
       </c>
       <c r="J5" t="n">
-        <v>1.252074807704806</v>
+        <v>1.251995958523708</v>
       </c>
       <c r="K5" t="n">
-        <v>1.252074807704806</v>
+        <v>1.251995958523708</v>
       </c>
       <c r="L5" t="n">
-        <v>1.252074807704806</v>
+        <v>1.251995958523708</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.51778090034143</v>
+        <v>1.517672969347075</v>
       </c>
       <c r="C6" t="n">
-        <v>2.16493774281394</v>
+        <v>2.164780426704052</v>
       </c>
       <c r="D6" t="n">
-        <v>2.315559977909791</v>
+        <v>2.315391355828901</v>
       </c>
       <c r="E6" t="n">
-        <v>1.983449421347509</v>
+        <v>1.983305839954065</v>
       </c>
       <c r="F6" t="n">
-        <v>1.523886673486171</v>
+        <v>1.523777991294522</v>
       </c>
       <c r="G6" t="n">
-        <v>2.176159399064328</v>
+        <v>2.17600132338278</v>
       </c>
       <c r="H6" t="n">
-        <v>2.178546024887061</v>
+        <v>2.178387826150067</v>
       </c>
       <c r="I6" t="n">
-        <v>2.162921266973862</v>
+        <v>2.16276382682344</v>
       </c>
       <c r="J6" t="n">
-        <v>2.178675883702657</v>
+        <v>2.178517675086624</v>
       </c>
       <c r="K6" t="n">
-        <v>1.505506848953507</v>
+        <v>1.505399851708275</v>
       </c>
       <c r="L6" t="n">
-        <v>2.868770449327226</v>
+        <v>2.868559741729737</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.753818661983137</v>
+        <v>2.753466389139453</v>
       </c>
       <c r="C7" t="n">
-        <v>3.367626604832153</v>
+        <v>3.367185637377449</v>
       </c>
       <c r="D7" t="n">
-        <v>3.383251550921818</v>
+        <v>3.382809824885455</v>
       </c>
       <c r="E7" t="n">
-        <v>4.093977435245002</v>
+        <v>4.093433240883293</v>
       </c>
       <c r="F7" t="n">
-        <v>3.367625540636042</v>
+        <v>3.36718457332683</v>
       </c>
       <c r="G7" t="n">
-        <v>3.380864736922617</v>
+        <v>3.380423133936789</v>
       </c>
       <c r="H7" t="n">
-        <v>3.38325136274479</v>
+        <v>3.382809636703514</v>
       </c>
       <c r="I7" t="n">
-        <v>3.367626604832153</v>
+        <v>3.367185637377449</v>
       </c>
       <c r="J7" t="n">
-        <v>3.38325136274479</v>
+        <v>3.382809636703514</v>
       </c>
       <c r="K7" t="n">
-        <v>3.018555663097076</v>
+        <v>3.018165766591858</v>
       </c>
       <c r="L7" t="n">
-        <v>3.38325136274479</v>
+        <v>3.382809636703514</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.35366401766216</v>
+        <v>10.35360134418883</v>
       </c>
       <c r="C8" t="n">
-        <v>10.94729221557528</v>
+        <v>10.94725434028802</v>
       </c>
       <c r="D8" t="n">
-        <v>9.991572699202772</v>
+        <v>9.991512801128145</v>
       </c>
       <c r="E8" t="n">
-        <v>10.94729221557528</v>
+        <v>10.94725434028802</v>
       </c>
       <c r="F8" t="n">
-        <v>10.94729221557528</v>
+        <v>10.94725434028802</v>
       </c>
       <c r="G8" t="n">
-        <v>10.22545955145347</v>
+        <v>10.22548817902285</v>
       </c>
       <c r="H8" t="n">
-        <v>9.519704824428411</v>
+        <v>9.519644064879623</v>
       </c>
       <c r="I8" t="n">
-        <v>10.94729221557528</v>
+        <v>10.94725434028802</v>
       </c>
       <c r="J8" t="n">
-        <v>10.03859288805151</v>
+        <v>10.03854185356813</v>
       </c>
       <c r="K8" t="n">
-        <v>10.47839191523696</v>
+        <v>10.47833120901137</v>
       </c>
       <c r="L8" t="n">
-        <v>9.803467662417148</v>
+        <v>10.5262667537964</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.429789553893501</v>
+        <v>4.429726207307015</v>
       </c>
       <c r="C9" t="n">
-        <v>4.770518566724859</v>
+        <v>4.770473380998816</v>
       </c>
       <c r="D9" t="n">
-        <v>4.282340465761276</v>
+        <v>4.28227824944958</v>
       </c>
       <c r="E9" t="n">
-        <v>4.770518566724859</v>
+        <v>4.770473380998816</v>
       </c>
       <c r="F9" t="n">
-        <v>4.770518566724859</v>
+        <v>4.770473380998816</v>
       </c>
       <c r="G9" t="n">
-        <v>4.375199145231844</v>
+        <v>4.375174408837591</v>
       </c>
       <c r="H9" t="n">
-        <v>4.091559055244566</v>
+        <v>4.091496484521393</v>
       </c>
       <c r="I9" t="n">
-        <v>4.770518566724859</v>
+        <v>4.770473380998816</v>
       </c>
       <c r="J9" t="n">
-        <v>4.301853501934527</v>
+        <v>4.301794890622009</v>
       </c>
       <c r="K9" t="n">
-        <v>4.480621307889836</v>
+        <v>4.480558762339611</v>
       </c>
       <c r="L9" t="n">
-        <v>4.206651300849764</v>
+        <v>4.500451478596299</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.20256459983904</v>
+        <v>23.20244335289462</v>
       </c>
       <c r="C2" t="n">
-        <v>15.13460732186453</v>
+        <v>15.13407807888706</v>
       </c>
       <c r="D2" t="n">
-        <v>40.84482042544416</v>
+        <v>40.84459059909546</v>
       </c>
       <c r="E2" t="n">
-        <v>15.13460732186453</v>
+        <v>15.13407807888706</v>
       </c>
       <c r="F2" t="n">
-        <v>15.13460732186453</v>
+        <v>15.13407807888706</v>
       </c>
       <c r="G2" t="n">
-        <v>33.7626541783357</v>
+        <v>33.75944828945904</v>
       </c>
       <c r="H2" t="n">
-        <v>63.35974811083654</v>
+        <v>63.35954606993268</v>
       </c>
       <c r="I2" t="n">
-        <v>15.13460732186453</v>
+        <v>15.13407807888706</v>
       </c>
       <c r="J2" t="n">
-        <v>38.54083441698517</v>
+        <v>38.54011990817393</v>
       </c>
       <c r="K2" t="n">
-        <v>23.03324224011547</v>
+        <v>23.03303473445335</v>
       </c>
       <c r="L2" t="n">
-        <v>57.13698030113397</v>
+        <v>28.4184821097013</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6574163244707413</v>
+        <v>0.6573792474045619</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6192432120159046</v>
+        <v>0.6192117795575454</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6574163244707413</v>
+        <v>0.6573792474045612</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6252938225072822</v>
+        <v>0.6252618805455006</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6252938225072825</v>
+        <v>0.6252618805455006</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6551985945599935</v>
+        <v>0.6551616209843433</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6574163244707413</v>
+        <v>0.6573792474045612</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6428687424756302</v>
+        <v>0.64283229929718</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6574163244707413</v>
+        <v>0.6573792474045612</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6574163244707413</v>
+        <v>0.6573792474045612</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6574163244707413</v>
+        <v>0.6573792474045612</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7943055547877751</v>
+        <v>1.217193676394546</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7491778660901985</v>
+        <v>0.7491201927223248</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8229531684764891</v>
+        <v>0.8228944726319669</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7369374454539201</v>
+        <v>0.7368808731969074</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7779634724195567</v>
+        <v>0.7779014537167879</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7920878248770242</v>
+        <v>1.214976049974325</v>
       </c>
       <c r="H4" t="n">
-        <v>1.269143664723996</v>
+        <v>1.268992283279295</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7797579727926626</v>
+        <v>1.202646728287164</v>
       </c>
       <c r="J4" t="n">
-        <v>0.818820340392035</v>
+        <v>1.242992575935496</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7905685588763445</v>
+        <v>0.7905101890296953</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8074499566546591</v>
+        <v>0.807386906470954</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.163302441219864</v>
+        <v>1.163229612657936</v>
       </c>
       <c r="C5" t="n">
-        <v>1.148754859224754</v>
+        <v>1.148682664550553</v>
       </c>
       <c r="D5" t="n">
-        <v>1.161405588158255</v>
+        <v>1.161332759933576</v>
       </c>
       <c r="E5" t="n">
-        <v>1.146362802726181</v>
+        <v>1.146290735706019</v>
       </c>
       <c r="F5" t="n">
-        <v>1.146362802726181</v>
+        <v>1.146290735706019</v>
       </c>
       <c r="G5" t="n">
-        <v>1.161084711309115</v>
+        <v>1.161011986237717</v>
       </c>
       <c r="H5" t="n">
-        <v>1.163302441219864</v>
+        <v>1.163229612657935</v>
       </c>
       <c r="I5" t="n">
-        <v>1.148754859224754</v>
+        <v>1.148682664550553</v>
       </c>
       <c r="J5" t="n">
-        <v>1.163302441219864</v>
+        <v>1.163229612657935</v>
       </c>
       <c r="K5" t="n">
-        <v>1.163302441219864</v>
+        <v>1.163229612657935</v>
       </c>
       <c r="L5" t="n">
-        <v>1.163302441219864</v>
+        <v>1.163229612657935</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.392161022378785</v>
+        <v>1.392062867297585</v>
       </c>
       <c r="C6" t="n">
-        <v>1.959308821084077</v>
+        <v>1.959167137175308</v>
       </c>
       <c r="D6" t="n">
-        <v>2.094203372472534</v>
+        <v>2.094051760910851</v>
       </c>
       <c r="E6" t="n">
-        <v>1.799736090082454</v>
+        <v>1.799606503277376</v>
       </c>
       <c r="F6" t="n">
-        <v>1.395749748736843</v>
+        <v>1.395650900024628</v>
       </c>
       <c r="G6" t="n">
-        <v>1.971413920032802</v>
+        <v>1.971271592803706</v>
       </c>
       <c r="H6" t="n">
-        <v>1.973631649944598</v>
+        <v>1.973489219224969</v>
       </c>
       <c r="I6" t="n">
-        <v>1.959084067948442</v>
+        <v>1.958942271116545</v>
       </c>
       <c r="J6" t="n">
-        <v>1.973745925246815</v>
+        <v>1.973603485825769</v>
       </c>
       <c r="K6" t="n">
-        <v>1.381359906971874</v>
+        <v>1.381262574333382</v>
       </c>
       <c r="L6" t="n">
-        <v>2.581026341909038</v>
+        <v>2.580837661582814</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.41911453831412</v>
+        <v>2.418822559760078</v>
       </c>
       <c r="C7" t="n">
-        <v>2.94166310222183</v>
+        <v>2.94129888359597</v>
       </c>
       <c r="D7" t="n">
-        <v>2.956210905769426</v>
+        <v>2.955846053220847</v>
       </c>
       <c r="E7" t="n">
-        <v>3.561459793653386</v>
+        <v>3.561011480089892</v>
       </c>
       <c r="F7" t="n">
-        <v>2.94166224386881</v>
+        <v>2.941298025321455</v>
       </c>
       <c r="G7" t="n">
-        <v>2.953992954306186</v>
+        <v>2.953628205283134</v>
       </c>
       <c r="H7" t="n">
-        <v>2.95621068421694</v>
+        <v>2.955845831703356</v>
       </c>
       <c r="I7" t="n">
-        <v>2.94166310222183</v>
+        <v>2.94129888359597</v>
       </c>
       <c r="J7" t="n">
-        <v>2.95621068421694</v>
+        <v>2.955845831703356</v>
       </c>
       <c r="K7" t="n">
-        <v>2.2799107077807</v>
+        <v>2.279637616599191</v>
       </c>
       <c r="L7" t="n">
-        <v>2.95621068421694</v>
+        <v>2.955845831703356</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.47448645630589</v>
+        <v>10.4744248615447</v>
       </c>
       <c r="C8" t="n">
-        <v>10.83824041006521</v>
+        <v>10.83820242225209</v>
       </c>
       <c r="D8" t="n">
-        <v>10.02398814859838</v>
+        <v>10.02392920009892</v>
       </c>
       <c r="E8" t="n">
-        <v>10.83824041006521</v>
+        <v>10.83820242225209</v>
       </c>
       <c r="F8" t="n">
-        <v>10.83824041006521</v>
+        <v>10.83820242225209</v>
       </c>
       <c r="G8" t="n">
-        <v>10.22257108467585</v>
+        <v>10.2225876411482</v>
       </c>
       <c r="H8" t="n">
-        <v>9.667969468061088</v>
+        <v>9.667909392879892</v>
       </c>
       <c r="I8" t="n">
-        <v>10.83824041006521</v>
+        <v>10.83820242225209</v>
       </c>
       <c r="J8" t="n">
-        <v>10.15818842074825</v>
+        <v>10.15814058752589</v>
       </c>
       <c r="K8" t="n">
-        <v>10.44805713650957</v>
+        <v>10.44799765683994</v>
       </c>
       <c r="L8" t="n">
-        <v>9.854849375876956</v>
+        <v>10.42040486741517</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.466366696014235</v>
+        <v>4.466304506302039</v>
       </c>
       <c r="C9" t="n">
-        <v>4.718329467874108</v>
+        <v>4.718284543683713</v>
       </c>
       <c r="D9" t="n">
-        <v>4.282908564642677</v>
+        <v>4.282847452615901</v>
       </c>
       <c r="E9" t="n">
-        <v>4.718329467874108</v>
+        <v>4.718284543683713</v>
       </c>
       <c r="F9" t="n">
-        <v>4.718329467874108</v>
+        <v>4.718284543683713</v>
       </c>
       <c r="G9" t="n">
-        <v>4.361874092555201</v>
+        <v>4.36184510576022</v>
       </c>
       <c r="H9" t="n">
-        <v>4.139154916989552</v>
+        <v>4.139093343029381</v>
       </c>
       <c r="I9" t="n">
-        <v>4.718329467874108</v>
+        <v>4.718284543683713</v>
       </c>
       <c r="J9" t="n">
-        <v>4.337876992262422</v>
+        <v>4.337820401570602</v>
       </c>
       <c r="K9" t="n">
-        <v>4.455633528270837</v>
+        <v>4.455572199810644</v>
       </c>
       <c r="L9" t="n">
-        <v>4.444794077927623</v>
+        <v>4.444765012171218</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.11953512221462</v>
+        <v>20.11941719582687</v>
       </c>
       <c r="C2" t="n">
-        <v>22.51161271419491</v>
+        <v>22.51114605144087</v>
       </c>
       <c r="D2" t="n">
-        <v>35.28823648383511</v>
+        <v>35.28801568265648</v>
       </c>
       <c r="E2" t="n">
-        <v>22.51161271419491</v>
+        <v>22.51114605144087</v>
       </c>
       <c r="F2" t="n">
-        <v>22.51161271419491</v>
+        <v>22.51114605144087</v>
       </c>
       <c r="G2" t="n">
-        <v>30.75602835020459</v>
+        <v>30.75333031466776</v>
       </c>
       <c r="H2" t="n">
-        <v>52.17094376236354</v>
+        <v>52.17075500019711</v>
       </c>
       <c r="I2" t="n">
-        <v>22.51161271419491</v>
+        <v>22.51114605144087</v>
       </c>
       <c r="J2" t="n">
-        <v>38.09531014743047</v>
+        <v>38.09472676323376</v>
       </c>
       <c r="K2" t="n">
-        <v>19.70684476252631</v>
+        <v>19.70665806811902</v>
       </c>
       <c r="L2" t="n">
-        <v>51.84555760444283</v>
+        <v>51.84513940007066</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6691030508745568</v>
+        <v>0.6690667498525024</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6342504779564433</v>
+        <v>0.6342194432597663</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6691030508745568</v>
+        <v>0.6690667498525024</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6401607238963832</v>
+        <v>0.6401291998031896</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6401607238963835</v>
+        <v>0.6401291998031892</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6672816944651109</v>
+        <v>0.6672454826844681</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6691030508745568</v>
+        <v>0.6690667498525024</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6570887214323549</v>
+        <v>0.6570529640197884</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6691030508745568</v>
+        <v>0.6690667498525024</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6691030508745568</v>
+        <v>0.6690667498525024</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6691030508745568</v>
+        <v>0.6690667498525024</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8139580236222392</v>
+        <v>0.8138959656281409</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7905657132393474</v>
+        <v>0.7905091492890964</v>
       </c>
       <c r="D4" t="n">
-        <v>1.237136752513967</v>
+        <v>1.236956811112349</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7780964914781194</v>
+        <v>0.7780409976357755</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8053921457698523</v>
+        <v>0.8053317047452947</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8121366672127814</v>
+        <v>0.8120746984601052</v>
       </c>
       <c r="H4" t="n">
-        <v>1.270345015358174</v>
+        <v>1.270197388682543</v>
       </c>
       <c r="I4" t="n">
-        <v>1.206735907223452</v>
+        <v>1.206557839382678</v>
       </c>
       <c r="J4" t="n">
-        <v>1.245422175926448</v>
+        <v>0.8397068834385706</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8074305127144862</v>
+        <v>0.8073733445000966</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8271430945048015</v>
+        <v>0.8270817415942078</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.16375140291464</v>
+        <v>1.16368086019829</v>
       </c>
       <c r="C5" t="n">
-        <v>1.151737073472435</v>
+        <v>1.151667074365577</v>
       </c>
       <c r="D5" t="n">
-        <v>1.161855294996607</v>
+        <v>1.161784752601039</v>
       </c>
       <c r="E5" t="n">
-        <v>1.147578008684406</v>
+        <v>1.147508119593292</v>
       </c>
       <c r="F5" t="n">
-        <v>1.147578008684406</v>
+        <v>1.147508119593292</v>
       </c>
       <c r="G5" t="n">
-        <v>1.161930046505197</v>
+        <v>1.161859593030256</v>
       </c>
       <c r="H5" t="n">
-        <v>1.16375140291464</v>
+        <v>1.16368086019829</v>
       </c>
       <c r="I5" t="n">
-        <v>1.151737073472435</v>
+        <v>1.151667074365577</v>
       </c>
       <c r="J5" t="n">
-        <v>1.16375140291464</v>
+        <v>1.16368086019829</v>
       </c>
       <c r="K5" t="n">
-        <v>1.16375140291464</v>
+        <v>1.16368086019829</v>
       </c>
       <c r="L5" t="n">
-        <v>1.16375140291464</v>
+        <v>1.16368086019829</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.376148526609294</v>
+        <v>1.376054266649028</v>
       </c>
       <c r="C6" t="n">
-        <v>1.921661446542218</v>
+        <v>1.92152573656371</v>
       </c>
       <c r="D6" t="n">
-        <v>2.051058203841835</v>
+        <v>2.050913126099278</v>
       </c>
       <c r="E6" t="n">
-        <v>1.768415175301644</v>
+        <v>1.768290966458834</v>
       </c>
       <c r="F6" t="n">
-        <v>1.380503601923557</v>
+        <v>1.380408616819295</v>
       </c>
       <c r="G6" t="n">
-        <v>1.933325004896773</v>
+        <v>1.933188744056502</v>
       </c>
       <c r="H6" t="n">
-        <v>1.93514636130743</v>
+        <v>1.93501001122576</v>
       </c>
       <c r="I6" t="n">
-        <v>1.92313203186401</v>
+        <v>1.922996225391822</v>
       </c>
       <c r="J6" t="n">
-        <v>1.935256220120168</v>
+        <v>1.9351198617666</v>
       </c>
       <c r="K6" t="n">
-        <v>1.365764854861735</v>
+        <v>1.36567137674709</v>
       </c>
       <c r="L6" t="n">
-        <v>2.519066342032889</v>
+        <v>2.518886025299865</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.304908229829478</v>
+        <v>2.30464548349809</v>
       </c>
       <c r="C7" t="n">
-        <v>2.793052707631741</v>
+        <v>2.792725589313874</v>
       </c>
       <c r="D7" t="n">
-        <v>2.805067236844355</v>
+        <v>2.804739574876593</v>
       </c>
       <c r="E7" t="n">
-        <v>3.370224679092447</v>
+        <v>3.36982264959083</v>
       </c>
       <c r="F7" t="n">
-        <v>2.793052013545388</v>
+        <v>2.79272489528679</v>
       </c>
       <c r="G7" t="n">
-        <v>2.803245680664496</v>
+        <v>2.802918107978558</v>
       </c>
       <c r="H7" t="n">
-        <v>2.805067037073944</v>
+        <v>2.804739375146589</v>
       </c>
       <c r="I7" t="n">
-        <v>2.793052707631741</v>
+        <v>2.792725589313874</v>
       </c>
       <c r="J7" t="n">
-        <v>2.805067037073944</v>
+        <v>2.804739375146589</v>
       </c>
       <c r="K7" t="n">
-        <v>2.515273143903983</v>
+        <v>2.514983094310877</v>
       </c>
       <c r="L7" t="n">
-        <v>2.805067037073944</v>
+        <v>2.804739375146589</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.52373092848885</v>
+        <v>10.52367032402574</v>
       </c>
       <c r="C8" t="n">
-        <v>10.65012721746412</v>
+        <v>10.65008848833902</v>
       </c>
       <c r="D8" t="n">
-        <v>10.12109668465738</v>
+        <v>10.12103863549618</v>
       </c>
       <c r="E8" t="n">
-        <v>10.65012721746412</v>
+        <v>10.65008848833902</v>
       </c>
       <c r="F8" t="n">
-        <v>10.65012721746412</v>
+        <v>10.65008848833902</v>
       </c>
       <c r="G8" t="n">
-        <v>10.26754607818501</v>
+        <v>10.26755288259755</v>
       </c>
       <c r="H8" t="n">
-        <v>9.84959236117051</v>
+        <v>9.849533062539027</v>
       </c>
       <c r="I8" t="n">
-        <v>10.65012721746412</v>
+        <v>10.65008848833902</v>
       </c>
       <c r="J8" t="n">
-        <v>10.15824912470771</v>
+        <v>10.15819938173105</v>
       </c>
       <c r="K8" t="n">
-        <v>10.49502717506534</v>
+        <v>10.49496831595303</v>
       </c>
       <c r="L8" t="n">
-        <v>9.937685449864102</v>
+        <v>9.937631037275688</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.479353271641997</v>
+        <v>4.479292141374886</v>
       </c>
       <c r="C9" t="n">
-        <v>4.649809200962856</v>
+        <v>4.649764424377675</v>
       </c>
       <c r="D9" t="n">
-        <v>4.31538696887797</v>
+        <v>4.31532687925479</v>
       </c>
       <c r="E9" t="n">
-        <v>4.649809200962856</v>
+        <v>4.649764424377675</v>
       </c>
       <c r="F9" t="n">
-        <v>4.649809200962856</v>
+        <v>4.649764424377675</v>
       </c>
       <c r="G9" t="n">
-        <v>4.374218775620236</v>
+        <v>4.374186435089804</v>
       </c>
       <c r="H9" t="n">
-        <v>4.205877938254478</v>
+        <v>4.205817337001272</v>
       </c>
       <c r="I9" t="n">
-        <v>4.649809200962856</v>
+        <v>4.649764424377675</v>
       </c>
       <c r="J9" t="n">
-        <v>4.33082665658217</v>
+        <v>4.330769945318667</v>
       </c>
       <c r="K9" t="n">
-        <v>4.467690611311773</v>
+        <v>4.467630191730048</v>
       </c>
       <c r="L9" t="n">
-        <v>4.241486492281626</v>
+        <v>4.241427877912149</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.840943414862362</v>
+        <v>5.840772989421816</v>
       </c>
       <c r="C2" t="n">
-        <v>5.04724914948288</v>
+        <v>5.04660045148481</v>
       </c>
       <c r="D2" t="n">
-        <v>12.84607971028086</v>
+        <v>12.84587306252798</v>
       </c>
       <c r="E2" t="n">
-        <v>5.04724914948288</v>
+        <v>5.04660045148481</v>
       </c>
       <c r="F2" t="n">
-        <v>5.04724914948288</v>
+        <v>5.04660045148481</v>
       </c>
       <c r="G2" t="n">
-        <v>11.1017100618152</v>
+        <v>11.09528545459682</v>
       </c>
       <c r="H2" t="n">
-        <v>21.81061872928194</v>
+        <v>21.81023761110933</v>
       </c>
       <c r="I2" t="n">
-        <v>5.04724914948288</v>
+        <v>5.04660045148481</v>
       </c>
       <c r="J2" t="n">
-        <v>38.48200166590083</v>
+        <v>38.4809027794176</v>
       </c>
       <c r="K2" t="n">
-        <v>9.565331703961119</v>
+        <v>9.56506336306747</v>
       </c>
       <c r="L2" t="n">
-        <v>11.08427866283607</v>
+        <v>16.51322131487717</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5506138330316752</v>
+        <v>0.5505699701455258</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5078708141594532</v>
+        <v>0.5078362165176405</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5506138330316752</v>
+        <v>0.5505699701455258</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5138027228563833</v>
+        <v>0.5137673493133983</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5138027228563834</v>
+        <v>0.5137673493133981</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5488572651519991</v>
+        <v>0.5488136173355024</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5506138330316752</v>
+        <v>0.5505699701455258</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5390034399737652</v>
+        <v>0.5389609205012682</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5506138330316752</v>
+        <v>0.5505699701455258</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5506138330316752</v>
+        <v>0.5505699701455258</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5506138330316752</v>
+        <v>0.5505699701455258</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6189159814272028</v>
+        <v>0.6188369571887319</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5906250753146697</v>
+        <v>0.5905582158499124</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6265711129923215</v>
+        <v>0.9273442180718108</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5820451805784722</v>
+        <v>0.5819796711865725</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6061102737817208</v>
+        <v>0.6060345394891696</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9065198179917598</v>
+        <v>0.6170806043787184</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9714390379058077</v>
+        <v>0.971248403772111</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8966659928135297</v>
+        <v>0.607227907544475</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9379928472395318</v>
+        <v>0.9377661452466496</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6220954912479577</v>
+        <v>0.6220266725958701</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6240809825176759</v>
+        <v>0.624002332870361</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.973366329913291</v>
+        <v>0.9732726160237389</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9617559368553762</v>
+        <v>0.9616635663794848</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9713362078797895</v>
+        <v>0.9712424943740203</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9553907111302465</v>
+        <v>0.9552985883583999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9553907111302465</v>
+        <v>0.9552985883583999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9716097620336063</v>
+        <v>0.9715162632137248</v>
       </c>
       <c r="H5" t="n">
-        <v>0.973366329913291</v>
+        <v>0.9732726160237389</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9617559368553762</v>
+        <v>0.9616635663794848</v>
       </c>
       <c r="J5" t="n">
-        <v>0.973366329913291</v>
+        <v>0.9732726160237389</v>
       </c>
       <c r="K5" t="n">
-        <v>0.973366329913291</v>
+        <v>0.9732726160237389</v>
       </c>
       <c r="L5" t="n">
-        <v>0.973366329913291</v>
+        <v>0.9732726160237389</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.112868576920718</v>
+        <v>1.112735791513825</v>
       </c>
       <c r="C6" t="n">
-        <v>1.550323794059426</v>
+        <v>1.55012783190929</v>
       </c>
       <c r="D6" t="n">
-        <v>1.659194024940846</v>
+        <v>1.658983070661719</v>
       </c>
       <c r="E6" t="n">
-        <v>1.426375540384541</v>
+        <v>1.426197261437144</v>
       </c>
       <c r="F6" t="n">
-        <v>1.113015546879906</v>
+        <v>1.112882200146091</v>
       </c>
       <c r="G6" t="n">
-        <v>1.563609213904599</v>
+        <v>1.563411899747856</v>
       </c>
       <c r="H6" t="n">
-        <v>1.565365781785327</v>
+        <v>1.565168252558935</v>
       </c>
       <c r="I6" t="n">
-        <v>1.553755388726364</v>
+        <v>1.553559202913625</v>
       </c>
       <c r="J6" t="n">
-        <v>1.56545471026885</v>
+        <v>1.565257168318467</v>
       </c>
       <c r="K6" t="n">
-        <v>1.104463209036362</v>
+        <v>1.104331626279155</v>
       </c>
       <c r="L6" t="n">
-        <v>2.038036949310314</v>
+        <v>2.037771789750681</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.929650783642742</v>
+        <v>1.929231006803314</v>
       </c>
       <c r="C7" t="n">
-        <v>2.340876606617143</v>
+        <v>2.340350624340595</v>
       </c>
       <c r="D7" t="n">
-        <v>2.352487067548356</v>
+        <v>2.351959741793527</v>
       </c>
       <c r="E7" t="n">
-        <v>2.82882018057901</v>
+        <v>2.828170089357877</v>
       </c>
       <c r="F7" t="n">
-        <v>2.340876194521586</v>
+        <v>2.340350212410812</v>
       </c>
       <c r="G7" t="n">
-        <v>2.350730431795379</v>
+        <v>2.350203321174833</v>
       </c>
       <c r="H7" t="n">
-        <v>2.352486999675058</v>
+        <v>2.351959673984854</v>
       </c>
       <c r="I7" t="n">
-        <v>2.340876606617143</v>
+        <v>2.340350624340595</v>
       </c>
       <c r="J7" t="n">
-        <v>2.352486999675058</v>
+        <v>2.351959673984854</v>
       </c>
       <c r="K7" t="n">
-        <v>1.820060710101491</v>
+        <v>2.107029052556357</v>
       </c>
       <c r="L7" t="n">
-        <v>2.352486999675058</v>
+        <v>2.351959673984854</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.77885708893675</v>
+        <v>10.77878641630892</v>
       </c>
       <c r="C8" t="n">
-        <v>10.98636177702499</v>
+        <v>10.98631955739328</v>
       </c>
       <c r="D8" t="n">
-        <v>10.5921061465419</v>
+        <v>10.59203576837388</v>
       </c>
       <c r="E8" t="n">
-        <v>10.98636177702499</v>
+        <v>10.98631955739328</v>
       </c>
       <c r="F8" t="n">
-        <v>10.98636177702499</v>
+        <v>10.98631955739328</v>
       </c>
       <c r="G8" t="n">
-        <v>10.65135428492489</v>
+        <v>10.6514373692406</v>
       </c>
       <c r="H8" t="n">
-        <v>10.42304828278846</v>
+        <v>10.4229815018412</v>
       </c>
       <c r="I8" t="n">
-        <v>10.98636177702499</v>
+        <v>10.98631955739328</v>
       </c>
       <c r="J8" t="n">
-        <v>10.08233277439433</v>
+        <v>10.08228233604834</v>
       </c>
       <c r="K8" t="n">
-        <v>10.6835038999287</v>
+        <v>10.68343554398879</v>
       </c>
       <c r="L8" t="n">
-        <v>10.57919985521955</v>
+        <v>10.68526393155661</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.512116822477558</v>
+        <v>4.512045268521534</v>
       </c>
       <c r="C9" t="n">
-        <v>4.705767179321065</v>
+        <v>4.705717136346427</v>
       </c>
       <c r="D9" t="n">
-        <v>4.436062675835944</v>
+        <v>4.435991241737081</v>
       </c>
       <c r="E9" t="n">
-        <v>4.705767179321065</v>
+        <v>4.705717136346428</v>
       </c>
       <c r="F9" t="n">
-        <v>4.705767179321065</v>
+        <v>4.705717136346428</v>
       </c>
       <c r="G9" t="n">
-        <v>4.459406914174321</v>
+        <v>4.459399664695814</v>
       </c>
       <c r="H9" t="n">
-        <v>4.367647549942112</v>
+        <v>4.367577575086693</v>
       </c>
       <c r="I9" t="n">
-        <v>4.705767179321065</v>
+        <v>4.705717136346428</v>
       </c>
       <c r="J9" t="n">
-        <v>4.228741051607338</v>
+        <v>4.228677730269721</v>
       </c>
       <c r="K9" t="n">
-        <v>4.473291834908556</v>
+        <v>4.473221224269547</v>
       </c>
       <c r="L9" t="n">
-        <v>4.474157253097799</v>
+        <v>4.430993077848425</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-8.492845480839343</v>
+        <v>-8.493103291908529</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.7603628623627099</v>
+        <v>-0.7609720920327767</v>
       </c>
       <c r="D2" t="n">
-        <v>1.837345782733115</v>
+        <v>1.837115541883604</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7603628623627099</v>
+        <v>-0.7609720920327767</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7603628623627099</v>
+        <v>-0.7609720920327767</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.514700136730316</v>
+        <v>-2.519021036227976</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2658296686793058</v>
+        <v>-0.266136484533388</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7603628623627099</v>
+        <v>-0.7609720920327767</v>
       </c>
       <c r="J2" t="n">
-        <v>2.582574291726116</v>
+        <v>2.581654499547351</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.875038666153897</v>
+        <v>-3.87536379361481</v>
       </c>
       <c r="L2" t="n">
-        <v>3.395870963142511</v>
+        <v>3.393870198265073</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4530491348986616</v>
+        <v>0.453009007603897</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4162797102736269</v>
+        <v>0.416246619690203</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4530491348986616</v>
+        <v>0.453009007603897</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4194972898529578</v>
+        <v>0.4194635875936569</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4194972898529576</v>
+        <v>0.4194635875936572</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4515882709908853</v>
+        <v>0.4515482966809163</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4530491348986616</v>
+        <v>0.453009007603897</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4433003490962288</v>
+        <v>0.4432611702800036</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4530491348986616</v>
+        <v>0.453009007603897</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4530491348986616</v>
+        <v>0.453009007603897</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4530491348986616</v>
+        <v>0.453009007603897</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4453360954970155</v>
+        <v>0.6245570909415776</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4363467571713064</v>
+        <v>0.436285418534633</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4568265958513668</v>
+        <v>0.4567577339388869</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4339416680227249</v>
+        <v>0.4338815330347657</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4396456765293469</v>
+        <v>0.4395782481454907</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4438752315892469</v>
+        <v>0.4438056910694725</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6689949081438165</v>
+        <v>0.4505394398088263</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4355873096945909</v>
+        <v>0.4355185646685679</v>
       </c>
       <c r="J4" t="n">
-        <v>0.458168646557942</v>
+        <v>0.6494089930959782</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4455946614152116</v>
+        <v>0.4455319635749933</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4524717317795648</v>
+        <v>0.4524024268966872</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7666448949189922</v>
+        <v>0.7665646694973232</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7568961091165608</v>
+        <v>0.756816832173431</v>
       </c>
       <c r="D5" t="n">
-        <v>0.764754392064398</v>
+        <v>0.7646741669902226</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7494013768042096</v>
+        <v>0.749322273304267</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7494013768042096</v>
+        <v>0.749322273304267</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7651840310112192</v>
+        <v>0.7651039585743347</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7666448949189922</v>
+        <v>0.7665646694973232</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7568961091165608</v>
+        <v>0.756816832173431</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7666448949189922</v>
+        <v>0.7665646694973232</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7666448949189922</v>
+        <v>0.7665646694973232</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7666448949189922</v>
+        <v>0.7665646694973232</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8188458077861481</v>
+        <v>0.818735155199169</v>
       </c>
       <c r="C6" t="n">
-        <v>1.100609715800881</v>
+        <v>1.100448802371564</v>
       </c>
       <c r="D6" t="n">
-        <v>1.176503445991701</v>
+        <v>1.17633077798553</v>
       </c>
       <c r="E6" t="n">
-        <v>1.019573995157887</v>
+        <v>1.019427113106113</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8151439240862087</v>
+        <v>0.8150326950583258</v>
       </c>
       <c r="G6" t="n">
-        <v>1.113616946551916</v>
+        <v>1.113455082320917</v>
       </c>
       <c r="H6" t="n">
-        <v>1.115077810459316</v>
+        <v>1.114915793243527</v>
       </c>
       <c r="I6" t="n">
-        <v>1.105329024657256</v>
+        <v>1.105167955920013</v>
       </c>
       <c r="J6" t="n">
-        <v>1.115136028650088</v>
+        <v>1.114974001339697</v>
       </c>
       <c r="K6" t="n">
-        <v>0.813343146233978</v>
+        <v>0.8132334477713519</v>
       </c>
       <c r="L6" t="n">
-        <v>1.424516907890919</v>
+        <v>1.424301236025322</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.302483461319872</v>
+        <v>1.302158692183274</v>
       </c>
       <c r="C7" t="n">
-        <v>1.555423210480127</v>
+        <v>1.555017818236031</v>
       </c>
       <c r="D7" t="n">
-        <v>1.565171942656056</v>
+        <v>1.564765601863245</v>
       </c>
       <c r="E7" t="n">
-        <v>1.858560036661352</v>
+        <v>1.858060512586214</v>
       </c>
       <c r="F7" t="n">
-        <v>1.555423110646689</v>
+        <v>1.555017718493061</v>
       </c>
       <c r="G7" t="n">
-        <v>1.563711132374777</v>
+        <v>1.563304944636938</v>
       </c>
       <c r="H7" t="n">
-        <v>1.565171996282552</v>
+        <v>1.564765655559921</v>
       </c>
       <c r="I7" t="n">
-        <v>1.555423210480127</v>
+        <v>1.555017818236031</v>
       </c>
       <c r="J7" t="n">
-        <v>1.565171996282552</v>
+        <v>1.564765655559921</v>
       </c>
       <c r="K7" t="n">
-        <v>1.406794147581492</v>
+        <v>1.406436987243747</v>
       </c>
       <c r="L7" t="n">
-        <v>1.565171996282552</v>
+        <v>1.564765655559921</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11.0178240569531</v>
+        <v>11.01776101399286</v>
       </c>
       <c r="C8" t="n">
-        <v>11.0208106003301</v>
+        <v>11.02077168575394</v>
       </c>
       <c r="D8" t="n">
-        <v>10.75341530093526</v>
+        <v>10.75335106590374</v>
       </c>
       <c r="E8" t="n">
-        <v>11.0208106003301</v>
+        <v>11.02077168575394</v>
       </c>
       <c r="F8" t="n">
-        <v>11.0208106003301</v>
+        <v>11.02077168575394</v>
       </c>
       <c r="G8" t="n">
-        <v>10.87146900542855</v>
+        <v>10.8715170791576</v>
       </c>
       <c r="H8" t="n">
-        <v>10.81301372432755</v>
+        <v>10.8129508575339</v>
       </c>
       <c r="I8" t="n">
-        <v>11.0208106003301</v>
+        <v>11.02077168575394</v>
       </c>
       <c r="J8" t="n">
-        <v>10.73806877956863</v>
+        <v>10.73802182672989</v>
       </c>
       <c r="K8" t="n">
-        <v>10.90818072391387</v>
+        <v>10.90811948541629</v>
       </c>
       <c r="L8" t="n">
-        <v>10.79056667205016</v>
+        <v>10.79052997835717</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.542208601868985</v>
+        <v>4.542143035545077</v>
       </c>
       <c r="C9" t="n">
-        <v>4.656523461578093</v>
+        <v>4.656476390904353</v>
       </c>
       <c r="D9" t="n">
-        <v>4.434517569913552</v>
+        <v>4.434451517959964</v>
       </c>
       <c r="E9" t="n">
-        <v>4.656523461578093</v>
+        <v>4.656476390904353</v>
       </c>
       <c r="F9" t="n">
-        <v>4.656523461578093</v>
+        <v>4.656476390904353</v>
       </c>
       <c r="G9" t="n">
-        <v>4.482595106712538</v>
+        <v>4.482576310348652</v>
       </c>
       <c r="H9" t="n">
-        <v>4.458769258303189</v>
+        <v>4.458703758720476</v>
       </c>
       <c r="I9" t="n">
-        <v>4.656523461578093</v>
+        <v>4.656476390904353</v>
       </c>
       <c r="J9" t="n">
-        <v>4.428285878105011</v>
+        <v>4.428226857060472</v>
       </c>
       <c r="K9" t="n">
-        <v>4.497545319908348</v>
+        <v>4.49748048815964</v>
       </c>
       <c r="L9" t="n">
-        <v>4.421177599053732</v>
+        <v>4.449592829942294</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-16.14602395888426</v>
+        <v>-16.14636523020397</v>
       </c>
       <c r="C2" t="n">
-        <v>-2.357611324179927</v>
+        <v>-2.35812344744242</v>
       </c>
       <c r="D2" t="n">
-        <v>1.178749844306758</v>
+        <v>1.178567613349098</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.357611324179927</v>
+        <v>-2.35812344744242</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.357611324179927</v>
+        <v>-2.35812344744242</v>
       </c>
       <c r="G2" t="n">
-        <v>-5.082362764881411</v>
+        <v>-5.085142344848856</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2399057874130879</v>
+        <v>0.2396533538297969</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.357611324179927</v>
+        <v>-2.35812344744242</v>
       </c>
       <c r="J2" t="n">
-        <v>-4.991094409030687</v>
+        <v>-4.991743022969862</v>
       </c>
       <c r="K2" t="n">
-        <v>-7.835444170691832</v>
+        <v>-7.835728329778264</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.731681895688464</v>
+        <v>0.8300362064258069</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4216180520374152</v>
+        <v>0.4215814049599568</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3799358735029246</v>
+        <v>0.3799046079481256</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4216180520374152</v>
+        <v>0.4215814049599568</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3826375788387655</v>
+        <v>0.3826058155296784</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3826375788387655</v>
+        <v>0.3826058155296783</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4201832660520772</v>
+        <v>0.420146711480289</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4216180520374152</v>
+        <v>0.4215814049599568</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4120294370915976</v>
+        <v>0.4119933543262317</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4216180520374152</v>
+        <v>0.4215814049599568</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4216180520374152</v>
+        <v>0.4215814049599568</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4216180520374152</v>
+        <v>0.4215814049599568</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3961106599458136</v>
+        <v>0.3960482518513458</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3889623130070319</v>
+        <v>0.3889051736636526</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5689800699523984</v>
+        <v>0.4120361583567966</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3884509492424162</v>
+        <v>0.3883949111473899</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3911771873238039</v>
+        <v>0.3911161022986567</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3946758739604773</v>
+        <v>0.5517769505410188</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5934686669052998</v>
+        <v>0.5933200204706863</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3865220449999973</v>
+        <v>0.3864602012176375</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4065671302223203</v>
+        <v>0.5777172568393339</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3933876732869855</v>
+        <v>0.3933297299958143</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4050307711356598</v>
+        <v>0.4049686377476877</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7150116763380514</v>
+        <v>0.7149409813818203</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7054230613922349</v>
+        <v>0.7053529307480997</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7131223726067454</v>
+        <v>0.7130516779671152</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6961228544937171</v>
+        <v>0.6960528454695621</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6961228544937171</v>
+        <v>0.6960528454695621</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7135768903527108</v>
+        <v>0.713506287902153</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7150116763380514</v>
+        <v>0.7149409813818203</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7054230613922349</v>
+        <v>0.7053529307480997</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7150116763380514</v>
+        <v>0.7149409813818203</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7150116763380514</v>
+        <v>0.7149409813818203</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7150116763380514</v>
+        <v>0.7149409813818203</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7473660973762261</v>
+        <v>0.7472712023083166</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9935794562966628</v>
+        <v>0.9934428847544351</v>
       </c>
       <c r="D6" t="n">
-        <v>1.06400282375806</v>
+        <v>1.063856799160993</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9220204491251629</v>
+        <v>0.9218954481653765</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7416696352667065</v>
+        <v>0.7415740344976335</v>
       </c>
       <c r="G6" t="n">
-        <v>1.008187507129323</v>
+        <v>1.008050356239529</v>
       </c>
       <c r="H6" t="n">
-        <v>1.009622293113502</v>
+        <v>1.009485049718025</v>
       </c>
       <c r="I6" t="n">
-        <v>1.000033678168842</v>
+        <v>0.999896999085479</v>
       </c>
       <c r="J6" t="n">
-        <v>1.009673834231207</v>
+        <v>1.009536582513097</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7424945538682439</v>
+        <v>0.7424004454422592</v>
       </c>
       <c r="L6" t="n">
-        <v>1.283570819329267</v>
+        <v>1.28338933956459</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.16883435617265</v>
+        <v>1.168568656287399</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3899530052659</v>
+        <v>1.389622200542008</v>
       </c>
       <c r="D7" t="n">
-        <v>1.39954148496234</v>
+        <v>1.399210115877531</v>
       </c>
       <c r="E7" t="n">
-        <v>1.656184041150181</v>
+        <v>1.655777455643221</v>
       </c>
       <c r="F7" t="n">
-        <v>1.38995289904989</v>
+        <v>1.389622094380892</v>
       </c>
       <c r="G7" t="n">
-        <v>1.398106834226378</v>
+        <v>1.39777555769607</v>
       </c>
       <c r="H7" t="n">
-        <v>1.399541620211715</v>
+        <v>1.399210251175715</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3899530052659</v>
+        <v>1.389622200542008</v>
       </c>
       <c r="J7" t="n">
-        <v>1.399541620211715</v>
+        <v>1.399210251175715</v>
       </c>
       <c r="K7" t="n">
-        <v>1.265868868484775</v>
+        <v>1.260153825183481</v>
       </c>
       <c r="L7" t="n">
-        <v>1.399541620211715</v>
+        <v>1.399210251175715</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11.17849251648409</v>
+        <v>11.17843731941752</v>
       </c>
       <c r="C8" t="n">
-        <v>11.02423175619137</v>
+        <v>11.02419380999647</v>
       </c>
       <c r="D8" t="n">
-        <v>10.73310722976892</v>
+        <v>10.7330477228609</v>
       </c>
       <c r="E8" t="n">
-        <v>11.02423175619137</v>
+        <v>11.02419380999647</v>
       </c>
       <c r="F8" t="n">
-        <v>11.02423175619137</v>
+        <v>11.02419380999647</v>
       </c>
       <c r="G8" t="n">
-        <v>10.89586317818768</v>
+        <v>10.89587323286687</v>
       </c>
       <c r="H8" t="n">
-        <v>10.75796409030476</v>
+        <v>10.75790584951493</v>
       </c>
       <c r="I8" t="n">
-        <v>11.02423175619137</v>
+        <v>11.02419380999647</v>
       </c>
       <c r="J8" t="n">
-        <v>10.88462928280574</v>
+        <v>10.88458112790754</v>
       </c>
       <c r="K8" t="n">
-        <v>10.98181162279851</v>
+        <v>10.98175509754009</v>
       </c>
       <c r="L8" t="n">
-        <v>10.80357645700669</v>
+        <v>10.80355172873996</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.585517300185324</v>
+        <v>4.585458166074483</v>
       </c>
       <c r="C9" t="n">
-        <v>4.63682338042431</v>
+        <v>4.636778752275629</v>
       </c>
       <c r="D9" t="n">
-        <v>4.404115204557555</v>
+        <v>4.404054314990708</v>
       </c>
       <c r="E9" t="n">
-        <v>4.63682338042431</v>
+        <v>4.636778752275629</v>
       </c>
       <c r="F9" t="n">
-        <v>4.63682338042431</v>
+        <v>4.636778752275629</v>
       </c>
       <c r="G9" t="n">
-        <v>4.470476837479917</v>
+        <v>4.47044562428855</v>
       </c>
       <c r="H9" t="n">
-        <v>4.414233110908308</v>
+        <v>4.414172732951731</v>
       </c>
       <c r="I9" t="n">
-        <v>4.63682338042431</v>
+        <v>4.636778752275629</v>
       </c>
       <c r="J9" t="n">
-        <v>4.465778034125429</v>
+        <v>4.46572176269361</v>
       </c>
       <c r="K9" t="n">
-        <v>4.505398260305282</v>
+        <v>4.505338584903281</v>
       </c>
       <c r="L9" t="n">
-        <v>4.432777809159433</v>
+        <v>4.408336045832104</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.3734415282676</v>
+        <v>19.3732810663274</v>
       </c>
       <c r="C2" t="n">
-        <v>10.84115916416737</v>
+        <v>10.84053620914785</v>
       </c>
       <c r="D2" t="n">
-        <v>42.42150203570706</v>
+        <v>42.42123609212501</v>
       </c>
       <c r="E2" t="n">
-        <v>10.84115916416737</v>
+        <v>10.84053620914785</v>
       </c>
       <c r="F2" t="n">
-        <v>10.84115916416737</v>
+        <v>10.84053620914785</v>
       </c>
       <c r="G2" t="n">
-        <v>30.26114105348914</v>
+        <v>30.25665620235311</v>
       </c>
       <c r="H2" t="n">
-        <v>66.19470281022942</v>
+        <v>66.19441548357774</v>
       </c>
       <c r="I2" t="n">
-        <v>10.84115916416737</v>
+        <v>10.84053620914785</v>
       </c>
       <c r="J2" t="n">
-        <v>40.48867816967746</v>
+        <v>40.48777115990622</v>
       </c>
       <c r="K2" t="n">
-        <v>20.48724782585881</v>
+        <v>20.48700408658036</v>
       </c>
       <c r="L2" t="n">
-        <v>56.27631938581703</v>
+        <v>56.27523781788103</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6470554966807239</v>
+        <v>0.6470159839199946</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6084784960375008</v>
+        <v>0.6084459063002691</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6470554966807239</v>
+        <v>0.6470159839199946</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6148422666629361</v>
+        <v>0.6148090900021772</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6148422666629361</v>
+        <v>0.6148090900021772</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6448304335709554</v>
+        <v>0.6447910617593249</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6470554966807239</v>
+        <v>0.6470159839199946</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6324578497907957</v>
+        <v>0.6324192092338288</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6470554966807239</v>
+        <v>0.6470159839199946</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6470554966807239</v>
+        <v>0.6470159839199946</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6470554966807239</v>
+        <v>0.6470159839199946</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7712736626046389</v>
+        <v>0.7712031010940413</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7231680844291281</v>
+        <v>0.7231059761616857</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8107988204251808</v>
+        <v>0.8107352991178522</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7109851664434282</v>
+        <v>0.7109243000661222</v>
       </c>
       <c r="F4" t="n">
-        <v>0.754564229612133</v>
+        <v>0.7544960664927339</v>
       </c>
       <c r="G4" t="n">
-        <v>1.197638398628443</v>
+        <v>1.197434020832629</v>
       </c>
       <c r="H4" t="n">
-        <v>1.256331086048544</v>
+        <v>1.256160679549452</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7566760157147098</v>
+        <v>1.185062168307131</v>
       </c>
       <c r="J4" t="n">
-        <v>1.227183509840633</v>
+        <v>1.226977875394523</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7671499758213878</v>
+        <v>0.767086785593738</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7857557483261723</v>
+        <v>0.7856859286769897</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.168187734979532</v>
+        <v>1.168105819657796</v>
       </c>
       <c r="C5" t="n">
-        <v>1.153590088089602</v>
+        <v>1.153509044971629</v>
       </c>
       <c r="D5" t="n">
-        <v>1.166152024370236</v>
+        <v>1.166070109441769</v>
       </c>
       <c r="E5" t="n">
-        <v>1.151572622374072</v>
+        <v>1.151491722828253</v>
       </c>
       <c r="F5" t="n">
-        <v>1.151572622374072</v>
+        <v>1.151491722828253</v>
       </c>
       <c r="G5" t="n">
-        <v>1.165962671869762</v>
+        <v>1.165880897497125</v>
       </c>
       <c r="H5" t="n">
-        <v>1.168187734979532</v>
+        <v>1.168105819657796</v>
       </c>
       <c r="I5" t="n">
-        <v>1.153590088089602</v>
+        <v>1.153509044971629</v>
       </c>
       <c r="J5" t="n">
-        <v>1.168187734979532</v>
+        <v>1.168105819657796</v>
       </c>
       <c r="K5" t="n">
-        <v>1.168187734979532</v>
+        <v>1.168105819657796</v>
       </c>
       <c r="L5" t="n">
-        <v>1.168187734979532</v>
+        <v>1.168105819657796</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.393826800598718</v>
+        <v>1.393713811386746</v>
       </c>
       <c r="C6" t="n">
-        <v>1.974301057192</v>
+        <v>1.974135903909214</v>
       </c>
       <c r="D6" t="n">
-        <v>2.111371567567953</v>
+        <v>2.111194392126588</v>
       </c>
       <c r="E6" t="n">
-        <v>1.811121296166918</v>
+        <v>1.81097066907385</v>
       </c>
       <c r="F6" t="n">
-        <v>1.398078766038184</v>
+        <v>1.397965049270319</v>
       </c>
       <c r="G6" t="n">
-        <v>1.985912331291543</v>
+        <v>1.985746320413794</v>
       </c>
       <c r="H6" t="n">
-        <v>1.98813739440191</v>
+        <v>1.98797124257506</v>
       </c>
       <c r="I6" t="n">
-        <v>1.973539747511382</v>
+        <v>1.973374467888298</v>
       </c>
       <c r="J6" t="n">
-        <v>1.988254193085274</v>
+        <v>1.988088030810466</v>
       </c>
       <c r="K6" t="n">
-        <v>1.382787176228085</v>
+        <v>1.382675174538976</v>
       </c>
       <c r="L6" t="n">
-        <v>2.608944504728568</v>
+        <v>2.608722820105113</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.540085787872888</v>
+        <v>2.539719858353157</v>
       </c>
       <c r="C7" t="n">
-        <v>3.101167642963934</v>
+        <v>3.100709494501672</v>
       </c>
       <c r="D7" t="n">
-        <v>3.115765330085385</v>
+        <v>3.115306309422201</v>
       </c>
       <c r="E7" t="n">
-        <v>3.765488352848112</v>
+        <v>3.764922779380635</v>
       </c>
       <c r="F7" t="n">
-        <v>3.101166630649371</v>
+        <v>3.100708482348066</v>
       </c>
       <c r="G7" t="n">
-        <v>3.11354022674409</v>
+        <v>3.113081347027166</v>
       </c>
       <c r="H7" t="n">
-        <v>3.11576528985386</v>
+        <v>3.115306269187837</v>
       </c>
       <c r="I7" t="n">
-        <v>3.101167642963934</v>
+        <v>3.100709494501672</v>
       </c>
       <c r="J7" t="n">
-        <v>3.11576528985386</v>
+        <v>3.115306269187837</v>
       </c>
       <c r="K7" t="n">
-        <v>2.768681757553506</v>
+        <v>2.781809259170402</v>
       </c>
       <c r="L7" t="n">
-        <v>3.11576528985386</v>
+        <v>3.115306269187837</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.56463757433558</v>
+        <v>10.56457362224661</v>
       </c>
       <c r="C8" t="n">
-        <v>10.94111201163883</v>
+        <v>10.94107356799109</v>
       </c>
       <c r="D8" t="n">
-        <v>9.998920034349167</v>
+        <v>9.998858450586546</v>
       </c>
       <c r="E8" t="n">
-        <v>10.94111201163883</v>
+        <v>10.94107356799109</v>
       </c>
       <c r="F8" t="n">
-        <v>10.94111201163883</v>
+        <v>10.94107356799109</v>
       </c>
       <c r="G8" t="n">
-        <v>10.31948723948128</v>
+        <v>10.31952667573078</v>
       </c>
       <c r="H8" t="n">
-        <v>9.552728836379391</v>
+        <v>9.552667022578651</v>
       </c>
       <c r="I8" t="n">
-        <v>10.94111201163883</v>
+        <v>10.94107356799109</v>
       </c>
       <c r="J8" t="n">
-        <v>10.14810310098735</v>
+        <v>10.14805536877186</v>
       </c>
       <c r="K8" t="n">
-        <v>10.54239390740571</v>
+        <v>10.54233195661484</v>
       </c>
       <c r="L8" t="n">
-        <v>10.61774408543175</v>
+        <v>9.916532291816562</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.487350371106816</v>
+        <v>4.487285508814779</v>
       </c>
       <c r="C9" t="n">
-        <v>4.741704158759219</v>
+        <v>4.741658104001674</v>
       </c>
       <c r="D9" t="n">
-        <v>4.256964126424387</v>
+        <v>4.256900228608657</v>
       </c>
       <c r="E9" t="n">
-        <v>4.741704158759219</v>
+        <v>4.741658104001674</v>
       </c>
       <c r="F9" t="n">
-        <v>4.741704158759219</v>
+        <v>4.741658104001674</v>
       </c>
       <c r="G9" t="n">
-        <v>4.385539066058004</v>
+        <v>4.385517786176866</v>
       </c>
       <c r="H9" t="n">
-        <v>4.076565961731397</v>
+        <v>4.076501966079396</v>
       </c>
       <c r="I9" t="n">
-        <v>4.741704158759219</v>
+        <v>4.741658104001674</v>
       </c>
       <c r="J9" t="n">
-        <v>4.318028537917645</v>
+        <v>4.317970274754167</v>
       </c>
       <c r="K9" t="n">
-        <v>4.47831557178619</v>
+        <v>4.47825152437458</v>
       </c>
       <c r="L9" t="n">
-        <v>4.509275394550141</v>
+        <v>4.224172946310021</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.849655102815209</v>
+        <v>-1.849829020526771</v>
       </c>
       <c r="C2" t="n">
-        <v>4.519732723214823</v>
+        <v>4.519161682816765</v>
       </c>
       <c r="D2" t="n">
-        <v>27.5180432925827</v>
+        <v>27.51775242415567</v>
       </c>
       <c r="E2" t="n">
-        <v>4.519732723214823</v>
+        <v>4.519161682816765</v>
       </c>
       <c r="F2" t="n">
-        <v>4.519732723214823</v>
+        <v>4.519161682816765</v>
       </c>
       <c r="G2" t="n">
-        <v>9.36753821158473</v>
+        <v>9.363727158020591</v>
       </c>
       <c r="H2" t="n">
-        <v>2.334283529317726</v>
+        <v>2.333976390774748</v>
       </c>
       <c r="I2" t="n">
-        <v>4.519732723214823</v>
+        <v>4.519161682816765</v>
       </c>
       <c r="J2" t="n">
-        <v>16.24479011930983</v>
+        <v>16.24387449588982</v>
       </c>
       <c r="K2" t="n">
-        <v>6.510006933792676</v>
+        <v>6.509815903212299</v>
       </c>
       <c r="L2" t="n">
-        <v>31.2370336447287</v>
+        <v>3.913513656158528</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.536622272516128</v>
+        <v>0.5365834264660241</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5051525571975845</v>
+        <v>0.5051201848818464</v>
       </c>
       <c r="D3" t="n">
-        <v>0.536622272516128</v>
+        <v>0.5365834264660241</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5093039400279828</v>
+        <v>0.5092709917577852</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5093039400279828</v>
+        <v>0.5092709917577851</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5349007116035703</v>
+        <v>0.5348619965775017</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5366222725161259</v>
+        <v>0.5365834264660241</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5252217989731692</v>
+        <v>0.5251837615778217</v>
       </c>
       <c r="J3" t="n">
-        <v>0.536622272516128</v>
+        <v>0.5365834264660241</v>
       </c>
       <c r="K3" t="n">
-        <v>0.536622272516128</v>
+        <v>0.5365834264660241</v>
       </c>
       <c r="L3" t="n">
-        <v>0.536622272516128</v>
+        <v>0.5365834264660241</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5865571110093821</v>
+        <v>0.8605783367675869</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5641818534100629</v>
+        <v>0.5641220116150744</v>
       </c>
       <c r="D4" t="n">
-        <v>0.631777418298439</v>
+        <v>0.6317161913621991</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5572989451907528</v>
+        <v>0.5572402585464145</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5760129773619943</v>
+        <v>0.5759478298094873</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8590468241143017</v>
+        <v>0.5847684868681552</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9015219372947164</v>
+        <v>0.9013627012467271</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8493679114839023</v>
+        <v>0.8491786718793853</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8857653023228933</v>
+        <v>0.6027141512073004</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5878244460177469</v>
+        <v>0.5877637145287313</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5977825697378496</v>
+        <v>0.5977159082974616</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9219061315154066</v>
+        <v>0.9218286225667365</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9105056579724479</v>
+        <v>0.9104289576785322</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9200121937276124</v>
+        <v>0.9199346851126634</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9064958802115335</v>
+        <v>0.9064193474778598</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9064958802115335</v>
+        <v>0.9064193474778598</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9201845706028479</v>
+        <v>0.9201071926782134</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9219061315154066</v>
+        <v>0.9218286225667365</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9105056579724479</v>
+        <v>0.9104289576785322</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9219061315154066</v>
+        <v>0.9218286225667365</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9219061315154066</v>
+        <v>0.9218286225667365</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9219061315154066</v>
+        <v>0.9218286225667365</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.042044629520314</v>
+        <v>1.041938750688296</v>
       </c>
       <c r="C6" t="n">
-        <v>1.435274650193595</v>
+        <v>1.43512102679341</v>
       </c>
       <c r="D6" t="n">
-        <v>1.53222045618228</v>
+        <v>1.532055774929886</v>
       </c>
       <c r="E6" t="n">
-        <v>1.323863095104023</v>
+        <v>1.323722775809469</v>
       </c>
       <c r="F6" t="n">
-        <v>1.042251241238072</v>
+        <v>1.042144726995556</v>
       </c>
       <c r="G6" t="n">
-        <v>1.446314025568704</v>
+        <v>1.446159574316731</v>
       </c>
       <c r="H6" t="n">
-        <v>1.448035586482173</v>
+        <v>1.447881004206164</v>
       </c>
       <c r="I6" t="n">
-        <v>1.436635112938305</v>
+        <v>1.436481339317054</v>
       </c>
       <c r="J6" t="n">
-        <v>1.448115375225231</v>
+        <v>1.44796078337762</v>
       </c>
       <c r="K6" t="n">
-        <v>1.034503139064338</v>
+        <v>1.034398164923792</v>
       </c>
       <c r="L6" t="n">
-        <v>1.872127089344313</v>
+        <v>1.871921632248564</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.714564031606348</v>
+        <v>1.714253886426551</v>
       </c>
       <c r="C7" t="n">
-        <v>2.065860928487822</v>
+        <v>2.065473902764837</v>
       </c>
       <c r="D7" t="n">
-        <v>2.077261694677386</v>
+        <v>2.07687386025487</v>
       </c>
       <c r="E7" t="n">
-        <v>2.484406123879376</v>
+        <v>2.483929446546522</v>
       </c>
       <c r="F7" t="n">
-        <v>2.065860813129364</v>
+        <v>2.06547378750059</v>
       </c>
       <c r="G7" t="n">
-        <v>2.075539841118214</v>
+        <v>2.075152137764516</v>
       </c>
       <c r="H7" t="n">
-        <v>2.077261402030781</v>
+        <v>2.076873567653043</v>
       </c>
       <c r="I7" t="n">
-        <v>2.065860928487822</v>
+        <v>2.065473902764837</v>
       </c>
       <c r="J7" t="n">
-        <v>2.077261402030781</v>
+        <v>2.076873567653043</v>
       </c>
       <c r="K7" t="n">
-        <v>1.867113244270399</v>
+        <v>1.62027058576865</v>
       </c>
       <c r="L7" t="n">
-        <v>2.077261402030781</v>
+        <v>2.076873567653043</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.95101589558421</v>
+        <v>10.95095278085727</v>
       </c>
       <c r="C8" t="n">
-        <v>10.9762833108125</v>
+        <v>10.97624451745756</v>
       </c>
       <c r="D8" t="n">
-        <v>10.15545396391781</v>
+        <v>10.15539364925889</v>
       </c>
       <c r="E8" t="n">
-        <v>10.9762833108125</v>
+        <v>10.97624451745756</v>
       </c>
       <c r="F8" t="n">
-        <v>10.9762833108125</v>
+        <v>10.97624451745756</v>
       </c>
       <c r="G8" t="n">
-        <v>10.66209011778928</v>
+        <v>10.66212344211596</v>
       </c>
       <c r="H8" t="n">
-        <v>10.84974137594118</v>
+        <v>10.84968071290202</v>
       </c>
       <c r="I8" t="n">
-        <v>10.9762833108125</v>
+        <v>10.97624451745756</v>
       </c>
       <c r="J8" t="n">
-        <v>10.52412214727897</v>
+        <v>10.5240761969105</v>
       </c>
       <c r="K8" t="n">
-        <v>10.73107712752729</v>
+        <v>10.73101435080554</v>
       </c>
       <c r="L8" t="n">
-        <v>10.81320012647402</v>
+        <v>10.22455513049952</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.573153266794435</v>
+        <v>4.573088852600696</v>
       </c>
       <c r="C9" t="n">
-        <v>4.693321617794852</v>
+        <v>4.693275280567574</v>
       </c>
       <c r="D9" t="n">
-        <v>4.249145442997616</v>
+        <v>4.249082169096856</v>
       </c>
       <c r="E9" t="n">
-        <v>4.693321617794852</v>
+        <v>4.693275280567574</v>
       </c>
       <c r="F9" t="n">
-        <v>4.693321617794852</v>
+        <v>4.693275280567574</v>
       </c>
       <c r="G9" t="n">
-        <v>4.454812315383928</v>
+        <v>4.45478862896174</v>
       </c>
       <c r="H9" t="n">
-        <v>4.531942314002804</v>
+        <v>4.531878893188454</v>
       </c>
       <c r="I9" t="n">
-        <v>4.693321617794852</v>
+        <v>4.693275280567574</v>
       </c>
       <c r="J9" t="n">
-        <v>4.399421762066185</v>
+        <v>4.399364331071543</v>
       </c>
       <c r="K9" t="n">
-        <v>4.483582016478035</v>
+        <v>4.483517739769172</v>
       </c>
       <c r="L9" t="n">
-        <v>4.517079132720585</v>
+        <v>4.277735737016112</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen climate change results.xlsx
+++ b/Results/Hydrogen/hydrogen climate change results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40.22943082527107</v>
+        <v>40.22943082527114</v>
       </c>
       <c r="C2" t="n">
-        <v>20.01211523602478</v>
+        <v>20.01211523602479</v>
       </c>
       <c r="D2" t="n">
-        <v>52.36685348707277</v>
+        <v>52.36685348707287</v>
       </c>
       <c r="E2" t="n">
-        <v>20.01211523602478</v>
+        <v>20.01211523602479</v>
       </c>
       <c r="F2" t="n">
-        <v>20.01211523602478</v>
+        <v>20.01211523602479</v>
       </c>
       <c r="G2" t="n">
-        <v>42.12306327559133</v>
+        <v>42.12306327559131</v>
       </c>
       <c r="H2" t="n">
-        <v>88.21900273035907</v>
+        <v>88.21900273035899</v>
       </c>
       <c r="I2" t="n">
-        <v>20.01211523602478</v>
+        <v>20.01211523602479</v>
       </c>
       <c r="J2" t="n">
-        <v>50.64972013614585</v>
+        <v>50.649720136146</v>
       </c>
       <c r="K2" t="n">
-        <v>33.58862766647781</v>
+        <v>33.58862766647785</v>
       </c>
       <c r="L2" t="n">
-        <v>27.68889892543006</v>
+        <v>71.29956574842173</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7381432294219801</v>
+        <v>0.7381432294219827</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7015614001163967</v>
+        <v>0.701561400116396</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7381432294219801</v>
+        <v>0.7381432294219827</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7093338263272406</v>
+        <v>0.7093338263272397</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7093338263272402</v>
+        <v>0.7093338263272397</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7359043517474942</v>
+        <v>0.7359043517474947</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7381432294219801</v>
+        <v>0.7381432294219827</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7234659359229074</v>
+        <v>0.7234659359229084</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7381432294219801</v>
+        <v>0.7381432294219827</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7381432294219801</v>
+        <v>0.7381432294219827</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7381432294219801</v>
+        <v>0.7381432294219827</v>
       </c>
     </row>
     <row r="4">
@@ -595,19 +595,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9077397083255937</v>
+        <v>0.9077397083255955</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8582292416063464</v>
+        <v>0.8582292416062496</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9467880818218793</v>
+        <v>0.9467941802138914</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8420907556342103</v>
+        <v>0.8420907556342292</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8920447771991344</v>
+        <v>0.8920447771991343</v>
       </c>
       <c r="G4" t="n">
         <v>1.43064750062835</v>
@@ -616,16 +616,16 @@
         <v>1.498361259798883</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8930624148265223</v>
+        <v>1.418209084803763</v>
       </c>
       <c r="J4" t="n">
-        <v>0.939577189619581</v>
+        <v>1.464936316495958</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9090005927729489</v>
+        <v>0.9090005927729504</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9243167086149436</v>
+        <v>0.9243167086149451</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.373358444053232</v>
+        <v>1.373358444053231</v>
       </c>
       <c r="C5" t="n">
-        <v>1.358681150554159</v>
+        <v>1.358681150554157</v>
       </c>
       <c r="D5" t="n">
         <v>1.371179838558332</v>
       </c>
       <c r="E5" t="n">
-        <v>1.357721348883492</v>
+        <v>1.35772134888349</v>
       </c>
       <c r="F5" t="n">
-        <v>1.357721348883492</v>
+        <v>1.35772134888349</v>
       </c>
       <c r="G5" t="n">
-        <v>1.371119566378746</v>
+        <v>1.371119566378743</v>
       </c>
       <c r="H5" t="n">
-        <v>1.373358444053232</v>
+        <v>1.373358444053231</v>
       </c>
       <c r="I5" t="n">
-        <v>1.358681150554159</v>
+        <v>1.358681150554157</v>
       </c>
       <c r="J5" t="n">
-        <v>1.373358444053232</v>
+        <v>1.373358444053231</v>
       </c>
       <c r="K5" t="n">
-        <v>1.373358444053232</v>
+        <v>1.373358444053231</v>
       </c>
       <c r="L5" t="n">
-        <v>1.373358444053232</v>
+        <v>1.373358444053231</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.677001272327971</v>
+        <v>1.677001272327966</v>
       </c>
       <c r="C6" t="n">
-        <v>2.408650453817536</v>
+        <v>2.408650453827182</v>
       </c>
       <c r="D6" t="n">
-        <v>2.575688990408214</v>
+        <v>2.575688990408209</v>
       </c>
       <c r="E6" t="n">
-        <v>2.204268826132764</v>
+        <v>2.204268826132757</v>
       </c>
       <c r="F6" t="n">
-        <v>1.686645587692821</v>
+        <v>1.686645587692818</v>
       </c>
       <c r="G6" t="n">
-        <v>2.419105682990746</v>
+        <v>2.419105682990749</v>
       </c>
       <c r="H6" t="n">
-        <v>2.421344560665485</v>
+        <v>2.421344560665477</v>
       </c>
       <c r="I6" t="n">
-        <v>2.406667267166171</v>
+        <v>2.406667267166164</v>
       </c>
       <c r="J6" t="n">
         <v>2.421490844892905</v>
       </c>
       <c r="K6" t="n">
-        <v>1.663174713646578</v>
+        <v>1.663174713646583</v>
       </c>
       <c r="L6" t="n">
-        <v>3.198873365792074</v>
+        <v>3.198873365792076</v>
       </c>
     </row>
     <row r="7">
@@ -718,34 +718,34 @@
         <v>3.283321765233496</v>
       </c>
       <c r="C7" t="n">
-        <v>4.036858495136696</v>
+        <v>4.036858495136689</v>
       </c>
       <c r="D7" t="n">
-        <v>4.051535916417158</v>
+        <v>4.051535916417151</v>
       </c>
       <c r="E7" t="n">
-        <v>4.923359807591758</v>
+        <v>4.923359807591754</v>
       </c>
       <c r="F7" t="n">
-        <v>4.036857297301143</v>
+        <v>4.036857297301153</v>
       </c>
       <c r="G7" t="n">
-        <v>4.049296910961288</v>
+        <v>4.049296910961277</v>
       </c>
       <c r="H7" t="n">
-        <v>4.051535788635767</v>
+        <v>4.051535788635762</v>
       </c>
       <c r="I7" t="n">
-        <v>4.036858495136696</v>
+        <v>4.036858495136689</v>
       </c>
       <c r="J7" t="n">
-        <v>4.051535788635767</v>
+        <v>4.051535788635762</v>
       </c>
       <c r="K7" t="n">
-        <v>3.606429620211598</v>
+        <v>3.08421717433596</v>
       </c>
       <c r="L7" t="n">
-        <v>4.051535788635767</v>
+        <v>4.051535788635762</v>
       </c>
     </row>
     <row r="8">
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.21921019805806</v>
+        <v>10.21921019805805</v>
       </c>
       <c r="C8" t="n">
         <v>10.85258812779364</v>
       </c>
       <c r="D8" t="n">
-        <v>9.984830458942817</v>
+        <v>9.984830458942815</v>
       </c>
       <c r="E8" t="n">
         <v>10.85258812779364</v>
@@ -798,34 +798,34 @@
         <v>4.39306701126648</v>
       </c>
       <c r="C9" t="n">
-        <v>4.75576220858407</v>
+        <v>4.755762208584072</v>
       </c>
       <c r="D9" t="n">
-        <v>4.297635041338408</v>
+        <v>4.297635041338405</v>
       </c>
       <c r="E9" t="n">
-        <v>4.75576220858407</v>
+        <v>4.755762208584072</v>
       </c>
       <c r="F9" t="n">
-        <v>4.75576220858407</v>
+        <v>4.755762208584072</v>
       </c>
       <c r="G9" t="n">
         <v>4.392127753066371</v>
       </c>
       <c r="H9" t="n">
-        <v>4.073127740868743</v>
+        <v>4.073127740868741</v>
       </c>
       <c r="I9" t="n">
-        <v>4.75576220858407</v>
+        <v>4.755762208584072</v>
       </c>
       <c r="J9" t="n">
-        <v>4.336429632347117</v>
+        <v>4.336429632347114</v>
       </c>
       <c r="K9" t="n">
         <v>4.461677911571195</v>
       </c>
       <c r="L9" t="n">
-        <v>4.537649326855785</v>
+        <v>4.221521365591612</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.96183733215084</v>
+        <v>-1.961837332150841</v>
       </c>
       <c r="C2" t="n">
-        <v>1.014153330034924</v>
+        <v>1.014153330034911</v>
       </c>
       <c r="D2" t="n">
-        <v>1.204256942798034</v>
+        <v>1.204256942798038</v>
       </c>
       <c r="E2" t="n">
-        <v>1.014153330034924</v>
+        <v>1.014153330034911</v>
       </c>
       <c r="F2" t="n">
-        <v>1.014153330034924</v>
+        <v>1.014153330034911</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.798178327686546</v>
+        <v>-1.798178327686525</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.714023194227144</v>
+        <v>-1.714023194227136</v>
       </c>
       <c r="I2" t="n">
-        <v>1.014153330034924</v>
+        <v>1.014153330034911</v>
       </c>
       <c r="J2" t="n">
-        <v>6.715696749679182</v>
+        <v>6.715696749679104</v>
       </c>
       <c r="K2" t="n">
-        <v>4.720142873404019</v>
+        <v>4.720142873404031</v>
       </c>
       <c r="L2" t="n">
-        <v>2.243526176321574</v>
+        <v>2.243526176321566</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4787082468514982</v>
+        <v>0.478708246851496</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4474674213607949</v>
+        <v>0.4474674213607939</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4787082468514982</v>
+        <v>0.478708246851496</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4507919998532299</v>
+        <v>0.4507919998532331</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4507919998532303</v>
+        <v>0.450791999853233</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4772874095841866</v>
+        <v>0.4772874095841996</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4787082468514982</v>
+        <v>0.478708246851496</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4692179720486337</v>
+        <v>0.4692179720486322</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4787082468514982</v>
+        <v>0.478708246851496</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4787082468514982</v>
+        <v>0.478708246851496</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4787082468514982</v>
+        <v>0.478708246851496</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6857635779552169</v>
+        <v>0.4907450384363412</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4787871816138128</v>
+        <v>0.4787871816139402</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6997852588784139</v>
+        <v>0.6997852588784206</v>
       </c>
       <c r="E4" t="n">
-        <v>0.474704790219538</v>
+        <v>0.4747047902194778</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4813029405089077</v>
+        <v>0.481302940508905</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4893242011690294</v>
+        <v>0.6843427406879004</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7267362590427908</v>
+        <v>0.7267362590427932</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4812547636334759</v>
+        <v>0.4812547636334772</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7092476781529895</v>
+        <v>0.5007881116659199</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5032141755973907</v>
+        <v>0.5032141755973843</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4930981269636981</v>
+        <v>0.4930981269636974</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.808912763933918</v>
+        <v>0.808912763933911</v>
       </c>
       <c r="C5" t="n">
-        <v>0.799422489131052</v>
+        <v>0.7994224891310563</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8070206707477998</v>
+        <v>0.8070206707477966</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7933090961223647</v>
+        <v>0.7933090961223668</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7933090961223647</v>
+        <v>0.7933090961223659</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8074919266666067</v>
+        <v>0.8074919266666076</v>
       </c>
       <c r="H5" t="n">
-        <v>0.808912763933918</v>
+        <v>0.808912763933911</v>
       </c>
       <c r="I5" t="n">
-        <v>0.799422489131052</v>
+        <v>0.7994224891310563</v>
       </c>
       <c r="J5" t="n">
-        <v>0.808912763933918</v>
+        <v>0.808912763933911</v>
       </c>
       <c r="K5" t="n">
-        <v>0.808912763933918</v>
+        <v>0.808912763933911</v>
       </c>
       <c r="L5" t="n">
-        <v>0.808912763933918</v>
+        <v>0.808912763933911</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8768849321154724</v>
+        <v>0.8768849321154825</v>
       </c>
       <c r="C6" t="n">
-        <v>1.186980034014433</v>
+        <v>1.186980034013473</v>
       </c>
       <c r="D6" t="n">
-        <v>1.26683248765833</v>
+        <v>1.266832487658325</v>
       </c>
       <c r="E6" t="n">
-        <v>1.098488411534104</v>
+        <v>1.098488411534096</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8751142974679166</v>
+        <v>0.8751142974678943</v>
       </c>
       <c r="G6" t="n">
-        <v>1.19844040788766</v>
+        <v>1.198440407887656</v>
       </c>
       <c r="H6" t="n">
-        <v>1.199861245156225</v>
+        <v>1.199861245156229</v>
       </c>
       <c r="I6" t="n">
-        <v>1.19037097035211</v>
+        <v>1.190370970352092</v>
       </c>
       <c r="J6" t="n">
-        <v>1.199924719274573</v>
+        <v>1.19992471927459</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8708854812772938</v>
+        <v>0.870885481277292</v>
       </c>
       <c r="L6" t="n">
-        <v>1.537237010995717</v>
+        <v>1.537237010995682</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.333689911760626</v>
+        <v>1.33368991176063</v>
       </c>
       <c r="C7" t="n">
-        <v>1.59110797590606</v>
+        <v>1.591107975906057</v>
       </c>
       <c r="D7" t="n">
-        <v>1.600598237124632</v>
+        <v>1.600598237124631</v>
       </c>
       <c r="E7" t="n">
-        <v>1.899114437453354</v>
+        <v>1.899114437453352</v>
       </c>
       <c r="F7" t="n">
-        <v>1.591107903947547</v>
+        <v>1.591107903947542</v>
       </c>
       <c r="G7" t="n">
-        <v>1.599177413441611</v>
+        <v>1.599177413441613</v>
       </c>
       <c r="H7" t="n">
-        <v>1.600598250708926</v>
+        <v>1.60059825070892</v>
       </c>
       <c r="I7" t="n">
-        <v>1.59110797590606</v>
+        <v>1.591107975906057</v>
       </c>
       <c r="J7" t="n">
-        <v>1.600598250708926</v>
+        <v>1.60059825070892</v>
       </c>
       <c r="K7" t="n">
-        <v>1.44595050517885</v>
+        <v>1.445950505178847</v>
       </c>
       <c r="L7" t="n">
-        <v>1.600598250708926</v>
+        <v>1.60059825070892</v>
       </c>
     </row>
     <row r="8">
@@ -1151,19 +1151,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.88752795114851</v>
+        <v>10.88752795114852</v>
       </c>
       <c r="C8" t="n">
-        <v>11.00564099185411</v>
+        <v>11.0056409918541</v>
       </c>
       <c r="D8" t="n">
-        <v>10.80585940566278</v>
+        <v>10.80585940566277</v>
       </c>
       <c r="E8" t="n">
-        <v>11.00564099185411</v>
+        <v>11.0056409918541</v>
       </c>
       <c r="F8" t="n">
-        <v>11.00564099185411</v>
+        <v>11.0056409918541</v>
       </c>
       <c r="G8" t="n">
         <v>10.88331703981609</v>
@@ -1172,16 +1172,16 @@
         <v>10.87609139141626</v>
       </c>
       <c r="I8" t="n">
-        <v>11.00564099185411</v>
+        <v>11.0056409918541</v>
       </c>
       <c r="J8" t="n">
         <v>10.67733635943306</v>
       </c>
       <c r="K8" t="n">
-        <v>10.70775088511601</v>
+        <v>10.707750885116</v>
       </c>
       <c r="L8" t="n">
-        <v>10.78594077318138</v>
+        <v>10.78594077318136</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.50873938467036</v>
+        <v>4.508739384670354</v>
       </c>
       <c r="C9" t="n">
-        <v>4.669255246524884</v>
+        <v>4.669255246524879</v>
       </c>
       <c r="D9" t="n">
-        <v>4.475476784655234</v>
+        <v>4.475476784655211</v>
       </c>
       <c r="E9" t="n">
-        <v>4.669255246524884</v>
+        <v>4.669255246524879</v>
       </c>
       <c r="F9" t="n">
-        <v>4.669255246524884</v>
+        <v>4.669255246524879</v>
       </c>
       <c r="G9" t="n">
-        <v>4.50714325724325</v>
+        <v>4.507143257243242</v>
       </c>
       <c r="H9" t="n">
-        <v>4.504032694408256</v>
+        <v>4.504032694408252</v>
       </c>
       <c r="I9" t="n">
-        <v>4.669255246524884</v>
+        <v>4.669255246524879</v>
       </c>
       <c r="J9" t="n">
-        <v>4.423185576279483</v>
+        <v>4.42318557627949</v>
       </c>
       <c r="K9" t="n">
-        <v>4.435523471770972</v>
+        <v>4.435523471770959</v>
       </c>
       <c r="L9" t="n">
-        <v>4.472448466641765</v>
+        <v>4.46739225700548</v>
       </c>
     </row>
   </sheetData>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.16862161484197</v>
+        <v>11.16862161484196</v>
       </c>
       <c r="C2" t="n">
-        <v>14.85015747556377</v>
+        <v>14.85015747556376</v>
       </c>
       <c r="D2" t="n">
         <v>28.68145304389607</v>
@@ -1322,22 +1322,22 @@
         <v>12.07683485092544</v>
       </c>
       <c r="G2" t="n">
-        <v>23.08017417920552</v>
+        <v>23.08017417920554</v>
       </c>
       <c r="H2" t="n">
-        <v>40.53026496011675</v>
+        <v>40.53026496011674</v>
       </c>
       <c r="I2" t="n">
         <v>12.07683485092544</v>
       </c>
       <c r="J2" t="n">
-        <v>34.86459160164421</v>
+        <v>34.86459160164415</v>
       </c>
       <c r="K2" t="n">
-        <v>18.09455420485605</v>
+        <v>18.09455420485601</v>
       </c>
       <c r="L2" t="n">
-        <v>21.50378474938267</v>
+        <v>21.50378474938266</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>0.6830200871918481</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6614875667884762</v>
+      </c>
+      <c r="D3" t="n">
         <v>0.6830200871918478</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.6614875667884768</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.6830200871918479</v>
       </c>
       <c r="E3" t="n">
         <v>0.6555791087662948</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6555791087662949</v>
+        <v>0.6555791087662948</v>
       </c>
       <c r="G3" t="n">
-        <v>0.680716493213085</v>
+        <v>0.6807164932130871</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6830200871918479</v>
+        <v>0.6830200871918481</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6678332525278001</v>
+        <v>0.6678332525278006</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6830200871918479</v>
+        <v>0.6830200871918481</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6830200871918479</v>
+        <v>0.6830200871918478</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6830200871918479</v>
+        <v>0.6830200871918478</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7939614127031336</v>
+        <v>1.191800101628733</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7762131020077584</v>
+        <v>0.7762131020077797</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8140144308050518</v>
+        <v>0.8140210402762333</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7444636667260008</v>
+        <v>0.7444636667260004</v>
       </c>
       <c r="F4" t="n">
-        <v>0.777399299254218</v>
+        <v>0.777399299254217</v>
       </c>
       <c r="G4" t="n">
-        <v>1.18949650764997</v>
+        <v>0.7916578187243698</v>
       </c>
       <c r="H4" t="n">
-        <v>1.271418163201664</v>
+        <v>1.271418163201663</v>
       </c>
       <c r="I4" t="n">
-        <v>1.176613266964687</v>
+        <v>0.7787745780390852</v>
       </c>
       <c r="J4" t="n">
         <v>1.225826774445845</v>
       </c>
       <c r="K4" t="n">
-        <v>0.793400548139188</v>
+        <v>0.7934005481391887</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7967268685299091</v>
+        <v>0.7967268685299087</v>
       </c>
     </row>
     <row r="5">
@@ -1433,7 +1433,7 @@
         <v>1.20605654761994</v>
       </c>
       <c r="D5" t="n">
-        <v>1.204973798836385</v>
+        <v>1.204973798836384</v>
       </c>
       <c r="E5" t="n">
         <v>1.190421352885985</v>
@@ -1448,7 +1448,7 @@
         <v>1.206975213139003</v>
       </c>
       <c r="I5" t="n">
-        <v>1.191788378474955</v>
+        <v>1.191788378474956</v>
       </c>
       <c r="J5" t="n">
         <v>1.206975213139003</v>
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.443556703736947</v>
+        <v>1.443556703736949</v>
       </c>
       <c r="C6" t="n">
         <v>2.056641243560789</v>
       </c>
       <c r="D6" t="n">
-        <v>2.183253570203951</v>
+        <v>2.183253570203956</v>
       </c>
       <c r="E6" t="n">
-        <v>1.874121603262554</v>
+        <v>1.874121603262557</v>
       </c>
       <c r="F6" t="n">
-        <v>1.448168631925004</v>
+        <v>1.448168631925006</v>
       </c>
       <c r="G6" t="n">
-        <v>2.053911307798263</v>
+        <v>2.053911307798265</v>
       </c>
       <c r="H6" t="n">
-        <v>2.056214901779585</v>
+        <v>2.056214901779587</v>
       </c>
       <c r="I6" t="n">
-        <v>2.041028067112978</v>
+        <v>2.04102806711298</v>
       </c>
       <c r="J6" t="n">
-        <v>2.056335306114171</v>
+        <v>2.056335306114174</v>
       </c>
       <c r="K6" t="n">
-        <v>1.432176263214863</v>
+        <v>1.432176263214864</v>
       </c>
       <c r="L6" t="n">
-        <v>2.696187618769439</v>
+        <v>2.696187618769443</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.368282665040455</v>
+        <v>2.368282665040454</v>
       </c>
       <c r="C7" t="n">
-        <v>2.889763116156041</v>
+        <v>2.88976311615604</v>
       </c>
       <c r="D7" t="n">
-        <v>2.890681984252476</v>
+        <v>2.890681984252481</v>
       </c>
       <c r="E7" t="n">
-        <v>3.478331898791555</v>
+        <v>3.478331898791552</v>
       </c>
       <c r="F7" t="n">
-        <v>2.875494358778193</v>
+        <v>2.875494358778191</v>
       </c>
       <c r="G7" t="n">
         <v>2.88837818769634</v>
       </c>
       <c r="H7" t="n">
-        <v>2.890681781675096</v>
+        <v>2.8906817816751</v>
       </c>
       <c r="I7" t="n">
-        <v>2.875494947011051</v>
+        <v>2.87549494701105</v>
       </c>
       <c r="J7" t="n">
-        <v>2.890681781675096</v>
+        <v>2.8906817816751</v>
       </c>
       <c r="K7" t="n">
         <v>2.588001767080614</v>
       </c>
       <c r="L7" t="n">
-        <v>2.890681781675096</v>
+        <v>2.8906817816751</v>
       </c>
     </row>
     <row r="8">
@@ -1550,16 +1550,16 @@
         <v>9.557912949204468</v>
       </c>
       <c r="C8" t="n">
-        <v>9.532880464207972</v>
+        <v>9.53288046420797</v>
       </c>
       <c r="D8" t="n">
         <v>11.48416085874909</v>
       </c>
       <c r="E8" t="n">
-        <v>10.47968966896888</v>
+        <v>10.47968966896887</v>
       </c>
       <c r="F8" t="n">
-        <v>10.47968966896888</v>
+        <v>10.47968966896887</v>
       </c>
       <c r="G8" t="n">
         <v>10.39850986057385</v>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.373406861037892</v>
+        <v>3.373406861037893</v>
       </c>
       <c r="C9" t="n">
         <v>3.397507265447509</v>
@@ -1596,7 +1596,7 @@
         <v>5.507879778800826</v>
       </c>
       <c r="E9" t="n">
-        <v>4.296231276119087</v>
+        <v>4.296231276119088</v>
       </c>
       <c r="F9" t="n">
         <v>4.296231276119088</v>
@@ -1605,19 +1605,19 @@
         <v>4.355772569509432</v>
       </c>
       <c r="H9" t="n">
-        <v>5.441552933998084</v>
+        <v>5.441552933998083</v>
       </c>
       <c r="I9" t="n">
         <v>4.296231276119088</v>
       </c>
       <c r="J9" t="n">
-        <v>5.294450655387709</v>
+        <v>5.294450655387707</v>
       </c>
       <c r="K9" t="n">
         <v>4.880058800424239</v>
       </c>
       <c r="L9" t="n">
-        <v>5.802636658332404</v>
+        <v>5.802636658332405</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.725402184150423</v>
+        <v>5.725402184150425</v>
       </c>
       <c r="C2" t="n">
-        <v>10.11956972254828</v>
+        <v>10.1195697225483</v>
       </c>
       <c r="D2" t="n">
         <v>19.15427538737585</v>
       </c>
       <c r="E2" t="n">
-        <v>6.543925335290116</v>
+        <v>6.543925335290134</v>
       </c>
       <c r="F2" t="n">
-        <v>6.543925335290116</v>
+        <v>6.543925335290134</v>
       </c>
       <c r="G2" t="n">
-        <v>14.54621765440987</v>
+        <v>14.54621765440993</v>
       </c>
       <c r="H2" t="n">
-        <v>21.22749112229006</v>
+        <v>21.22749112229007</v>
       </c>
       <c r="I2" t="n">
-        <v>6.543925335290116</v>
+        <v>6.543925335290134</v>
       </c>
       <c r="J2" t="n">
-        <v>25.64129144854703</v>
+        <v>25.64129144854706</v>
       </c>
       <c r="K2" t="n">
-        <v>8.463300067447701</v>
+        <v>8.463300067447703</v>
       </c>
       <c r="L2" t="n">
-        <v>11.01056531930908</v>
+        <v>11.01056531930909</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6331176455458581</v>
+        <v>0.6331176455458644</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6077803457366661</v>
+        <v>0.6077803457366662</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6331176455458581</v>
+        <v>0.6331176455458644</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6052265850847027</v>
+        <v>0.6052265850847038</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6052265850847034</v>
+        <v>0.6052265850847039</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6308924173826543</v>
+        <v>0.6308924173826567</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6331176455458581</v>
+        <v>0.6331176455458644</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6184267365316616</v>
+        <v>0.6184267365316617</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6331176455458583</v>
+        <v>0.6331176455458644</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6331176455458581</v>
+        <v>0.6331176455458644</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6331176455458581</v>
+        <v>0.6331176455458644</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.057275620535298</v>
+        <v>1.057275620535306</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7083248187481807</v>
+        <v>0.7083248187480203</v>
       </c>
       <c r="D4" t="n">
-        <v>1.083877475540682</v>
+        <v>1.083877475540696</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6771147583209458</v>
+        <v>0.6771147583209455</v>
       </c>
       <c r="F4" t="n">
         <v>0.7048225481486767</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7184630913026872</v>
+        <v>1.055050392372099</v>
       </c>
       <c r="H4" t="n">
         <v>1.134813964890856</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7059974104516964</v>
+        <v>0.7059974104516967</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7414438773717484</v>
+        <v>0.7414438773717461</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7166607160868141</v>
+        <v>0.7166607160868165</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7219188356574172</v>
+        <v>0.7219188356574195</v>
       </c>
     </row>
     <row r="5">
@@ -1823,13 +1823,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.08683383016833</v>
+        <v>1.086833830168331</v>
       </c>
       <c r="C5" t="n">
         <v>1.086079765407646</v>
       </c>
       <c r="D5" t="n">
-        <v>1.084940288099583</v>
+        <v>1.084940288099576</v>
       </c>
       <c r="E5" t="n">
         <v>1.070080932490938</v>
@@ -1838,22 +1838,22 @@
         <v>1.070080932490938</v>
       </c>
       <c r="G5" t="n">
-        <v>1.084608602005126</v>
+        <v>1.084608602005123</v>
       </c>
       <c r="H5" t="n">
-        <v>1.08683383016833</v>
+        <v>1.086833830168331</v>
       </c>
       <c r="I5" t="n">
         <v>1.072142921154129</v>
       </c>
       <c r="J5" t="n">
-        <v>1.08683383016833</v>
+        <v>1.086833830168331</v>
       </c>
       <c r="K5" t="n">
-        <v>1.08683383016833</v>
+        <v>1.086833830168331</v>
       </c>
       <c r="L5" t="n">
-        <v>1.08683383016833</v>
+        <v>1.086833830168331</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.283090888019865</v>
+        <v>1.283090888019875</v>
       </c>
       <c r="C6" t="n">
-        <v>1.811905592677845</v>
+        <v>1.811905592670751</v>
       </c>
       <c r="D6" t="n">
-        <v>1.921832974455325</v>
+        <v>1.921832974455328</v>
       </c>
       <c r="E6" t="n">
-        <v>1.652702707516627</v>
+        <v>1.652702707516629</v>
       </c>
       <c r="F6" t="n">
-        <v>1.28506930153916</v>
+        <v>1.285069301539161</v>
       </c>
       <c r="G6" t="n">
-        <v>1.80990747878584</v>
+        <v>1.809907478785838</v>
       </c>
       <c r="H6" t="n">
-        <v>1.81213270695292</v>
+        <v>1.812132706952929</v>
       </c>
       <c r="I6" t="n">
         <v>1.797441797934844</v>
       </c>
       <c r="J6" t="n">
-        <v>1.812236678245655</v>
+        <v>1.812236678245661</v>
       </c>
       <c r="K6" t="n">
-        <v>1.273263664672113</v>
+        <v>1.273263664672115</v>
       </c>
       <c r="L6" t="n">
-        <v>2.364761124043973</v>
+        <v>2.364761124043985</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.926427535451644</v>
+        <v>1.92642753545165</v>
       </c>
       <c r="C7" t="n">
         <v>2.333858612668688</v>
       </c>
       <c r="D7" t="n">
-        <v>2.334612884919641</v>
+        <v>2.334612884919651</v>
       </c>
       <c r="E7" t="n">
-        <v>2.790958497264107</v>
+        <v>2.790958497264108</v>
       </c>
       <c r="F7" t="n">
-        <v>2.319921402305454</v>
+        <v>2.319921402305457</v>
       </c>
       <c r="G7" t="n">
-        <v>2.332387449266164</v>
+        <v>2.332387449266168</v>
       </c>
       <c r="H7" t="n">
-        <v>2.33461267742937</v>
+        <v>2.334612677429378</v>
       </c>
       <c r="I7" t="n">
-        <v>2.319921768415169</v>
+        <v>2.319921768415172</v>
       </c>
       <c r="J7" t="n">
-        <v>2.33461267742937</v>
+        <v>2.334612677429378</v>
       </c>
       <c r="K7" t="n">
-        <v>2.098108690370339</v>
+        <v>2.09810869037034</v>
       </c>
       <c r="L7" t="n">
-        <v>2.33461267742937</v>
+        <v>2.334612677429378</v>
       </c>
     </row>
     <row r="8">
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.643507869509245</v>
+        <v>9.643507869509243</v>
       </c>
       <c r="C8" t="n">
         <v>9.600979300699038</v>
@@ -1973,7 +1973,7 @@
         <v>11.15743443581558</v>
       </c>
       <c r="L8" t="n">
-        <v>12.08671982455647</v>
+        <v>12.08671982455648</v>
       </c>
     </row>
     <row r="9">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.39136121218457</v>
+        <v>3.391361212184572</v>
       </c>
       <c r="C9" t="n">
-        <v>3.410444237495148</v>
+        <v>3.410444237495147</v>
       </c>
       <c r="D9" t="n">
-        <v>5.541235550644327</v>
+        <v>5.541235550644324</v>
       </c>
       <c r="E9" t="n">
         <v>4.312776571935561</v>
@@ -1998,22 +1998,22 @@
         <v>4.312776571935561</v>
       </c>
       <c r="G9" t="n">
-        <v>4.398443518981107</v>
+        <v>4.398443518981108</v>
       </c>
       <c r="H9" t="n">
-        <v>5.545364252828231</v>
+        <v>5.545364252828236</v>
       </c>
       <c r="I9" t="n">
         <v>4.312776571935561</v>
       </c>
       <c r="J9" t="n">
-        <v>5.329391930462106</v>
+        <v>5.329391930462109</v>
       </c>
       <c r="K9" t="n">
         <v>4.922433151325711</v>
       </c>
       <c r="L9" t="n">
-        <v>5.853601759330855</v>
+        <v>5.853601759330857</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.694164972919921</v>
+        <v>2.694164972919923</v>
       </c>
       <c r="C2" t="n">
-        <v>6.677343233682686</v>
+        <v>6.677343233682683</v>
       </c>
       <c r="D2" t="n">
         <v>12.99054857639739</v>
       </c>
       <c r="E2" t="n">
-        <v>2.70686003693972</v>
+        <v>2.706860036939721</v>
       </c>
       <c r="F2" t="n">
-        <v>2.70686003693972</v>
+        <v>2.706860036939721</v>
       </c>
       <c r="G2" t="n">
-        <v>9.381665715046347</v>
+        <v>9.381665715046363</v>
       </c>
       <c r="H2" t="n">
-        <v>12.07058222176496</v>
+        <v>12.07058222176494</v>
       </c>
       <c r="I2" t="n">
-        <v>2.70686003693972</v>
+        <v>2.706860036939721</v>
       </c>
       <c r="J2" t="n">
-        <v>18.28433997394301</v>
+        <v>18.28433997394302</v>
       </c>
       <c r="K2" t="n">
-        <v>3.734877182359631</v>
+        <v>3.734877182359619</v>
       </c>
       <c r="L2" t="n">
-        <v>5.605198848675525</v>
+        <v>5.605198848675522</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6064845129489483</v>
+        <v>0.606484512948947</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5763372423789577</v>
+        <v>0.5763372423789579</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6064845129489482</v>
+        <v>0.6064845129489473</v>
       </c>
       <c r="E3" t="n">
         <v>0.5786002103829384</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5786002103829384</v>
+        <v>0.5786002103829385</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6043034225674454</v>
+        <v>0.6043034225674461</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6064845129489482</v>
+        <v>0.6064845129489473</v>
       </c>
       <c r="I3" t="n">
-        <v>0.592069804028391</v>
+        <v>0.5920698040283912</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6064845129489483</v>
+        <v>0.6064845129489473</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6064845129489482</v>
+        <v>0.6064845129489473</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6064845129489482</v>
+        <v>0.6064845129489473</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6821620497750679</v>
+        <v>0.6821620497750657</v>
       </c>
       <c r="C4" t="n">
-        <v>0.671427766145578</v>
+        <v>0.671427766145607</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6958500204527868</v>
+        <v>0.6958432202003144</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6404177909026338</v>
+        <v>0.6404177909026155</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6663979427641633</v>
+        <v>0.6663979427641624</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9912327209166329</v>
+        <v>0.9912327209166331</v>
       </c>
       <c r="H4" t="n">
-        <v>1.062839475144986</v>
+        <v>1.062839475144984</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9789991023775779</v>
+        <v>0.9789991023775783</v>
       </c>
       <c r="J4" t="n">
         <v>1.026128297417414</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6781971923369454</v>
+        <v>0.6781971923369272</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6825600587061705</v>
+        <v>0.6825600587061215</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.031269507657255</v>
+        <v>1.031269507657254</v>
       </c>
       <c r="C5" t="n">
-        <v>1.030618341438423</v>
+        <v>1.030618341438424</v>
       </c>
       <c r="D5" t="n">
-        <v>1.029376716309631</v>
+        <v>1.02937671630963</v>
       </c>
       <c r="E5" t="n">
-        <v>1.014481390510506</v>
+        <v>1.014481390510505</v>
       </c>
       <c r="F5" t="n">
-        <v>1.014481390510506</v>
+        <v>1.014481390510505</v>
       </c>
       <c r="G5" t="n">
-        <v>1.029088417275753</v>
+        <v>1.029088417275754</v>
       </c>
       <c r="H5" t="n">
-        <v>1.031269507657255</v>
+        <v>1.031269507657254</v>
       </c>
       <c r="I5" t="n">
         <v>1.016854798736699</v>
       </c>
       <c r="J5" t="n">
-        <v>1.031269507657255</v>
+        <v>1.031269507657254</v>
       </c>
       <c r="K5" t="n">
-        <v>1.031269507657255</v>
+        <v>1.031269507657254</v>
       </c>
       <c r="L5" t="n">
-        <v>1.031269507657255</v>
+        <v>1.031269507657254</v>
       </c>
     </row>
     <row r="6">
@@ -2262,34 +2262,34 @@
         <v>1.206326739208676</v>
       </c>
       <c r="C6" t="n">
-        <v>1.700179130553469</v>
+        <v>1.700179130559499</v>
       </c>
       <c r="D6" t="n">
         <v>1.803102168973559</v>
       </c>
       <c r="E6" t="n">
-        <v>1.550688990882107</v>
+        <v>1.550688990882105</v>
       </c>
       <c r="F6" t="n">
-        <v>1.207293317545004</v>
+        <v>1.207293317545002</v>
       </c>
       <c r="G6" t="n">
-        <v>1.698428342207857</v>
+        <v>1.698428342207856</v>
       </c>
       <c r="H6" t="n">
-        <v>1.700609432592022</v>
+        <v>1.700609432592023</v>
       </c>
       <c r="I6" t="n">
-        <v>1.686194723668803</v>
+        <v>1.686194723668802</v>
       </c>
       <c r="J6" t="n">
-        <v>1.70070657262927</v>
+        <v>1.700706572629269</v>
       </c>
       <c r="K6" t="n">
-        <v>1.197145184473975</v>
+        <v>1.197145184473974</v>
       </c>
       <c r="L6" t="n">
-        <v>2.216929036444688</v>
+        <v>2.216929036444686</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.700520035657846</v>
+        <v>1.700520035657849</v>
       </c>
       <c r="C7" t="n">
-        <v>2.051678656058915</v>
+        <v>2.051678656058917</v>
       </c>
       <c r="D7" t="n">
-        <v>2.052330001198833</v>
+        <v>2.052330001198834</v>
       </c>
       <c r="E7" t="n">
-        <v>2.443895964743185</v>
+        <v>2.443895964743186</v>
       </c>
       <c r="F7" t="n">
-        <v>2.037914837723731</v>
+        <v>2.03791483772373</v>
       </c>
       <c r="G7" t="n">
-        <v>2.050148731896246</v>
+        <v>2.050148731896244</v>
       </c>
       <c r="H7" t="n">
-        <v>2.052329822277746</v>
+        <v>2.052329822277748</v>
       </c>
       <c r="I7" t="n">
-        <v>2.03791511335719</v>
+        <v>2.037915113357191</v>
       </c>
       <c r="J7" t="n">
-        <v>2.052329822277746</v>
+        <v>2.052329822277748</v>
       </c>
       <c r="K7" t="n">
-        <v>1.609338456726018</v>
+        <v>1.840219876140379</v>
       </c>
       <c r="L7" t="n">
-        <v>2.052329822277746</v>
+        <v>2.052329822277748</v>
       </c>
     </row>
     <row r="8">
@@ -2354,7 +2354,7 @@
         <v>10.64474614956722</v>
       </c>
       <c r="G8" t="n">
-        <v>10.65525535066931</v>
+        <v>10.65525535066932</v>
       </c>
       <c r="H8" t="n">
         <v>11.80700728614756</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.404922365723294</v>
+        <v>3.404922365723295</v>
       </c>
       <c r="C9" t="n">
         <v>3.429046321268924</v>
@@ -2394,7 +2394,7 @@
         <v>4.337258297497233</v>
       </c>
       <c r="G9" t="n">
-        <v>4.438125122521449</v>
+        <v>4.438125122521448</v>
       </c>
       <c r="H9" t="n">
         <v>5.5943002747052</v>
@@ -2403,13 +2403,13 @@
         <v>4.337258297497233</v>
       </c>
       <c r="J9" t="n">
-        <v>5.375135449897454</v>
+        <v>5.375135449897455</v>
       </c>
       <c r="K9" t="n">
         <v>4.98039576952393</v>
       </c>
       <c r="L9" t="n">
-        <v>5.882487782085904</v>
+        <v>5.882487782085905</v>
       </c>
     </row>
   </sheetData>
@@ -2495,34 +2495,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.283489406358719</v>
+        <v>3.283489406358716</v>
       </c>
       <c r="C2" t="n">
-        <v>2.489352998656965</v>
+        <v>2.489352998656961</v>
       </c>
       <c r="D2" t="n">
-        <v>16.15214528957522</v>
+        <v>16.15214528957519</v>
       </c>
       <c r="E2" t="n">
-        <v>4.812520923821572</v>
+        <v>4.812520923821568</v>
       </c>
       <c r="F2" t="n">
-        <v>4.812520923821572</v>
+        <v>4.812520923821568</v>
       </c>
       <c r="G2" t="n">
-        <v>14.6520813629752</v>
+        <v>14.65208136297524</v>
       </c>
       <c r="H2" t="n">
-        <v>31.28619312081163</v>
+        <v>31.28619312081161</v>
       </c>
       <c r="I2" t="n">
-        <v>4.812520923821572</v>
+        <v>4.812520923821568</v>
       </c>
       <c r="J2" t="n">
-        <v>31.66406713194777</v>
+        <v>31.66406713194776</v>
       </c>
       <c r="K2" t="n">
-        <v>11.8423479351516</v>
+        <v>11.84234793515161</v>
       </c>
       <c r="L2" t="n">
         <v>16.70869772565927</v>
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6220222949904478</v>
+        <v>0.6220222949904487</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6006962681346218</v>
+        <v>0.6006962681346223</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6220222949904478</v>
+        <v>0.6220222949904487</v>
       </c>
       <c r="E3" t="n">
-        <v>0.596230512844647</v>
+        <v>0.5962305128446478</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5962305128446471</v>
+        <v>0.5962305128446478</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6197798323603083</v>
+        <v>0.6197798323603085</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6220222949904478</v>
+        <v>0.6220222949904487</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6072200978222674</v>
+        <v>0.6072200978222684</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6220222949904478</v>
+        <v>0.6220222949904487</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6220222949904478</v>
+        <v>0.6220222949904487</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6220222949904478</v>
+        <v>0.6220222949904487</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6924165088131247</v>
+        <v>0.6924165088131231</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6671550559060033</v>
+        <v>0.6671550559058458</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7033472061698364</v>
+        <v>0.7033404196784794</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6478195797887175</v>
+        <v>0.6478195797886327</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6766008511572527</v>
+        <v>0.6766008511572513</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6901740461829845</v>
+        <v>0.6901740461829846</v>
       </c>
       <c r="H4" t="n">
         <v>1.10755194725838</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6776143116449446</v>
+        <v>1.021024933170217</v>
       </c>
       <c r="J4" t="n">
-        <v>1.066113384300777</v>
+        <v>0.7144090053619863</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6942618608297907</v>
+        <v>0.6942618608297918</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6964161051639111</v>
+        <v>0.6964161051639102</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.096217447109786</v>
+        <v>1.096217447109787</v>
       </c>
       <c r="C5" t="n">
-        <v>1.095277006391512</v>
+        <v>1.095277006391514</v>
       </c>
       <c r="D5" t="n">
-        <v>1.09421600156776</v>
+        <v>1.094216001567761</v>
       </c>
       <c r="E5" t="n">
-        <v>1.080266401716333</v>
+        <v>1.080266401716334</v>
       </c>
       <c r="F5" t="n">
-        <v>1.080266401716333</v>
+        <v>1.080266401716334</v>
       </c>
       <c r="G5" t="n">
-        <v>1.093974984479646</v>
+        <v>1.093974984479647</v>
       </c>
       <c r="H5" t="n">
-        <v>1.096217447109786</v>
+        <v>1.096217447109787</v>
       </c>
       <c r="I5" t="n">
-        <v>1.081415249941606</v>
+        <v>1.081415249941607</v>
       </c>
       <c r="J5" t="n">
-        <v>1.096217447109786</v>
+        <v>1.096217447109787</v>
       </c>
       <c r="K5" t="n">
-        <v>1.096217447109786</v>
+        <v>1.096217447109787</v>
       </c>
       <c r="L5" t="n">
-        <v>1.096217447109786</v>
+        <v>1.096217447109787</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.295197090281328</v>
+        <v>1.29519709028133</v>
       </c>
       <c r="C6" t="n">
-        <v>1.840554309664967</v>
+        <v>1.840554309673501</v>
       </c>
       <c r="D6" t="n">
         <v>1.952913186920493</v>
       </c>
       <c r="E6" t="n">
-        <v>1.67699048058798</v>
+        <v>1.676990480587982</v>
       </c>
       <c r="F6" t="n">
-        <v>1.298171469644949</v>
+        <v>1.298171469644951</v>
       </c>
       <c r="G6" t="n">
-        <v>1.837711780014038</v>
+        <v>1.837711780014041</v>
       </c>
       <c r="H6" t="n">
-        <v>1.839954242646282</v>
+        <v>1.839954242646287</v>
       </c>
       <c r="I6" t="n">
-        <v>1.825152045475999</v>
+        <v>1.825152045476002</v>
       </c>
       <c r="J6" t="n">
-        <v>1.840061302553376</v>
+        <v>1.840061302553378</v>
       </c>
       <c r="K6" t="n">
-        <v>1.285077946537356</v>
+        <v>1.285077946537357</v>
       </c>
       <c r="L6" t="n">
-        <v>2.408998639700684</v>
+        <v>2.40899863970069</v>
       </c>
     </row>
     <row r="7">
@@ -2695,22 +2695,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.05691874592333</v>
+        <v>2.056918745923328</v>
       </c>
       <c r="C7" t="n">
-        <v>2.503743665425499</v>
+        <v>2.503743665425497</v>
       </c>
       <c r="D7" t="n">
-        <v>2.504684225210058</v>
+        <v>2.504684225210055</v>
       </c>
       <c r="E7" t="n">
-        <v>3.006593140689759</v>
+        <v>3.006593140689754</v>
       </c>
       <c r="F7" t="n">
         <v>2.489881423012076</v>
       </c>
       <c r="G7" t="n">
-        <v>2.50244164351363</v>
+        <v>2.502441643513629</v>
       </c>
       <c r="H7" t="n">
         <v>2.50468410614377</v>
@@ -2722,7 +2722,7 @@
         <v>2.50468410614377</v>
       </c>
       <c r="K7" t="n">
-        <v>1.94086756093273</v>
+        <v>2.245247148000609</v>
       </c>
       <c r="L7" t="n">
         <v>2.50468410614377</v>
@@ -2781,7 +2781,7 @@
         <v>3.445832547208004</v>
       </c>
       <c r="D9" t="n">
-        <v>5.551869510377162</v>
+        <v>5.551869510377161</v>
       </c>
       <c r="E9" t="n">
         <v>4.301490480501799</v>
@@ -2805,7 +2805,7 @@
         <v>4.858877745008726</v>
       </c>
       <c r="L9" t="n">
-        <v>5.796946144559209</v>
+        <v>5.79694614455921</v>
       </c>
     </row>
   </sheetData>
@@ -2894,34 +2894,34 @@
         <v>1.544415551581109</v>
       </c>
       <c r="C2" t="n">
-        <v>1.349334518963903</v>
+        <v>1.349334518963906</v>
       </c>
       <c r="D2" t="n">
-        <v>2.095895988108304</v>
+        <v>2.095895988108305</v>
       </c>
       <c r="E2" t="n">
-        <v>2.035066062995643</v>
+        <v>2.035066062995638</v>
       </c>
       <c r="F2" t="n">
-        <v>2.035066062995643</v>
+        <v>2.035066062995638</v>
       </c>
       <c r="G2" t="n">
-        <v>3.315109124841486</v>
+        <v>3.31510912484144</v>
       </c>
       <c r="H2" t="n">
-        <v>3.117470067594295</v>
+        <v>3.117470067594291</v>
       </c>
       <c r="I2" t="n">
-        <v>2.035066062995643</v>
+        <v>2.035066062995638</v>
       </c>
       <c r="J2" t="n">
         <v>11.61269080155997</v>
       </c>
       <c r="K2" t="n">
-        <v>2.289676999837645</v>
+        <v>2.289676999837643</v>
       </c>
       <c r="L2" t="n">
-        <v>3.98772604407775</v>
+        <v>3.987726044077751</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5609227247993389</v>
+        <v>0.5609227247993384</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5467430748485927</v>
+        <v>0.5467430748485935</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5609227247993389</v>
+        <v>0.5609227247993384</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5411702573882989</v>
+        <v>0.5411702573882992</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5411702573882989</v>
+        <v>0.5411702573882992</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5589808193591581</v>
+        <v>0.5589808193591593</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5609227247993389</v>
+        <v>0.5609227247993384</v>
       </c>
       <c r="I3" t="n">
-        <v>0.548026794878682</v>
+        <v>0.5480267948786822</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5609227247993389</v>
+        <v>0.5609227247993384</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5609227247993389</v>
+        <v>0.5609227247993384</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5609227247993389</v>
+        <v>0.5609227247993384</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5994958077036362</v>
+        <v>0.5994958077036385</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5904097244409913</v>
+        <v>0.5904097244409093</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5988984640317022</v>
+        <v>0.8797239054095651</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5719653251713026</v>
+        <v>0.5719653251713024</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5863900123802914</v>
+        <v>0.586390012380292</v>
       </c>
       <c r="G4" t="n">
-        <v>0.860681424745722</v>
+        <v>0.5975539022634584</v>
       </c>
       <c r="H4" t="n">
-        <v>0.917250934429521</v>
+        <v>0.9172509344295192</v>
       </c>
       <c r="I4" t="n">
-        <v>0.849727400265246</v>
+        <v>0.8497274002652455</v>
       </c>
       <c r="J4" t="n">
-        <v>0.612293075580589</v>
+        <v>0.887571607488771</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5983609604646277</v>
+        <v>0.5983609604646281</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6003896563492739</v>
+        <v>0.6003896563492743</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9430283366797841</v>
+        <v>0.9430283366797836</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9425459225152223</v>
+        <v>0.942545922515223</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9411335212142512</v>
+        <v>0.9411335212142505</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9286810921700264</v>
+        <v>0.9286810921700255</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9286810921700264</v>
+        <v>0.9286810921700255</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9410864312396043</v>
+        <v>0.9410864312396042</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9430283366797841</v>
+        <v>0.9430283366797836</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9301324067591282</v>
+        <v>0.9301324067591287</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9430283366797841</v>
+        <v>0.9430283366797836</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9430283366797841</v>
+        <v>0.9430283366797836</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9430283366797841</v>
+        <v>0.9430283366797836</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.077550283995456</v>
+        <v>1.077550283995455</v>
       </c>
       <c r="C6" t="n">
-        <v>1.500888141818625</v>
+        <v>1.500888141812889</v>
       </c>
       <c r="D6" t="n">
-        <v>1.587934030005306</v>
+        <v>1.587934030005307</v>
       </c>
       <c r="E6" t="n">
-        <v>1.372223716542372</v>
+        <v>1.372223716542371</v>
       </c>
       <c r="F6" t="n">
-        <v>1.078318757929564</v>
+        <v>1.078318757929563</v>
       </c>
       <c r="G6" t="n">
         <v>1.498336661335202</v>
       </c>
       <c r="H6" t="n">
-        <v>1.500278566776912</v>
+        <v>1.500278566776911</v>
       </c>
       <c r="I6" t="n">
-        <v>1.487382636854726</v>
+        <v>1.487382636854725</v>
       </c>
       <c r="J6" t="n">
         <v>1.500361644609072</v>
       </c>
       <c r="K6" t="n">
-        <v>1.069697889147536</v>
+        <v>1.069697889147537</v>
       </c>
       <c r="L6" t="n">
-        <v>1.941853605748272</v>
+        <v>1.941853605748274</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.572549738442008</v>
+        <v>1.572549738442009</v>
       </c>
       <c r="C7" t="n">
-        <v>1.892955824586127</v>
+        <v>1.892955824586126</v>
       </c>
       <c r="D7" t="n">
         <v>1.893438339345597</v>
       </c>
       <c r="E7" t="n">
-        <v>2.250840731661946</v>
+        <v>2.250840731661945</v>
       </c>
       <c r="F7" t="n">
-        <v>1.880542154010266</v>
+        <v>1.880542154010267</v>
       </c>
       <c r="G7" t="n">
-        <v>1.891496333310505</v>
+        <v>1.891496333310506</v>
       </c>
       <c r="H7" t="n">
-        <v>1.893438238750689</v>
+        <v>1.893438238750687</v>
       </c>
       <c r="I7" t="n">
         <v>1.880542308830031</v>
       </c>
       <c r="J7" t="n">
-        <v>1.893438238750689</v>
+        <v>1.893438238750687</v>
       </c>
       <c r="K7" t="n">
-        <v>1.489382312395333</v>
+        <v>1.70751422375528</v>
       </c>
       <c r="L7" t="n">
-        <v>1.893438238750689</v>
+        <v>1.893438238750687</v>
       </c>
     </row>
     <row r="8">
@@ -3134,7 +3134,7 @@
         <v>9.313256428790996</v>
       </c>
       <c r="C8" t="n">
-        <v>9.735028899785878</v>
+        <v>9.735028899785879</v>
       </c>
       <c r="D8" t="n">
         <v>11.95913646191887</v>
@@ -3155,7 +3155,7 @@
         <v>10.58862406529054</v>
       </c>
       <c r="J8" t="n">
-        <v>11.55939743495506</v>
+        <v>11.55939743495507</v>
       </c>
       <c r="K8" t="n">
         <v>11.18306696203656</v>
@@ -3174,34 +3174,34 @@
         <v>3.009516353230762</v>
       </c>
       <c r="C9" t="n">
-        <v>3.422656359047376</v>
+        <v>3.422656359047377</v>
       </c>
       <c r="D9" t="n">
         <v>5.622821234887043</v>
       </c>
       <c r="E9" t="n">
-        <v>4.272832036651034</v>
+        <v>4.272832036651035</v>
       </c>
       <c r="F9" t="n">
-        <v>4.272832036651034</v>
+        <v>4.272832036651035</v>
       </c>
       <c r="G9" t="n">
-        <v>4.401487868320756</v>
+        <v>4.401487868320755</v>
       </c>
       <c r="H9" t="n">
         <v>5.615849248519665</v>
       </c>
       <c r="I9" t="n">
-        <v>4.272832036651034</v>
+        <v>4.272832036651035</v>
       </c>
       <c r="J9" t="n">
-        <v>5.355477075186704</v>
+        <v>5.355477075186705</v>
       </c>
       <c r="K9" t="n">
-        <v>4.861520782373881</v>
+        <v>4.861520782373876</v>
       </c>
       <c r="L9" t="n">
-        <v>5.849505704407509</v>
+        <v>5.849505704407507</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.328585633237907</v>
+        <v>1.328585633237925</v>
       </c>
       <c r="C2" t="n">
         <v>1.213134573041391</v>
       </c>
       <c r="D2" t="n">
-        <v>1.485402409203228</v>
+        <v>1.485402409203246</v>
       </c>
       <c r="E2" t="n">
-        <v>1.593082915254614</v>
+        <v>1.593082915254627</v>
       </c>
       <c r="F2" t="n">
-        <v>1.593082915254614</v>
+        <v>1.593082915254627</v>
       </c>
       <c r="G2" t="n">
-        <v>1.643046172034849</v>
+        <v>1.643046172034825</v>
       </c>
       <c r="H2" t="n">
-        <v>1.706764681381889</v>
+        <v>1.70676468138191</v>
       </c>
       <c r="I2" t="n">
-        <v>1.593082915254614</v>
+        <v>1.593082915254627</v>
       </c>
       <c r="J2" t="n">
-        <v>2.909157641823925</v>
+        <v>2.909157641823934</v>
       </c>
       <c r="K2" t="n">
-        <v>1.069598964270017</v>
+        <v>1.06959896427004</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5276494654872</v>
+        <v>1.527649465487195</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5230830220505008</v>
+        <v>0.5230830220505164</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5121485860857391</v>
+        <v>0.5121485860857395</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5230830220505008</v>
+        <v>0.5230830220505164</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5014711594869062</v>
+        <v>0.5014711594869061</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5014711594869062</v>
+        <v>0.501471159486906</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5211884862033443</v>
+        <v>0.5211884862033174</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5230830220505008</v>
+        <v>0.5230830220505164</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5104750252323185</v>
+        <v>0.5104750252322824</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5230830220505008</v>
+        <v>0.5230830220505164</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5230830220505008</v>
+        <v>0.5230830220505164</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5230830220505008</v>
+        <v>0.5230830220505164</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7800813143812575</v>
+        <v>0.7800813143812624</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5394400855615091</v>
+        <v>0.5394400855613325</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5464430449411312</v>
+        <v>0.5464430449411474</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5225444561092062</v>
+        <v>0.5225444561091708</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5326974481292748</v>
+        <v>0.5326974481292761</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7781867785340778</v>
+        <v>0.7781867785340806</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8227089947530728</v>
+        <v>0.5462096033139093</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5330099910231519</v>
+        <v>0.767473317563041</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8014553687814602</v>
+        <v>0.5538347112366824</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5436371352497931</v>
+        <v>0.5436371352497968</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5461109581068947</v>
+        <v>0.5461109581069095</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8752459852203907</v>
+        <v>0.8752459852203986</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8748675116075567</v>
+        <v>0.8748675116075562</v>
       </c>
       <c r="D5" t="n">
-        <v>0.87335093954272</v>
+        <v>0.8733509395427302</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8601960617405148</v>
+        <v>0.8601960617405154</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8601960617405148</v>
+        <v>0.8601960617405154</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8733514493732117</v>
+        <v>0.8733514493732203</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8752459852203907</v>
+        <v>0.8752459852203986</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8626379884021738</v>
+        <v>0.8626379884021751</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8752459852203907</v>
+        <v>0.8752459852203986</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8752459852203907</v>
+        <v>0.8752459852203986</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8752459852203907</v>
+        <v>0.8752459852203986</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9807730796919855</v>
+        <v>0.9807730796919837</v>
       </c>
       <c r="C6" t="n">
-        <v>1.351495580830154</v>
+        <v>1.351495580833275</v>
       </c>
       <c r="D6" t="n">
-        <v>1.428661700195845</v>
+        <v>1.428661700195843</v>
       </c>
       <c r="E6" t="n">
-        <v>1.237273264193274</v>
+        <v>1.237273264193275</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9795979019127951</v>
+        <v>0.9795979019127914</v>
       </c>
       <c r="G6" t="n">
         <v>1.349844878288684</v>
       </c>
       <c r="H6" t="n">
-        <v>1.351739414136731</v>
+        <v>1.351739414136733</v>
       </c>
       <c r="I6" t="n">
-        <v>1.33913141731765</v>
+        <v>1.339131417317647</v>
       </c>
       <c r="J6" t="n">
-        <v>1.35181231948009</v>
+        <v>1.351812319480096</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9738821895899572</v>
+        <v>0.9738821895899634</v>
       </c>
       <c r="L6" t="n">
-        <v>1.739244770007389</v>
+        <v>1.739244770007384</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.422907953209126</v>
+        <v>1.422907953209131</v>
       </c>
       <c r="C7" t="n">
-        <v>1.706268491666324</v>
+        <v>1.70626849166632</v>
       </c>
       <c r="D7" t="n">
-        <v>1.706647013754719</v>
+        <v>1.706647013754708</v>
       </c>
       <c r="E7" t="n">
-        <v>2.021467638621251</v>
+        <v>2.021467638621246</v>
       </c>
       <c r="F7" t="n">
-        <v>1.694038826580537</v>
+        <v>1.69403882658053</v>
       </c>
       <c r="G7" t="n">
-        <v>1.704752429431985</v>
+        <v>1.704752429431976</v>
       </c>
       <c r="H7" t="n">
-        <v>1.706646965279162</v>
+        <v>1.706646965279163</v>
       </c>
       <c r="I7" t="n">
-        <v>1.694038968460946</v>
+        <v>1.694038968460938</v>
       </c>
       <c r="J7" t="n">
-        <v>1.706646965279162</v>
+        <v>1.706646965279163</v>
       </c>
       <c r="K7" t="n">
-        <v>1.535577591307431</v>
+        <v>1.542247487745316</v>
       </c>
       <c r="L7" t="n">
-        <v>1.706646965279162</v>
+        <v>1.706646965279163</v>
       </c>
     </row>
     <row r="8">
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.117739263788831</v>
+        <v>9.117739263788836</v>
       </c>
       <c r="C8" t="n">
         <v>9.721402388781435</v>
@@ -3542,7 +3542,7 @@
         <v>10.56818808988023</v>
       </c>
       <c r="G8" t="n">
-        <v>10.70945930866263</v>
+        <v>10.70945930866264</v>
       </c>
       <c r="H8" t="n">
         <v>11.9332932993448</v>
@@ -3554,7 +3554,7 @@
         <v>11.69523450016747</v>
       </c>
       <c r="K8" t="n">
-        <v>11.22164253920973</v>
+        <v>11.22164253920974</v>
       </c>
       <c r="L8" t="n">
         <v>12.18960999308456</v>
@@ -3567,13 +3567,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.81424034436657</v>
+        <v>2.814240344366573</v>
       </c>
       <c r="C9" t="n">
-        <v>3.407521394569886</v>
+        <v>3.407521394569887</v>
       </c>
       <c r="D9" t="n">
-        <v>5.59065189282189</v>
+        <v>5.590651892821885</v>
       </c>
       <c r="E9" t="n">
         <v>4.246722562742716</v>
@@ -3582,22 +3582,22 @@
         <v>4.246722562742716</v>
       </c>
       <c r="G9" t="n">
-        <v>4.386002437418029</v>
+        <v>4.386002437418036</v>
       </c>
       <c r="H9" t="n">
-        <v>5.589970997104285</v>
+        <v>5.589970997104287</v>
       </c>
       <c r="I9" t="n">
         <v>4.246722562742716</v>
       </c>
       <c r="J9" t="n">
-        <v>5.372919205680152</v>
+        <v>5.372919205680153</v>
       </c>
       <c r="K9" t="n">
-        <v>4.882546737102684</v>
+        <v>4.88254673710269</v>
       </c>
       <c r="L9" t="n">
-        <v>5.839769155537748</v>
+        <v>5.839769155537754</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.072838665037255</v>
+        <v>2.072838665037264</v>
       </c>
       <c r="C2" t="n">
-        <v>1.516735966769699</v>
+        <v>1.516735966769695</v>
       </c>
       <c r="D2" t="n">
-        <v>4.598660153693683</v>
+        <v>4.598660153693699</v>
       </c>
       <c r="E2" t="n">
-        <v>2.594477377966216</v>
+        <v>2.594477377966233</v>
       </c>
       <c r="F2" t="n">
-        <v>2.594477377966216</v>
+        <v>2.594477377966233</v>
       </c>
       <c r="G2" t="n">
-        <v>7.293791374317287</v>
+        <v>7.293791374317382</v>
       </c>
       <c r="H2" t="n">
-        <v>25.80574636082396</v>
+        <v>25.80574636082401</v>
       </c>
       <c r="I2" t="n">
-        <v>2.594477377966216</v>
+        <v>2.594477377966233</v>
       </c>
       <c r="J2" t="n">
-        <v>11.4512428150026</v>
+        <v>11.45124281500259</v>
       </c>
       <c r="K2" t="n">
-        <v>4.576293297191821</v>
+        <v>4.576293297191835</v>
       </c>
       <c r="L2" t="n">
-        <v>13.28160122662345</v>
+        <v>13.28160122662347</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5949540427459349</v>
+        <v>0.5949540427459465</v>
       </c>
       <c r="C3" t="n">
-        <v>0.57866210444773</v>
+        <v>0.5786621044477303</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5949540427459349</v>
+        <v>0.5949540427459465</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5731386293888648</v>
+        <v>0.5731386293888645</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5731386293888647</v>
+        <v>0.5731386293888645</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5928999802864204</v>
+        <v>0.5928999802864181</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5949540427459349</v>
+        <v>0.5949540427459465</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5813507565814716</v>
+        <v>0.5813507565814724</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5949540427459349</v>
+        <v>0.5949540427459465</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5949540427459349</v>
+        <v>0.5949540427459465</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5949540427459349</v>
+        <v>0.5949540427459465</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6407211991527283</v>
+        <v>0.6407211991527463</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6255773833110584</v>
+        <v>0.6255773833109021</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6394418534001357</v>
+        <v>0.6394418534001446</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6062487589283749</v>
+        <v>0.6062487589283748</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6264891847551274</v>
+        <v>0.6264891847551269</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9479237239797165</v>
+        <v>0.6386671366932215</v>
       </c>
       <c r="H4" t="n">
-        <v>1.020417623823136</v>
+        <v>1.020417623823143</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9363745002747754</v>
+        <v>0.6271179129882711</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9785369372231526</v>
+        <v>0.6546893468231956</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6386432205813591</v>
+        <v>0.6386432205813741</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6441456519592268</v>
+        <v>0.6441456519592295</v>
       </c>
     </row>
     <row r="5">
@@ -3803,13 +3803,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.03026350894049</v>
+        <v>1.030263508940497</v>
       </c>
       <c r="C5" t="n">
-        <v>1.029610356821719</v>
+        <v>1.029610356821721</v>
       </c>
       <c r="D5" t="n">
-        <v>1.028262299134999</v>
+        <v>1.028262299135011</v>
       </c>
       <c r="E5" t="n">
         <v>1.015482596042529</v>
@@ -3818,22 +3818,22 @@
         <v>1.015482596042529</v>
       </c>
       <c r="G5" t="n">
-        <v>1.028209446480963</v>
+        <v>1.028209446480976</v>
       </c>
       <c r="H5" t="n">
-        <v>1.03026350894049</v>
+        <v>1.030263508940497</v>
       </c>
       <c r="I5" t="n">
         <v>1.01666022277602</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03026350894049</v>
+        <v>1.030263508940497</v>
       </c>
       <c r="K5" t="n">
-        <v>1.03026350894049</v>
+        <v>1.030263508940497</v>
       </c>
       <c r="L5" t="n">
-        <v>1.03026350894049</v>
+        <v>1.030263508940497</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.200051369038309</v>
+        <v>1.200051369038321</v>
       </c>
       <c r="C6" t="n">
-        <v>1.694069572902544</v>
+        <v>1.694069572894493</v>
       </c>
       <c r="D6" t="n">
-        <v>1.795481784642919</v>
+        <v>1.795481784642929</v>
       </c>
       <c r="E6" t="n">
-        <v>1.545530302978643</v>
+        <v>1.545530302978646</v>
       </c>
       <c r="F6" t="n">
-        <v>1.202572075992872</v>
+        <v>1.202572075992873</v>
       </c>
       <c r="G6" t="n">
-        <v>1.691165984208838</v>
+        <v>1.691165984208855</v>
       </c>
       <c r="H6" t="n">
-        <v>1.693220046670648</v>
+        <v>1.69322004667065</v>
       </c>
       <c r="I6" t="n">
-        <v>1.679616760503892</v>
+        <v>1.679616760503895</v>
       </c>
       <c r="J6" t="n">
-        <v>1.693316967991981</v>
+        <v>1.693316967991993</v>
       </c>
       <c r="K6" t="n">
-        <v>1.19089050769561</v>
+        <v>1.190890507695613</v>
       </c>
       <c r="L6" t="n">
-        <v>2.208375968134572</v>
+        <v>2.208375968134587</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.841839890844177</v>
+        <v>1.841839890844186</v>
       </c>
       <c r="C7" t="n">
-        <v>2.233330094905554</v>
+        <v>2.233330094905553</v>
       </c>
       <c r="D7" t="n">
-        <v>2.233983185962272</v>
+        <v>2.233983185962285</v>
       </c>
       <c r="E7" t="n">
-        <v>2.672904455860508</v>
+        <v>2.672904455860505</v>
       </c>
       <c r="F7" t="n">
-        <v>2.220379506419716</v>
+        <v>2.220379506419715</v>
       </c>
       <c r="G7" t="n">
-        <v>2.231929184564799</v>
+        <v>2.231929184564806</v>
       </c>
       <c r="H7" t="n">
-        <v>2.233983247024321</v>
+        <v>2.233983247024327</v>
       </c>
       <c r="I7" t="n">
-        <v>2.220379960859854</v>
+        <v>2.220379960859852</v>
       </c>
       <c r="J7" t="n">
-        <v>2.233983247024321</v>
+        <v>2.233983247024327</v>
       </c>
       <c r="K7" t="n">
-        <v>2.006773820705303</v>
+        <v>2.006773820705306</v>
       </c>
       <c r="L7" t="n">
-        <v>2.233983247024321</v>
+        <v>2.233983247024327</v>
       </c>
     </row>
     <row r="8">
@@ -3923,13 +3923,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.327093418119526</v>
+        <v>9.327093418119532</v>
       </c>
       <c r="C8" t="n">
         <v>9.713526391142072</v>
       </c>
       <c r="D8" t="n">
-        <v>11.93055282611551</v>
+        <v>11.93055282611552</v>
       </c>
       <c r="E8" t="n">
         <v>10.59929993697645</v>
@@ -3938,7 +3938,7 @@
         <v>10.59929993697645</v>
       </c>
       <c r="G8" t="n">
-        <v>10.63314437056992</v>
+        <v>10.63314437056993</v>
       </c>
       <c r="H8" t="n">
         <v>11.5096025796872</v>
@@ -3950,10 +3950,10 @@
         <v>11.60821405185529</v>
       </c>
       <c r="K8" t="n">
-        <v>11.14476464302984</v>
+        <v>11.14476464302985</v>
       </c>
       <c r="L8" t="n">
-        <v>12.01191381315388</v>
+        <v>12.01191381315389</v>
       </c>
     </row>
     <row r="9">
@@ -3963,13 +3963,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.029077951623913</v>
+        <v>3.029077951623921</v>
       </c>
       <c r="C9" t="n">
         <v>3.402870561835814</v>
       </c>
       <c r="D9" t="n">
-        <v>5.626692831259729</v>
+        <v>5.626692831259739</v>
       </c>
       <c r="E9" t="n">
         <v>4.289388674953996</v>
@@ -3978,22 +3978,22 @@
         <v>4.289388674953996</v>
       </c>
       <c r="G9" t="n">
-        <v>4.382886989749878</v>
+        <v>4.382886989749879</v>
       </c>
       <c r="H9" t="n">
-        <v>5.455719381977469</v>
+        <v>5.455719381977477</v>
       </c>
       <c r="I9" t="n">
         <v>4.289388674953996</v>
       </c>
       <c r="J9" t="n">
-        <v>5.393462002509447</v>
+        <v>5.393462002509453</v>
       </c>
       <c r="K9" t="n">
-        <v>4.852678966282517</v>
+        <v>4.852678966282521</v>
       </c>
       <c r="L9" t="n">
-        <v>5.79960590841696</v>
+        <v>5.799605908416964</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8846392486171316</v>
+        <v>0.8846392486171305</v>
       </c>
       <c r="C2" t="n">
-        <v>1.126980630660797</v>
+        <v>1.126980630660796</v>
       </c>
       <c r="D2" t="n">
-        <v>1.526783282120132</v>
+        <v>1.52678328212013</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7723152492784564</v>
+        <v>0.772315249278456</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7723152492784564</v>
+        <v>0.772315249278456</v>
       </c>
       <c r="G2" t="n">
-        <v>1.281832481942582</v>
+        <v>1.281832481942508</v>
       </c>
       <c r="H2" t="n">
         <v>1.689832324420631</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7723152492784564</v>
+        <v>0.772315249278456</v>
       </c>
       <c r="J2" t="n">
-        <v>1.301479047730188</v>
+        <v>1.301479047730183</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0009846219054792105</v>
+        <v>0.0009846219054800986</v>
       </c>
       <c r="L2" t="n">
-        <v>1.824435277143759</v>
+        <v>1.824435277143764</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5264766484105482</v>
+        <v>0.5264766484105472</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5146650248247291</v>
+        <v>0.5146650248247276</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5264766484105482</v>
+        <v>0.5264766484105472</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5066728221170728</v>
+        <v>0.5066728221170724</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5066728221170728</v>
+        <v>0.5066728221170724</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5245997156756578</v>
+        <v>0.5245997156756572</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5264766484105482</v>
+        <v>0.5264766484105472</v>
       </c>
       <c r="I3" t="n">
         <v>0.5139921585208668</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5264766484105482</v>
+        <v>0.5264766484105472</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5264766484105482</v>
+        <v>0.5264766484105472</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5264766484105482</v>
+        <v>0.5264766484105472</v>
       </c>
     </row>
     <row r="4">
@@ -4159,34 +4159,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5465624348644937</v>
+        <v>0.7832970898922743</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5408221140616813</v>
+        <v>0.5408221140614763</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5480019661889506</v>
+        <v>0.5480086195871144</v>
       </c>
       <c r="E4" t="n">
-        <v>0.52286851093883</v>
+        <v>0.5228685109388292</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5336995449917011</v>
+        <v>0.5336995449916992</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5446855021296027</v>
+        <v>0.5446855021296005</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8379202325887957</v>
+        <v>0.837920232588788</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7708126000025952</v>
+        <v>0.7708126000025927</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8067658231303124</v>
+        <v>0.5544224275219538</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5424434644266032</v>
+        <v>0.5424434644265833</v>
       </c>
       <c r="L4" t="n">
         <v>0.5473359798718966</v>
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8798991385947816</v>
+        <v>0.8798991385947821</v>
       </c>
       <c r="C5" t="n">
-        <v>0.879525838599868</v>
+        <v>0.8795258385998654</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8780045465301179</v>
+        <v>0.8780045465301153</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8655921438428713</v>
+        <v>0.8655921438428696</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8655921438428713</v>
+        <v>0.8655921438428696</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8780222058598907</v>
+        <v>0.8780222058598884</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8798991385947816</v>
+        <v>0.8798991385947821</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8674146487051011</v>
+        <v>0.8674146487050993</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8798991385947816</v>
+        <v>0.8798991385947821</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8798991385947816</v>
+        <v>0.8798991385947821</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8798991385947816</v>
+        <v>0.8798991385947821</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.987145833491884</v>
+        <v>0.9871458334918819</v>
       </c>
       <c r="C6" t="n">
-        <v>1.363102769251462</v>
+        <v>1.363102769251456</v>
       </c>
       <c r="D6" t="n">
-        <v>1.440632726296814</v>
+        <v>1.440632726296813</v>
       </c>
       <c r="E6" t="n">
-        <v>1.247668097191188</v>
+        <v>1.247668097191184</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9866103866867907</v>
+        <v>0.9866103866867894</v>
       </c>
       <c r="G6" t="n">
-        <v>1.360872036542468</v>
+        <v>1.360872036542472</v>
       </c>
       <c r="H6" t="n">
-        <v>1.362748969280327</v>
+        <v>1.362748969280323</v>
       </c>
       <c r="I6" t="n">
-        <v>1.35026447938768</v>
+        <v>1.350264479387674</v>
       </c>
       <c r="J6" t="n">
-        <v>1.362822785829289</v>
+        <v>1.362822785829285</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9801688124308381</v>
+        <v>0.9801688124308351</v>
       </c>
       <c r="L6" t="n">
-        <v>1.755097851821101</v>
+        <v>1.755097851821099</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.469868654579495</v>
+        <v>1.469868654579493</v>
       </c>
       <c r="C7" t="n">
-        <v>1.766477361829943</v>
+        <v>1.766477361829939</v>
       </c>
       <c r="D7" t="n">
-        <v>1.766850702350566</v>
+        <v>1.766850702350558</v>
       </c>
       <c r="E7" t="n">
-        <v>2.097076960409746</v>
+        <v>2.097076960409743</v>
       </c>
       <c r="F7" t="n">
-        <v>1.754366021947001</v>
+        <v>1.754366021946999</v>
       </c>
       <c r="G7" t="n">
-        <v>1.764973729089966</v>
+        <v>1.764973729089962</v>
       </c>
       <c r="H7" t="n">
-        <v>1.766850661824857</v>
+        <v>1.766850661824853</v>
       </c>
       <c r="I7" t="n">
-        <v>1.754366171935173</v>
+        <v>1.754366171935171</v>
       </c>
       <c r="J7" t="n">
-        <v>1.766850661824857</v>
+        <v>1.766850661824853</v>
       </c>
       <c r="K7" t="n">
-        <v>1.594778137533506</v>
+        <v>1.392897293098786</v>
       </c>
       <c r="L7" t="n">
-        <v>1.766850661824857</v>
+        <v>1.766850661824853</v>
       </c>
     </row>
     <row r="8">
@@ -4337,7 +4337,7 @@
         <v>10.63965573583552</v>
       </c>
       <c r="H8" t="n">
-        <v>11.93497682270472</v>
+        <v>11.93497682270473</v>
       </c>
       <c r="I8" t="n">
         <v>10.55744799986867</v>
@@ -4359,13 +4359,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.062507701175011</v>
+        <v>2.06250770117501</v>
       </c>
       <c r="C9" t="n">
         <v>3.345523743845546</v>
       </c>
       <c r="D9" t="n">
-        <v>5.59156019165014</v>
+        <v>5.591560191650141</v>
       </c>
       <c r="E9" t="n">
         <v>4.224727810984626</v>
@@ -4374,7 +4374,7 @@
         <v>4.224727810984626</v>
       </c>
       <c r="G9" t="n">
-        <v>4.31237394635549</v>
+        <v>4.312373946355489</v>
       </c>
       <c r="H9" t="n">
         <v>5.591439352823842</v>
@@ -4383,13 +4383,13 @@
         <v>4.224727810984626</v>
       </c>
       <c r="J9" t="n">
-        <v>5.395908771559211</v>
+        <v>5.395908771559207</v>
       </c>
       <c r="K9" t="n">
-        <v>4.736203340265073</v>
+        <v>4.736203340265069</v>
       </c>
       <c r="L9" t="n">
-        <v>5.840814638419017</v>
+        <v>5.840814638419016</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8347735266085944</v>
+        <v>0.8347735266085835</v>
       </c>
       <c r="C2" t="n">
-        <v>1.040845744581319</v>
+        <v>1.040845744581315</v>
       </c>
       <c r="D2" t="n">
-        <v>1.141360518298043</v>
+        <v>1.141360518298029</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6002645685876786</v>
+        <v>0.6002645685876787</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6002645685876786</v>
+        <v>0.6002645685876787</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9504488351782739</v>
+        <v>0.9504488351782665</v>
       </c>
       <c r="H2" t="n">
-        <v>1.317520996370702</v>
+        <v>1.317520996370698</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6002645685876786</v>
+        <v>0.6002645685876787</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7509912921048398</v>
+        <v>0.7509912921048356</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.02350249314089015</v>
+        <v>-0.0235024931409159</v>
       </c>
       <c r="L2" t="n">
-        <v>1.434093050303632</v>
+        <v>1.434093050303619</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4769542231695197</v>
+        <v>0.4769542231695073</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4694483883570268</v>
+        <v>0.4694483883570267</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4769542231695197</v>
+        <v>0.4769542231695073</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4622857743034977</v>
+        <v>0.4622857743034974</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4622857743034977</v>
+        <v>0.4622857743034974</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4752494897960297</v>
+        <v>0.4752494897960224</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4769542231695197</v>
+        <v>0.4769542231695073</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4655898967005409</v>
+        <v>0.4655898967005402</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4769542231695197</v>
+        <v>0.4769542231695073</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4769542231695197</v>
+        <v>0.4769542231695073</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4769542231695197</v>
+        <v>0.4769542231695073</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4794716901271714</v>
+        <v>0.679403423657614</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4748726519214197</v>
+        <v>0.4748726519214192</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4796221046627311</v>
+        <v>0.4796157990910508</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4615759196742273</v>
+        <v>0.4615759196742272</v>
       </c>
       <c r="F4" t="n">
-        <v>0.467924186271943</v>
+        <v>0.4679241862719433</v>
       </c>
       <c r="G4" t="n">
-        <v>0.677698690284144</v>
+        <v>0.4777669567536792</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7230913873013062</v>
+        <v>0.7230913873012857</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6680390971886545</v>
+        <v>0.4681073636581932</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4843374840068089</v>
+        <v>0.698690365479688</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4750590210580151</v>
+        <v>0.4750590210580136</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4803138333164609</v>
+        <v>0.4803138333165046</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8014661387407324</v>
+        <v>0.8014661387407305</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8011727426211557</v>
+        <v>0.8011727426211552</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7995703363028084</v>
+        <v>0.79957033630278</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7891872514120233</v>
+        <v>0.7891872514120231</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7891872514120233</v>
+        <v>0.7891872514120231</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7997614053672426</v>
+        <v>0.7997614053672282</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8014661387407324</v>
+        <v>0.8014661387407305</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7901018122717537</v>
+        <v>0.7901018122717528</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8014661387407324</v>
+        <v>0.8014661387407305</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8014661387407324</v>
+        <v>0.8014661387407305</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8014661387407324</v>
+        <v>0.8014661387407305</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8742956084858892</v>
+        <v>0.874295608485874</v>
       </c>
       <c r="C6" t="n">
-        <v>1.190896344676747</v>
+        <v>1.190896344676276</v>
       </c>
       <c r="D6" t="n">
-        <v>1.254986716160888</v>
+        <v>1.25498671616088</v>
       </c>
       <c r="E6" t="n">
-        <v>1.092900759990253</v>
+        <v>1.09290075999025</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8735114678152194</v>
+        <v>0.8735114678152177</v>
       </c>
       <c r="G6" t="n">
-        <v>1.187900481781661</v>
+        <v>1.187900481781649</v>
       </c>
       <c r="H6" t="n">
-        <v>1.189605215158011</v>
+        <v>1.189605215157995</v>
       </c>
       <c r="I6" t="n">
-        <v>1.178240888686171</v>
+        <v>1.178240888686169</v>
       </c>
       <c r="J6" t="n">
-        <v>1.189667182682458</v>
+        <v>1.189667182682451</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8684385706476636</v>
+        <v>0.8684385706476645</v>
       </c>
       <c r="L6" t="n">
-        <v>1.518972465231112</v>
+        <v>1.518972465231094</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.33094862606394</v>
+        <v>1.330948626063921</v>
       </c>
       <c r="C7" t="n">
-        <v>1.59418455867934</v>
+        <v>1.594184558679338</v>
       </c>
       <c r="D7" t="n">
-        <v>1.594477964336075</v>
+        <v>1.594477964336074</v>
       </c>
       <c r="E7" t="n">
-        <v>1.887220712096993</v>
+        <v>1.88722071209699</v>
       </c>
       <c r="F7" t="n">
-        <v>1.583113482337841</v>
+        <v>1.58311348233784</v>
       </c>
       <c r="G7" t="n">
-        <v>1.592773221425427</v>
+        <v>1.592773221425418</v>
       </c>
       <c r="H7" t="n">
-        <v>1.594477954798915</v>
+        <v>1.594477954798897</v>
       </c>
       <c r="I7" t="n">
-        <v>1.583113628329936</v>
+        <v>1.583113628329935</v>
       </c>
       <c r="J7" t="n">
-        <v>1.594477954798915</v>
+        <v>1.594477954798897</v>
       </c>
       <c r="K7" t="n">
-        <v>1.435593207301055</v>
+        <v>1.43559320730103</v>
       </c>
       <c r="L7" t="n">
-        <v>1.594477954798915</v>
+        <v>1.594477954798897</v>
       </c>
     </row>
     <row r="8">
@@ -4715,13 +4715,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.736890351929001</v>
+        <v>5.736890351928989</v>
       </c>
       <c r="C8" t="n">
         <v>9.614692053106555</v>
       </c>
       <c r="D8" t="n">
-        <v>11.89573146807448</v>
+        <v>11.89573146807447</v>
       </c>
       <c r="E8" t="n">
         <v>10.53230905651378</v>
@@ -4733,13 +4733,13 @@
         <v>10.44316236140265</v>
       </c>
       <c r="H8" t="n">
-        <v>11.89404732828366</v>
+        <v>11.89404732828365</v>
       </c>
       <c r="I8" t="n">
         <v>10.53230905651378</v>
       </c>
       <c r="J8" t="n">
-        <v>11.67352992393274</v>
+        <v>11.67352992393273</v>
       </c>
       <c r="K8" t="n">
         <v>11.13222464091971</v>
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8285453530828796</v>
+        <v>0.8285453530828715</v>
       </c>
       <c r="C9" t="n">
-        <v>3.300322420004482</v>
+        <v>3.300322420004483</v>
       </c>
       <c r="D9" t="n">
-        <v>5.547360658962461</v>
+        <v>5.547360658962452</v>
       </c>
       <c r="E9" t="n">
-        <v>4.197776231006854</v>
+        <v>4.197776231006853</v>
       </c>
       <c r="F9" t="n">
-        <v>4.197776231006854</v>
+        <v>4.197776231006853</v>
       </c>
       <c r="G9" t="n">
-        <v>4.114621227939415</v>
+        <v>4.114621227939411</v>
       </c>
       <c r="H9" t="n">
-        <v>5.546691099956089</v>
+        <v>5.546691099956085</v>
       </c>
       <c r="I9" t="n">
-        <v>4.197776231006854</v>
+        <v>4.197776231006853</v>
       </c>
       <c r="J9" t="n">
-        <v>5.322900109914911</v>
+        <v>5.322900109914901</v>
       </c>
       <c r="K9" t="n">
-        <v>4.779429483463959</v>
+        <v>4.77942948346396</v>
       </c>
       <c r="L9" t="n">
-        <v>5.807340559462879</v>
+        <v>5.807340559462871</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.44171062636335</v>
+        <v>30.4417106263637</v>
       </c>
       <c r="C2" t="n">
-        <v>12.52290970921389</v>
+        <v>12.52290970921386</v>
       </c>
       <c r="D2" t="n">
-        <v>46.88450307453918</v>
+        <v>46.88450307453914</v>
       </c>
       <c r="E2" t="n">
-        <v>12.52290970921389</v>
+        <v>12.52290970921386</v>
       </c>
       <c r="F2" t="n">
-        <v>12.52290970921389</v>
+        <v>12.52290970921386</v>
       </c>
       <c r="G2" t="n">
-        <v>37.48092762597145</v>
+        <v>37.4809276259715</v>
       </c>
       <c r="H2" t="n">
-        <v>76.16851182359288</v>
+        <v>76.16851182359272</v>
       </c>
       <c r="I2" t="n">
-        <v>12.52290970921389</v>
+        <v>12.52290970921386</v>
       </c>
       <c r="J2" t="n">
-        <v>47.83635972355363</v>
+        <v>47.83635972355361</v>
       </c>
       <c r="K2" t="n">
-        <v>25.91214323707197</v>
+        <v>25.91214323707203</v>
       </c>
       <c r="L2" t="n">
-        <v>26.67837620155558</v>
+        <v>26.67837620155561</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6849966485917566</v>
+        <v>0.6849966485917487</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6468970433018389</v>
+        <v>0.6468970433018391</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6849966485917566</v>
+        <v>0.6849966485917487</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6536978419145378</v>
+        <v>0.6536978419145387</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6536978419145378</v>
+        <v>0.6536978419145386</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6826101458250303</v>
+        <v>0.6826101458250279</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6849966485917566</v>
+        <v>0.6849966485917487</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6693726492656903</v>
+        <v>0.6693726492656904</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6849966485917566</v>
+        <v>0.6849966485917487</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6849966485917566</v>
+        <v>0.6849966485917487</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6849966485917566</v>
+        <v>0.6849966485917487</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.301736632306952</v>
+        <v>0.8290253770855199</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7728300325536938</v>
+        <v>0.7728300325537211</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8647536299839809</v>
+        <v>0.864759120164534</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7589290824268263</v>
+        <v>0.7589290824268264</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8099202401647138</v>
+        <v>0.8099202401647142</v>
       </c>
       <c r="G4" t="n">
-        <v>1.299350129540222</v>
+        <v>0.8266388743187973</v>
       </c>
       <c r="H4" t="n">
-        <v>1.360186609858338</v>
+        <v>1.360186609858337</v>
       </c>
       <c r="I4" t="n">
-        <v>1.286112632980886</v>
+        <v>1.286112632980885</v>
       </c>
       <c r="J4" t="n">
-        <v>1.330159926660563</v>
+        <v>0.8579554871535855</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8242619021380546</v>
+        <v>0.8242619021380416</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8441990787272682</v>
+        <v>0.8441990787272637</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.251995958523708</v>
+        <v>1.251995958523709</v>
       </c>
       <c r="C5" t="n">
-        <v>1.236371959197644</v>
+        <v>1.236371959197645</v>
       </c>
       <c r="D5" t="n">
-        <v>1.249958358381538</v>
+        <v>1.249958358381536</v>
       </c>
       <c r="E5" t="n">
-        <v>1.23565089945782</v>
+        <v>1.235650899457822</v>
       </c>
       <c r="F5" t="n">
-        <v>1.23565089945782</v>
+        <v>1.235650899457822</v>
       </c>
       <c r="G5" t="n">
-        <v>1.249609455756984</v>
+        <v>1.249609455756982</v>
       </c>
       <c r="H5" t="n">
-        <v>1.251995958523708</v>
+        <v>1.251995958523709</v>
       </c>
       <c r="I5" t="n">
-        <v>1.236371959197644</v>
+        <v>1.236371959197645</v>
       </c>
       <c r="J5" t="n">
-        <v>1.251995958523708</v>
+        <v>1.251995958523709</v>
       </c>
       <c r="K5" t="n">
-        <v>1.251995958523708</v>
+        <v>1.251995958523709</v>
       </c>
       <c r="L5" t="n">
-        <v>1.251995958523708</v>
+        <v>1.251995958523709</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.517672969347075</v>
+        <v>1.517672969347072</v>
       </c>
       <c r="C6" t="n">
-        <v>2.164780426704052</v>
+        <v>2.164780426712169</v>
       </c>
       <c r="D6" t="n">
-        <v>2.315391355828901</v>
+        <v>2.315391355828897</v>
       </c>
       <c r="E6" t="n">
         <v>1.983305839954065</v>
       </c>
       <c r="F6" t="n">
-        <v>1.523777991294522</v>
+        <v>1.523777991294521</v>
       </c>
       <c r="G6" t="n">
-        <v>2.17600132338278</v>
+        <v>2.176001323382777</v>
       </c>
       <c r="H6" t="n">
-        <v>2.178387826150067</v>
+        <v>2.178387826150063</v>
       </c>
       <c r="I6" t="n">
-        <v>2.16276382682344</v>
+        <v>2.162763826823439</v>
       </c>
       <c r="J6" t="n">
         <v>2.178517675086624</v>
       </c>
       <c r="K6" t="n">
-        <v>1.505399851708275</v>
+        <v>1.505399851708279</v>
       </c>
       <c r="L6" t="n">
-        <v>2.868559741729737</v>
+        <v>2.868559741729739</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.753466389139453</v>
+        <v>2.753466389139457</v>
       </c>
       <c r="C7" t="n">
-        <v>3.367185637377449</v>
+        <v>3.367185637377453</v>
       </c>
       <c r="D7" t="n">
-        <v>3.382809824885455</v>
+        <v>3.382809824885456</v>
       </c>
       <c r="E7" t="n">
-        <v>4.093433240883293</v>
+        <v>4.093433240883297</v>
       </c>
       <c r="F7" t="n">
-        <v>3.36718457332683</v>
+        <v>3.367184573326834</v>
       </c>
       <c r="G7" t="n">
-        <v>3.380423133936789</v>
+        <v>3.380423133936787</v>
       </c>
       <c r="H7" t="n">
-        <v>3.382809636703514</v>
+        <v>3.382809636703519</v>
       </c>
       <c r="I7" t="n">
-        <v>3.367185637377449</v>
+        <v>3.367185637377453</v>
       </c>
       <c r="J7" t="n">
-        <v>3.382809636703514</v>
+        <v>3.382809636703519</v>
       </c>
       <c r="K7" t="n">
-        <v>3.018165766591858</v>
+        <v>3.018165766591867</v>
       </c>
       <c r="L7" t="n">
-        <v>3.382809636703514</v>
+        <v>3.382809636703519</v>
       </c>
     </row>
     <row r="8">
@@ -5111,13 +5111,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.35360134418883</v>
+        <v>10.35360134418882</v>
       </c>
       <c r="C8" t="n">
         <v>10.94725434028802</v>
       </c>
       <c r="D8" t="n">
-        <v>9.991512801128145</v>
+        <v>9.991512801128147</v>
       </c>
       <c r="E8" t="n">
         <v>10.94725434028802</v>
@@ -5126,10 +5126,10 @@
         <v>10.94725434028802</v>
       </c>
       <c r="G8" t="n">
-        <v>10.22548817902285</v>
+        <v>10.22548817902284</v>
       </c>
       <c r="H8" t="n">
-        <v>9.519644064879623</v>
+        <v>9.519644064879625</v>
       </c>
       <c r="I8" t="n">
         <v>10.94725434028802</v>
@@ -5151,13 +5151,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.429726207307015</v>
+        <v>4.42972620730701</v>
       </c>
       <c r="C9" t="n">
         <v>4.770473380998816</v>
       </c>
       <c r="D9" t="n">
-        <v>4.28227824944958</v>
+        <v>4.282278249449578</v>
       </c>
       <c r="E9" t="n">
         <v>4.770473380998816</v>
@@ -5166,22 +5166,22 @@
         <v>4.770473380998816</v>
       </c>
       <c r="G9" t="n">
-        <v>4.375174408837591</v>
+        <v>4.375174408837592</v>
       </c>
       <c r="H9" t="n">
-        <v>4.091496484521393</v>
+        <v>4.091496484521395</v>
       </c>
       <c r="I9" t="n">
         <v>4.770473380998816</v>
       </c>
       <c r="J9" t="n">
-        <v>4.301794890622009</v>
+        <v>4.301794890622006</v>
       </c>
       <c r="K9" t="n">
-        <v>4.480558762339611</v>
+        <v>4.480558762339609</v>
       </c>
       <c r="L9" t="n">
-        <v>4.500451478596299</v>
+        <v>4.206588103203175</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.20244335289462</v>
+        <v>23.2024433528946</v>
       </c>
       <c r="C2" t="n">
-        <v>15.13407807888706</v>
+        <v>15.13407807888704</v>
       </c>
       <c r="D2" t="n">
-        <v>40.84459059909546</v>
+        <v>40.84459059909562</v>
       </c>
       <c r="E2" t="n">
-        <v>15.13407807888706</v>
+        <v>15.13407807888704</v>
       </c>
       <c r="F2" t="n">
-        <v>15.13407807888706</v>
+        <v>15.13407807888704</v>
       </c>
       <c r="G2" t="n">
-        <v>33.75944828945904</v>
+        <v>33.75944828945894</v>
       </c>
       <c r="H2" t="n">
-        <v>63.35954606993268</v>
+        <v>63.35954606993256</v>
       </c>
       <c r="I2" t="n">
-        <v>15.13407807888706</v>
+        <v>15.13407807888704</v>
       </c>
       <c r="J2" t="n">
-        <v>38.54011990817393</v>
+        <v>38.54011990817401</v>
       </c>
       <c r="K2" t="n">
-        <v>23.03303473445335</v>
+        <v>23.03303473445333</v>
       </c>
       <c r="L2" t="n">
-        <v>28.4184821097013</v>
+        <v>28.41848210970128</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6573792474045619</v>
+        <v>0.6573792474045587</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6192117795575454</v>
+        <v>0.6192117795575457</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6573792474045612</v>
+        <v>0.65737924740456</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6252618805455006</v>
+        <v>0.6252618805455005</v>
       </c>
       <c r="F3" t="n">
         <v>0.6252618805455006</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6551616209843433</v>
+        <v>0.6551616209843386</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6573792474045612</v>
+        <v>0.65737924740456</v>
       </c>
       <c r="I3" t="n">
-        <v>0.64283229929718</v>
+        <v>0.6428322992971797</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6573792474045612</v>
+        <v>0.65737924740456</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6573792474045612</v>
+        <v>0.65737924740456</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6573792474045612</v>
+        <v>0.65737924740456</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.217193676394546</v>
+        <v>0.794241838970184</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7491201927223248</v>
+        <v>0.7491201927222428</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8228944726319669</v>
+        <v>0.8228944726319712</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7368808731969074</v>
+        <v>0.7368808731969079</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7779014537167879</v>
+        <v>0.7779014537167898</v>
       </c>
       <c r="G4" t="n">
-        <v>1.214976049974325</v>
+        <v>0.7920242125499666</v>
       </c>
       <c r="H4" t="n">
-        <v>1.268992283279295</v>
+        <v>1.26899228327929</v>
       </c>
       <c r="I4" t="n">
-        <v>1.202646728287164</v>
+        <v>1.202646728287159</v>
       </c>
       <c r="J4" t="n">
-        <v>1.242992575935496</v>
+        <v>0.8187554153161067</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7905101890296953</v>
+        <v>0.7905101890296946</v>
       </c>
       <c r="L4" t="n">
-        <v>0.807386906470954</v>
+        <v>0.8073869064709507</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.163229612657936</v>
+        <v>1.163229612657925</v>
       </c>
       <c r="C5" t="n">
         <v>1.148682664550553</v>
       </c>
       <c r="D5" t="n">
-        <v>1.161332759933576</v>
+        <v>1.161332759933575</v>
       </c>
       <c r="E5" t="n">
-        <v>1.146290735706019</v>
+        <v>1.146290735706018</v>
       </c>
       <c r="F5" t="n">
-        <v>1.146290735706019</v>
+        <v>1.146290735706018</v>
       </c>
       <c r="G5" t="n">
         <v>1.161011986237717</v>
       </c>
       <c r="H5" t="n">
-        <v>1.163229612657935</v>
+        <v>1.163229612657924</v>
       </c>
       <c r="I5" t="n">
         <v>1.148682664550553</v>
       </c>
       <c r="J5" t="n">
-        <v>1.163229612657935</v>
+        <v>1.163229612657924</v>
       </c>
       <c r="K5" t="n">
-        <v>1.163229612657935</v>
+        <v>1.163229612657924</v>
       </c>
       <c r="L5" t="n">
-        <v>1.163229612657935</v>
+        <v>1.163229612657924</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.392062867297585</v>
+        <v>1.392062867297581</v>
       </c>
       <c r="C6" t="n">
-        <v>1.959167137175308</v>
+        <v>1.95916713717531</v>
       </c>
       <c r="D6" t="n">
-        <v>2.094051760910851</v>
+        <v>2.094051760910842</v>
       </c>
       <c r="E6" t="n">
-        <v>1.799606503277376</v>
+        <v>1.799606503277377</v>
       </c>
       <c r="F6" t="n">
-        <v>1.395650900024628</v>
+        <v>1.395650900024631</v>
       </c>
       <c r="G6" t="n">
-        <v>1.971271592803706</v>
+        <v>1.971271592803703</v>
       </c>
       <c r="H6" t="n">
-        <v>1.973489219224969</v>
+        <v>1.973489219224965</v>
       </c>
       <c r="I6" t="n">
-        <v>1.958942271116545</v>
+        <v>1.958942271116541</v>
       </c>
       <c r="J6" t="n">
-        <v>1.973603485825769</v>
+        <v>1.973603485825766</v>
       </c>
       <c r="K6" t="n">
-        <v>1.381262574333382</v>
+        <v>1.381262574333378</v>
       </c>
       <c r="L6" t="n">
-        <v>2.580837661582814</v>
+        <v>2.580837661582811</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.418822559760078</v>
+        <v>2.418822559760059</v>
       </c>
       <c r="C7" t="n">
         <v>2.94129888359597</v>
       </c>
       <c r="D7" t="n">
-        <v>2.955846053220847</v>
+        <v>2.95584605322084</v>
       </c>
       <c r="E7" t="n">
-        <v>3.561011480089892</v>
+        <v>3.561011480089891</v>
       </c>
       <c r="F7" t="n">
-        <v>2.941298025321455</v>
+        <v>2.941298025321453</v>
       </c>
       <c r="G7" t="n">
-        <v>2.953628205283134</v>
+        <v>2.95362820528313</v>
       </c>
       <c r="H7" t="n">
-        <v>2.955845831703356</v>
+        <v>2.955845831703349</v>
       </c>
       <c r="I7" t="n">
         <v>2.94129888359597</v>
       </c>
       <c r="J7" t="n">
-        <v>2.955845831703356</v>
+        <v>2.955845831703349</v>
       </c>
       <c r="K7" t="n">
-        <v>2.279637616599191</v>
+        <v>2.644692532055692</v>
       </c>
       <c r="L7" t="n">
-        <v>2.955845831703356</v>
+        <v>2.955845831703349</v>
       </c>
     </row>
     <row r="8">
@@ -5513,7 +5513,7 @@
         <v>10.83820242225209</v>
       </c>
       <c r="D8" t="n">
-        <v>10.02392920009892</v>
+        <v>10.02392920009891</v>
       </c>
       <c r="E8" t="n">
         <v>10.83820242225209</v>
@@ -5522,10 +5522,10 @@
         <v>10.83820242225209</v>
       </c>
       <c r="G8" t="n">
-        <v>10.2225876411482</v>
+        <v>10.22258764114819</v>
       </c>
       <c r="H8" t="n">
-        <v>9.667909392879892</v>
+        <v>9.66790939287989</v>
       </c>
       <c r="I8" t="n">
         <v>10.83820242225209</v>
@@ -5534,7 +5534,7 @@
         <v>10.15814058752589</v>
       </c>
       <c r="K8" t="n">
-        <v>10.44799765683994</v>
+        <v>10.44799765683993</v>
       </c>
       <c r="L8" t="n">
         <v>10.42040486741517</v>
@@ -5553,7 +5553,7 @@
         <v>4.718284543683713</v>
       </c>
       <c r="D9" t="n">
-        <v>4.282847452615901</v>
+        <v>4.2828474526159</v>
       </c>
       <c r="E9" t="n">
         <v>4.718284543683713</v>
@@ -5562,22 +5562,22 @@
         <v>4.718284543683713</v>
       </c>
       <c r="G9" t="n">
-        <v>4.36184510576022</v>
+        <v>4.361845105760217</v>
       </c>
       <c r="H9" t="n">
-        <v>4.139093343029381</v>
+        <v>4.139093343029382</v>
       </c>
       <c r="I9" t="n">
         <v>4.718284543683713</v>
       </c>
       <c r="J9" t="n">
-        <v>4.337820401570602</v>
+        <v>4.337820401570601</v>
       </c>
       <c r="K9" t="n">
-        <v>4.455572199810644</v>
+        <v>4.455572199810639</v>
       </c>
       <c r="L9" t="n">
-        <v>4.444765012171218</v>
+        <v>4.214830087515404</v>
       </c>
     </row>
   </sheetData>
@@ -5663,13 +5663,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.11941719582687</v>
+        <v>20.11941719582692</v>
       </c>
       <c r="C2" t="n">
         <v>22.51114605144087</v>
       </c>
       <c r="D2" t="n">
-        <v>35.28801568265648</v>
+        <v>35.2880156826565</v>
       </c>
       <c r="E2" t="n">
         <v>22.51114605144087</v>
@@ -5678,22 +5678,22 @@
         <v>22.51114605144087</v>
       </c>
       <c r="G2" t="n">
-        <v>30.75333031466776</v>
+        <v>30.75333031466786</v>
       </c>
       <c r="H2" t="n">
-        <v>52.17075500019711</v>
+        <v>52.17075500019714</v>
       </c>
       <c r="I2" t="n">
         <v>22.51114605144087</v>
       </c>
       <c r="J2" t="n">
-        <v>38.09472676323376</v>
+        <v>38.09472676323377</v>
       </c>
       <c r="K2" t="n">
-        <v>19.70665806811902</v>
+        <v>19.70665806811898</v>
       </c>
       <c r="L2" t="n">
-        <v>51.84513940007066</v>
+        <v>19.65196640284066</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6690667498525024</v>
+        <v>0.6690667498525246</v>
       </c>
       <c r="C3" t="n">
         <v>0.6342194432597663</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6690667498525024</v>
+        <v>0.6690667498525245</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6401291998031896</v>
+        <v>0.6401291998031886</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6401291998031892</v>
+        <v>0.6401291998031883</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6672454826844681</v>
+        <v>0.6672454826844698</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6690667498525024</v>
+        <v>0.6690667498525245</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6570529640197884</v>
+        <v>0.6570529640197877</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6690667498525024</v>
+        <v>0.6690667498525247</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6690667498525024</v>
+        <v>0.6690667498525245</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6690667498525024</v>
+        <v>0.6690667498525245</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8138959656281409</v>
+        <v>0.8138959656281527</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7905091492890964</v>
+        <v>0.7905091492893319</v>
       </c>
       <c r="D4" t="n">
-        <v>1.236956811112349</v>
+        <v>0.8357382805599769</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7780409976357755</v>
+        <v>0.7780409976357286</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8053317047452947</v>
+        <v>0.805331704745295</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8120746984601052</v>
+        <v>1.216750358047377</v>
       </c>
       <c r="H4" t="n">
-        <v>1.270197388682543</v>
+        <v>1.270197388682549</v>
       </c>
       <c r="I4" t="n">
-        <v>1.206557839382678</v>
+        <v>0.8018821797954262</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8397068834385706</v>
+        <v>1.24524168346307</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8073733445000966</v>
+        <v>0.8073733445000936</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8270817415942078</v>
+        <v>0.8270817415942129</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.16368086019829</v>
+        <v>1.163680860198297</v>
       </c>
       <c r="C5" t="n">
         <v>1.151667074365577</v>
       </c>
       <c r="D5" t="n">
-        <v>1.161784752601039</v>
+        <v>1.161784752601044</v>
       </c>
       <c r="E5" t="n">
-        <v>1.147508119593292</v>
+        <v>1.147508119593293</v>
       </c>
       <c r="F5" t="n">
-        <v>1.147508119593292</v>
+        <v>1.147508119593293</v>
       </c>
       <c r="G5" t="n">
-        <v>1.161859593030256</v>
+        <v>1.161859593030259</v>
       </c>
       <c r="H5" t="n">
-        <v>1.16368086019829</v>
+        <v>1.163680860198296</v>
       </c>
       <c r="I5" t="n">
         <v>1.151667074365577</v>
       </c>
       <c r="J5" t="n">
-        <v>1.16368086019829</v>
+        <v>1.163680860198296</v>
       </c>
       <c r="K5" t="n">
-        <v>1.16368086019829</v>
+        <v>1.163680860198296</v>
       </c>
       <c r="L5" t="n">
-        <v>1.16368086019829</v>
+        <v>1.163680860198296</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.376054266649028</v>
+        <v>1.376054266649038</v>
       </c>
       <c r="C6" t="n">
-        <v>1.92152573656371</v>
+        <v>1.921525736563712</v>
       </c>
       <c r="D6" t="n">
-        <v>2.050913126099278</v>
+        <v>2.050913126099273</v>
       </c>
       <c r="E6" t="n">
-        <v>1.768290966458834</v>
+        <v>1.768290966458836</v>
       </c>
       <c r="F6" t="n">
         <v>1.380408616819295</v>
       </c>
       <c r="G6" t="n">
-        <v>1.933188744056502</v>
+        <v>1.933188744056512</v>
       </c>
       <c r="H6" t="n">
-        <v>1.93501001122576</v>
+        <v>1.935010011225767</v>
       </c>
       <c r="I6" t="n">
-        <v>1.922996225391822</v>
+        <v>1.922996225391825</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9351198617666</v>
+        <v>1.935119861766618</v>
       </c>
       <c r="K6" t="n">
-        <v>1.36567137674709</v>
+        <v>1.365671376747096</v>
       </c>
       <c r="L6" t="n">
-        <v>2.518886025299865</v>
+        <v>2.518886025299878</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.30464548349809</v>
+        <v>2.304645483498104</v>
       </c>
       <c r="C7" t="n">
-        <v>2.792725589313874</v>
+        <v>2.792725589313875</v>
       </c>
       <c r="D7" t="n">
-        <v>2.804739574876593</v>
+        <v>2.804739574876595</v>
       </c>
       <c r="E7" t="n">
-        <v>3.36982264959083</v>
+        <v>3.369822649590829</v>
       </c>
       <c r="F7" t="n">
-        <v>2.79272489528679</v>
+        <v>2.792724895286794</v>
       </c>
       <c r="G7" t="n">
-        <v>2.802918107978558</v>
+        <v>2.802918107978555</v>
       </c>
       <c r="H7" t="n">
-        <v>2.804739375146589</v>
+        <v>2.804739375146585</v>
       </c>
       <c r="I7" t="n">
-        <v>2.792725589313874</v>
+        <v>2.792725589313875</v>
       </c>
       <c r="J7" t="n">
-        <v>2.804739375146589</v>
+        <v>2.804739375146585</v>
       </c>
       <c r="K7" t="n">
-        <v>2.514983094310877</v>
+        <v>2.514983094310883</v>
       </c>
       <c r="L7" t="n">
-        <v>2.804739375146589</v>
+        <v>2.804739375146585</v>
       </c>
     </row>
     <row r="8">
@@ -5918,7 +5918,7 @@
         <v>10.65008848833902</v>
       </c>
       <c r="G8" t="n">
-        <v>10.26755288259755</v>
+        <v>10.26755288259756</v>
       </c>
       <c r="H8" t="n">
         <v>9.849533062539027</v>
@@ -5933,7 +5933,7 @@
         <v>10.49496831595303</v>
       </c>
       <c r="L8" t="n">
-        <v>9.937631037275688</v>
+        <v>9.937631037275693</v>
       </c>
     </row>
     <row r="9">
@@ -5943,13 +5943,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.479292141374886</v>
+        <v>4.47929214137489</v>
       </c>
       <c r="C9" t="n">
         <v>4.649764424377675</v>
       </c>
       <c r="D9" t="n">
-        <v>4.31532687925479</v>
+        <v>4.315326879254791</v>
       </c>
       <c r="E9" t="n">
         <v>4.649764424377675</v>
@@ -5958,22 +5958,22 @@
         <v>4.649764424377675</v>
       </c>
       <c r="G9" t="n">
-        <v>4.374186435089804</v>
+        <v>4.374186435089807</v>
       </c>
       <c r="H9" t="n">
-        <v>4.205817337001272</v>
+        <v>4.205817337001276</v>
       </c>
       <c r="I9" t="n">
         <v>4.649764424377675</v>
       </c>
       <c r="J9" t="n">
-        <v>4.330769945318667</v>
+        <v>4.330769945318671</v>
       </c>
       <c r="K9" t="n">
-        <v>4.467630191730048</v>
+        <v>4.467630191730054</v>
       </c>
       <c r="L9" t="n">
-        <v>4.241427877912149</v>
+        <v>4.241427877912152</v>
       </c>
     </row>
   </sheetData>
@@ -6059,34 +6059,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.840772989421816</v>
+        <v>5.840772989421843</v>
       </c>
       <c r="C2" t="n">
-        <v>5.04660045148481</v>
+        <v>5.046600451484818</v>
       </c>
       <c r="D2" t="n">
         <v>12.84587306252798</v>
       </c>
       <c r="E2" t="n">
-        <v>5.04660045148481</v>
+        <v>5.046600451484818</v>
       </c>
       <c r="F2" t="n">
-        <v>5.04660045148481</v>
+        <v>5.046600451484818</v>
       </c>
       <c r="G2" t="n">
         <v>11.09528545459682</v>
       </c>
       <c r="H2" t="n">
-        <v>21.81023761110933</v>
+        <v>21.81023761110935</v>
       </c>
       <c r="I2" t="n">
-        <v>5.04660045148481</v>
+        <v>5.046600451484818</v>
       </c>
       <c r="J2" t="n">
         <v>38.4809027794176</v>
       </c>
       <c r="K2" t="n">
-        <v>9.56506336306747</v>
+        <v>9.565063363067464</v>
       </c>
       <c r="L2" t="n">
         <v>16.51322131487717</v>
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5505699701455258</v>
+        <v>0.5505699701455187</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5078362165176405</v>
+        <v>0.5078362165176398</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5505699701455258</v>
+        <v>0.5505699701455187</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5137673493133983</v>
+        <v>0.5137673493133972</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5137673493133981</v>
+        <v>0.5137673493133972</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5488136173355024</v>
+        <v>0.5488136173354973</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5505699701455258</v>
+        <v>0.5505699701455187</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5389609205012682</v>
+        <v>0.5389609205012681</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5505699701455258</v>
+        <v>0.5505699701455187</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5505699701455258</v>
+        <v>0.5505699701455187</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5505699701455258</v>
+        <v>0.5505699701455187</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6188369571887319</v>
+        <v>0.9080511702998605</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5905582158499124</v>
+        <v>0.5905582158499942</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9273442180718108</v>
+        <v>0.927344218071805</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5819796711865725</v>
+        <v>0.5819796711865728</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6060345394891696</v>
+        <v>0.6060345394891686</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6170806043787184</v>
+        <v>0.9062948174898376</v>
       </c>
       <c r="H4" t="n">
-        <v>0.971248403772111</v>
+        <v>0.6258561686930753</v>
       </c>
       <c r="I4" t="n">
-        <v>0.607227907544475</v>
+        <v>0.896442120655609</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9377661452466496</v>
+        <v>0.9377661452466539</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6220266725958701</v>
+        <v>0.622026672595863</v>
       </c>
       <c r="L4" t="n">
-        <v>0.624002332870361</v>
+        <v>0.6240023328703597</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9732726160237389</v>
+        <v>0.9732726160237342</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9616635663794848</v>
+        <v>0.9616635663794832</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9712424943740203</v>
+        <v>0.9712424943740109</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9552985883583999</v>
+        <v>0.9552985883583992</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9552985883583999</v>
+        <v>0.9552985883583992</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9715162632137248</v>
+        <v>0.9715162632137117</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9732726160237389</v>
+        <v>0.9732726160237342</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9616635663794848</v>
+        <v>0.9616635663794832</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9732726160237389</v>
+        <v>0.9732726160237342</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9732726160237389</v>
+        <v>0.9732726160237342</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9732726160237389</v>
+        <v>0.9732726160237342</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.112735791513825</v>
+        <v>1.112735791513818</v>
       </c>
       <c r="C6" t="n">
         <v>1.55012783190929</v>
       </c>
       <c r="D6" t="n">
-        <v>1.658983070661719</v>
+        <v>1.658983070661706</v>
       </c>
       <c r="E6" t="n">
         <v>1.426197261437144</v>
       </c>
       <c r="F6" t="n">
-        <v>1.112882200146091</v>
+        <v>1.112882200146089</v>
       </c>
       <c r="G6" t="n">
-        <v>1.563411899747856</v>
+        <v>1.563411899747855</v>
       </c>
       <c r="H6" t="n">
-        <v>1.565168252558935</v>
+        <v>1.565168252558928</v>
       </c>
       <c r="I6" t="n">
         <v>1.553559202913625</v>
       </c>
       <c r="J6" t="n">
-        <v>1.565257168318467</v>
+        <v>1.565257168318461</v>
       </c>
       <c r="K6" t="n">
-        <v>1.104331626279155</v>
+        <v>1.104331626279148</v>
       </c>
       <c r="L6" t="n">
-        <v>2.037771789750681</v>
+        <v>2.037771789750673</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.929231006803314</v>
+        <v>1.929231006803305</v>
       </c>
       <c r="C7" t="n">
-        <v>2.340350624340595</v>
+        <v>2.340350624340596</v>
       </c>
       <c r="D7" t="n">
         <v>2.351959741793527</v>
       </c>
       <c r="E7" t="n">
-        <v>2.828170089357877</v>
+        <v>2.828170089357879</v>
       </c>
       <c r="F7" t="n">
-        <v>2.340350212410812</v>
+        <v>2.340350212410813</v>
       </c>
       <c r="G7" t="n">
-        <v>2.350203321174833</v>
+        <v>2.350203321174826</v>
       </c>
       <c r="H7" t="n">
-        <v>2.351959673984854</v>
+        <v>2.351959673984848</v>
       </c>
       <c r="I7" t="n">
-        <v>2.340350624340595</v>
+        <v>2.340350624340596</v>
       </c>
       <c r="J7" t="n">
-        <v>2.351959673984854</v>
+        <v>2.351959673984848</v>
       </c>
       <c r="K7" t="n">
-        <v>2.107029052556357</v>
+        <v>2.107029052556352</v>
       </c>
       <c r="L7" t="n">
-        <v>2.351959673984854</v>
+        <v>2.351959673984848</v>
       </c>
     </row>
     <row r="8">
@@ -6314,7 +6314,7 @@
         <v>10.98631955739328</v>
       </c>
       <c r="G8" t="n">
-        <v>10.6514373692406</v>
+        <v>10.65143736924059</v>
       </c>
       <c r="H8" t="n">
         <v>10.4229815018412</v>
@@ -6323,13 +6323,13 @@
         <v>10.98631955739328</v>
       </c>
       <c r="J8" t="n">
-        <v>10.08228233604834</v>
+        <v>10.08228233604833</v>
       </c>
       <c r="K8" t="n">
-        <v>10.68343554398879</v>
+        <v>10.68343554398878</v>
       </c>
       <c r="L8" t="n">
-        <v>10.68526393155661</v>
+        <v>10.57917739026504</v>
       </c>
     </row>
     <row r="9">
@@ -6339,13 +6339,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.512045268521534</v>
+        <v>4.51204526852153</v>
       </c>
       <c r="C9" t="n">
-        <v>4.705717136346427</v>
+        <v>4.705717136346428</v>
       </c>
       <c r="D9" t="n">
-        <v>4.435991241737081</v>
+        <v>4.435991241737076</v>
       </c>
       <c r="E9" t="n">
         <v>4.705717136346428</v>
@@ -6354,22 +6354,22 @@
         <v>4.705717136346428</v>
       </c>
       <c r="G9" t="n">
-        <v>4.459399664695814</v>
+        <v>4.459399664695813</v>
       </c>
       <c r="H9" t="n">
-        <v>4.367577575086693</v>
+        <v>4.367577575086688</v>
       </c>
       <c r="I9" t="n">
         <v>4.705717136346428</v>
       </c>
       <c r="J9" t="n">
-        <v>4.228677730269721</v>
+        <v>4.228677730269719</v>
       </c>
       <c r="K9" t="n">
-        <v>4.473221224269547</v>
+        <v>4.473221224269544</v>
       </c>
       <c r="L9" t="n">
-        <v>4.430993077848425</v>
+        <v>4.430993077848419</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-8.493103291908529</v>
+        <v>-8.493103291908531</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.7609720920327767</v>
+        <v>-0.7609720920327794</v>
       </c>
       <c r="D2" t="n">
-        <v>1.837115541883604</v>
+        <v>1.837115541883596</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7609720920327767</v>
+        <v>-0.7609720920327794</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7609720920327767</v>
+        <v>-0.7609720920327794</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.519021036227976</v>
+        <v>-2.519021036227966</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.266136484533388</v>
+        <v>-0.2661364845333938</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7609720920327767</v>
+        <v>-0.7609720920327794</v>
       </c>
       <c r="J2" t="n">
-        <v>2.581654499547351</v>
+        <v>2.581654499547328</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.87536379361481</v>
+        <v>-3.875363793614806</v>
       </c>
       <c r="L2" t="n">
-        <v>3.393870198265073</v>
+        <v>3.393870198265062</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.453009007603897</v>
+        <v>0.4530090076039007</v>
       </c>
       <c r="C3" t="n">
-        <v>0.416246619690203</v>
+        <v>0.4162466196902009</v>
       </c>
       <c r="D3" t="n">
-        <v>0.453009007603897</v>
+        <v>0.4530090076039007</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4194635875936569</v>
+        <v>0.4194635875936547</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4194635875936572</v>
+        <v>0.4194635875936542</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4515482966809163</v>
+        <v>0.4515482966809091</v>
       </c>
       <c r="H3" t="n">
-        <v>0.453009007603897</v>
+        <v>0.4530090076039007</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4432611702800036</v>
+        <v>0.4432611702800035</v>
       </c>
       <c r="J3" t="n">
-        <v>0.453009007603897</v>
+        <v>0.4530090076039007</v>
       </c>
       <c r="K3" t="n">
-        <v>0.453009007603897</v>
+        <v>0.4530090076039007</v>
       </c>
       <c r="L3" t="n">
-        <v>0.453009007603897</v>
+        <v>0.4530090076039007</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6245570909415776</v>
+        <v>0.6245570909415753</v>
       </c>
       <c r="C4" t="n">
-        <v>0.436285418534633</v>
+        <v>0.4362854185346251</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4567577339388869</v>
+        <v>0.456763858836191</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4338815330347657</v>
+        <v>0.4338815330347662</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4395782481454907</v>
+        <v>0.4395782481454897</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4438056910694725</v>
+        <v>0.623096380018585</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4505394398088263</v>
+        <v>0.6688299330384098</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4355185646685679</v>
+        <v>0.614809253617681</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6494089930959782</v>
+        <v>0.4580975056552228</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4455319635749933</v>
+        <v>0.4455319635749931</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4524024268966872</v>
+        <v>0.4524024268966865</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7665646694973232</v>
+        <v>0.7665646694973242</v>
       </c>
       <c r="C5" t="n">
-        <v>0.756816832173431</v>
+        <v>0.7568168321734311</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7646741669902226</v>
+        <v>0.7646741669902285</v>
       </c>
       <c r="E5" t="n">
-        <v>0.749322273304267</v>
+        <v>0.7493222733042675</v>
       </c>
       <c r="F5" t="n">
-        <v>0.749322273304267</v>
+        <v>0.7493222733042675</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7651039585743347</v>
+        <v>0.7651039585743369</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7665646694973232</v>
+        <v>0.7665646694973242</v>
       </c>
       <c r="I5" t="n">
-        <v>0.756816832173431</v>
+        <v>0.7568168321734311</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7665646694973232</v>
+        <v>0.7665646694973242</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7665646694973232</v>
+        <v>0.7665646694973242</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7665646694973232</v>
+        <v>0.7665646694973242</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.818735155199169</v>
+        <v>0.8187351551991719</v>
       </c>
       <c r="C6" t="n">
-        <v>1.100448802371564</v>
+        <v>1.100448802371562</v>
       </c>
       <c r="D6" t="n">
-        <v>1.17633077798553</v>
+        <v>1.176330777985528</v>
       </c>
       <c r="E6" t="n">
         <v>1.019427113106113</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8150326950583258</v>
+        <v>0.8150326950583265</v>
       </c>
       <c r="G6" t="n">
-        <v>1.113455082320917</v>
+        <v>1.113455082320924</v>
       </c>
       <c r="H6" t="n">
-        <v>1.114915793243527</v>
+        <v>1.114915793243525</v>
       </c>
       <c r="I6" t="n">
-        <v>1.105167955920013</v>
+        <v>1.105167955920012</v>
       </c>
       <c r="J6" t="n">
-        <v>1.114974001339697</v>
+        <v>1.114974001339691</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8132334477713519</v>
+        <v>0.8132334477713486</v>
       </c>
       <c r="L6" t="n">
-        <v>1.424301236025322</v>
+        <v>1.42430123602532</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.302158692183274</v>
+        <v>1.302158692183273</v>
       </c>
       <c r="C7" t="n">
         <v>1.555017818236031</v>
       </c>
       <c r="D7" t="n">
-        <v>1.564765601863245</v>
+        <v>1.564765601863244</v>
       </c>
       <c r="E7" t="n">
-        <v>1.858060512586214</v>
+        <v>1.858060512586221</v>
       </c>
       <c r="F7" t="n">
-        <v>1.555017718493061</v>
+        <v>1.555017718493063</v>
       </c>
       <c r="G7" t="n">
-        <v>1.563304944636938</v>
+        <v>1.563304944636937</v>
       </c>
       <c r="H7" t="n">
-        <v>1.564765655559921</v>
+        <v>1.564765655559916</v>
       </c>
       <c r="I7" t="n">
         <v>1.555017818236031</v>
       </c>
       <c r="J7" t="n">
-        <v>1.564765655559921</v>
+        <v>1.564765655559916</v>
       </c>
       <c r="K7" t="n">
-        <v>1.406436987243747</v>
+        <v>1.412610127057747</v>
       </c>
       <c r="L7" t="n">
-        <v>1.564765655559921</v>
+        <v>1.564765655559916</v>
       </c>
     </row>
     <row r="8">
@@ -6710,7 +6710,7 @@
         <v>11.02077168575394</v>
       </c>
       <c r="G8" t="n">
-        <v>10.8715170791576</v>
+        <v>10.87151707915761</v>
       </c>
       <c r="H8" t="n">
         <v>10.8129508575339</v>
@@ -6725,7 +6725,7 @@
         <v>10.90811948541629</v>
       </c>
       <c r="L8" t="n">
-        <v>10.79052997835717</v>
+        <v>10.72051591757403</v>
       </c>
     </row>
     <row r="9">
@@ -6735,13 +6735,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.542143035545077</v>
+        <v>4.542143035545076</v>
       </c>
       <c r="C9" t="n">
         <v>4.656476390904353</v>
       </c>
       <c r="D9" t="n">
-        <v>4.434451517959964</v>
+        <v>4.434451517959965</v>
       </c>
       <c r="E9" t="n">
         <v>4.656476390904353</v>
@@ -6750,22 +6750,22 @@
         <v>4.656476390904353</v>
       </c>
       <c r="G9" t="n">
-        <v>4.482576310348652</v>
+        <v>4.482576310348654</v>
       </c>
       <c r="H9" t="n">
-        <v>4.458703758720476</v>
+        <v>4.458703758720475</v>
       </c>
       <c r="I9" t="n">
         <v>4.656476390904353</v>
       </c>
       <c r="J9" t="n">
-        <v>4.428226857060472</v>
+        <v>4.428226857060475</v>
       </c>
       <c r="K9" t="n">
         <v>4.49748048815964</v>
       </c>
       <c r="L9" t="n">
-        <v>4.449592829942294</v>
+        <v>4.421128833963014</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-16.14636523020397</v>
+        <v>-16.14636523020396</v>
       </c>
       <c r="C2" t="n">
-        <v>-2.35812344744242</v>
+        <v>-2.358123447442418</v>
       </c>
       <c r="D2" t="n">
-        <v>1.178567613349098</v>
+        <v>1.178567613349101</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.35812344744242</v>
+        <v>-2.358123447442418</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.35812344744242</v>
+        <v>-2.358123447442418</v>
       </c>
       <c r="G2" t="n">
-        <v>-5.085142344848856</v>
+        <v>-5.085142344848873</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2396533538297969</v>
+        <v>0.2396533538298173</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.35812344744242</v>
+        <v>-2.358123447442418</v>
       </c>
       <c r="J2" t="n">
-        <v>-4.991743022969862</v>
+        <v>-4.991743022969878</v>
       </c>
       <c r="K2" t="n">
-        <v>-7.835728329778264</v>
+        <v>-7.835728329778241</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8300362064258069</v>
+        <v>-1.733351953262783</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4215814049599568</v>
+        <v>0.4215814049599435</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3799046079481256</v>
+        <v>0.3799046079481255</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4215814049599568</v>
+        <v>0.4215814049599434</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3826058155296784</v>
+        <v>0.3826058155296777</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3826058155296783</v>
+        <v>0.3826058155296779</v>
       </c>
       <c r="G3" t="n">
-        <v>0.420146711480289</v>
+        <v>0.4201467114802857</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4215814049599568</v>
+        <v>0.4215814049599434</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4119933543262317</v>
+        <v>0.4119933543262311</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4215814049599568</v>
+        <v>0.4215814049599435</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4215814049599568</v>
+        <v>0.4215814049599434</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4215814049599568</v>
+        <v>0.4215814049599434</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3960482518513458</v>
+        <v>0.3960482518513515</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3889051736636526</v>
+        <v>0.3889051736635056</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4120361583567966</v>
+        <v>0.4120361583568302</v>
       </c>
       <c r="E4" t="n">
         <v>0.3883949111473899</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3911161022986567</v>
+        <v>0.391116102298656</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5517769505410188</v>
+        <v>0.3946135583716932</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5933200204706863</v>
+        <v>0.5933200204706798</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3864602012176375</v>
+        <v>0.386460201217636</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5777172568393339</v>
+        <v>0.4065033080957539</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3933297299958143</v>
+        <v>0.3933297299957994</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4049686377476877</v>
+        <v>0.4049686377476835</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7149409813818203</v>
+        <v>0.7149409813817971</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7053529307480997</v>
+        <v>0.7053529307480987</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7130516779671152</v>
+        <v>0.7130516779671046</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6960528454695621</v>
+        <v>0.6960528454695618</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6960528454695621</v>
+        <v>0.6960528454695618</v>
       </c>
       <c r="G5" t="n">
-        <v>0.713506287902153</v>
+        <v>0.7135062879021519</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7149409813818203</v>
+        <v>0.7149409813817971</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7053529307480997</v>
+        <v>0.7053529307480987</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7149409813818203</v>
+        <v>0.7149409813817971</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7149409813818203</v>
+        <v>0.7149409813817971</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7149409813818203</v>
+        <v>0.7149409813817971</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7472712023083166</v>
+        <v>0.7472712023082955</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9934428847544351</v>
+        <v>0.9934428847544372</v>
       </c>
       <c r="D6" t="n">
-        <v>1.063856799160993</v>
+        <v>1.063856799160994</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9218954481653765</v>
+        <v>0.9218954481653795</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7415740344976335</v>
+        <v>0.7415740344976337</v>
       </c>
       <c r="G6" t="n">
         <v>1.008050356239529</v>
       </c>
       <c r="H6" t="n">
-        <v>1.009485049718025</v>
+        <v>1.009485049718029</v>
       </c>
       <c r="I6" t="n">
-        <v>0.999896999085479</v>
+        <v>0.9998969990854785</v>
       </c>
       <c r="J6" t="n">
-        <v>1.009536582513097</v>
+        <v>1.009536582513096</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7424004454422592</v>
+        <v>0.7424004454422528</v>
       </c>
       <c r="L6" t="n">
-        <v>1.28338933956459</v>
+        <v>1.283389339564585</v>
       </c>
     </row>
     <row r="7">
@@ -7054,34 +7054,34 @@
         <v>1.168568656287399</v>
       </c>
       <c r="C7" t="n">
-        <v>1.389622200542008</v>
+        <v>1.389622200542005</v>
       </c>
       <c r="D7" t="n">
-        <v>1.399210115877531</v>
+        <v>1.39921011587752</v>
       </c>
       <c r="E7" t="n">
-        <v>1.655777455643221</v>
+        <v>1.655777455643219</v>
       </c>
       <c r="F7" t="n">
-        <v>1.389622094380892</v>
+        <v>1.38962209438089</v>
       </c>
       <c r="G7" t="n">
-        <v>1.39777555769607</v>
+        <v>1.397775557696061</v>
       </c>
       <c r="H7" t="n">
-        <v>1.399210251175715</v>
+        <v>1.399210251175722</v>
       </c>
       <c r="I7" t="n">
-        <v>1.389622200542008</v>
+        <v>1.389622200542005</v>
       </c>
       <c r="J7" t="n">
-        <v>1.399210251175715</v>
+        <v>1.399210251175722</v>
       </c>
       <c r="K7" t="n">
-        <v>1.260153825183481</v>
+        <v>1.260153825183462</v>
       </c>
       <c r="L7" t="n">
-        <v>1.399210251175715</v>
+        <v>1.399210251175722</v>
       </c>
     </row>
     <row r="8">
@@ -7091,13 +7091,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11.17843731941752</v>
+        <v>11.1784373194175</v>
       </c>
       <c r="C8" t="n">
         <v>11.02419380999647</v>
       </c>
       <c r="D8" t="n">
-        <v>10.7330477228609</v>
+        <v>10.73304772286091</v>
       </c>
       <c r="E8" t="n">
         <v>11.02419380999647</v>
@@ -7109,19 +7109,19 @@
         <v>10.89587323286687</v>
       </c>
       <c r="H8" t="n">
-        <v>10.75790584951493</v>
+        <v>10.75790584951492</v>
       </c>
       <c r="I8" t="n">
         <v>11.02419380999647</v>
       </c>
       <c r="J8" t="n">
-        <v>10.88458112790754</v>
+        <v>10.88458112790753</v>
       </c>
       <c r="K8" t="n">
         <v>10.98175509754009</v>
       </c>
       <c r="L8" t="n">
-        <v>10.80355172873996</v>
+        <v>10.74354619513948</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.585458166074483</v>
+        <v>4.585458166074485</v>
       </c>
       <c r="C9" t="n">
-        <v>4.636778752275629</v>
+        <v>4.636778752275627</v>
       </c>
       <c r="D9" t="n">
-        <v>4.404054314990708</v>
+        <v>4.404054314990704</v>
       </c>
       <c r="E9" t="n">
-        <v>4.636778752275629</v>
+        <v>4.636778752275627</v>
       </c>
       <c r="F9" t="n">
-        <v>4.636778752275629</v>
+        <v>4.636778752275627</v>
       </c>
       <c r="G9" t="n">
         <v>4.47044562428855</v>
       </c>
       <c r="H9" t="n">
-        <v>4.414172732951731</v>
+        <v>4.414172732951736</v>
       </c>
       <c r="I9" t="n">
-        <v>4.636778752275629</v>
+        <v>4.636778752275627</v>
       </c>
       <c r="J9" t="n">
-        <v>4.46572176269361</v>
+        <v>4.465721762693612</v>
       </c>
       <c r="K9" t="n">
-        <v>4.505338584903281</v>
+        <v>4.505338584903287</v>
       </c>
       <c r="L9" t="n">
-        <v>4.408336045832104</v>
+        <v>4.408336045832102</v>
       </c>
     </row>
   </sheetData>
@@ -7247,13 +7247,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.3732810663274</v>
+        <v>19.37328106632741</v>
       </c>
       <c r="C2" t="n">
         <v>10.84053620914785</v>
       </c>
       <c r="D2" t="n">
-        <v>42.42123609212501</v>
+        <v>42.421236092125</v>
       </c>
       <c r="E2" t="n">
         <v>10.84053620914785</v>
@@ -7262,22 +7262,22 @@
         <v>10.84053620914785</v>
       </c>
       <c r="G2" t="n">
-        <v>30.25665620235311</v>
+        <v>30.25665620235305</v>
       </c>
       <c r="H2" t="n">
-        <v>66.19441548357774</v>
+        <v>66.19441548357777</v>
       </c>
       <c r="I2" t="n">
         <v>10.84053620914785</v>
       </c>
       <c r="J2" t="n">
-        <v>40.48777115990622</v>
+        <v>40.4877711599062</v>
       </c>
       <c r="K2" t="n">
-        <v>20.48700408658036</v>
+        <v>20.48700408658032</v>
       </c>
       <c r="L2" t="n">
-        <v>56.27523781788103</v>
+        <v>19.82344641934541</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6470159839199946</v>
+        <v>0.6470159839199962</v>
       </c>
       <c r="C3" t="n">
         <v>0.6084459063002691</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6470159839199946</v>
+        <v>0.6470159839199962</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6148090900021772</v>
+        <v>0.6148090900021765</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6148090900021772</v>
+        <v>0.6148090900021748</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6447910617593249</v>
+        <v>0.6447910617593202</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6470159839199946</v>
+        <v>0.6470159839199962</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6324192092338288</v>
+        <v>0.6324192092338276</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6470159839199946</v>
+        <v>0.6470159839199962</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6470159839199946</v>
+        <v>0.6470159839199962</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6470159839199946</v>
+        <v>0.6470159839199962</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7712031010940413</v>
+        <v>0.7712031010940449</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7231059761616857</v>
+        <v>0.7231059761614467</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8107352991178522</v>
+        <v>0.810735299117866</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7109243000661222</v>
+        <v>0.7109243000661767</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7544960664927339</v>
+        <v>0.7544960664927352</v>
       </c>
       <c r="G4" t="n">
-        <v>1.197434020832629</v>
+        <v>1.19743402083263</v>
       </c>
       <c r="H4" t="n">
-        <v>1.256160679549452</v>
+        <v>1.25616067954946</v>
       </c>
       <c r="I4" t="n">
-        <v>1.185062168307131</v>
+        <v>1.185062168307132</v>
       </c>
       <c r="J4" t="n">
-        <v>1.226977875394523</v>
+        <v>1.226977875394524</v>
       </c>
       <c r="K4" t="n">
-        <v>0.767086785593738</v>
+        <v>0.7670867855937624</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7856859286769897</v>
+        <v>0.7856859286769959</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.168105819657796</v>
+        <v>1.168105819657791</v>
       </c>
       <c r="C5" t="n">
-        <v>1.153509044971629</v>
+        <v>1.153509044971628</v>
       </c>
       <c r="D5" t="n">
-        <v>1.166070109441769</v>
+        <v>1.166070109441767</v>
       </c>
       <c r="E5" t="n">
-        <v>1.151491722828253</v>
+        <v>1.15149172282825</v>
       </c>
       <c r="F5" t="n">
-        <v>1.151491722828253</v>
+        <v>1.15149172282825</v>
       </c>
       <c r="G5" t="n">
-        <v>1.165880897497125</v>
+        <v>1.165880897497126</v>
       </c>
       <c r="H5" t="n">
-        <v>1.168105819657796</v>
+        <v>1.168105819657791</v>
       </c>
       <c r="I5" t="n">
-        <v>1.153509044971629</v>
+        <v>1.153509044971628</v>
       </c>
       <c r="J5" t="n">
-        <v>1.168105819657796</v>
+        <v>1.168105819657791</v>
       </c>
       <c r="K5" t="n">
-        <v>1.168105819657796</v>
+        <v>1.168105819657791</v>
       </c>
       <c r="L5" t="n">
-        <v>1.168105819657796</v>
+        <v>1.168105819657791</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.393713811386746</v>
+        <v>1.393713811386737</v>
       </c>
       <c r="C6" t="n">
-        <v>1.974135903909214</v>
+        <v>1.974135903903104</v>
       </c>
       <c r="D6" t="n">
-        <v>2.111194392126588</v>
+        <v>2.111194392126584</v>
       </c>
       <c r="E6" t="n">
-        <v>1.81097066907385</v>
+        <v>1.810970669073845</v>
       </c>
       <c r="F6" t="n">
-        <v>1.397965049270319</v>
+        <v>1.397965049270314</v>
       </c>
       <c r="G6" t="n">
-        <v>1.985746320413794</v>
+        <v>1.985746320413793</v>
       </c>
       <c r="H6" t="n">
-        <v>1.98797124257506</v>
+        <v>1.987971242575058</v>
       </c>
       <c r="I6" t="n">
-        <v>1.973374467888298</v>
+        <v>1.973374467888288</v>
       </c>
       <c r="J6" t="n">
-        <v>1.988088030810466</v>
+        <v>1.988088030810461</v>
       </c>
       <c r="K6" t="n">
-        <v>1.382675174538976</v>
+        <v>1.382675174538974</v>
       </c>
       <c r="L6" t="n">
-        <v>2.608722820105113</v>
+        <v>2.608722820105098</v>
       </c>
     </row>
     <row r="7">
@@ -7447,34 +7447,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.539719858353157</v>
+        <v>2.539719858353155</v>
       </c>
       <c r="C7" t="n">
-        <v>3.100709494501672</v>
+        <v>3.100709494501666</v>
       </c>
       <c r="D7" t="n">
-        <v>3.115306309422201</v>
+        <v>3.115306309422195</v>
       </c>
       <c r="E7" t="n">
-        <v>3.764922779380635</v>
+        <v>3.764922779380629</v>
       </c>
       <c r="F7" t="n">
-        <v>3.100708482348066</v>
+        <v>3.100708482348062</v>
       </c>
       <c r="G7" t="n">
-        <v>3.113081347027166</v>
+        <v>3.113081347027162</v>
       </c>
       <c r="H7" t="n">
         <v>3.115306269187837</v>
       </c>
       <c r="I7" t="n">
-        <v>3.100709494501672</v>
+        <v>3.100709494501666</v>
       </c>
       <c r="J7" t="n">
         <v>3.115306269187837</v>
       </c>
       <c r="K7" t="n">
-        <v>2.781809259170402</v>
+        <v>2.781809259170401</v>
       </c>
       <c r="L7" t="n">
         <v>3.115306269187837</v>
@@ -7511,13 +7511,13 @@
         <v>10.94107356799109</v>
       </c>
       <c r="J8" t="n">
-        <v>10.14805536877186</v>
+        <v>10.14805536877187</v>
       </c>
       <c r="K8" t="n">
         <v>10.54233195661484</v>
       </c>
       <c r="L8" t="n">
-        <v>9.916532291816562</v>
+        <v>9.916532291816559</v>
       </c>
     </row>
     <row r="9">
@@ -7530,34 +7530,34 @@
         <v>4.487285508814779</v>
       </c>
       <c r="C9" t="n">
-        <v>4.741658104001674</v>
+        <v>4.741658104001672</v>
       </c>
       <c r="D9" t="n">
-        <v>4.256900228608657</v>
+        <v>4.256900228608655</v>
       </c>
       <c r="E9" t="n">
-        <v>4.741658104001674</v>
+        <v>4.741658104001672</v>
       </c>
       <c r="F9" t="n">
-        <v>4.741658104001674</v>
+        <v>4.741658104001672</v>
       </c>
       <c r="G9" t="n">
-        <v>4.385517786176866</v>
+        <v>4.385517786176867</v>
       </c>
       <c r="H9" t="n">
-        <v>4.076501966079396</v>
+        <v>4.076501966079401</v>
       </c>
       <c r="I9" t="n">
-        <v>4.741658104001674</v>
+        <v>4.741658104001672</v>
       </c>
       <c r="J9" t="n">
-        <v>4.317970274754167</v>
+        <v>4.317970274754165</v>
       </c>
       <c r="K9" t="n">
-        <v>4.47825152437458</v>
+        <v>4.478251524374579</v>
       </c>
       <c r="L9" t="n">
-        <v>4.224172946310021</v>
+        <v>4.509270471368746</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.849829020526771</v>
+        <v>-1.849829020526768</v>
       </c>
       <c r="C2" t="n">
-        <v>4.519161682816765</v>
+        <v>4.51916168281678</v>
       </c>
       <c r="D2" t="n">
-        <v>27.51775242415567</v>
+        <v>27.51775242415582</v>
       </c>
       <c r="E2" t="n">
-        <v>4.519161682816765</v>
+        <v>4.51916168281678</v>
       </c>
       <c r="F2" t="n">
-        <v>4.519161682816765</v>
+        <v>4.51916168281678</v>
       </c>
       <c r="G2" t="n">
-        <v>9.363727158020591</v>
+        <v>9.363727158020659</v>
       </c>
       <c r="H2" t="n">
-        <v>2.333976390774748</v>
+        <v>2.33397639077475</v>
       </c>
       <c r="I2" t="n">
-        <v>4.519161682816765</v>
+        <v>4.51916168281678</v>
       </c>
       <c r="J2" t="n">
         <v>16.24387449588982</v>
       </c>
       <c r="K2" t="n">
-        <v>6.509815903212299</v>
+        <v>6.509815903212308</v>
       </c>
       <c r="L2" t="n">
-        <v>3.913513656158528</v>
+        <v>31.2359880270873</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5365834264660241</v>
+        <v>0.5365834264660156</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5051201848818464</v>
+        <v>0.5051201848818467</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5365834264660241</v>
+        <v>0.5365834264660156</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5092709917577852</v>
+        <v>0.5092709917577856</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5092709917577851</v>
+        <v>0.5092709917577855</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5348619965775017</v>
+        <v>0.5348619965774993</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5365834264660241</v>
+        <v>0.5365834264660156</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5251837615778217</v>
+        <v>0.5251837615778218</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5365834264660241</v>
+        <v>0.5365834264660156</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5365834264660241</v>
+        <v>0.5365834264660156</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5365834264660241</v>
+        <v>0.5365834264660156</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8605783367675869</v>
+        <v>0.860578336767583</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5641220116150744</v>
+        <v>0.5641220116151326</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6317161913621991</v>
+        <v>0.6317223486354903</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5572402585464145</v>
+        <v>0.5572402585464131</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5759478298094873</v>
+        <v>0.5759478298094884</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5847684868681552</v>
+        <v>0.8588569068790701</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9013627012467271</v>
+        <v>0.9013627012467298</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8491786718793853</v>
+        <v>0.8491786718793829</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6027141512073004</v>
+        <v>0.6027141512073013</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5877637145287313</v>
+        <v>0.5877637145287339</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5977159082974616</v>
+        <v>0.5977159082974512</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9218286225667365</v>
+        <v>0.921828622566736</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9104289576785322</v>
+        <v>0.910428957678533</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9199346851126634</v>
+        <v>0.9199346851126612</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9064193474778598</v>
+        <v>0.906419347477859</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9064193474778598</v>
+        <v>0.906419347477859</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9201071926782134</v>
+        <v>0.9201071926782192</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9218286225667365</v>
+        <v>0.921828622566736</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9104289576785322</v>
+        <v>0.910428957678533</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9218286225667365</v>
+        <v>0.921828622566736</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9218286225667365</v>
+        <v>0.921828622566736</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9218286225667365</v>
+        <v>0.921828622566736</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.041938750688296</v>
+        <v>1.041938750688289</v>
       </c>
       <c r="C6" t="n">
-        <v>1.43512102679341</v>
+        <v>1.435121026793415</v>
       </c>
       <c r="D6" t="n">
-        <v>1.532055774929886</v>
+        <v>1.53205577492988</v>
       </c>
       <c r="E6" t="n">
-        <v>1.323722775809469</v>
+        <v>1.323722775809473</v>
       </c>
       <c r="F6" t="n">
-        <v>1.042144726995556</v>
+        <v>1.042144726995557</v>
       </c>
       <c r="G6" t="n">
-        <v>1.446159574316731</v>
+        <v>1.446159574316738</v>
       </c>
       <c r="H6" t="n">
-        <v>1.447881004206164</v>
+        <v>1.447881004206163</v>
       </c>
       <c r="I6" t="n">
-        <v>1.436481339317054</v>
+        <v>1.436481339317049</v>
       </c>
       <c r="J6" t="n">
-        <v>1.44796078337762</v>
+        <v>1.447960783377617</v>
       </c>
       <c r="K6" t="n">
         <v>1.034398164923792</v>
       </c>
       <c r="L6" t="n">
-        <v>1.871921632248564</v>
+        <v>1.871921632248573</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.714253886426551</v>
+        <v>1.71425388642655</v>
       </c>
       <c r="C7" t="n">
-        <v>2.065473902764837</v>
+        <v>2.065473902764845</v>
       </c>
       <c r="D7" t="n">
-        <v>2.07687386025487</v>
+        <v>2.076873860254869</v>
       </c>
       <c r="E7" t="n">
-        <v>2.483929446546522</v>
+        <v>2.483929446546524</v>
       </c>
       <c r="F7" t="n">
         <v>2.06547378750059</v>
       </c>
       <c r="G7" t="n">
-        <v>2.075152137764516</v>
+        <v>2.075152137764517</v>
       </c>
       <c r="H7" t="n">
-        <v>2.076873567653043</v>
+        <v>2.076873567653036</v>
       </c>
       <c r="I7" t="n">
-        <v>2.065473902764837</v>
+        <v>2.065473902764845</v>
       </c>
       <c r="J7" t="n">
-        <v>2.076873567653043</v>
+        <v>2.076873567653036</v>
       </c>
       <c r="K7" t="n">
-        <v>1.62027058576865</v>
+        <v>1.866770423300216</v>
       </c>
       <c r="L7" t="n">
-        <v>2.076873567653043</v>
+        <v>2.076873567653036</v>
       </c>
     </row>
     <row r="8">
@@ -7883,13 +7883,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.95095278085727</v>
+        <v>10.95095278085726</v>
       </c>
       <c r="C8" t="n">
         <v>10.97624451745756</v>
       </c>
       <c r="D8" t="n">
-        <v>10.15539364925889</v>
+        <v>10.15539364925888</v>
       </c>
       <c r="E8" t="n">
         <v>10.97624451745756</v>
@@ -7898,7 +7898,7 @@
         <v>10.97624451745756</v>
       </c>
       <c r="G8" t="n">
-        <v>10.66212344211596</v>
+        <v>10.66212344211597</v>
       </c>
       <c r="H8" t="n">
         <v>10.84968071290202</v>
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.573088852600696</v>
+        <v>4.573088852600695</v>
       </c>
       <c r="C9" t="n">
-        <v>4.693275280567574</v>
+        <v>4.693275280567573</v>
       </c>
       <c r="D9" t="n">
-        <v>4.249082169096856</v>
+        <v>4.249082169096853</v>
       </c>
       <c r="E9" t="n">
-        <v>4.693275280567574</v>
+        <v>4.693275280567573</v>
       </c>
       <c r="F9" t="n">
-        <v>4.693275280567574</v>
+        <v>4.693275280567573</v>
       </c>
       <c r="G9" t="n">
-        <v>4.45478862896174</v>
+        <v>4.454788628961736</v>
       </c>
       <c r="H9" t="n">
-        <v>4.531878893188454</v>
+        <v>4.53187889318845</v>
       </c>
       <c r="I9" t="n">
-        <v>4.693275280567574</v>
+        <v>4.693275280567573</v>
       </c>
       <c r="J9" t="n">
-        <v>4.399364331071543</v>
+        <v>4.399364331071542</v>
       </c>
       <c r="K9" t="n">
-        <v>4.483517739769172</v>
+        <v>4.483517739769168</v>
       </c>
       <c r="L9" t="n">
-        <v>4.277735737016112</v>
+        <v>4.27773573701611</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen climate change results.xlsx
+++ b/Results/Hydrogen/hydrogen climate change results.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,321 +511,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40.22943082527114</v>
+        <v>4.790214324539813</v>
       </c>
       <c r="C2" t="n">
-        <v>20.01211523602479</v>
+        <v>4.947409534735074</v>
       </c>
       <c r="D2" t="n">
-        <v>52.36685348707287</v>
+        <v>4.801425882833084</v>
       </c>
       <c r="E2" t="n">
-        <v>20.01211523602479</v>
+        <v>4.947409534735074</v>
       </c>
       <c r="F2" t="n">
-        <v>20.01211523602479</v>
+        <v>4.947409534735074</v>
       </c>
       <c r="G2" t="n">
-        <v>42.12306327559131</v>
+        <v>4.78652022215485</v>
       </c>
       <c r="H2" t="n">
-        <v>88.21900273035899</v>
+        <v>4.82942105399982</v>
       </c>
       <c r="I2" t="n">
-        <v>20.01211523602479</v>
+        <v>4.947409534735074</v>
       </c>
       <c r="J2" t="n">
-        <v>50.649720136146</v>
+        <v>4.797280794310403</v>
       </c>
       <c r="K2" t="n">
-        <v>33.58862766647785</v>
+        <v>4.782219079303323</v>
       </c>
       <c r="L2" t="n">
-        <v>71.29956574842173</v>
+        <v>4.773711613944083</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7381432294219827</v>
+        <v>11.0920553226316</v>
       </c>
       <c r="C3" t="n">
-        <v>0.701561400116396</v>
+        <v>11.27378809233509</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7381432294219827</v>
+        <v>11.0920553226316</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7093338263272397</v>
+        <v>11.27378809233509</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7093338263272397</v>
+        <v>11.27378809233509</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7359043517474947</v>
+        <v>11.08844516959193</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7381432294219827</v>
+        <v>11.0920553226316</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7234659359229084</v>
+        <v>11.27378809233509</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7381432294219827</v>
+        <v>11.0920553226316</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7381432294219827</v>
+        <v>11.0920553226316</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7381432294219827</v>
+        <v>11.0920553226316</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9077397083255955</v>
+        <v>40.22943082527119</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8582292416062496</v>
+        <v>20.01211523602484</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9467941802138914</v>
+        <v>52.36685348707285</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8420907556342292</v>
+        <v>20.01211523602484</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8920447771991343</v>
+        <v>20.01211523602484</v>
       </c>
       <c r="G4" t="n">
-        <v>1.43064750062835</v>
+        <v>42.12306327559126</v>
       </c>
       <c r="H4" t="n">
-        <v>1.498361259798883</v>
+        <v>88.21900273035901</v>
       </c>
       <c r="I4" t="n">
-        <v>1.418209084803763</v>
+        <v>20.01211523602484</v>
       </c>
       <c r="J4" t="n">
-        <v>1.464936316495958</v>
+        <v>50.64972013614599</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9090005927729504</v>
+        <v>33.58862766647788</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9243167086149451</v>
+        <v>71.2995657484219</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.373358444053231</v>
+        <v>0.7381432294219826</v>
       </c>
       <c r="C5" t="n">
-        <v>1.358681150554157</v>
+        <v>0.7015614001163969</v>
       </c>
       <c r="D5" t="n">
-        <v>1.371179838558332</v>
+        <v>0.7381432294219826</v>
       </c>
       <c r="E5" t="n">
-        <v>1.35772134888349</v>
+        <v>0.7093338263272398</v>
       </c>
       <c r="F5" t="n">
-        <v>1.35772134888349</v>
+        <v>0.7093338263272397</v>
       </c>
       <c r="G5" t="n">
-        <v>1.371119566378743</v>
+        <v>0.7359043517474949</v>
       </c>
       <c r="H5" t="n">
-        <v>1.373358444053231</v>
+        <v>0.7381432294219826</v>
       </c>
       <c r="I5" t="n">
-        <v>1.358681150554157</v>
+        <v>0.7234659359229081</v>
       </c>
       <c r="J5" t="n">
-        <v>1.373358444053231</v>
+        <v>0.7381432294219826</v>
       </c>
       <c r="K5" t="n">
-        <v>1.373358444053231</v>
+        <v>0.7381432294219826</v>
       </c>
       <c r="L5" t="n">
-        <v>1.373358444053231</v>
+        <v>0.7381432294219826</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.677001272327966</v>
+        <v>0.9077397083255963</v>
       </c>
       <c r="C6" t="n">
-        <v>2.408650453827182</v>
+        <v>0.8582292416063565</v>
       </c>
       <c r="D6" t="n">
-        <v>2.575688990408209</v>
+        <v>0.9467941802138921</v>
       </c>
       <c r="E6" t="n">
-        <v>2.204268826132757</v>
+        <v>0.84209075563421</v>
       </c>
       <c r="F6" t="n">
-        <v>1.686645587692818</v>
+        <v>0.8920447771991353</v>
       </c>
       <c r="G6" t="n">
-        <v>2.419105682990749</v>
+        <v>1.43064750062835</v>
       </c>
       <c r="H6" t="n">
-        <v>2.421344560665477</v>
+        <v>1.498361259798884</v>
       </c>
       <c r="I6" t="n">
-        <v>2.406667267166164</v>
+        <v>1.418209084803763</v>
       </c>
       <c r="J6" t="n">
-        <v>2.421490844892905</v>
+        <v>1.46493631649596</v>
       </c>
       <c r="K6" t="n">
-        <v>1.663174713646583</v>
+        <v>0.909000592772952</v>
       </c>
       <c r="L6" t="n">
-        <v>3.198873365792076</v>
+        <v>0.9243167086149447</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.283321765233496</v>
+        <v>1.373358444053232</v>
       </c>
       <c r="C7" t="n">
-        <v>4.036858495136689</v>
+        <v>1.358681150554157</v>
       </c>
       <c r="D7" t="n">
-        <v>4.051535916417151</v>
+        <v>1.371179838558331</v>
       </c>
       <c r="E7" t="n">
-        <v>4.923359807591754</v>
+        <v>1.35772134888349</v>
       </c>
       <c r="F7" t="n">
-        <v>4.036857297301153</v>
+        <v>1.35772134888349</v>
       </c>
       <c r="G7" t="n">
-        <v>4.049296910961277</v>
+        <v>1.371119566378744</v>
       </c>
       <c r="H7" t="n">
-        <v>4.051535788635762</v>
+        <v>1.373358444053232</v>
       </c>
       <c r="I7" t="n">
-        <v>4.036858495136689</v>
+        <v>1.358681150554157</v>
       </c>
       <c r="J7" t="n">
-        <v>4.051535788635762</v>
+        <v>1.373358444053232</v>
       </c>
       <c r="K7" t="n">
-        <v>3.08421717433596</v>
+        <v>1.373358444053232</v>
       </c>
       <c r="L7" t="n">
-        <v>4.051535788635762</v>
+        <v>1.373358444053232</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.21921019805805</v>
+        <v>1.677001272327966</v>
       </c>
       <c r="C8" t="n">
-        <v>10.85258812779364</v>
+        <v>2.408650453827184</v>
       </c>
       <c r="D8" t="n">
-        <v>9.984830458942815</v>
+        <v>2.575688990408212</v>
       </c>
       <c r="E8" t="n">
-        <v>10.85258812779364</v>
+        <v>2.204268826132758</v>
       </c>
       <c r="F8" t="n">
-        <v>10.85258812779364</v>
+        <v>1.686645587692817</v>
       </c>
       <c r="G8" t="n">
-        <v>10.22165460521644</v>
+        <v>2.419105682990751</v>
       </c>
       <c r="H8" t="n">
-        <v>9.429883858664754</v>
+        <v>2.421344560665478</v>
       </c>
       <c r="I8" t="n">
-        <v>10.85258812779364</v>
+        <v>2.406667267166164</v>
       </c>
       <c r="J8" t="n">
-        <v>10.0792027200084</v>
+        <v>2.421490844892905</v>
       </c>
       <c r="K8" t="n">
-        <v>10.38757417387575</v>
+        <v>1.663174713646582</v>
       </c>
       <c r="L8" t="n">
-        <v>10.57324074301768</v>
+        <v>3.198873365792079</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.283321765233497</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.036858495136691</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.05153591641715</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.923359807591754</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.036857297301153</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.049296910961278</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.051535788635766</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.036858495136691</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.051535788635766</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.084217174335962</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.051535788635766</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10.21921019805805</v>
+      </c>
+      <c r="C10" t="n">
+        <v>10.85258812779364</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.98483045894282</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.85258812779364</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10.85258812779364</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.22165460521644</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.429883858664756</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.85258812779364</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10.0792027200084</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10.38757417387575</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10.57324074301768</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>4.39306701126648</v>
       </c>
-      <c r="C9" t="n">
-        <v>4.755762208584072</v>
-      </c>
-      <c r="D9" t="n">
-        <v>4.297635041338405</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.755762208584072</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.755762208584072</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.392127753066371</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4.073127740868741</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.755762208584072</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.336429632347114</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.461677911571195</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4.221521365591612</v>
+      <c r="C11" t="n">
+        <v>4.755762208584073</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.297635041338406</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.755762208584073</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.755762208584073</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.392127753066373</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.073127740868743</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.755762208584073</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.336429632347117</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.461677911571197</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.221521365591614</v>
       </c>
     </row>
   </sheetData>
@@ -839,7 +919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,321 +987,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.961837332150841</v>
+        <v>4.479405803673794</v>
       </c>
       <c r="C2" t="n">
-        <v>1.014153330034911</v>
+        <v>4.674808799634833</v>
       </c>
       <c r="D2" t="n">
-        <v>1.204256942798038</v>
+        <v>4.483302652116876</v>
       </c>
       <c r="E2" t="n">
-        <v>1.014153330034911</v>
+        <v>4.674808799634833</v>
       </c>
       <c r="F2" t="n">
-        <v>1.014153330034911</v>
+        <v>4.674808799634833</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.798178327686525</v>
+        <v>4.479827676949503</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.714023194227136</v>
+        <v>4.479902784536004</v>
       </c>
       <c r="I2" t="n">
-        <v>1.014153330034911</v>
+        <v>4.674808799634833</v>
       </c>
       <c r="J2" t="n">
-        <v>6.715696749679104</v>
+        <v>4.489489839354298</v>
       </c>
       <c r="K2" t="n">
-        <v>4.720142873404031</v>
+        <v>4.487989028734701</v>
       </c>
       <c r="L2" t="n">
-        <v>2.243526176321566</v>
+        <v>4.483678073612626</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.478708246851496</v>
+        <v>10.82305899390412</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4474674213607939</v>
+        <v>11.0178465175975</v>
       </c>
       <c r="D3" t="n">
-        <v>0.478708246851496</v>
+        <v>10.82305899390412</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4507919998532331</v>
+        <v>11.0178465175975</v>
       </c>
       <c r="F3" t="n">
-        <v>0.450791999853233</v>
+        <v>11.0178465175975</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4772874095841996</v>
+        <v>10.82328321788793</v>
       </c>
       <c r="H3" t="n">
-        <v>0.478708246851496</v>
+        <v>10.82305899390412</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4692179720486322</v>
+        <v>11.0178465175975</v>
       </c>
       <c r="J3" t="n">
-        <v>0.478708246851496</v>
+        <v>10.82305899390412</v>
       </c>
       <c r="K3" t="n">
-        <v>0.478708246851496</v>
+        <v>10.82305899390412</v>
       </c>
       <c r="L3" t="n">
-        <v>0.478708246851496</v>
+        <v>10.82305899390412</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4907450384363412</v>
+        <v>-1.961837332150825</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4787871816139402</v>
+        <v>1.014153330034935</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6997852588784206</v>
+        <v>1.20425694279803</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4747047902194778</v>
+        <v>1.014153330034935</v>
       </c>
       <c r="F4" t="n">
-        <v>0.481302940508905</v>
+        <v>1.014153330034935</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6843427406879004</v>
+        <v>-1.798178327686519</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7267362590427932</v>
+        <v>-1.714023194227134</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4812547636334772</v>
+        <v>1.014153330034935</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5007881116659199</v>
+        <v>6.715696749679196</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5032141755973843</v>
+        <v>4.720142873404024</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4930981269636974</v>
+        <v>2.243526176321586</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.808912763933911</v>
+        <v>0.4787082468515008</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7994224891310563</v>
+        <v>0.4474674213607946</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8070206707477966</v>
+        <v>0.4787082468515008</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7933090961223668</v>
+        <v>0.4507919998532307</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7933090961223659</v>
+        <v>0.4507919998532307</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8074919266666076</v>
+        <v>0.477287409584191</v>
       </c>
       <c r="H5" t="n">
-        <v>0.808912763933911</v>
+        <v>0.4787082468515008</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7994224891310563</v>
+        <v>0.4692179720486336</v>
       </c>
       <c r="J5" t="n">
-        <v>0.808912763933911</v>
+        <v>0.4787082468515008</v>
       </c>
       <c r="K5" t="n">
-        <v>0.808912763933911</v>
+        <v>0.4787082468515008</v>
       </c>
       <c r="L5" t="n">
-        <v>0.808912763933911</v>
+        <v>0.4787082468515008</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8768849321154825</v>
+        <v>0.4907450384363495</v>
       </c>
       <c r="C6" t="n">
-        <v>1.186980034013473</v>
+        <v>0.4787871816138417</v>
       </c>
       <c r="D6" t="n">
-        <v>1.266832487658325</v>
+        <v>0.6997852588784189</v>
       </c>
       <c r="E6" t="n">
-        <v>1.098488411534096</v>
+        <v>0.4747047902195395</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8751142974678943</v>
+        <v>0.4813029405089064</v>
       </c>
       <c r="G6" t="n">
-        <v>1.198440407887656</v>
+        <v>0.6843427406879136</v>
       </c>
       <c r="H6" t="n">
-        <v>1.199861245156229</v>
+        <v>0.7267362590428001</v>
       </c>
       <c r="I6" t="n">
-        <v>1.190370970352092</v>
+        <v>0.4812547636334771</v>
       </c>
       <c r="J6" t="n">
-        <v>1.19992471927459</v>
+        <v>0.500788111665841</v>
       </c>
       <c r="K6" t="n">
-        <v>0.870885481277292</v>
+        <v>0.5032141755973859</v>
       </c>
       <c r="L6" t="n">
-        <v>1.537237010995682</v>
+        <v>0.493098126963706</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.33368991176063</v>
+        <v>0.8089127639339233</v>
       </c>
       <c r="C7" t="n">
-        <v>1.591107975906057</v>
+        <v>0.799422489131053</v>
       </c>
       <c r="D7" t="n">
-        <v>1.600598237124631</v>
+        <v>0.8070206707478029</v>
       </c>
       <c r="E7" t="n">
-        <v>1.899114437453352</v>
+        <v>0.7933090961223658</v>
       </c>
       <c r="F7" t="n">
-        <v>1.591107903947542</v>
+        <v>0.7933090961223658</v>
       </c>
       <c r="G7" t="n">
-        <v>1.599177413441613</v>
+        <v>0.8074919266666081</v>
       </c>
       <c r="H7" t="n">
-        <v>1.60059825070892</v>
+        <v>0.8089127639339233</v>
       </c>
       <c r="I7" t="n">
-        <v>1.591107975906057</v>
+        <v>0.799422489131053</v>
       </c>
       <c r="J7" t="n">
-        <v>1.60059825070892</v>
+        <v>0.8089127639339233</v>
       </c>
       <c r="K7" t="n">
-        <v>1.445950505178847</v>
+        <v>0.8089127639339233</v>
       </c>
       <c r="L7" t="n">
-        <v>1.60059825070892</v>
+        <v>0.8089127639339233</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.88752795114852</v>
+        <v>0.8768849321154691</v>
       </c>
       <c r="C8" t="n">
-        <v>11.0056409918541</v>
+        <v>1.18698003401348</v>
       </c>
       <c r="D8" t="n">
-        <v>10.80585940566277</v>
+        <v>1.266832487658344</v>
       </c>
       <c r="E8" t="n">
-        <v>11.0056409918541</v>
+        <v>1.098488411534106</v>
       </c>
       <c r="F8" t="n">
-        <v>11.0056409918541</v>
+        <v>0.8751142974679172</v>
       </c>
       <c r="G8" t="n">
-        <v>10.88331703981609</v>
+        <v>1.19844040788767</v>
       </c>
       <c r="H8" t="n">
-        <v>10.87609139141626</v>
+        <v>1.199861245156237</v>
       </c>
       <c r="I8" t="n">
-        <v>11.0056409918541</v>
+        <v>1.190370970352111</v>
       </c>
       <c r="J8" t="n">
-        <v>10.67733635943306</v>
+        <v>1.199924719274585</v>
       </c>
       <c r="K8" t="n">
-        <v>10.707750885116</v>
+        <v>0.8708854812772983</v>
       </c>
       <c r="L8" t="n">
-        <v>10.78594077318136</v>
+        <v>1.53723701099572</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.333689911760632</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.59110797590606</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.600598237124638</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.899114437453355</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.591107903947546</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.599177413441615</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.600598250708929</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.59110797590606</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.600598250708929</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.445950505178849</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.600598250708929</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10.88752795114851</v>
+      </c>
+      <c r="C10" t="n">
+        <v>11.00564099185411</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10.80585940566278</v>
+      </c>
+      <c r="E10" t="n">
+        <v>11.00564099185411</v>
+      </c>
+      <c r="F10" t="n">
+        <v>11.00564099185411</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.88331703981609</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10.87609139141626</v>
+      </c>
+      <c r="I10" t="n">
+        <v>11.00564099185411</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10.67733635943306</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10.70775088511602</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10.78594077318139</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>4.508739384670354</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4.669255246524879</v>
-      </c>
-      <c r="D9" t="n">
-        <v>4.475476784655211</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.669255246524879</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.669255246524879</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.507143257243242</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4.504032694408252</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.669255246524879</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.42318557627949</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.435523471770959</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4.46739225700548</v>
+      <c r="B11" t="n">
+        <v>4.508739384670366</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.669255246524885</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.475476784655234</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.669255246524885</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.669255246524885</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.507143257243251</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.504032694408255</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.669255246524885</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.423185576279483</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.435523471770977</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.467392257005471</v>
       </c>
     </row>
   </sheetData>
@@ -1235,7 +1395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,320 +1463,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.16862161484196</v>
+        <v>3.480095951564768</v>
       </c>
       <c r="C2" t="n">
-        <v>14.85015747556376</v>
+        <v>3.542608160261536</v>
       </c>
       <c r="D2" t="n">
-        <v>28.68145304389607</v>
+        <v>5.802547021235982</v>
       </c>
       <c r="E2" t="n">
-        <v>12.07683485092544</v>
+        <v>4.41521732723857</v>
       </c>
       <c r="F2" t="n">
-        <v>12.07683485092544</v>
+        <v>4.41521732723857</v>
       </c>
       <c r="G2" t="n">
-        <v>23.08017417920554</v>
+        <v>4.584583402101806</v>
       </c>
       <c r="H2" t="n">
-        <v>40.53026496011674</v>
+        <v>5.811144908343705</v>
       </c>
       <c r="I2" t="n">
-        <v>12.07683485092544</v>
+        <v>4.41521732723857</v>
       </c>
       <c r="J2" t="n">
-        <v>34.86459160164415</v>
+        <v>5.635855698340571</v>
       </c>
       <c r="K2" t="n">
-        <v>18.09455420485601</v>
+        <v>5.062625090382656</v>
       </c>
       <c r="L2" t="n">
-        <v>21.50378474938266</v>
+        <v>5.991933039935107</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6830200871918481</v>
+        <v>9.792392824553591</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6614875667884762</v>
+        <v>9.851781296158245</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6830200871918478</v>
+        <v>12.13177663590542</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6555791087662948</v>
+        <v>10.74119564204446</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6555791087662948</v>
+        <v>10.74119564204446</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6807164932130871</v>
+        <v>10.90138728918285</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6830200871918481</v>
+        <v>12.13177663590542</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6678332525278006</v>
+        <v>10.74119564204446</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6830200871918481</v>
+        <v>11.95716671319627</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6830200871918478</v>
+        <v>11.39202309226323</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6830200871918478</v>
+        <v>12.3350773065791</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.191800101628733</v>
+        <v>11.16862161484197</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7762131020077797</v>
+        <v>14.85015747556372</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8140210402762333</v>
+        <v>28.68145304389607</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7444636667260004</v>
+        <v>12.07683485092543</v>
       </c>
       <c r="F4" t="n">
-        <v>0.777399299254217</v>
+        <v>12.07683485092543</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7916578187243698</v>
+        <v>23.08017417920557</v>
       </c>
       <c r="H4" t="n">
-        <v>1.271418163201663</v>
+        <v>40.53026496011676</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7787745780390852</v>
+        <v>12.07683485092543</v>
       </c>
       <c r="J4" t="n">
-        <v>1.225826774445845</v>
+        <v>34.86459160164413</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7934005481391887</v>
+        <v>18.09455420485602</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7967268685299087</v>
+        <v>21.50378474938266</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.206975213139003</v>
+        <v>0.6830200871918479</v>
       </c>
       <c r="C5" t="n">
-        <v>1.20605654761994</v>
+        <v>0.661487566788478</v>
       </c>
       <c r="D5" t="n">
-        <v>1.204973798836384</v>
+        <v>0.6830200871918479</v>
       </c>
       <c r="E5" t="n">
-        <v>1.190421352885985</v>
+        <v>0.6555791087662934</v>
       </c>
       <c r="F5" t="n">
-        <v>1.190421352885985</v>
+        <v>0.655579108766294</v>
       </c>
       <c r="G5" t="n">
-        <v>1.204671619160239</v>
+        <v>0.6807164932130849</v>
       </c>
       <c r="H5" t="n">
-        <v>1.206975213139003</v>
+        <v>0.6830200871918479</v>
       </c>
       <c r="I5" t="n">
-        <v>1.191788378474956</v>
+        <v>0.6678332525277999</v>
       </c>
       <c r="J5" t="n">
-        <v>1.206975213139003</v>
+        <v>0.6830200871918479</v>
       </c>
       <c r="K5" t="n">
-        <v>1.206975213139003</v>
+        <v>0.6830200871918479</v>
       </c>
       <c r="L5" t="n">
-        <v>1.206975213139003</v>
+        <v>0.6830200871918479</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.443556703736949</v>
+        <v>1.191800101628736</v>
       </c>
       <c r="C6" t="n">
-        <v>2.056641243560789</v>
+        <v>0.776213102007698</v>
       </c>
       <c r="D6" t="n">
-        <v>2.183253570203956</v>
+        <v>0.8140210402762339</v>
       </c>
       <c r="E6" t="n">
-        <v>1.874121603262557</v>
+        <v>0.7444636667259994</v>
       </c>
       <c r="F6" t="n">
-        <v>1.448168631925006</v>
+        <v>0.7773992992542182</v>
       </c>
       <c r="G6" t="n">
-        <v>2.053911307798265</v>
+        <v>0.7916578187243704</v>
       </c>
       <c r="H6" t="n">
-        <v>2.056214901779587</v>
+        <v>1.271418163201666</v>
       </c>
       <c r="I6" t="n">
-        <v>2.04102806711298</v>
+        <v>0.7787745780390861</v>
       </c>
       <c r="J6" t="n">
-        <v>2.056335306114174</v>
+        <v>1.225826774445844</v>
       </c>
       <c r="K6" t="n">
-        <v>1.432176263214864</v>
+        <v>0.7934005481391863</v>
       </c>
       <c r="L6" t="n">
-        <v>2.696187618769443</v>
+        <v>0.7967268685299104</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.368282665040454</v>
+        <v>1.206975213139004</v>
       </c>
       <c r="C7" t="n">
-        <v>2.88976311615604</v>
+        <v>1.20605654761994</v>
       </c>
       <c r="D7" t="n">
-        <v>2.890681984252481</v>
+        <v>1.204973798836385</v>
       </c>
       <c r="E7" t="n">
-        <v>3.478331898791552</v>
+        <v>1.190421352885984</v>
       </c>
       <c r="F7" t="n">
-        <v>2.875494358778191</v>
+        <v>1.190421352885984</v>
       </c>
       <c r="G7" t="n">
-        <v>2.88837818769634</v>
+        <v>1.204671619160239</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8906817816751</v>
+        <v>1.206975213139004</v>
       </c>
       <c r="I7" t="n">
-        <v>2.87549494701105</v>
+        <v>1.191788378474955</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8906817816751</v>
+        <v>1.206975213139004</v>
       </c>
       <c r="K7" t="n">
-        <v>2.588001767080614</v>
+        <v>1.206975213139004</v>
       </c>
       <c r="L7" t="n">
-        <v>2.8906817816751</v>
+        <v>1.206975213139004</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.557912949204468</v>
+        <v>1.443556703736949</v>
       </c>
       <c r="C8" t="n">
-        <v>9.53288046420797</v>
+        <v>2.056641243560791</v>
       </c>
       <c r="D8" t="n">
-        <v>11.48416085874909</v>
+        <v>2.183253570203952</v>
       </c>
       <c r="E8" t="n">
-        <v>10.47968966896887</v>
+        <v>1.874121603262555</v>
       </c>
       <c r="F8" t="n">
-        <v>10.47968966896887</v>
+        <v>1.448168631925003</v>
       </c>
       <c r="G8" t="n">
-        <v>10.39850986057385</v>
+        <v>2.053911307798264</v>
       </c>
       <c r="H8" t="n">
-        <v>11.31949227162202</v>
+        <v>2.056214901779585</v>
       </c>
       <c r="I8" t="n">
-        <v>10.47968966896888</v>
+        <v>2.04102806711298</v>
       </c>
       <c r="J8" t="n">
-        <v>11.20683121478856</v>
+        <v>2.056335306114173</v>
       </c>
       <c r="K8" t="n">
-        <v>10.99078130923746</v>
+        <v>1.432176263214865</v>
       </c>
       <c r="L8" t="n">
-        <v>11.91904421694413</v>
+        <v>2.69618761876944</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.368282665040457</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.889763116156041</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.890681984252477</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.478331898791557</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.875494358778196</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.888378187696342</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.890681781675101</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.875494947011052</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.890681781675101</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.588001767080613</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.890681781675101</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.557912949204468</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.53288046420797</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11.48416085874909</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.47968966896888</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10.47968966896888</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.39850986057385</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11.31949227162202</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.47968966896888</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11.20683121478856</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10.99078130923746</v>
+      </c>
+      <c r="L10" t="n">
+        <v>11.91904421694413</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>3.373406861037893</v>
       </c>
-      <c r="C9" t="n">
-        <v>3.397507265447509</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="C11" t="n">
+        <v>3.39750726544751</v>
+      </c>
+      <c r="D11" t="n">
         <v>5.507879778800826</v>
       </c>
-      <c r="E9" t="n">
-        <v>4.296231276119088</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.296231276119088</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="E11" t="n">
+        <v>4.296231276119089</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.296231276119089</v>
+      </c>
+      <c r="G11" t="n">
         <v>4.355772569509432</v>
       </c>
-      <c r="H9" t="n">
-        <v>5.441552933998083</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.296231276119088</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.294450655387707</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.880058800424239</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="H11" t="n">
+        <v>5.441552933998084</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.296231276119089</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.294450655387708</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.880058800424236</v>
+      </c>
+      <c r="L11" t="n">
         <v>5.802636658332405</v>
       </c>
     </row>
@@ -1631,7 +1871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1699,321 +1939,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.725402184150425</v>
+        <v>3.44596807410923</v>
       </c>
       <c r="C2" t="n">
-        <v>10.1195697225483</v>
+        <v>3.51308010410027</v>
       </c>
       <c r="D2" t="n">
-        <v>19.15427538737585</v>
+        <v>5.747108723677069</v>
       </c>
       <c r="E2" t="n">
-        <v>6.543925335290134</v>
+        <v>4.378130470187606</v>
       </c>
       <c r="F2" t="n">
-        <v>6.543925335290134</v>
+        <v>4.378130470187606</v>
       </c>
       <c r="G2" t="n">
-        <v>14.54621765440993</v>
+        <v>4.548586319586853</v>
       </c>
       <c r="H2" t="n">
-        <v>21.22749112229007</v>
+        <v>5.747075005330816</v>
       </c>
       <c r="I2" t="n">
-        <v>6.543925335290134</v>
+        <v>4.378130470187606</v>
       </c>
       <c r="J2" t="n">
-        <v>25.64129144854706</v>
+        <v>5.593147593909602</v>
       </c>
       <c r="K2" t="n">
-        <v>8.463300067447703</v>
+        <v>5.009245934381565</v>
       </c>
       <c r="L2" t="n">
-        <v>11.01056531930909</v>
+        <v>5.953239821243343</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6331176455458644</v>
+        <v>9.76352211008499</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6077803457366662</v>
+        <v>9.826551053997054</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6331176455458644</v>
+        <v>12.08514424451381</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6052265850847038</v>
+        <v>10.7094496390746</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6052265850847039</v>
+        <v>10.7094496390746</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6308924173826567</v>
+        <v>10.87345725014517</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6331176455458644</v>
+        <v>12.08514424451381</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6184267365316617</v>
+        <v>10.7094496390746</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6331176455458644</v>
+        <v>11.92234426843684</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6331176455458644</v>
+        <v>11.34823042488176</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6331176455458644</v>
+        <v>12.30570304225841</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.057275620535306</v>
+        <v>5.725402184150427</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7083248187480203</v>
+        <v>10.11956972254831</v>
       </c>
       <c r="D4" t="n">
-        <v>1.083877475540696</v>
+        <v>19.1542753873759</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6771147583209455</v>
+        <v>6.543925335290126</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7048225481486767</v>
+        <v>6.543925335290126</v>
       </c>
       <c r="G4" t="n">
-        <v>1.055050392372099</v>
+        <v>14.54621765440991</v>
       </c>
       <c r="H4" t="n">
-        <v>1.134813964890856</v>
+        <v>21.22749112229005</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7059974104516967</v>
+        <v>6.543925335290126</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7414438773717461</v>
+        <v>25.64129144854701</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7166607160868165</v>
+        <v>8.463300067447715</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7219188356574195</v>
+        <v>11.01056531930911</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.086833830168331</v>
+        <v>0.633117645545859</v>
       </c>
       <c r="C5" t="n">
-        <v>1.086079765407646</v>
+        <v>0.6077803457366663</v>
       </c>
       <c r="D5" t="n">
-        <v>1.084940288099576</v>
+        <v>0.633117645545859</v>
       </c>
       <c r="E5" t="n">
-        <v>1.070080932490938</v>
+        <v>0.6052265850847035</v>
       </c>
       <c r="F5" t="n">
-        <v>1.070080932490938</v>
+        <v>0.6052265850847032</v>
       </c>
       <c r="G5" t="n">
-        <v>1.084608602005123</v>
+        <v>0.6308924173826558</v>
       </c>
       <c r="H5" t="n">
-        <v>1.086833830168331</v>
+        <v>0.633117645545859</v>
       </c>
       <c r="I5" t="n">
-        <v>1.072142921154129</v>
+        <v>0.6184267365316619</v>
       </c>
       <c r="J5" t="n">
-        <v>1.086833830168331</v>
+        <v>0.633117645545859</v>
       </c>
       <c r="K5" t="n">
-        <v>1.086833830168331</v>
+        <v>0.633117645545859</v>
       </c>
       <c r="L5" t="n">
-        <v>1.086833830168331</v>
+        <v>0.633117645545859</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.283090888019875</v>
+        <v>1.057275620535306</v>
       </c>
       <c r="C6" t="n">
-        <v>1.811905592670751</v>
+        <v>0.708324818748308</v>
       </c>
       <c r="D6" t="n">
-        <v>1.921832974455328</v>
+        <v>1.083877475540693</v>
       </c>
       <c r="E6" t="n">
-        <v>1.652702707516629</v>
+        <v>0.6771147583209473</v>
       </c>
       <c r="F6" t="n">
-        <v>1.285069301539161</v>
+        <v>0.704822548148678</v>
       </c>
       <c r="G6" t="n">
-        <v>1.809907478785838</v>
+        <v>1.055050392372097</v>
       </c>
       <c r="H6" t="n">
-        <v>1.812132706952929</v>
+        <v>1.13481396489085</v>
       </c>
       <c r="I6" t="n">
-        <v>1.797441797934844</v>
+        <v>0.7059974104516972</v>
       </c>
       <c r="J6" t="n">
-        <v>1.812236678245661</v>
+        <v>0.7414438773717503</v>
       </c>
       <c r="K6" t="n">
-        <v>1.273263664672115</v>
+        <v>0.7166607160868202</v>
       </c>
       <c r="L6" t="n">
-        <v>2.364761124043985</v>
+        <v>0.7219188356574204</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.92642753545165</v>
+        <v>1.086833830168332</v>
       </c>
       <c r="C7" t="n">
-        <v>2.333858612668688</v>
+        <v>1.086079765407647</v>
       </c>
       <c r="D7" t="n">
-        <v>2.334612884919651</v>
+        <v>1.084940288099576</v>
       </c>
       <c r="E7" t="n">
-        <v>2.790958497264108</v>
+        <v>1.070080932490939</v>
       </c>
       <c r="F7" t="n">
-        <v>2.319921402305457</v>
+        <v>1.070080932490939</v>
       </c>
       <c r="G7" t="n">
-        <v>2.332387449266168</v>
+        <v>1.084608602005121</v>
       </c>
       <c r="H7" t="n">
-        <v>2.334612677429378</v>
+        <v>1.086833830168332</v>
       </c>
       <c r="I7" t="n">
-        <v>2.319921768415172</v>
+        <v>1.072142921154129</v>
       </c>
       <c r="J7" t="n">
-        <v>2.334612677429378</v>
+        <v>1.086833830168332</v>
       </c>
       <c r="K7" t="n">
-        <v>2.09810869037034</v>
+        <v>1.086833830168332</v>
       </c>
       <c r="L7" t="n">
-        <v>2.334612677429378</v>
+        <v>1.086833830168332</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.643507869509243</v>
+        <v>1.28309088801987</v>
       </c>
       <c r="C8" t="n">
-        <v>9.600979300699038</v>
+        <v>1.811905592670745</v>
       </c>
       <c r="D8" t="n">
-        <v>11.63267890141216</v>
+        <v>1.921832974455324</v>
       </c>
       <c r="E8" t="n">
-        <v>10.56581570387053</v>
+        <v>1.65270270751663</v>
       </c>
       <c r="F8" t="n">
-        <v>10.56581570387053</v>
+        <v>1.28506930153916</v>
       </c>
       <c r="G8" t="n">
-        <v>10.54347538417608</v>
+        <v>1.809907478785835</v>
       </c>
       <c r="H8" t="n">
-        <v>11.64182701432832</v>
+        <v>1.812132706952923</v>
       </c>
       <c r="I8" t="n">
-        <v>10.56581570387053</v>
+        <v>1.797441797934844</v>
       </c>
       <c r="J8" t="n">
-        <v>11.34266555168731</v>
+        <v>1.812236678245666</v>
       </c>
       <c r="K8" t="n">
-        <v>11.15743443581558</v>
+        <v>1.273263664672118</v>
       </c>
       <c r="L8" t="n">
-        <v>12.08671982455648</v>
+        <v>2.364761124043979</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.926427535451646</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.333858612668686</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.334612884919648</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.790958497264105</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.319921402305456</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.332387449266162</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.334612677429374</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.319921768415171</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.334612677429374</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.098108690370335</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.334612677429374</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.643507869509245</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.600979300699038</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11.63267890141215</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.56581570387053</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10.56581570387053</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.54347538417607</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11.64182701432832</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.56581570387053</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11.34266555168731</v>
+      </c>
+      <c r="K10" t="n">
+        <v>11.15743443581558</v>
+      </c>
+      <c r="L10" t="n">
+        <v>12.08671982455648</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>3.391361212184572</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>3.391361212184571</v>
+      </c>
+      <c r="C11" t="n">
         <v>3.410444237495147</v>
       </c>
-      <c r="D9" t="n">
-        <v>5.541235550644324</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>5.541235550644323</v>
+      </c>
+      <c r="E11" t="n">
         <v>4.312776571935561</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>4.312776571935561</v>
       </c>
-      <c r="G9" t="n">
-        <v>4.398443518981108</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="G11" t="n">
+        <v>4.398443518981109</v>
+      </c>
+      <c r="H11" t="n">
         <v>5.545364252828236</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I11" t="n">
         <v>4.312776571935561</v>
       </c>
-      <c r="J9" t="n">
-        <v>5.329391930462109</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.922433151325711</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.853601759330857</v>
+      <c r="J11" t="n">
+        <v>5.329391930462104</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.922433151325707</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.853601759330858</v>
       </c>
     </row>
   </sheetData>
@@ -2027,7 +2347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2095,320 +2415,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.694164972919923</v>
+        <v>3.427220560586866</v>
       </c>
       <c r="C2" t="n">
-        <v>6.677343233682683</v>
+        <v>3.494825058742597</v>
       </c>
       <c r="D2" t="n">
-        <v>12.99054857639739</v>
+        <v>5.709092459298208</v>
       </c>
       <c r="E2" t="n">
-        <v>2.706860036939721</v>
+        <v>4.36076661476273</v>
       </c>
       <c r="F2" t="n">
-        <v>2.706860036939721</v>
+        <v>4.36076661476273</v>
       </c>
       <c r="G2" t="n">
-        <v>9.381665715046363</v>
+        <v>4.53293321914955</v>
       </c>
       <c r="H2" t="n">
-        <v>12.07058222176494</v>
+        <v>5.706650546559594</v>
       </c>
       <c r="I2" t="n">
-        <v>2.706860036939721</v>
+        <v>4.36076661476273</v>
       </c>
       <c r="J2" t="n">
-        <v>18.28433997394302</v>
+        <v>5.561662260959692</v>
       </c>
       <c r="K2" t="n">
-        <v>3.734877182359619</v>
+        <v>5.015258798048705</v>
       </c>
       <c r="L2" t="n">
-        <v>5.605198848675522</v>
+        <v>5.930538006871307</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.606484512948947</v>
+        <v>9.748083278225092</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5763372423789579</v>
+        <v>9.812097626255913</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6064845129489473</v>
+        <v>12.05392923111645</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5786002103829384</v>
+        <v>10.69641241905044</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5786002103829385</v>
+        <v>10.69641241905044</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6043034225674461</v>
+        <v>10.8636233344028</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6064845129489473</v>
+        <v>12.05392923111645</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5920698040283912</v>
+        <v>10.69641241905044</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6064845129489473</v>
+        <v>11.8988017832485</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6064845129489473</v>
+        <v>11.3600267587252</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6064845129489473</v>
+        <v>12.28837481637054</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6821620497750657</v>
+        <v>2.694164972919925</v>
       </c>
       <c r="C4" t="n">
-        <v>0.671427766145607</v>
+        <v>6.677343233682689</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6958432202003144</v>
+        <v>12.99054857639738</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6404177909026155</v>
+        <v>2.70686003693972</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6663979427641624</v>
+        <v>2.70686003693972</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9912327209166331</v>
+        <v>9.381665715046331</v>
       </c>
       <c r="H4" t="n">
-        <v>1.062839475144984</v>
+        <v>12.07058222176498</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9789991023775783</v>
+        <v>2.70686003693972</v>
       </c>
       <c r="J4" t="n">
-        <v>1.026128297417414</v>
+        <v>18.28433997394302</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6781971923369272</v>
+        <v>3.734877182359624</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6825600587061215</v>
+        <v>5.605198848675525</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.031269507657254</v>
+        <v>0.6064845129489475</v>
       </c>
       <c r="C5" t="n">
-        <v>1.030618341438424</v>
+        <v>0.5763372423789579</v>
       </c>
       <c r="D5" t="n">
-        <v>1.02937671630963</v>
+        <v>0.6064845129489475</v>
       </c>
       <c r="E5" t="n">
-        <v>1.014481390510505</v>
+        <v>0.578600210382939</v>
       </c>
       <c r="F5" t="n">
-        <v>1.014481390510505</v>
+        <v>0.5786002103829392</v>
       </c>
       <c r="G5" t="n">
-        <v>1.029088417275754</v>
+        <v>0.604303422567446</v>
       </c>
       <c r="H5" t="n">
-        <v>1.031269507657254</v>
+        <v>0.6064845129489475</v>
       </c>
       <c r="I5" t="n">
-        <v>1.016854798736699</v>
+        <v>0.5920698040283915</v>
       </c>
       <c r="J5" t="n">
-        <v>1.031269507657254</v>
+        <v>0.6064845129489475</v>
       </c>
       <c r="K5" t="n">
-        <v>1.031269507657254</v>
+        <v>0.6064845129489475</v>
       </c>
       <c r="L5" t="n">
-        <v>1.031269507657254</v>
+        <v>0.6064845129489475</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.206326739208676</v>
+        <v>0.6821620497750671</v>
       </c>
       <c r="C6" t="n">
-        <v>1.700179130559499</v>
+        <v>0.6714277661456133</v>
       </c>
       <c r="D6" t="n">
-        <v>1.803102168973559</v>
+        <v>0.6958432202002062</v>
       </c>
       <c r="E6" t="n">
-        <v>1.550688990882105</v>
+        <v>0.6404177909026164</v>
       </c>
       <c r="F6" t="n">
-        <v>1.207293317545002</v>
+        <v>0.6663979427641643</v>
       </c>
       <c r="G6" t="n">
-        <v>1.698428342207856</v>
+        <v>0.9912327209166325</v>
       </c>
       <c r="H6" t="n">
-        <v>1.700609432592023</v>
+        <v>1.062839475144986</v>
       </c>
       <c r="I6" t="n">
-        <v>1.686194723668802</v>
+        <v>0.9789991023775784</v>
       </c>
       <c r="J6" t="n">
-        <v>1.700706572629269</v>
+        <v>1.026128297417415</v>
       </c>
       <c r="K6" t="n">
-        <v>1.197145184473974</v>
+        <v>0.6781971923369297</v>
       </c>
       <c r="L6" t="n">
-        <v>2.216929036444686</v>
+        <v>0.6825600587061228</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.700520035657849</v>
+        <v>1.031269507657256</v>
       </c>
       <c r="C7" t="n">
-        <v>2.051678656058917</v>
+        <v>1.030618341438425</v>
       </c>
       <c r="D7" t="n">
-        <v>2.052330001198834</v>
+        <v>1.029376716309631</v>
       </c>
       <c r="E7" t="n">
-        <v>2.443895964743186</v>
+        <v>1.014481390510507</v>
       </c>
       <c r="F7" t="n">
-        <v>2.03791483772373</v>
+        <v>1.014481390510507</v>
       </c>
       <c r="G7" t="n">
-        <v>2.050148731896244</v>
+        <v>1.029088417275755</v>
       </c>
       <c r="H7" t="n">
-        <v>2.052329822277748</v>
+        <v>1.031269507657256</v>
       </c>
       <c r="I7" t="n">
-        <v>2.037915113357191</v>
+        <v>1.0168547987367</v>
       </c>
       <c r="J7" t="n">
-        <v>2.052329822277748</v>
+        <v>1.031269507657256</v>
       </c>
       <c r="K7" t="n">
-        <v>1.840219876140379</v>
+        <v>1.031269507657256</v>
       </c>
       <c r="L7" t="n">
-        <v>2.052329822277748</v>
+        <v>1.031269507657256</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.699076599788713</v>
+        <v>1.206326739208679</v>
       </c>
       <c r="C8" t="n">
-        <v>9.667529985016492</v>
+        <v>1.700179130559497</v>
       </c>
       <c r="D8" t="n">
-        <v>11.75114117614617</v>
+        <v>1.803102168973558</v>
       </c>
       <c r="E8" t="n">
-        <v>10.64474614956722</v>
+        <v>1.550688990882107</v>
       </c>
       <c r="F8" t="n">
-        <v>10.64474614956722</v>
+        <v>1.207293317545002</v>
       </c>
       <c r="G8" t="n">
-        <v>10.65525535066932</v>
+        <v>1.698428342207857</v>
       </c>
       <c r="H8" t="n">
-        <v>11.80700728614756</v>
+        <v>1.700609432592021</v>
       </c>
       <c r="I8" t="n">
-        <v>10.64474614956722</v>
+        <v>1.686194723668804</v>
       </c>
       <c r="J8" t="n">
-        <v>11.48885561920161</v>
+        <v>1.70070657262927</v>
       </c>
       <c r="K8" t="n">
-        <v>11.28340525466689</v>
+        <v>1.197145184473975</v>
       </c>
       <c r="L8" t="n">
-        <v>12.18277066638165</v>
+        <v>2.216929036444686</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.700520035657849</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.051678656058917</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.052330001198835</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.443895964743188</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.037914837723732</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.050148731896247</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.052329822277747</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.037915113357191</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.052329822277747</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.840219876140381</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.052329822277747</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.699076599788713</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.66752998501649</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11.75114117614617</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.64474614956722</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10.64474614956722</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.65525535066932</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11.80700728614756</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.64474614956722</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11.48885561920162</v>
+      </c>
+      <c r="K10" t="n">
+        <v>11.2834052546669</v>
+      </c>
+      <c r="L10" t="n">
+        <v>12.18277066638165</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>3.404922365723295</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>3.404922365723296</v>
+      </c>
+      <c r="C11" t="n">
         <v>3.429046321268924</v>
       </c>
-      <c r="D9" t="n">
-        <v>5.571322929358455</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.337258297497233</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.337258297497233</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="D11" t="n">
+        <v>5.571322929358454</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.337258297497234</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.337258297497234</v>
+      </c>
+      <c r="G11" t="n">
         <v>4.438125122521448</v>
       </c>
-      <c r="H9" t="n">
-        <v>5.5943002747052</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.337258297497233</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.375135449897455</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.98039576952393</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="H11" t="n">
+        <v>5.594300274705201</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.337258297497234</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.375135449897456</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.980395769523932</v>
+      </c>
+      <c r="L11" t="n">
         <v>5.882487782085905</v>
       </c>
     </row>
@@ -2423,7 +2823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2491,321 +2891,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.283489406358716</v>
+        <v>3.158455743730009</v>
       </c>
       <c r="C2" t="n">
-        <v>2.489352998656961</v>
+        <v>3.465075407659889</v>
       </c>
       <c r="D2" t="n">
-        <v>16.15214528957519</v>
+        <v>5.71535958677565</v>
       </c>
       <c r="E2" t="n">
-        <v>4.812520923821568</v>
+        <v>4.345431540235399</v>
       </c>
       <c r="F2" t="n">
-        <v>4.812520923821568</v>
+        <v>4.345431540235399</v>
       </c>
       <c r="G2" t="n">
-        <v>14.65208136297524</v>
+        <v>4.503155758743822</v>
       </c>
       <c r="H2" t="n">
-        <v>31.28619312081161</v>
+        <v>5.728609779439108</v>
       </c>
       <c r="I2" t="n">
-        <v>4.812520923821568</v>
+        <v>4.345431540235399</v>
       </c>
       <c r="J2" t="n">
-        <v>31.66406713194776</v>
+        <v>5.575150447647789</v>
       </c>
       <c r="K2" t="n">
-        <v>11.84234793515161</v>
+        <v>4.976546930189015</v>
       </c>
       <c r="L2" t="n">
-        <v>16.70869772565927</v>
+        <v>5.943160983172217</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6220222949904487</v>
+        <v>9.474457768614405</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6006962681346223</v>
+        <v>9.7867621262571</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6220222949904487</v>
+        <v>12.05745941276112</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5962305128446478</v>
+        <v>10.67857780827795</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5962305128446478</v>
+        <v>10.67857780827795</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6197798323603085</v>
+        <v>10.8280872717728</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6220222949904487</v>
+        <v>12.05745941276112</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6072200978222684</v>
+        <v>10.67857780827795</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6220222949904487</v>
+        <v>11.89914609733418</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6220222949904487</v>
+        <v>11.31177376460468</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6220222949904487</v>
+        <v>12.29047181721287</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6924165088131231</v>
+        <v>3.283489406358725</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6671550559058458</v>
+        <v>2.489352998656963</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7033404196784794</v>
+        <v>16.15214528957521</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6478195797886327</v>
+        <v>4.812520923821602</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6766008511572513</v>
+        <v>4.812520923821602</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6901740461829846</v>
+        <v>14.65208136297524</v>
       </c>
       <c r="H4" t="n">
-        <v>1.10755194725838</v>
+        <v>31.28619312081164</v>
       </c>
       <c r="I4" t="n">
-        <v>1.021024933170217</v>
+        <v>4.812520923821602</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7144090053619863</v>
+        <v>31.66406713194781</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6942618608297918</v>
+        <v>11.8423479351516</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6964161051639102</v>
+        <v>16.70869772565927</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.096217447109787</v>
+        <v>0.622022294990449</v>
       </c>
       <c r="C5" t="n">
-        <v>1.095277006391514</v>
+        <v>0.6006962681346224</v>
       </c>
       <c r="D5" t="n">
-        <v>1.094216001567761</v>
+        <v>0.622022294990449</v>
       </c>
       <c r="E5" t="n">
-        <v>1.080266401716334</v>
+        <v>0.5962305128446485</v>
       </c>
       <c r="F5" t="n">
-        <v>1.080266401716334</v>
+        <v>0.5962305128446486</v>
       </c>
       <c r="G5" t="n">
-        <v>1.093974984479647</v>
+        <v>0.6197798323603093</v>
       </c>
       <c r="H5" t="n">
-        <v>1.096217447109787</v>
+        <v>0.622022294990449</v>
       </c>
       <c r="I5" t="n">
-        <v>1.081415249941607</v>
+        <v>0.6072200978222688</v>
       </c>
       <c r="J5" t="n">
-        <v>1.096217447109787</v>
+        <v>0.622022294990449</v>
       </c>
       <c r="K5" t="n">
-        <v>1.096217447109787</v>
+        <v>0.622022294990449</v>
       </c>
       <c r="L5" t="n">
-        <v>1.096217447109787</v>
+        <v>0.622022294990449</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.29519709028133</v>
+        <v>0.6924165088131263</v>
       </c>
       <c r="C6" t="n">
-        <v>1.840554309673501</v>
+        <v>0.6671550559060175</v>
       </c>
       <c r="D6" t="n">
-        <v>1.952913186920493</v>
+        <v>0.7033404196784823</v>
       </c>
       <c r="E6" t="n">
-        <v>1.676990480587982</v>
+        <v>0.6478195797887177</v>
       </c>
       <c r="F6" t="n">
-        <v>1.298171469644951</v>
+        <v>0.6766008511572535</v>
       </c>
       <c r="G6" t="n">
-        <v>1.837711780014041</v>
+        <v>0.6901740461829853</v>
       </c>
       <c r="H6" t="n">
-        <v>1.839954242646287</v>
+        <v>1.107551947258381</v>
       </c>
       <c r="I6" t="n">
-        <v>1.825152045476002</v>
+        <v>1.021024933170219</v>
       </c>
       <c r="J6" t="n">
-        <v>1.840061302553378</v>
+        <v>0.714409005361989</v>
       </c>
       <c r="K6" t="n">
-        <v>1.285077946537357</v>
+        <v>0.694261860829792</v>
       </c>
       <c r="L6" t="n">
-        <v>2.40899863970069</v>
+        <v>0.6964161051639112</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.056918745923328</v>
+        <v>1.09621744710979</v>
       </c>
       <c r="C7" t="n">
-        <v>2.503743665425497</v>
+        <v>1.095277006391516</v>
       </c>
       <c r="D7" t="n">
-        <v>2.504684225210055</v>
+        <v>1.094216001567763</v>
       </c>
       <c r="E7" t="n">
-        <v>3.006593140689754</v>
+        <v>1.080266401716337</v>
       </c>
       <c r="F7" t="n">
-        <v>2.489881423012076</v>
+        <v>1.080266401716337</v>
       </c>
       <c r="G7" t="n">
-        <v>2.502441643513629</v>
+        <v>1.09397498447965</v>
       </c>
       <c r="H7" t="n">
-        <v>2.50468410614377</v>
+        <v>1.09621744710979</v>
       </c>
       <c r="I7" t="n">
-        <v>2.489881908975589</v>
+        <v>1.081415249941608</v>
       </c>
       <c r="J7" t="n">
-        <v>2.50468410614377</v>
+        <v>1.09621744710979</v>
       </c>
       <c r="K7" t="n">
-        <v>2.245247148000609</v>
+        <v>1.09621744710979</v>
       </c>
       <c r="L7" t="n">
-        <v>2.50468410614377</v>
+        <v>1.09621744710979</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.415358651613179</v>
+        <v>1.295197090281332</v>
       </c>
       <c r="C8" t="n">
-        <v>9.744470421474201</v>
+        <v>1.840554309673506</v>
       </c>
       <c r="D8" t="n">
-        <v>11.6981430801781</v>
+        <v>1.9529131869205</v>
       </c>
       <c r="E8" t="n">
-        <v>10.58200472701762</v>
+        <v>1.676990480587985</v>
       </c>
       <c r="F8" t="n">
-        <v>10.58200472701762</v>
+        <v>1.298171469644952</v>
       </c>
       <c r="G8" t="n">
-        <v>10.51303766485157</v>
+        <v>1.837711780014045</v>
       </c>
       <c r="H8" t="n">
-        <v>11.43245009091116</v>
+        <v>1.839954242646291</v>
       </c>
       <c r="I8" t="n">
-        <v>10.58200472701762</v>
+        <v>1.825152045476007</v>
       </c>
       <c r="J8" t="n">
-        <v>11.2178277160418</v>
+        <v>1.840061302553382</v>
       </c>
       <c r="K8" t="n">
-        <v>11.05316198211361</v>
+        <v>1.28507794653736</v>
       </c>
       <c r="L8" t="n">
-        <v>11.96912277428018</v>
+        <v>2.408998639700695</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.056918745923333</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.503743665425503</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.504684225210063</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.006593140689766</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.489881423012081</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.502441643513636</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.504684106143778</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.489881908975595</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.504684106143778</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.245247148000614</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.504684106143778</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.415358651613179</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.744470421474201</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11.6981430801781</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.58200472701763</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10.58200472701763</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.51303766485157</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11.43245009091116</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.58200472701763</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11.21782771604181</v>
+      </c>
+      <c r="K10" t="n">
+        <v>11.05316198211361</v>
+      </c>
+      <c r="L10" t="n">
+        <v>11.96912277428018</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>3.13156545715674</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>3.131565457156741</v>
+      </c>
+      <c r="C11" t="n">
         <v>3.445832547208004</v>
       </c>
-      <c r="D9" t="n">
-        <v>5.551869510377161</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.301490480501799</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.301490480501799</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.359807183591137</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="D11" t="n">
+        <v>5.551869510377163</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.301490480501801</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.301490480501801</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.359807183591138</v>
+      </c>
+      <c r="H11" t="n">
         <v>5.444228546210851</v>
       </c>
-      <c r="I9" t="n">
-        <v>4.301490480501799</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.265148412926903</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.858877745008726</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.79694614455921</v>
+      <c r="I11" t="n">
+        <v>4.301490480501801</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.265148412926906</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.858877745008733</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.796946144559212</v>
       </c>
     </row>
   </sheetData>
@@ -2819,7 +3299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,321 +3367,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.544415551581109</v>
+        <v>3.019685208453339</v>
       </c>
       <c r="C2" t="n">
-        <v>1.349334518963906</v>
+        <v>3.431215306301013</v>
       </c>
       <c r="D2" t="n">
-        <v>2.095895988108305</v>
+        <v>5.639953199292645</v>
       </c>
       <c r="E2" t="n">
-        <v>2.035066062995638</v>
+        <v>4.289251299359111</v>
       </c>
       <c r="F2" t="n">
-        <v>2.035066062995638</v>
+        <v>4.289251299359111</v>
       </c>
       <c r="G2" t="n">
-        <v>3.31510912484144</v>
+        <v>4.431228190734851</v>
       </c>
       <c r="H2" t="n">
-        <v>3.117470067594291</v>
+        <v>5.640826788481057</v>
       </c>
       <c r="I2" t="n">
-        <v>2.035066062995638</v>
+        <v>4.289251299359111</v>
       </c>
       <c r="J2" t="n">
-        <v>11.61269080155997</v>
+        <v>5.471987549004073</v>
       </c>
       <c r="K2" t="n">
-        <v>2.289676999837643</v>
+        <v>4.880718237156469</v>
       </c>
       <c r="L2" t="n">
-        <v>3.987726044077751</v>
+        <v>5.882313285692054</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5609227247993384</v>
+        <v>9.335605404616528</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5467430748485935</v>
+        <v>9.75383964112074</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5609227247993384</v>
+        <v>11.99678886722548</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5411702573882992</v>
+        <v>10.62471010421074</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5411702573882992</v>
+        <v>10.62471010421074</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5589808193591593</v>
+        <v>10.76749138341876</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5609227247993384</v>
+        <v>11.99678886722548</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5480267948786822</v>
+        <v>10.62471010421074</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5609227247993384</v>
+        <v>11.81546261690244</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5609227247993384</v>
+        <v>11.22525887483864</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5609227247993384</v>
+        <v>12.24127533064306</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5994958077036385</v>
+        <v>1.544415551581105</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5904097244409093</v>
+        <v>1.349334518963902</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8797239054095651</v>
+        <v>2.0958959881083</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5719653251713024</v>
+        <v>2.035066062995636</v>
       </c>
       <c r="F4" t="n">
-        <v>0.586390012380292</v>
+        <v>2.035066062995636</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5975539022634584</v>
+        <v>3.315109124841488</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9172509344295192</v>
+        <v>3.117470067594284</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8497274002652455</v>
+        <v>2.035066062995636</v>
       </c>
       <c r="J4" t="n">
-        <v>0.887571607488771</v>
+        <v>11.61269080155996</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5983609604646281</v>
+        <v>2.289676999837643</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6003896563492743</v>
+        <v>3.987726044077747</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9430283366797836</v>
+        <v>0.56092272479934</v>
       </c>
       <c r="C5" t="n">
-        <v>0.942545922515223</v>
+        <v>0.5467430748485925</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9411335212142505</v>
+        <v>0.5609227247993399</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9286810921700255</v>
+        <v>0.5411702573882995</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9286810921700255</v>
+        <v>0.5411702573882995</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9410864312396042</v>
+        <v>0.5589808193591557</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9430283366797836</v>
+        <v>0.56092272479934</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9301324067591287</v>
+        <v>0.5480267948786831</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9430283366797836</v>
+        <v>0.56092272479934</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9430283366797836</v>
+        <v>0.56092272479934</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9430283366797836</v>
+        <v>0.56092272479934</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.077550283995455</v>
+        <v>0.5994958077036343</v>
       </c>
       <c r="C6" t="n">
-        <v>1.500888141812889</v>
+        <v>0.5904097244409096</v>
       </c>
       <c r="D6" t="n">
-        <v>1.587934030005307</v>
+        <v>0.8797239054095577</v>
       </c>
       <c r="E6" t="n">
-        <v>1.372223716542371</v>
+        <v>0.5719653251712953</v>
       </c>
       <c r="F6" t="n">
-        <v>1.078318757929563</v>
+        <v>0.5863900123802923</v>
       </c>
       <c r="G6" t="n">
-        <v>1.498336661335202</v>
+        <v>0.5975539022634568</v>
       </c>
       <c r="H6" t="n">
-        <v>1.500278566776911</v>
+        <v>0.9172509344295119</v>
       </c>
       <c r="I6" t="n">
-        <v>1.487382636854725</v>
+        <v>0.8497274002652476</v>
       </c>
       <c r="J6" t="n">
-        <v>1.500361644609072</v>
+        <v>0.8875716074887706</v>
       </c>
       <c r="K6" t="n">
-        <v>1.069697889147537</v>
+        <v>0.598360960464638</v>
       </c>
       <c r="L6" t="n">
-        <v>1.941853605748274</v>
+        <v>0.6003896563492707</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.572549738442009</v>
+        <v>0.9430283366797839</v>
       </c>
       <c r="C7" t="n">
-        <v>1.892955824586126</v>
+        <v>0.942545922515222</v>
       </c>
       <c r="D7" t="n">
-        <v>1.893438339345597</v>
+        <v>0.941133521214249</v>
       </c>
       <c r="E7" t="n">
-        <v>2.250840731661945</v>
+        <v>0.9286810921700259</v>
       </c>
       <c r="F7" t="n">
-        <v>1.880542154010267</v>
+        <v>0.9286810921700259</v>
       </c>
       <c r="G7" t="n">
-        <v>1.891496333310506</v>
+        <v>0.9410864312396009</v>
       </c>
       <c r="H7" t="n">
-        <v>1.893438238750687</v>
+        <v>0.9430283366797839</v>
       </c>
       <c r="I7" t="n">
-        <v>1.880542308830031</v>
+        <v>0.9301324067591281</v>
       </c>
       <c r="J7" t="n">
-        <v>1.893438238750687</v>
+        <v>0.9430283366797839</v>
       </c>
       <c r="K7" t="n">
-        <v>1.70751422375528</v>
+        <v>0.9430283366797839</v>
       </c>
       <c r="L7" t="n">
-        <v>1.893438238750687</v>
+        <v>0.9430283366797839</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.313256428790996</v>
+        <v>1.077550283995454</v>
       </c>
       <c r="C8" t="n">
-        <v>9.735028899785879</v>
+        <v>1.500888141812889</v>
       </c>
       <c r="D8" t="n">
-        <v>11.95913646191887</v>
+        <v>1.587934030005299</v>
       </c>
       <c r="E8" t="n">
-        <v>10.58862406529054</v>
+        <v>1.372223716542372</v>
       </c>
       <c r="F8" t="n">
-        <v>10.58862406529054</v>
+        <v>1.078318757929564</v>
       </c>
       <c r="G8" t="n">
-        <v>10.70212849525408</v>
+        <v>1.498336661335196</v>
       </c>
       <c r="H8" t="n">
-        <v>11.94189355948828</v>
+        <v>1.500278566776901</v>
       </c>
       <c r="I8" t="n">
-        <v>10.58862406529054</v>
+        <v>1.487382636854725</v>
       </c>
       <c r="J8" t="n">
-        <v>11.55939743495507</v>
+        <v>1.500361644609071</v>
       </c>
       <c r="K8" t="n">
-        <v>11.18306696203656</v>
+        <v>1.069697889147532</v>
       </c>
       <c r="L8" t="n">
-        <v>12.16917126140677</v>
+        <v>1.941853605748266</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.572549738442008</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.892955824586128</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.893438339345594</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.250840731661948</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.880542154010268</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.891496333310508</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.89343823875069</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.880542308830034</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.89343823875069</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.707514223755283</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.89343823875069</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.313256428790996</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.735028899785878</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11.95913646191887</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.58862406529054</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10.58862406529054</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.70212849525408</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11.94189355948828</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.58862406529054</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11.55939743495506</v>
+      </c>
+      <c r="K10" t="n">
+        <v>11.18306696203655</v>
+      </c>
+      <c r="L10" t="n">
+        <v>12.16917126140677</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>3.009516353230762</v>
       </c>
-      <c r="C9" t="n">
-        <v>3.422656359047377</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5.622821234887043</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.272832036651035</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.272832036651035</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.401487868320755</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5.615849248519665</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.272832036651035</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.355477075186705</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.861520782373876</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.849505704407507</v>
+      <c r="C11" t="n">
+        <v>3.422656359047376</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.622821234887041</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.272832036651034</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.272832036651034</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.401487868320757</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.615849248519664</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.272832036651034</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.355477075186704</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.861520782373873</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.849505704407509</v>
       </c>
     </row>
   </sheetData>
@@ -3215,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3283,321 +3843,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.328585633237925</v>
+        <v>2.822309959385976</v>
       </c>
       <c r="C2" t="n">
-        <v>1.213134573041391</v>
+        <v>3.414846989484822</v>
       </c>
       <c r="D2" t="n">
-        <v>1.485402409203246</v>
+        <v>5.601259205572607</v>
       </c>
       <c r="E2" t="n">
-        <v>1.593082915254627</v>
+        <v>4.258532624452129</v>
       </c>
       <c r="F2" t="n">
-        <v>1.593082915254627</v>
+        <v>4.258532624452129</v>
       </c>
       <c r="G2" t="n">
-        <v>1.643046172034825</v>
+        <v>4.397971404980591</v>
       </c>
       <c r="H2" t="n">
-        <v>1.70676468138191</v>
+        <v>5.60136518646964</v>
       </c>
       <c r="I2" t="n">
-        <v>1.593082915254627</v>
+        <v>4.258532624452129</v>
       </c>
       <c r="J2" t="n">
-        <v>2.909157641823934</v>
+        <v>5.397940470513802</v>
       </c>
       <c r="K2" t="n">
-        <v>1.06959896427004</v>
+        <v>4.888508145254431</v>
       </c>
       <c r="L2" t="n">
-        <v>1.527649465487195</v>
+        <v>5.849192710840111</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5230830220505164</v>
+        <v>9.135474557196256</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5121485860857395</v>
+        <v>9.73750248462094</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5230830220505164</v>
+        <v>11.95833529838049</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5014711594869061</v>
+        <v>10.59414408766607</v>
       </c>
       <c r="F3" t="n">
-        <v>0.501471159486906</v>
+        <v>10.59414408766607</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5211884862033174</v>
+        <v>10.73576454763568</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5230830220505164</v>
+        <v>11.95833529838049</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5104750252322824</v>
+        <v>10.59414408766607</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5230830220505164</v>
+        <v>11.75022590585194</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5230830220505164</v>
+        <v>11.23474444338216</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5230830220505164</v>
+        <v>12.21032095858001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7800813143812624</v>
+        <v>1.328585633237908</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5394400855613325</v>
+        <v>1.213134573041392</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5464430449411474</v>
+        <v>1.485402409203229</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5225444561091708</v>
+        <v>1.593082915254617</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5326974481292761</v>
+        <v>1.593082915254617</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7781867785340806</v>
+        <v>1.643046172034834</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5462096033139093</v>
+        <v>1.706764681381887</v>
       </c>
       <c r="I4" t="n">
-        <v>0.767473317563041</v>
+        <v>1.593082915254617</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5538347112366824</v>
+        <v>2.909157641823926</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5436371352497968</v>
+        <v>1.069598964270019</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5461109581069095</v>
+        <v>1.527649465487199</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8752459852203986</v>
+        <v>0.5230830220505013</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8748675116075562</v>
+        <v>0.5121485860857345</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8733509395427302</v>
+        <v>0.5230830220505013</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8601960617405154</v>
+        <v>0.5014711594869068</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8601960617405154</v>
+        <v>0.5014711594869069</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8733514493732203</v>
+        <v>0.5211884862033225</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8752459852203986</v>
+        <v>0.5230830220505013</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8626379884021751</v>
+        <v>0.5104750252322847</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8752459852203986</v>
+        <v>0.5230830220505013</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8752459852203986</v>
+        <v>0.5230830220505013</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8752459852203986</v>
+        <v>0.5230830220505013</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9807730796919837</v>
+        <v>0.7800813143812575</v>
       </c>
       <c r="C6" t="n">
-        <v>1.351495580833275</v>
+        <v>0.5394400855614708</v>
       </c>
       <c r="D6" t="n">
-        <v>1.428661700195843</v>
+        <v>0.5464430449411316</v>
       </c>
       <c r="E6" t="n">
-        <v>1.237273264193275</v>
+        <v>0.5225444561092722</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9795979019127914</v>
+        <v>0.5326974481292744</v>
       </c>
       <c r="G6" t="n">
-        <v>1.349844878288684</v>
+        <v>0.7781867785340785</v>
       </c>
       <c r="H6" t="n">
-        <v>1.351739414136733</v>
+        <v>0.5462096033138969</v>
       </c>
       <c r="I6" t="n">
-        <v>1.339131417317647</v>
+        <v>0.7674733175630407</v>
       </c>
       <c r="J6" t="n">
-        <v>1.351812319480096</v>
+        <v>0.553834711236682</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9738821895899634</v>
+        <v>0.5436371352497946</v>
       </c>
       <c r="L6" t="n">
-        <v>1.739244770007384</v>
+        <v>0.5461109581068953</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.422907953209131</v>
+        <v>0.875245985220391</v>
       </c>
       <c r="C7" t="n">
-        <v>1.70626849166632</v>
+        <v>0.8748675116075553</v>
       </c>
       <c r="D7" t="n">
-        <v>1.706647013754708</v>
+        <v>0.8733509395427197</v>
       </c>
       <c r="E7" t="n">
-        <v>2.021467638621246</v>
+        <v>0.8601960617405152</v>
       </c>
       <c r="F7" t="n">
-        <v>1.69403882658053</v>
+        <v>0.8601960617405152</v>
       </c>
       <c r="G7" t="n">
-        <v>1.704752429431976</v>
+        <v>0.8733514493732119</v>
       </c>
       <c r="H7" t="n">
-        <v>1.706646965279163</v>
+        <v>0.875245985220391</v>
       </c>
       <c r="I7" t="n">
-        <v>1.694038968460938</v>
+        <v>0.8626379884021736</v>
       </c>
       <c r="J7" t="n">
-        <v>1.706646965279163</v>
+        <v>0.875245985220391</v>
       </c>
       <c r="K7" t="n">
-        <v>1.542247487745316</v>
+        <v>0.875245985220391</v>
       </c>
       <c r="L7" t="n">
-        <v>1.706646965279163</v>
+        <v>0.875245985220391</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.117739263788836</v>
+        <v>0.9807730796919855</v>
       </c>
       <c r="C8" t="n">
-        <v>9.721402388781435</v>
+        <v>1.351495580833274</v>
       </c>
       <c r="D8" t="n">
-        <v>11.93502268638526</v>
+        <v>1.428661700195841</v>
       </c>
       <c r="E8" t="n">
-        <v>10.56818808988023</v>
+        <v>1.237273264193275</v>
       </c>
       <c r="F8" t="n">
-        <v>10.56818808988023</v>
+        <v>0.9795979019127915</v>
       </c>
       <c r="G8" t="n">
-        <v>10.70945930866264</v>
+        <v>1.349844878288683</v>
       </c>
       <c r="H8" t="n">
-        <v>11.9332932993448</v>
+        <v>1.351739414136729</v>
       </c>
       <c r="I8" t="n">
-        <v>10.56818808988023</v>
+        <v>1.339131417317647</v>
       </c>
       <c r="J8" t="n">
-        <v>11.69523450016747</v>
+        <v>1.351812319480088</v>
       </c>
       <c r="K8" t="n">
-        <v>11.22164253920974</v>
+        <v>0.973882189589956</v>
       </c>
       <c r="L8" t="n">
-        <v>12.18960999308456</v>
+        <v>1.739244770007386</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.422907953209124</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.70626849166632</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.70664701375471</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.021467638621246</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.694038826580532</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.704752429431976</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.706646965279157</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.694038968460939</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.706646965279157</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.542247487745325</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.706646965279157</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.117739263788829</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.721402388781435</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11.93502268638526</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.56818808988023</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10.56818808988023</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.70945930866263</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11.9332932993448</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.56818808988023</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11.69523450016747</v>
+      </c>
+      <c r="K10" t="n">
+        <v>11.22164253920973</v>
+      </c>
+      <c r="L10" t="n">
+        <v>12.18960999308456</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.814240344366573</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.407521394569887</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5.590651892821885</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.246722562742716</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.246722562742716</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.386002437418036</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5.589970997104287</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.246722562742716</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.372919205680153</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.88254673710269</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.839769155537754</v>
+      <c r="B11" t="n">
+        <v>2.81424034436657</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.407521394569885</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.590651892821891</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.246722562742717</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.246722562742717</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.38600243741803</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.589970997104285</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.246722562742717</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.372919205680156</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.882546737102686</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.839769155537749</v>
       </c>
     </row>
   </sheetData>
@@ -3611,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3679,321 +4319,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.072838665037264</v>
+        <v>3.04382233439591</v>
       </c>
       <c r="C2" t="n">
-        <v>1.516735966769695</v>
+        <v>3.41241071033319</v>
       </c>
       <c r="D2" t="n">
-        <v>4.598660153693699</v>
+        <v>5.668954293926976</v>
       </c>
       <c r="E2" t="n">
-        <v>2.594477377966233</v>
+        <v>4.31048940432999</v>
       </c>
       <c r="F2" t="n">
-        <v>2.594477377966233</v>
+        <v>4.31048940432999</v>
       </c>
       <c r="G2" t="n">
-        <v>7.293791374317382</v>
+        <v>4.451386682468166</v>
       </c>
       <c r="H2" t="n">
-        <v>25.80574636082401</v>
+        <v>5.689514548258441</v>
       </c>
       <c r="I2" t="n">
-        <v>2.594477377966233</v>
+        <v>4.31048940432999</v>
       </c>
       <c r="J2" t="n">
-        <v>11.45124281500259</v>
+        <v>5.501932582545538</v>
       </c>
       <c r="K2" t="n">
-        <v>4.576293297191835</v>
+        <v>4.894523631180405</v>
       </c>
       <c r="L2" t="n">
-        <v>13.28160122662347</v>
+        <v>5.914902184784196</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5949540427459465</v>
+        <v>9.359498428017011</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5786621044477303</v>
+        <v>9.734493603623019</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5949540427459465</v>
+        <v>12.02343451110644</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5731386293888645</v>
+        <v>10.64567484156534</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5731386293888645</v>
+        <v>10.64567484156534</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5928999802864181</v>
+        <v>10.78369209134172</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5949540427459465</v>
+        <v>12.02343451110644</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5813507565814724</v>
+        <v>10.64567484156534</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5949540427459465</v>
+        <v>11.84660926134019</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5949540427459465</v>
+        <v>11.23673029538313</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5949540427459465</v>
+        <v>12.26531044796723</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6407211991527463</v>
+        <v>2.072838665037264</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6255773833109021</v>
+        <v>1.516735966769699</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6394418534001446</v>
+        <v>4.598660153693698</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6062487589283748</v>
+        <v>2.594477377966246</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6264891847551269</v>
+        <v>2.594477377966246</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6386671366932215</v>
+        <v>7.293791374317327</v>
       </c>
       <c r="H4" t="n">
-        <v>1.020417623823143</v>
+        <v>25.80574636082398</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6271179129882711</v>
+        <v>2.594477377966246</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6546893468231956</v>
+        <v>11.45124281500262</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6386432205813741</v>
+        <v>4.576293297191837</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6441456519592295</v>
+        <v>13.28160122662347</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.030263508940497</v>
+        <v>0.5949540427459443</v>
       </c>
       <c r="C5" t="n">
-        <v>1.029610356821721</v>
+        <v>0.5786621044477347</v>
       </c>
       <c r="D5" t="n">
-        <v>1.028262299135011</v>
+        <v>0.5949540427459443</v>
       </c>
       <c r="E5" t="n">
-        <v>1.015482596042529</v>
+        <v>0.5731386293888637</v>
       </c>
       <c r="F5" t="n">
-        <v>1.015482596042529</v>
+        <v>0.5731386293888646</v>
       </c>
       <c r="G5" t="n">
-        <v>1.028209446480976</v>
+        <v>0.5928999802864233</v>
       </c>
       <c r="H5" t="n">
-        <v>1.030263508940497</v>
+        <v>0.5949540427459443</v>
       </c>
       <c r="I5" t="n">
-        <v>1.01666022277602</v>
+        <v>0.5813507565814732</v>
       </c>
       <c r="J5" t="n">
-        <v>1.030263508940497</v>
+        <v>0.5949540427459443</v>
       </c>
       <c r="K5" t="n">
-        <v>1.030263508940497</v>
+        <v>0.5949540427459443</v>
       </c>
       <c r="L5" t="n">
-        <v>1.030263508940497</v>
+        <v>0.5949540427459443</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.200051369038321</v>
+        <v>0.6407211991527432</v>
       </c>
       <c r="C6" t="n">
-        <v>1.694069572894493</v>
+        <v>0.6255773833109823</v>
       </c>
       <c r="D6" t="n">
-        <v>1.795481784642929</v>
+        <v>0.639441853400138</v>
       </c>
       <c r="E6" t="n">
-        <v>1.545530302978646</v>
+        <v>0.6062487589283301</v>
       </c>
       <c r="F6" t="n">
-        <v>1.202572075992873</v>
+        <v>0.6264891847551256</v>
       </c>
       <c r="G6" t="n">
-        <v>1.691165984208855</v>
+        <v>0.6386671366932225</v>
       </c>
       <c r="H6" t="n">
-        <v>1.69322004667065</v>
+        <v>1.020417623823145</v>
       </c>
       <c r="I6" t="n">
-        <v>1.679616760503895</v>
+        <v>0.6271179129882696</v>
       </c>
       <c r="J6" t="n">
-        <v>1.693316967991993</v>
+        <v>0.6546893468231874</v>
       </c>
       <c r="K6" t="n">
-        <v>1.190890507695613</v>
+        <v>0.6386432205813751</v>
       </c>
       <c r="L6" t="n">
-        <v>2.208375968134587</v>
+        <v>0.6441456519592305</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.841839890844186</v>
+        <v>1.030263508940492</v>
       </c>
       <c r="C7" t="n">
-        <v>2.233330094905553</v>
+        <v>1.02961035682172</v>
       </c>
       <c r="D7" t="n">
-        <v>2.233983185962285</v>
+        <v>1.028262299135009</v>
       </c>
       <c r="E7" t="n">
-        <v>2.672904455860505</v>
+        <v>1.01548259604253</v>
       </c>
       <c r="F7" t="n">
-        <v>2.220379506419715</v>
+        <v>1.01548259604253</v>
       </c>
       <c r="G7" t="n">
-        <v>2.231929184564806</v>
+        <v>1.028209446480971</v>
       </c>
       <c r="H7" t="n">
-        <v>2.233983247024327</v>
+        <v>1.030263508940492</v>
       </c>
       <c r="I7" t="n">
-        <v>2.220379960859852</v>
+        <v>1.016660222776019</v>
       </c>
       <c r="J7" t="n">
-        <v>2.233983247024327</v>
+        <v>1.030263508940492</v>
       </c>
       <c r="K7" t="n">
-        <v>2.006773820705306</v>
+        <v>1.030263508940492</v>
       </c>
       <c r="L7" t="n">
-        <v>2.233983247024327</v>
+        <v>1.030263508940492</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.327093418119532</v>
+        <v>1.200051369038318</v>
       </c>
       <c r="C8" t="n">
-        <v>9.713526391142072</v>
+        <v>1.694069572894496</v>
       </c>
       <c r="D8" t="n">
-        <v>11.93055282611552</v>
+        <v>1.79548178464293</v>
       </c>
       <c r="E8" t="n">
-        <v>10.59929993697645</v>
+        <v>1.545530302978646</v>
       </c>
       <c r="F8" t="n">
-        <v>10.59929993697645</v>
+        <v>1.202572075992872</v>
       </c>
       <c r="G8" t="n">
-        <v>10.63314437056993</v>
+        <v>1.691165984208845</v>
       </c>
       <c r="H8" t="n">
-        <v>11.5096025796872</v>
+        <v>1.693220046670653</v>
       </c>
       <c r="I8" t="n">
-        <v>10.59929993697645</v>
+        <v>1.679616760503893</v>
       </c>
       <c r="J8" t="n">
-        <v>11.60821405185529</v>
+        <v>1.693316967991988</v>
       </c>
       <c r="K8" t="n">
-        <v>11.14476464302985</v>
+        <v>1.190890507695616</v>
       </c>
       <c r="L8" t="n">
-        <v>12.01191381315389</v>
+        <v>2.208375968134582</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.841839890844185</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.233330094905552</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.233983185962277</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.672904455860506</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.220379506419714</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.231929184564802</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.233983247024321</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.22037996085985</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.233983247024321</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.006773820705305</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.233983247024321</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.32709341811953</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.713526391142073</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11.93055282611552</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.59929993697645</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10.59929993697645</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.63314437056992</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11.5096025796872</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.59929993697645</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11.6082140518553</v>
+      </c>
+      <c r="K10" t="n">
+        <v>11.14476464302984</v>
+      </c>
+      <c r="L10" t="n">
+        <v>12.01191381315389</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>3.029077951623921</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.402870561835814</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5.626692831259739</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.289388674953996</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.289388674953996</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="B11" t="n">
+        <v>3.029077951623918</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.402870561835816</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.626692831259738</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.289388674953995</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.289388674953995</v>
+      </c>
+      <c r="G11" t="n">
         <v>4.382886989749879</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H11" t="n">
         <v>5.455719381977477</v>
       </c>
-      <c r="I9" t="n">
-        <v>4.289388674953996</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.393462002509453</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.852678966282521</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.799605908416964</v>
+      <c r="I11" t="n">
+        <v>4.289388674953995</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.393462002509456</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.852678966282517</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.799605908416963</v>
       </c>
     </row>
   </sheetData>
@@ -4007,7 +4727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4075,321 +4795,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8846392486171305</v>
+        <v>2.065802942416714</v>
       </c>
       <c r="C2" t="n">
-        <v>1.126980630660796</v>
+        <v>3.351916905848007</v>
       </c>
       <c r="D2" t="n">
-        <v>1.52678328212013</v>
+        <v>5.602630172373505</v>
       </c>
       <c r="E2" t="n">
-        <v>0.772315249278456</v>
+        <v>4.227520566172819</v>
       </c>
       <c r="F2" t="n">
-        <v>0.772315249278456</v>
+        <v>4.227520566172819</v>
       </c>
       <c r="G2" t="n">
-        <v>1.281832481942508</v>
+        <v>4.320453310714631</v>
       </c>
       <c r="H2" t="n">
-        <v>1.689832324420631</v>
+        <v>5.602670150843668</v>
       </c>
       <c r="I2" t="n">
-        <v>0.772315249278456</v>
+        <v>4.227520566172819</v>
       </c>
       <c r="J2" t="n">
-        <v>1.301479047730183</v>
+        <v>5.403988674382507</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0009846219054800986</v>
+        <v>4.730354355012554</v>
       </c>
       <c r="L2" t="n">
-        <v>1.824435277143764</v>
+        <v>5.853088637632553</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5264766484105472</v>
+        <v>8.367429381412574</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5146650248247276</v>
+        <v>9.673651936057828</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5264766484105472</v>
+        <v>11.95965972239724</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5066728221170724</v>
+        <v>10.56358588036961</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5066728221170724</v>
+        <v>10.56358588036961</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5245997156756572</v>
+        <v>10.65741245621317</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5264766484105472</v>
+        <v>11.95965972239724</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5139921585208668</v>
+        <v>10.56358588036961</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5264766484105472</v>
+        <v>11.75817089041868</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5264766484105472</v>
+        <v>11.07531573942527</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5264766484105472</v>
+        <v>12.21395109956309</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7832970898922743</v>
+        <v>0.8846392486171364</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5408221140614763</v>
+        <v>1.126980630660805</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5480086195871144</v>
+        <v>1.526783282120134</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5228685109388292</v>
+        <v>0.7723152492784575</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5336995449916992</v>
+        <v>0.7723152492784575</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5446855021296005</v>
+        <v>1.281832481942578</v>
       </c>
       <c r="H4" t="n">
-        <v>0.837920232588788</v>
+        <v>1.689832324420635</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7708126000025927</v>
+        <v>0.7723152492784575</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5544224275219538</v>
+        <v>1.301479047730184</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5424434644265833</v>
+        <v>0.0009846219054834293</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5473359798718966</v>
+        <v>1.824435277143769</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8798991385947821</v>
+        <v>0.5264766484105518</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8795258385998654</v>
+        <v>0.5146650248247396</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8780045465301153</v>
+        <v>0.5264766484105518</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8655921438428696</v>
+        <v>0.506672822117073</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8655921438428696</v>
+        <v>0.5066728221170731</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8780222058598884</v>
+        <v>0.5245997156756566</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8798991385947821</v>
+        <v>0.5264766484105518</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8674146487050993</v>
+        <v>0.5139921585208671</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8798991385947821</v>
+        <v>0.5264766484105513</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8798991385947821</v>
+        <v>0.5264766484105518</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8798991385947821</v>
+        <v>0.5264766484105518</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9871458334918819</v>
+        <v>0.7832970898922752</v>
       </c>
       <c r="C6" t="n">
-        <v>1.363102769251456</v>
+        <v>0.5408221140616168</v>
       </c>
       <c r="D6" t="n">
-        <v>1.440632726296813</v>
+        <v>0.5480086195871184</v>
       </c>
       <c r="E6" t="n">
-        <v>1.247668097191184</v>
+        <v>0.5228685109388302</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9866103866867894</v>
+        <v>0.5336995449917021</v>
       </c>
       <c r="G6" t="n">
-        <v>1.360872036542472</v>
+        <v>0.5446855021296031</v>
       </c>
       <c r="H6" t="n">
-        <v>1.362748969280323</v>
+        <v>0.837920232588785</v>
       </c>
       <c r="I6" t="n">
-        <v>1.350264479387674</v>
+        <v>0.7708126000025946</v>
       </c>
       <c r="J6" t="n">
-        <v>1.362822785829285</v>
+        <v>0.554422427521953</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9801688124308351</v>
+        <v>0.5424434644266111</v>
       </c>
       <c r="L6" t="n">
-        <v>1.755097851821099</v>
+        <v>0.5473359798718972</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.469868654579493</v>
+        <v>0.8798991385947785</v>
       </c>
       <c r="C7" t="n">
-        <v>1.766477361829939</v>
+        <v>0.8795258385998802</v>
       </c>
       <c r="D7" t="n">
-        <v>1.766850702350558</v>
+        <v>0.8780045465301181</v>
       </c>
       <c r="E7" t="n">
-        <v>2.097076960409743</v>
+        <v>0.8655921438428699</v>
       </c>
       <c r="F7" t="n">
-        <v>1.754366021946999</v>
+        <v>0.8655921438428699</v>
       </c>
       <c r="G7" t="n">
-        <v>1.764973729089962</v>
+        <v>0.8780222058598899</v>
       </c>
       <c r="H7" t="n">
-        <v>1.766850661824853</v>
+        <v>0.8798991385947785</v>
       </c>
       <c r="I7" t="n">
-        <v>1.754366171935171</v>
+        <v>0.8674146487050995</v>
       </c>
       <c r="J7" t="n">
-        <v>1.766850661824853</v>
+        <v>0.8798991385947785</v>
       </c>
       <c r="K7" t="n">
-        <v>1.392897293098786</v>
+        <v>0.8798991385947785</v>
       </c>
       <c r="L7" t="n">
-        <v>1.766850661824853</v>
+        <v>0.8798991385947785</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.360187143693743</v>
+        <v>0.9871458334918777</v>
       </c>
       <c r="C8" t="n">
-        <v>9.65960112896949</v>
+        <v>1.363102769251466</v>
       </c>
       <c r="D8" t="n">
-        <v>11.93533026483683</v>
+        <v>1.440632726296813</v>
       </c>
       <c r="E8" t="n">
-        <v>10.55744799986867</v>
+        <v>1.247668097191186</v>
       </c>
       <c r="F8" t="n">
-        <v>10.55744799986867</v>
+        <v>0.9866103866867895</v>
       </c>
       <c r="G8" t="n">
-        <v>10.63965573583552</v>
+        <v>1.360872036542472</v>
       </c>
       <c r="H8" t="n">
-        <v>11.93497682270473</v>
+        <v>1.362748969280327</v>
       </c>
       <c r="I8" t="n">
-        <v>10.55744799986867</v>
+        <v>1.350264479387679</v>
       </c>
       <c r="J8" t="n">
-        <v>11.74041298661161</v>
+        <v>1.362822785829286</v>
       </c>
       <c r="K8" t="n">
-        <v>11.08817056203325</v>
+        <v>0.9801688124308369</v>
       </c>
       <c r="L8" t="n">
-        <v>12.18697546605256</v>
+        <v>1.755097851821103</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.469868654579489</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.766477361829949</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.766850702350562</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.097076960409742</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.754366021947</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.764973729089965</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.766850661824859</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.754366171935175</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.766850661824859</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.392897293098783</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.766850661824859</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8.360187143693743</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.65960112896949</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11.93533026483683</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.55744799986867</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10.55744799986867</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.63965573583552</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11.93497682270473</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.55744799986867</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11.74041298661161</v>
+      </c>
+      <c r="K10" t="n">
+        <v>11.08817056203325</v>
+      </c>
+      <c r="L10" t="n">
+        <v>12.18697546605256</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.06250770117501</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.345523743845546</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>2.062507701175005</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.345523743845547</v>
+      </c>
+      <c r="D11" t="n">
         <v>5.591560191650141</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E11" t="n">
         <v>4.224727810984626</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>4.224727810984626</v>
       </c>
-      <c r="G9" t="n">
-        <v>4.312373946355489</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5.591439352823842</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>4.312373946355488</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.591439352823841</v>
+      </c>
+      <c r="I11" t="n">
         <v>4.224727810984626</v>
       </c>
-      <c r="J9" t="n">
-        <v>5.395908771559207</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.736203340265069</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.840814638419016</v>
+      <c r="J11" t="n">
+        <v>5.395908771559208</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.736203340265068</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.840814638419015</v>
       </c>
     </row>
   </sheetData>
@@ -4403,7 +5203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4471,321 +5271,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8347735266085835</v>
+        <v>0.831568320157245</v>
       </c>
       <c r="C2" t="n">
-        <v>1.040845744581315</v>
+        <v>3.306054568108329</v>
       </c>
       <c r="D2" t="n">
-        <v>1.141360518298029</v>
+        <v>5.554438193671431</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6002645685876787</v>
+        <v>4.198950052723383</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6002645685876787</v>
+        <v>4.198950052723383</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9504488351782665</v>
+        <v>4.119406860526874</v>
       </c>
       <c r="H2" t="n">
-        <v>1.317520996370698</v>
+        <v>5.554534923636912</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6002645685876787</v>
+        <v>4.198950052723383</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7509912921048356</v>
+        <v>5.32545240606466</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0235024931409159</v>
+        <v>4.773595211519694</v>
       </c>
       <c r="L2" t="n">
-        <v>1.434093050303619</v>
+        <v>5.816122797744031</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4769542231695073</v>
+        <v>5.743534189075612</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4694483883570267</v>
+        <v>9.627290092570899</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4769542231695073</v>
+        <v>11.91128638046658</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4622857743034974</v>
+        <v>10.53488886639326</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4622857743034974</v>
+        <v>10.53488886639326</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4752494897960224</v>
+        <v>10.45368016155477</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4769542231695073</v>
+        <v>11.91128638046658</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4655898967005402</v>
+        <v>10.53488886639326</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4769542231695073</v>
+        <v>11.67913932673196</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4769542231695073</v>
+        <v>11.11940215502646</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4769542231695073</v>
+        <v>12.17693509690857</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.679403423657614</v>
+        <v>0.8347735266085945</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4748726519214192</v>
+        <v>1.040845744581316</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4796157990910508</v>
+        <v>1.141360518298044</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4615759196742272</v>
+        <v>0.6002645685876772</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4679241862719433</v>
+        <v>0.6002645685876772</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4777669567536792</v>
+        <v>0.9504488351782974</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7230913873012857</v>
+        <v>1.317520996370701</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4681073636581932</v>
+        <v>0.6002645685876772</v>
       </c>
       <c r="J4" t="n">
-        <v>0.698690365479688</v>
+        <v>0.7509912921048392</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4750590210580136</v>
+        <v>-0.02350249314089126</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4803138333165046</v>
+        <v>1.434093050303604</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8014661387407305</v>
+        <v>0.4769542231695192</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8011727426211552</v>
+        <v>0.4694483883570151</v>
       </c>
       <c r="D5" t="n">
-        <v>0.79957033630278</v>
+        <v>0.4769542231695192</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7891872514120231</v>
+        <v>0.4622857743034973</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7891872514120231</v>
+        <v>0.4622857743034973</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7997614053672282</v>
+        <v>0.4752494897960291</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8014661387407305</v>
+        <v>0.4769542231695192</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7901018122717528</v>
+        <v>0.4655898967005399</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8014661387407305</v>
+        <v>0.4769542231695192</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8014661387407305</v>
+        <v>0.4769542231695192</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8014661387407305</v>
+        <v>0.4769542231695192</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.874295608485874</v>
+        <v>0.6794034236576345</v>
       </c>
       <c r="C6" t="n">
-        <v>1.190896344676276</v>
+        <v>0.4748726519214062</v>
       </c>
       <c r="D6" t="n">
-        <v>1.25498671616088</v>
+        <v>0.4796157990910679</v>
       </c>
       <c r="E6" t="n">
-        <v>1.09290075999025</v>
+        <v>0.4615759196742261</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8735114678152177</v>
+        <v>0.467924186271944</v>
       </c>
       <c r="G6" t="n">
-        <v>1.187900481781649</v>
+        <v>0.4777669567536821</v>
       </c>
       <c r="H6" t="n">
-        <v>1.189605215157995</v>
+        <v>0.7230913873013061</v>
       </c>
       <c r="I6" t="n">
-        <v>1.178240888686169</v>
+        <v>0.4681073636581942</v>
       </c>
       <c r="J6" t="n">
-        <v>1.189667182682451</v>
+        <v>0.698690365479697</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8684385706476645</v>
+        <v>0.4750590210580153</v>
       </c>
       <c r="L6" t="n">
-        <v>1.518972465231094</v>
+        <v>0.4803138333165038</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.330948626063921</v>
+        <v>0.8014661387407319</v>
       </c>
       <c r="C7" t="n">
-        <v>1.594184558679338</v>
+        <v>0.8011727426211497</v>
       </c>
       <c r="D7" t="n">
-        <v>1.594477964336074</v>
+        <v>0.7995703363028087</v>
       </c>
       <c r="E7" t="n">
-        <v>1.88722071209699</v>
+        <v>0.7891872514120239</v>
       </c>
       <c r="F7" t="n">
-        <v>1.58311348233784</v>
+        <v>0.7891872514120239</v>
       </c>
       <c r="G7" t="n">
-        <v>1.592773221425418</v>
+        <v>0.7997614053672433</v>
       </c>
       <c r="H7" t="n">
-        <v>1.594477954798897</v>
+        <v>0.8014661387407319</v>
       </c>
       <c r="I7" t="n">
-        <v>1.583113628329935</v>
+        <v>0.7901018122717544</v>
       </c>
       <c r="J7" t="n">
-        <v>1.594477954798897</v>
+        <v>0.8014661387407319</v>
       </c>
       <c r="K7" t="n">
-        <v>1.43559320730103</v>
+        <v>0.8014661387407319</v>
       </c>
       <c r="L7" t="n">
-        <v>1.594477954798897</v>
+        <v>0.8014661387407319</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.736890351928989</v>
+        <v>0.8742956084858884</v>
       </c>
       <c r="C8" t="n">
-        <v>9.614692053106555</v>
+        <v>1.190896344676281</v>
       </c>
       <c r="D8" t="n">
-        <v>11.89573146807447</v>
+        <v>1.254986716160885</v>
       </c>
       <c r="E8" t="n">
-        <v>10.53230905651378</v>
+        <v>1.092900759990251</v>
       </c>
       <c r="F8" t="n">
-        <v>10.53230905651378</v>
+        <v>0.8735114678152182</v>
       </c>
       <c r="G8" t="n">
-        <v>10.44316236140265</v>
+        <v>1.18790048178166</v>
       </c>
       <c r="H8" t="n">
-        <v>11.89404732828365</v>
+        <v>1.18960521515801</v>
       </c>
       <c r="I8" t="n">
-        <v>10.53230905651378</v>
+        <v>1.17824088868617</v>
       </c>
       <c r="J8" t="n">
-        <v>11.67352992393273</v>
+        <v>1.189667182682456</v>
       </c>
       <c r="K8" t="n">
-        <v>11.13222464091971</v>
+        <v>0.8684385706476633</v>
       </c>
       <c r="L8" t="n">
-        <v>12.15763360949985</v>
+        <v>1.518972465231111</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.33094862606394</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.594184558679327</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.594477964336076</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.887220712096993</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.583113482337842</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.592773221425428</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.594477954798916</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.583113628329939</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.594477954798917</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.435593207301057</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.594477954798916</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5.736890351928995</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9.614692053106554</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11.89573146807448</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.53230905651378</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10.53230905651378</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.44316236140265</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11.89404732828366</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.53230905651378</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11.67352992393274</v>
+      </c>
+      <c r="K10" t="n">
+        <v>11.13222464091971</v>
+      </c>
+      <c r="L10" t="n">
+        <v>12.15763360949985</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.8285453530828715</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.300322420004483</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5.547360658962452</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="B11" t="n">
+        <v>0.8285453530828804</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.300322420004484</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.547360658962462</v>
+      </c>
+      <c r="E11" t="n">
         <v>4.197776231006853</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>4.197776231006853</v>
       </c>
-      <c r="G9" t="n">
-        <v>4.114621227939411</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5.546691099956085</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>4.114621227939415</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.54669109995609</v>
+      </c>
+      <c r="I11" t="n">
         <v>4.197776231006853</v>
       </c>
-      <c r="J9" t="n">
-        <v>5.322900109914901</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.77942948346396</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.807340559462871</v>
+      <c r="J11" t="n">
+        <v>5.322900109914911</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.779429483463965</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.807340559462877</v>
       </c>
     </row>
   </sheetData>
@@ -4799,7 +5679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4867,321 +5747,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.4417106263637</v>
+        <v>4.751563328430596</v>
       </c>
       <c r="C2" t="n">
-        <v>12.52290970921386</v>
+        <v>4.900372651625192</v>
       </c>
       <c r="D2" t="n">
-        <v>46.88450307453914</v>
+        <v>4.768866811573488</v>
       </c>
       <c r="E2" t="n">
-        <v>12.52290970921386</v>
+        <v>4.900372651625192</v>
       </c>
       <c r="F2" t="n">
-        <v>12.52290970921386</v>
+        <v>4.900372651625192</v>
       </c>
       <c r="G2" t="n">
-        <v>37.4809276259715</v>
+        <v>4.75333153214614</v>
       </c>
       <c r="H2" t="n">
-        <v>76.16851182359272</v>
+        <v>4.792786825394825</v>
       </c>
       <c r="I2" t="n">
-        <v>12.52290970921386</v>
+        <v>4.900372651625192</v>
       </c>
       <c r="J2" t="n">
-        <v>47.83635972355361</v>
+        <v>4.766985084013025</v>
       </c>
       <c r="K2" t="n">
-        <v>25.91214323707203</v>
+        <v>4.745643397478441</v>
       </c>
       <c r="L2" t="n">
-        <v>26.67837620155561</v>
+        <v>4.74372528809642</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6849966485917487</v>
+        <v>11.06093072220773</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6468970433018391</v>
+        <v>11.23274524319099</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6849966485917487</v>
+        <v>11.06093072220773</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6536978419145387</v>
+        <v>11.23274524319099</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6536978419145386</v>
+        <v>11.23274524319099</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6826101458250279</v>
+        <v>11.05659691467594</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6849966485917487</v>
+        <v>11.06093072220773</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6693726492656904</v>
+        <v>11.23274524319099</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6849966485917487</v>
+        <v>11.06093072220773</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6849966485917487</v>
+        <v>11.06093072220773</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6849966485917487</v>
+        <v>11.06093072220773</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8290253770855199</v>
+        <v>30.44171062636357</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7728300325537211</v>
+        <v>12.52290970921391</v>
       </c>
       <c r="D4" t="n">
-        <v>0.864759120164534</v>
+        <v>46.88450307453925</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7589290824268264</v>
+        <v>12.52290970921391</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8099202401647142</v>
+        <v>12.52290970921391</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8266388743187973</v>
+        <v>37.48092762597149</v>
       </c>
       <c r="H4" t="n">
-        <v>1.360186609858337</v>
+        <v>76.16851182359281</v>
       </c>
       <c r="I4" t="n">
-        <v>1.286112632980885</v>
+        <v>12.52290970921391</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8579554871535855</v>
+        <v>47.83635972355363</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8242619021380416</v>
+        <v>25.91214323707203</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8441990787272637</v>
+        <v>26.67837620155555</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.251995958523709</v>
+        <v>0.6849966485917538</v>
       </c>
       <c r="C5" t="n">
-        <v>1.236371959197645</v>
+        <v>0.6468970433018389</v>
       </c>
       <c r="D5" t="n">
-        <v>1.249958358381536</v>
+        <v>0.6849966485917538</v>
       </c>
       <c r="E5" t="n">
-        <v>1.235650899457822</v>
+        <v>0.6536978419145394</v>
       </c>
       <c r="F5" t="n">
-        <v>1.235650899457822</v>
+        <v>0.6536978419145395</v>
       </c>
       <c r="G5" t="n">
-        <v>1.249609455756982</v>
+        <v>0.682610145825034</v>
       </c>
       <c r="H5" t="n">
-        <v>1.251995958523709</v>
+        <v>0.6849966485917538</v>
       </c>
       <c r="I5" t="n">
-        <v>1.236371959197645</v>
+        <v>0.6693726492656946</v>
       </c>
       <c r="J5" t="n">
-        <v>1.251995958523709</v>
+        <v>0.6849966485917538</v>
       </c>
       <c r="K5" t="n">
-        <v>1.251995958523709</v>
+        <v>0.6849966485917538</v>
       </c>
       <c r="L5" t="n">
-        <v>1.251995958523709</v>
+        <v>0.6849966485917538</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.517672969347072</v>
+        <v>0.8290253770855238</v>
       </c>
       <c r="C6" t="n">
-        <v>2.164780426712169</v>
+        <v>0.7728300325535953</v>
       </c>
       <c r="D6" t="n">
-        <v>2.315391355828897</v>
+        <v>0.8647591201645364</v>
       </c>
       <c r="E6" t="n">
-        <v>1.983305839954065</v>
+        <v>0.7589290824268267</v>
       </c>
       <c r="F6" t="n">
-        <v>1.523777991294521</v>
+        <v>0.8099202401647148</v>
       </c>
       <c r="G6" t="n">
-        <v>2.176001323382777</v>
+        <v>0.8266388743188005</v>
       </c>
       <c r="H6" t="n">
-        <v>2.178387826150063</v>
+        <v>1.36018660985834</v>
       </c>
       <c r="I6" t="n">
-        <v>2.162763826823439</v>
+        <v>1.286112632980885</v>
       </c>
       <c r="J6" t="n">
-        <v>2.178517675086624</v>
+        <v>0.8579554871535876</v>
       </c>
       <c r="K6" t="n">
-        <v>1.505399851708279</v>
+        <v>0.8242619021380495</v>
       </c>
       <c r="L6" t="n">
-        <v>2.868559741729739</v>
+        <v>0.8441990787272684</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.753466389139457</v>
+        <v>1.251995958523707</v>
       </c>
       <c r="C7" t="n">
-        <v>3.367185637377453</v>
+        <v>1.236371959197645</v>
       </c>
       <c r="D7" t="n">
-        <v>3.382809824885456</v>
+        <v>1.249958358381538</v>
       </c>
       <c r="E7" t="n">
-        <v>4.093433240883297</v>
+        <v>1.235650899457821</v>
       </c>
       <c r="F7" t="n">
-        <v>3.367184573326834</v>
+        <v>1.235650899457821</v>
       </c>
       <c r="G7" t="n">
-        <v>3.380423133936787</v>
+        <v>1.249609455756983</v>
       </c>
       <c r="H7" t="n">
-        <v>3.382809636703519</v>
+        <v>1.251995958523707</v>
       </c>
       <c r="I7" t="n">
-        <v>3.367185637377453</v>
+        <v>1.236371959197645</v>
       </c>
       <c r="J7" t="n">
-        <v>3.382809636703519</v>
+        <v>1.251995958523707</v>
       </c>
       <c r="K7" t="n">
-        <v>3.018165766591867</v>
+        <v>1.251995958523707</v>
       </c>
       <c r="L7" t="n">
-        <v>3.382809636703519</v>
+        <v>1.251995958523707</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.35360134418882</v>
+        <v>1.517672969347074</v>
       </c>
       <c r="C8" t="n">
-        <v>10.94725434028802</v>
+        <v>2.164780426712171</v>
       </c>
       <c r="D8" t="n">
-        <v>9.991512801128147</v>
+        <v>2.315391355828903</v>
       </c>
       <c r="E8" t="n">
-        <v>10.94725434028802</v>
+        <v>1.983305839954068</v>
       </c>
       <c r="F8" t="n">
-        <v>10.94725434028802</v>
+        <v>1.523777991294526</v>
       </c>
       <c r="G8" t="n">
-        <v>10.22548817902284</v>
+        <v>2.176001323382789</v>
       </c>
       <c r="H8" t="n">
-        <v>9.519644064879625</v>
+        <v>2.178387826150074</v>
       </c>
       <c r="I8" t="n">
-        <v>10.94725434028802</v>
+        <v>2.162763826823442</v>
       </c>
       <c r="J8" t="n">
-        <v>10.03854185356813</v>
+        <v>2.178517675086629</v>
       </c>
       <c r="K8" t="n">
-        <v>10.47833120901137</v>
+        <v>1.505399851708281</v>
       </c>
       <c r="L8" t="n">
-        <v>10.5262667537964</v>
+        <v>2.868559741729742</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.753466389139453</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.367185637377452</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.382809824885453</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.093433240883295</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.367184573326833</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.380423133936787</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.382809636703514</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.367185637377452</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.382809636703514</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.01816576659186</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.382809636703514</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10.35360134418883</v>
+      </c>
+      <c r="C10" t="n">
+        <v>10.94725434028802</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.991512801128149</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.94725434028802</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10.94725434028802</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.22548817902285</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.519644064879627</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.94725434028802</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10.03854185356813</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10.47833120901137</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10.5262667537964</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>4.42972620730701</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4.770473380998816</v>
-      </c>
-      <c r="D9" t="n">
-        <v>4.282278249449578</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.770473380998816</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.770473380998816</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.375174408837592</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4.091496484521395</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.770473380998816</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="B11" t="n">
+        <v>4.429726207307013</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.770473380998814</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.282278249449579</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.770473380998814</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.770473380998814</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.37517440883759</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.091496484521397</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.770473380998814</v>
+      </c>
+      <c r="J11" t="n">
         <v>4.301794890622006</v>
       </c>
-      <c r="K9" t="n">
-        <v>4.480558762339609</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4.206588103203175</v>
+      <c r="K11" t="n">
+        <v>4.480558762339614</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.206588103203177</v>
       </c>
     </row>
   </sheetData>
@@ -5195,7 +6155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5263,321 +6223,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.2024433528946</v>
+        <v>4.723260048825782</v>
       </c>
       <c r="C2" t="n">
-        <v>15.13407807888704</v>
+        <v>4.891691153926295</v>
       </c>
       <c r="D2" t="n">
-        <v>40.84459059909562</v>
+        <v>4.744779956741963</v>
       </c>
       <c r="E2" t="n">
-        <v>15.13407807888704</v>
+        <v>4.891691153926295</v>
       </c>
       <c r="F2" t="n">
-        <v>15.13407807888704</v>
+        <v>4.891691153926295</v>
       </c>
       <c r="G2" t="n">
-        <v>33.75944828945894</v>
+        <v>4.731790663196402</v>
       </c>
       <c r="H2" t="n">
-        <v>63.35954606993256</v>
+        <v>4.763015994007907</v>
       </c>
       <c r="I2" t="n">
-        <v>15.13407807888704</v>
+        <v>4.891691153926295</v>
       </c>
       <c r="J2" t="n">
-        <v>38.54011990817401</v>
+        <v>4.738686296711077</v>
       </c>
       <c r="K2" t="n">
-        <v>23.03303473445333</v>
+        <v>4.72455220469355</v>
       </c>
       <c r="L2" t="n">
-        <v>28.41848210970128</v>
+        <v>4.726299824175404</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6573792474045587</v>
+        <v>11.03915836225868</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6192117795575457</v>
+        <v>11.21931318206451</v>
       </c>
       <c r="D3" t="n">
-        <v>0.65737924740456</v>
+        <v>11.03915836225868</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6252618805455005</v>
+        <v>11.21931318206451</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6252618805455006</v>
+        <v>11.21931318206451</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6551616209843386</v>
+        <v>11.03564910568233</v>
       </c>
       <c r="H3" t="n">
-        <v>0.65737924740456</v>
+        <v>11.03915836225868</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6428322992971797</v>
+        <v>11.21931318206451</v>
       </c>
       <c r="J3" t="n">
-        <v>0.65737924740456</v>
+        <v>11.03915836225868</v>
       </c>
       <c r="K3" t="n">
-        <v>0.65737924740456</v>
+        <v>11.03915836225868</v>
       </c>
       <c r="L3" t="n">
-        <v>0.65737924740456</v>
+        <v>11.03915836225868</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.794241838970184</v>
+        <v>23.20244335289469</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7491201927222428</v>
+        <v>15.13407807888709</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8228944726319712</v>
+        <v>40.84459059909564</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7368808731969079</v>
+        <v>15.13407807888709</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7779014537167898</v>
+        <v>15.13407807888709</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7920242125499666</v>
+        <v>33.75944828945898</v>
       </c>
       <c r="H4" t="n">
-        <v>1.26899228327929</v>
+        <v>63.35954606993263</v>
       </c>
       <c r="I4" t="n">
-        <v>1.202646728287159</v>
+        <v>15.13407807888709</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8187554153161067</v>
+        <v>38.54011990817397</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7905101890296946</v>
+        <v>23.03303473445333</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8073869064709507</v>
+        <v>28.41848210970126</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.163229612657925</v>
+        <v>0.6573792474045611</v>
       </c>
       <c r="C5" t="n">
-        <v>1.148682664550553</v>
+        <v>0.6192117795575456</v>
       </c>
       <c r="D5" t="n">
-        <v>1.161332759933575</v>
+        <v>0.6573792474045607</v>
       </c>
       <c r="E5" t="n">
-        <v>1.146290735706018</v>
+        <v>0.6252618805455001</v>
       </c>
       <c r="F5" t="n">
-        <v>1.146290735706018</v>
+        <v>0.625261880545501</v>
       </c>
       <c r="G5" t="n">
-        <v>1.161011986237717</v>
+        <v>0.6551616209843466</v>
       </c>
       <c r="H5" t="n">
-        <v>1.163229612657924</v>
+        <v>0.6573792474045607</v>
       </c>
       <c r="I5" t="n">
-        <v>1.148682664550553</v>
+        <v>0.6428322992971793</v>
       </c>
       <c r="J5" t="n">
-        <v>1.163229612657924</v>
+        <v>0.6573792474045607</v>
       </c>
       <c r="K5" t="n">
-        <v>1.163229612657924</v>
+        <v>0.6573792474045607</v>
       </c>
       <c r="L5" t="n">
-        <v>1.163229612657924</v>
+        <v>0.6573792474045607</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.392062867297581</v>
+        <v>0.7942418389701877</v>
       </c>
       <c r="C6" t="n">
-        <v>1.95916713717531</v>
+        <v>0.7491201927222322</v>
       </c>
       <c r="D6" t="n">
-        <v>2.094051760910842</v>
+        <v>0.8228944726319768</v>
       </c>
       <c r="E6" t="n">
-        <v>1.799606503277377</v>
+        <v>0.7368808731969076</v>
       </c>
       <c r="F6" t="n">
-        <v>1.395650900024631</v>
+        <v>0.77790145371679</v>
       </c>
       <c r="G6" t="n">
-        <v>1.971271592803703</v>
+        <v>0.7920242125499662</v>
       </c>
       <c r="H6" t="n">
-        <v>1.973489219224965</v>
+        <v>1.268992283279295</v>
       </c>
       <c r="I6" t="n">
-        <v>1.958942271116541</v>
+        <v>1.20264672828716</v>
       </c>
       <c r="J6" t="n">
-        <v>1.973603485825766</v>
+        <v>0.8187554153161031</v>
       </c>
       <c r="K6" t="n">
-        <v>1.381262574333378</v>
+        <v>0.7905101890296993</v>
       </c>
       <c r="L6" t="n">
-        <v>2.580837661582811</v>
+        <v>0.8073869064709532</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.418822559760059</v>
+        <v>1.163229612657937</v>
       </c>
       <c r="C7" t="n">
-        <v>2.94129888359597</v>
+        <v>1.148682664550553</v>
       </c>
       <c r="D7" t="n">
-        <v>2.95584605322084</v>
+        <v>1.161332759933583</v>
       </c>
       <c r="E7" t="n">
-        <v>3.561011480089891</v>
+        <v>1.146290735706018</v>
       </c>
       <c r="F7" t="n">
-        <v>2.941298025321453</v>
+        <v>1.146290735706018</v>
       </c>
       <c r="G7" t="n">
-        <v>2.95362820528313</v>
+        <v>1.161011986237716</v>
       </c>
       <c r="H7" t="n">
-        <v>2.955845831703349</v>
+        <v>1.163229612657937</v>
       </c>
       <c r="I7" t="n">
-        <v>2.94129888359597</v>
+        <v>1.148682664550553</v>
       </c>
       <c r="J7" t="n">
-        <v>2.955845831703349</v>
+        <v>1.163229612657937</v>
       </c>
       <c r="K7" t="n">
-        <v>2.644692532055692</v>
+        <v>1.163229612657937</v>
       </c>
       <c r="L7" t="n">
-        <v>2.955845831703349</v>
+        <v>1.163229612657937</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.4744248615447</v>
+        <v>1.392062867297585</v>
       </c>
       <c r="C8" t="n">
-        <v>10.83820242225209</v>
+        <v>1.959167137175307</v>
       </c>
       <c r="D8" t="n">
-        <v>10.02392920009891</v>
+        <v>2.094051760910843</v>
       </c>
       <c r="E8" t="n">
-        <v>10.83820242225209</v>
+        <v>1.799606503277373</v>
       </c>
       <c r="F8" t="n">
-        <v>10.83820242225209</v>
+        <v>1.395650900024631</v>
       </c>
       <c r="G8" t="n">
-        <v>10.22258764114819</v>
+        <v>1.971271592803706</v>
       </c>
       <c r="H8" t="n">
-        <v>9.66790939287989</v>
+        <v>1.973489219224968</v>
       </c>
       <c r="I8" t="n">
-        <v>10.83820242225209</v>
+        <v>1.95894227111654</v>
       </c>
       <c r="J8" t="n">
-        <v>10.15814058752589</v>
+        <v>1.973603485825768</v>
       </c>
       <c r="K8" t="n">
-        <v>10.44799765683993</v>
+        <v>1.381262574333383</v>
       </c>
       <c r="L8" t="n">
-        <v>10.42040486741517</v>
+        <v>2.580837661582812</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.418822559760069</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.941298883595972</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.955846053220854</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.561011480089894</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.941298025321454</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.953628205283133</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.95584583170335</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.941298883595972</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.95584583170335</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.644692532055706</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.95584583170335</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10.4744248615447</v>
+      </c>
+      <c r="C10" t="n">
+        <v>10.83820242225209</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10.02392920009891</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.83820242225209</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10.83820242225209</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.2225876411482</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.667909392879892</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.83820242225209</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10.15814058752589</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10.44799765683994</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10.42040486741517</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>4.466304506302039</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4.718284543683713</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>4.46630450630204</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.718284543683714</v>
+      </c>
+      <c r="D11" t="n">
         <v>4.2828474526159</v>
       </c>
-      <c r="E9" t="n">
-        <v>4.718284543683713</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.718284543683713</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.361845105760217</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4.139093343029382</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.718284543683713</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.337820401570601</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.455572199810639</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4.214830087515404</v>
+      <c r="E11" t="n">
+        <v>4.718284543683714</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.718284543683714</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.36184510576022</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.139093343029379</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.718284543683714</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.3378204015706</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.455572199810642</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.214830087515407</v>
       </c>
     </row>
   </sheetData>
@@ -5591,7 +6631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5659,321 +6699,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.11941719582692</v>
+        <v>4.708297164375132</v>
       </c>
       <c r="C2" t="n">
-        <v>22.51114605144087</v>
+        <v>4.915096312268572</v>
       </c>
       <c r="D2" t="n">
-        <v>35.2880156826565</v>
+        <v>4.727530603647049</v>
       </c>
       <c r="E2" t="n">
-        <v>22.51114605144087</v>
+        <v>4.915096312268572</v>
       </c>
       <c r="F2" t="n">
-        <v>22.51114605144087</v>
+        <v>4.915096312268572</v>
       </c>
       <c r="G2" t="n">
-        <v>30.75333031466786</v>
+        <v>4.718981256061245</v>
       </c>
       <c r="H2" t="n">
-        <v>52.17075500019714</v>
+        <v>4.741556962325959</v>
       </c>
       <c r="I2" t="n">
-        <v>22.51114605144087</v>
+        <v>4.915096312268572</v>
       </c>
       <c r="J2" t="n">
-        <v>38.09472676323377</v>
+        <v>4.726065411749788</v>
       </c>
       <c r="K2" t="n">
-        <v>19.70665806811898</v>
+        <v>4.709694719871252</v>
       </c>
       <c r="L2" t="n">
-        <v>19.65196640284066</v>
+        <v>4.737082643980068</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6690667498525246</v>
+        <v>11.02697454175073</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6342194432597663</v>
+        <v>11.23323141037126</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6690667498525245</v>
+        <v>11.02697454175073</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6401291998031886</v>
+        <v>11.23323141037126</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6401291998031883</v>
+        <v>11.23323141037126</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6672454826844698</v>
+        <v>11.02533839040485</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6690667498525245</v>
+        <v>11.02697454175073</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6570529640197877</v>
+        <v>11.23323141037126</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6690667498525247</v>
+        <v>11.02697454175073</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6690667498525245</v>
+        <v>11.02697454175073</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6690667498525245</v>
+        <v>11.02697454175073</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8138959656281527</v>
+        <v>20.11941719582689</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7905091492893319</v>
+        <v>22.5111460514409</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8357382805599769</v>
+        <v>35.28801568265649</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7780409976357286</v>
+        <v>22.5111460514409</v>
       </c>
       <c r="F4" t="n">
-        <v>0.805331704745295</v>
+        <v>22.5111460514409</v>
       </c>
       <c r="G4" t="n">
-        <v>1.216750358047377</v>
+        <v>30.75333031466777</v>
       </c>
       <c r="H4" t="n">
-        <v>1.270197388682549</v>
+        <v>52.17075500019716</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8018821797954262</v>
+        <v>22.5111460514409</v>
       </c>
       <c r="J4" t="n">
-        <v>1.24524168346307</v>
+        <v>38.09472676323379</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8073733445000936</v>
+        <v>19.706658068119</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8270817415942129</v>
+        <v>19.65196640284076</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.163680860198297</v>
+        <v>0.6690667498525054</v>
       </c>
       <c r="C5" t="n">
-        <v>1.151667074365577</v>
+        <v>0.634219443259766</v>
       </c>
       <c r="D5" t="n">
-        <v>1.161784752601044</v>
+        <v>0.6690667498525055</v>
       </c>
       <c r="E5" t="n">
-        <v>1.147508119593293</v>
+        <v>0.6401291998031885</v>
       </c>
       <c r="F5" t="n">
-        <v>1.147508119593293</v>
+        <v>0.6401291998031884</v>
       </c>
       <c r="G5" t="n">
-        <v>1.161859593030259</v>
+        <v>0.667245482684471</v>
       </c>
       <c r="H5" t="n">
-        <v>1.163680860198296</v>
+        <v>0.6690667498525055</v>
       </c>
       <c r="I5" t="n">
-        <v>1.151667074365577</v>
+        <v>0.6570529640197877</v>
       </c>
       <c r="J5" t="n">
-        <v>1.163680860198296</v>
+        <v>0.6690667498525055</v>
       </c>
       <c r="K5" t="n">
-        <v>1.163680860198296</v>
+        <v>0.6690667498525055</v>
       </c>
       <c r="L5" t="n">
-        <v>1.163680860198296</v>
+        <v>0.6690667498525055</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.376054266649038</v>
+        <v>0.8138959656281601</v>
       </c>
       <c r="C6" t="n">
-        <v>1.921525736563712</v>
+        <v>0.7905091492891902</v>
       </c>
       <c r="D6" t="n">
-        <v>2.050913126099273</v>
+        <v>0.8357382805599756</v>
       </c>
       <c r="E6" t="n">
-        <v>1.768290966458836</v>
+        <v>0.7780409976357759</v>
       </c>
       <c r="F6" t="n">
-        <v>1.380408616819295</v>
+        <v>0.8053317047452946</v>
       </c>
       <c r="G6" t="n">
-        <v>1.933188744056512</v>
+        <v>1.216750358047374</v>
       </c>
       <c r="H6" t="n">
-        <v>1.935010011225767</v>
+        <v>1.270197388682564</v>
       </c>
       <c r="I6" t="n">
-        <v>1.922996225391825</v>
+        <v>0.8018821797954224</v>
       </c>
       <c r="J6" t="n">
-        <v>1.935119861766618</v>
+        <v>1.24524168346307</v>
       </c>
       <c r="K6" t="n">
-        <v>1.365671376747096</v>
+        <v>0.8073733445001126</v>
       </c>
       <c r="L6" t="n">
-        <v>2.518886025299878</v>
+        <v>0.8270817415942199</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.304645483498104</v>
+        <v>1.163680860198312</v>
       </c>
       <c r="C7" t="n">
-        <v>2.792725589313875</v>
+        <v>1.151667074365579</v>
       </c>
       <c r="D7" t="n">
-        <v>2.804739574876595</v>
+        <v>1.161784752601047</v>
       </c>
       <c r="E7" t="n">
-        <v>3.369822649590829</v>
+        <v>1.147508119593293</v>
       </c>
       <c r="F7" t="n">
-        <v>2.792724895286794</v>
+        <v>1.147508119593293</v>
       </c>
       <c r="G7" t="n">
-        <v>2.802918107978555</v>
+        <v>1.161859593030264</v>
       </c>
       <c r="H7" t="n">
-        <v>2.804739375146585</v>
+        <v>1.163680860198314</v>
       </c>
       <c r="I7" t="n">
-        <v>2.792725589313875</v>
+        <v>1.151667074365579</v>
       </c>
       <c r="J7" t="n">
-        <v>2.804739375146585</v>
+        <v>1.163680860198314</v>
       </c>
       <c r="K7" t="n">
-        <v>2.514983094310883</v>
+        <v>1.163680860198314</v>
       </c>
       <c r="L7" t="n">
-        <v>2.804739375146585</v>
+        <v>1.163680860198314</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.52367032402574</v>
+        <v>1.37605426664906</v>
       </c>
       <c r="C8" t="n">
-        <v>10.65008848833902</v>
+        <v>1.921525736563713</v>
       </c>
       <c r="D8" t="n">
-        <v>10.12103863549618</v>
+        <v>2.050913126099296</v>
       </c>
       <c r="E8" t="n">
-        <v>10.65008848833902</v>
+        <v>1.768290966458836</v>
       </c>
       <c r="F8" t="n">
-        <v>10.65008848833902</v>
+        <v>1.380408616819295</v>
       </c>
       <c r="G8" t="n">
-        <v>10.26755288259756</v>
+        <v>1.933188744056511</v>
       </c>
       <c r="H8" t="n">
-        <v>9.849533062539027</v>
+        <v>1.935010011225788</v>
       </c>
       <c r="I8" t="n">
-        <v>10.65008848833902</v>
+        <v>1.922996225391827</v>
       </c>
       <c r="J8" t="n">
-        <v>10.15819938173105</v>
+        <v>1.935119861766627</v>
       </c>
       <c r="K8" t="n">
-        <v>10.49496831595303</v>
+        <v>1.365671376747107</v>
       </c>
       <c r="L8" t="n">
-        <v>9.937631037275693</v>
+        <v>2.518886025299888</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.304645483498111</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.792725589313878</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.804739574876607</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.369822649590832</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.792724895286797</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.802918107978573</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.804739375146611</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.792725589313878</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.804739375146611</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.514983094310889</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.804739375146611</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10.52367032402574</v>
+      </c>
+      <c r="C10" t="n">
+        <v>10.65008848833902</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10.12103863549618</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.65008848833902</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10.65008848833902</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.26755288259757</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.849533062539022</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.65008848833902</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10.15819938173105</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10.49496831595303</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.93763103727569</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>4.47929214137489</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>4.479292141374891</v>
+      </c>
+      <c r="C11" t="n">
         <v>4.649764424377675</v>
       </c>
-      <c r="D9" t="n">
-        <v>4.315326879254791</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>4.315326879254793</v>
+      </c>
+      <c r="E11" t="n">
         <v>4.649764424377675</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>4.649764424377675</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G11" t="n">
         <v>4.374186435089807</v>
       </c>
-      <c r="H9" t="n">
-        <v>4.205817337001276</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="H11" t="n">
+        <v>4.205817337001279</v>
+      </c>
+      <c r="I11" t="n">
         <v>4.649764424377675</v>
       </c>
-      <c r="J9" t="n">
-        <v>4.330769945318671</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.467630191730054</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4.241427877912152</v>
+      <c r="J11" t="n">
+        <v>4.330769945318674</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.467630191730055</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.241427877912154</v>
       </c>
     </row>
   </sheetData>
@@ -5987,7 +7107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6055,321 +7175,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.840772989421843</v>
+        <v>4.569406298770951</v>
       </c>
       <c r="C2" t="n">
-        <v>5.046600451484818</v>
+        <v>4.754760871558624</v>
       </c>
       <c r="D2" t="n">
-        <v>12.84587306252798</v>
+        <v>4.578324411935943</v>
       </c>
       <c r="E2" t="n">
-        <v>5.046600451484818</v>
+        <v>4.754760871558624</v>
       </c>
       <c r="F2" t="n">
-        <v>5.046600451484818</v>
+        <v>4.754760871558624</v>
       </c>
       <c r="G2" t="n">
-        <v>11.09528545459682</v>
+        <v>4.574062484269806</v>
       </c>
       <c r="H2" t="n">
-        <v>21.81023761110935</v>
+        <v>4.586830975301905</v>
       </c>
       <c r="I2" t="n">
-        <v>5.046600451484818</v>
+        <v>4.754760871558624</v>
       </c>
       <c r="J2" t="n">
-        <v>38.4809027794176</v>
+        <v>4.602950336664513</v>
       </c>
       <c r="K2" t="n">
-        <v>9.565063363067464</v>
+        <v>4.573967205289827</v>
       </c>
       <c r="L2" t="n">
-        <v>16.51322131487717</v>
+        <v>4.574032729682838</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5505699701455187</v>
+        <v>10.90485373168633</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5078362165176398</v>
+        <v>11.09410723148836</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5505699701455187</v>
+        <v>10.90485373168633</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5137673493133972</v>
+        <v>11.09410723148836</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5137673493133972</v>
+        <v>11.09410723148836</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5488136173354973</v>
+        <v>10.90344180107251</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5505699701455187</v>
+        <v>10.90485373168633</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5389609205012681</v>
+        <v>11.09410723148836</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5505699701455187</v>
+        <v>10.90485373168633</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5505699701455187</v>
+        <v>10.90485373168633</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5505699701455187</v>
+        <v>10.90485373168633</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9080511702998605</v>
+        <v>5.84077298942181</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5905582158499942</v>
+        <v>5.046600451484807</v>
       </c>
       <c r="D4" t="n">
-        <v>0.927344218071805</v>
+        <v>12.84587306252797</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5819796711865728</v>
+        <v>5.046600451484807</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6060345394891686</v>
+        <v>5.046600451484807</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9062948174898376</v>
+        <v>11.09528545459682</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6258561686930753</v>
+        <v>21.81023761110934</v>
       </c>
       <c r="I4" t="n">
-        <v>0.896442120655609</v>
+        <v>5.046600451484807</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9377661452466539</v>
+        <v>38.48090277941766</v>
       </c>
       <c r="K4" t="n">
-        <v>0.622026672595863</v>
+        <v>9.565063363067464</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6240023328703597</v>
+        <v>16.51322131487714</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9732726160237342</v>
+        <v>0.5505699701455182</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9616635663794832</v>
+        <v>0.5078362165176401</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9712424943740109</v>
+        <v>0.5505699701455182</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9552985883583992</v>
+        <v>0.513767349313398</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9552985883583992</v>
+        <v>0.513767349313398</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9715162632137117</v>
+        <v>0.5488136173354977</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9732726160237342</v>
+        <v>0.5505699701455186</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9616635663794832</v>
+        <v>0.5389609205012679</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9732726160237342</v>
+        <v>0.5505699701455181</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9732726160237342</v>
+        <v>0.5505699701455182</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9732726160237342</v>
+        <v>0.5505699701455182</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.112735791513818</v>
+        <v>0.9080511702998598</v>
       </c>
       <c r="C6" t="n">
-        <v>1.55012783190929</v>
+        <v>0.590558215849922</v>
       </c>
       <c r="D6" t="n">
-        <v>1.658983070661706</v>
+        <v>0.9273442180718063</v>
       </c>
       <c r="E6" t="n">
-        <v>1.426197261437144</v>
+        <v>0.581979671186574</v>
       </c>
       <c r="F6" t="n">
-        <v>1.112882200146089</v>
+        <v>0.6060345394891694</v>
       </c>
       <c r="G6" t="n">
-        <v>1.563411899747855</v>
+        <v>0.9062948174898382</v>
       </c>
       <c r="H6" t="n">
-        <v>1.565168252558928</v>
+        <v>0.6258561686930741</v>
       </c>
       <c r="I6" t="n">
-        <v>1.553559202913625</v>
+        <v>0.8964421206556081</v>
       </c>
       <c r="J6" t="n">
-        <v>1.565257168318461</v>
+        <v>0.9377661452466549</v>
       </c>
       <c r="K6" t="n">
-        <v>1.104331626279148</v>
+        <v>0.6220266725958633</v>
       </c>
       <c r="L6" t="n">
-        <v>2.037771789750673</v>
+        <v>0.6240023328703593</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.929231006803305</v>
+        <v>0.973272616023735</v>
       </c>
       <c r="C7" t="n">
-        <v>2.340350624340596</v>
+        <v>0.9616635663794831</v>
       </c>
       <c r="D7" t="n">
-        <v>2.351959741793527</v>
+        <v>0.9712424943740121</v>
       </c>
       <c r="E7" t="n">
-        <v>2.828170089357879</v>
+        <v>0.9552985883584006</v>
       </c>
       <c r="F7" t="n">
-        <v>2.340350212410813</v>
+        <v>0.9552985883584003</v>
       </c>
       <c r="G7" t="n">
-        <v>2.350203321174826</v>
+        <v>0.9715162632137132</v>
       </c>
       <c r="H7" t="n">
-        <v>2.351959673984848</v>
+        <v>0.973272616023735</v>
       </c>
       <c r="I7" t="n">
-        <v>2.340350624340596</v>
+        <v>0.9616635663794831</v>
       </c>
       <c r="J7" t="n">
-        <v>2.351959673984848</v>
+        <v>0.973272616023735</v>
       </c>
       <c r="K7" t="n">
-        <v>2.107029052556352</v>
+        <v>0.973272616023735</v>
       </c>
       <c r="L7" t="n">
-        <v>2.351959673984848</v>
+        <v>0.973272616023735</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.77878641630892</v>
+        <v>1.112735791513819</v>
       </c>
       <c r="C8" t="n">
-        <v>10.98631955739328</v>
+        <v>1.550127831909291</v>
       </c>
       <c r="D8" t="n">
-        <v>10.59203576837388</v>
+        <v>1.658983070661707</v>
       </c>
       <c r="E8" t="n">
-        <v>10.98631955739328</v>
+        <v>1.426197261437144</v>
       </c>
       <c r="F8" t="n">
-        <v>10.98631955739328</v>
+        <v>1.11288220014609</v>
       </c>
       <c r="G8" t="n">
-        <v>10.65143736924059</v>
+        <v>1.563411899747856</v>
       </c>
       <c r="H8" t="n">
-        <v>10.4229815018412</v>
+        <v>1.56516825255893</v>
       </c>
       <c r="I8" t="n">
-        <v>10.98631955739328</v>
+        <v>1.553559202913625</v>
       </c>
       <c r="J8" t="n">
-        <v>10.08228233604833</v>
+        <v>1.565257168318463</v>
       </c>
       <c r="K8" t="n">
-        <v>10.68343554398878</v>
+        <v>1.104331626279149</v>
       </c>
       <c r="L8" t="n">
-        <v>10.57917739026504</v>
+        <v>2.037771789750673</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.929231006803301</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.340350624340594</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.351959741793527</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.828170089357876</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.340350212410809</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.350203321174825</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.351959673984846</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.340350624340594</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.351959673984846</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.107029052556351</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.351959673984846</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10.77878641630892</v>
+      </c>
+      <c r="C10" t="n">
+        <v>10.98631955739328</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10.59203576837388</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.98631955739328</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10.98631955739328</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.65143736924059</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10.4229815018412</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.98631955739328</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10.08228233604833</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10.68343554398879</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10.57917739026504</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>4.51204526852153</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4.705717136346428</v>
-      </c>
-      <c r="D9" t="n">
-        <v>4.435991241737076</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.705717136346428</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.705717136346428</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="B11" t="n">
+        <v>4.512045268521529</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.70571713634643</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.435991241737077</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.70571713634643</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.70571713634643</v>
+      </c>
+      <c r="G11" t="n">
         <v>4.459399664695813</v>
       </c>
-      <c r="H9" t="n">
-        <v>4.367577575086688</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.705717136346428</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="H11" t="n">
+        <v>4.367577575086687</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.70571713634643</v>
+      </c>
+      <c r="J11" t="n">
         <v>4.228677730269719</v>
       </c>
-      <c r="K9" t="n">
-        <v>4.473221224269544</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4.430993077848419</v>
+      <c r="K11" t="n">
+        <v>4.473221224269543</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.430993077848421</v>
       </c>
     </row>
   </sheetData>
@@ -6383,7 +7583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6451,321 +7651,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-8.493103291908531</v>
+        <v>4.438144929065677</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.7609720920327794</v>
+        <v>4.640298176029895</v>
       </c>
       <c r="D2" t="n">
-        <v>1.837115541883596</v>
+        <v>4.450760780485615</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7609720920327794</v>
+        <v>4.640298176029895</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7609720920327794</v>
+        <v>4.640298176029895</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.519021036227966</v>
+        <v>4.445132509282627</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2661364845333938</v>
+        <v>4.44789492612114</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7609720920327794</v>
+        <v>4.640298176029895</v>
       </c>
       <c r="J2" t="n">
-        <v>2.581654499547328</v>
+        <v>4.451510972261612</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.875363793614806</v>
+        <v>4.443369626589393</v>
       </c>
       <c r="L2" t="n">
-        <v>3.393870198265062</v>
+        <v>4.452378193618096</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4530090076039007</v>
+        <v>10.78919534787452</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4162466196902009</v>
+        <v>10.98521541858173</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4530090076039007</v>
+        <v>10.78919534787452</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4194635875936547</v>
+        <v>10.98521541858173</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4194635875936542</v>
+        <v>10.98521541858173</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4515482966809091</v>
+        <v>10.7892235872626</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4530090076039007</v>
+        <v>10.78919534787452</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4432611702800035</v>
+        <v>10.98521541858173</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4530090076039007</v>
+        <v>10.78919534787452</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4530090076039007</v>
+        <v>10.78919534787452</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4530090076039007</v>
+        <v>10.78919534787452</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6245570909415753</v>
+        <v>-8.493103291908534</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4362854185346251</v>
+        <v>-0.7609720920327807</v>
       </c>
       <c r="D4" t="n">
-        <v>0.456763858836191</v>
+        <v>1.837115541883591</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4338815330347662</v>
+        <v>-0.7609720920327807</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4395782481454897</v>
+        <v>-0.7609720920327807</v>
       </c>
       <c r="G4" t="n">
-        <v>0.623096380018585</v>
+        <v>-2.51902103622798</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6688299330384098</v>
+        <v>-0.2661364845333971</v>
       </c>
       <c r="I4" t="n">
-        <v>0.614809253617681</v>
+        <v>-0.7609720920327807</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4580975056552228</v>
+        <v>2.581654499547328</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4455319635749931</v>
+        <v>-3.875363793614814</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4524024268966865</v>
+        <v>3.393870198265055</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7665646694973242</v>
+        <v>0.45300900760389</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7568168321734311</v>
+        <v>0.4162466196902029</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7646741669902285</v>
+        <v>0.45300900760389</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7493222733042675</v>
+        <v>0.419463587593657</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7493222733042675</v>
+        <v>0.419463587593657</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7651039585743369</v>
+        <v>0.4515482966809005</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7665646694973242</v>
+        <v>0.45300900760389</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7568168321734311</v>
+        <v>0.4432611702800039</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7665646694973242</v>
+        <v>0.45300900760389</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7665646694973242</v>
+        <v>0.45300900760389</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7665646694973242</v>
+        <v>0.45300900760389</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8187351551991719</v>
+        <v>0.6245570909415594</v>
       </c>
       <c r="C6" t="n">
-        <v>1.100448802371562</v>
+        <v>0.4362854185345916</v>
       </c>
       <c r="D6" t="n">
-        <v>1.176330777985528</v>
+        <v>0.4567638588361828</v>
       </c>
       <c r="E6" t="n">
-        <v>1.019427113106113</v>
+        <v>0.4338815330347658</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8150326950583265</v>
+        <v>0.4395782481454897</v>
       </c>
       <c r="G6" t="n">
-        <v>1.113455082320924</v>
+        <v>0.6230963800185826</v>
       </c>
       <c r="H6" t="n">
-        <v>1.114915793243525</v>
+        <v>0.6688299330384084</v>
       </c>
       <c r="I6" t="n">
-        <v>1.105167955920012</v>
+        <v>0.614809253617676</v>
       </c>
       <c r="J6" t="n">
-        <v>1.114974001339691</v>
+        <v>0.458097505655219</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8132334477713486</v>
+        <v>0.4455319635749918</v>
       </c>
       <c r="L6" t="n">
-        <v>1.42430123602532</v>
+        <v>0.4524024268966837</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.302158692183273</v>
+        <v>0.7665646694973181</v>
       </c>
       <c r="C7" t="n">
-        <v>1.555017818236031</v>
+        <v>0.7568168321734308</v>
       </c>
       <c r="D7" t="n">
-        <v>1.564765601863244</v>
+        <v>0.7646741669902233</v>
       </c>
       <c r="E7" t="n">
-        <v>1.858060512586221</v>
+        <v>0.749322273304267</v>
       </c>
       <c r="F7" t="n">
-        <v>1.555017718493063</v>
+        <v>0.749322273304267</v>
       </c>
       <c r="G7" t="n">
-        <v>1.563304944636937</v>
+        <v>0.7651039585743333</v>
       </c>
       <c r="H7" t="n">
-        <v>1.564765655559916</v>
+        <v>0.7665646694973181</v>
       </c>
       <c r="I7" t="n">
-        <v>1.555017818236031</v>
+        <v>0.7568168321734308</v>
       </c>
       <c r="J7" t="n">
-        <v>1.564765655559916</v>
+        <v>0.7665646694973181</v>
       </c>
       <c r="K7" t="n">
-        <v>1.412610127057747</v>
+        <v>0.7665646694973181</v>
       </c>
       <c r="L7" t="n">
-        <v>1.564765655559916</v>
+        <v>0.7665646694973181</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11.01776101399286</v>
+        <v>0.8187351551991702</v>
       </c>
       <c r="C8" t="n">
-        <v>11.02077168575394</v>
+        <v>1.100448802371562</v>
       </c>
       <c r="D8" t="n">
-        <v>10.75335106590374</v>
+        <v>1.176330777985522</v>
       </c>
       <c r="E8" t="n">
-        <v>11.02077168575394</v>
+        <v>1.019427113106112</v>
       </c>
       <c r="F8" t="n">
-        <v>11.02077168575394</v>
+        <v>0.815032695058325</v>
       </c>
       <c r="G8" t="n">
-        <v>10.87151707915761</v>
+        <v>1.113455082320911</v>
       </c>
       <c r="H8" t="n">
-        <v>10.8129508575339</v>
+        <v>1.11491579324352</v>
       </c>
       <c r="I8" t="n">
-        <v>11.02077168575394</v>
+        <v>1.10516795592001</v>
       </c>
       <c r="J8" t="n">
-        <v>10.73802182672989</v>
+        <v>1.114974001339691</v>
       </c>
       <c r="K8" t="n">
-        <v>10.90811948541629</v>
+        <v>0.8132334477713483</v>
       </c>
       <c r="L8" t="n">
-        <v>10.72051591757403</v>
+        <v>1.424301236025314</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.302158692183265</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.555017818236026</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.564765601863238</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.858060512586213</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.555017718493058</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.563304944636934</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.564765655559907</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.555017818236026</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.564765655559907</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.412610127057736</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.564765655559907</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>11.01776101399285</v>
+      </c>
+      <c r="C10" t="n">
+        <v>11.02077168575394</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10.75335106590374</v>
+      </c>
+      <c r="E10" t="n">
+        <v>11.02077168575394</v>
+      </c>
+      <c r="F10" t="n">
+        <v>11.02077168575394</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.8715170791576</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10.8129508575339</v>
+      </c>
+      <c r="I10" t="n">
+        <v>11.02077168575394</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10.73802182672989</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10.90811948541628</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10.72051591757403</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>4.542143035545076</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4.656476390904353</v>
-      </c>
-      <c r="D9" t="n">
-        <v>4.434451517959965</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.656476390904353</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.656476390904353</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.482576310348654</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4.458703758720475</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.656476390904353</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.428226857060475</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.49748048815964</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4.421128833963014</v>
+      <c r="B11" t="n">
+        <v>4.542143035545074</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.656476390904352</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.434451517959962</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.656476390904352</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.656476390904352</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.482576310348651</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.458703758720471</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.656476390904352</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.428226857060467</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.497480488159634</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.421128833963012</v>
       </c>
     </row>
   </sheetData>
@@ -6779,7 +8059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6847,321 +8127,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-16.14636523020396</v>
+        <v>4.391015331806339</v>
       </c>
       <c r="C2" t="n">
-        <v>-2.358123447442418</v>
+        <v>4.602520380587237</v>
       </c>
       <c r="D2" t="n">
-        <v>1.178567613349101</v>
+        <v>4.412265166528237</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.358123447442418</v>
+        <v>4.602520380587237</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.358123447442418</v>
+        <v>4.602520380587237</v>
       </c>
       <c r="G2" t="n">
-        <v>-5.085142344848873</v>
+        <v>4.404653218914002</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2396533538298173</v>
+        <v>4.411073057643553</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.358123447442418</v>
+        <v>4.602520380587237</v>
       </c>
       <c r="J2" t="n">
-        <v>-4.991743022969878</v>
+        <v>4.404984432026623</v>
       </c>
       <c r="K2" t="n">
-        <v>-7.835728329778241</v>
+        <v>4.400386788378418</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.733351953262783</v>
+        <v>4.408862360629826</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4215814049599435</v>
+        <v>10.7510934240242</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3799046079481255</v>
+        <v>10.94890121275444</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4215814049599434</v>
+        <v>10.7510934240242</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3826058155296777</v>
+        <v>10.94890121275444</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3826058155296779</v>
+        <v>10.94890121275444</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4201467114802857</v>
+        <v>10.75127555249526</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4215814049599434</v>
+        <v>10.7510934240242</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4119933543262311</v>
+        <v>10.94890121275444</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4215814049599435</v>
+        <v>10.7510934240242</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4215814049599434</v>
+        <v>10.7510934240242</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4215814049599434</v>
+        <v>10.7510934240242</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3960482518513515</v>
+        <v>-16.14636523020398</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3889051736635056</v>
+        <v>-2.358123447442429</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4120361583568302</v>
+        <v>1.178567613349119</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3883949111473899</v>
+        <v>-2.358123447442429</v>
       </c>
       <c r="F4" t="n">
-        <v>0.391116102298656</v>
+        <v>-2.358123447442429</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3946135583716932</v>
+        <v>-5.085142344848839</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5933200204706798</v>
+        <v>0.2396533538298324</v>
       </c>
       <c r="I4" t="n">
-        <v>0.386460201217636</v>
+        <v>-2.358123447442429</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4065033080957539</v>
+        <v>-4.991743022969882</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3933297299957994</v>
+        <v>-7.835728329778245</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4049686377476835</v>
+        <v>-1.73335195326278</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7149409813817971</v>
+        <v>0.4215814049599548</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7053529307480987</v>
+        <v>0.3799046079481251</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7130516779671046</v>
+        <v>0.4215814049599548</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6960528454695618</v>
+        <v>0.3826058155296773</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6960528454695618</v>
+        <v>0.3826058155296774</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7135062879021519</v>
+        <v>0.4201467114802927</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7149409813817971</v>
+        <v>0.4215814049599548</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7053529307480987</v>
+        <v>0.411993354326231</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7149409813817971</v>
+        <v>0.4215814049599548</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7149409813817971</v>
+        <v>0.4215814049599548</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7149409813817971</v>
+        <v>0.4215814049599548</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7472712023082955</v>
+        <v>0.3960482518513548</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9934428847544372</v>
+        <v>0.3889051736635304</v>
       </c>
       <c r="D6" t="n">
-        <v>1.063856799160994</v>
+        <v>0.412036158356841</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9218954481653795</v>
+        <v>0.3883949111474911</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7415740344976337</v>
+        <v>0.3911161022986559</v>
       </c>
       <c r="G6" t="n">
-        <v>1.008050356239529</v>
+        <v>0.3946135583716978</v>
       </c>
       <c r="H6" t="n">
-        <v>1.009485049718029</v>
+        <v>0.5933200204706902</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9998969990854785</v>
+        <v>0.3864602012176355</v>
       </c>
       <c r="J6" t="n">
-        <v>1.009536582513096</v>
+        <v>0.4065033080957671</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7424004454422528</v>
+        <v>0.3933297299958204</v>
       </c>
       <c r="L6" t="n">
-        <v>1.283389339564585</v>
+        <v>0.4049686377476896</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.168568656287399</v>
+        <v>0.7149409813818246</v>
       </c>
       <c r="C7" t="n">
-        <v>1.389622200542005</v>
+        <v>0.705352930748099</v>
       </c>
       <c r="D7" t="n">
-        <v>1.39921011587752</v>
+        <v>0.713051677967121</v>
       </c>
       <c r="E7" t="n">
-        <v>1.655777455643219</v>
+        <v>0.6960528454695616</v>
       </c>
       <c r="F7" t="n">
-        <v>1.38962209438089</v>
+        <v>0.6960528454695616</v>
       </c>
       <c r="G7" t="n">
-        <v>1.397775557696061</v>
+        <v>0.7135062879021569</v>
       </c>
       <c r="H7" t="n">
-        <v>1.399210251175722</v>
+        <v>0.7149409813818246</v>
       </c>
       <c r="I7" t="n">
-        <v>1.389622200542005</v>
+        <v>0.705352930748099</v>
       </c>
       <c r="J7" t="n">
-        <v>1.399210251175722</v>
+        <v>0.7149409813818246</v>
       </c>
       <c r="K7" t="n">
-        <v>1.260153825183462</v>
+        <v>0.7149409813818246</v>
       </c>
       <c r="L7" t="n">
-        <v>1.399210251175722</v>
+        <v>0.7149409813818246</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11.1784373194175</v>
+        <v>0.7472712023083131</v>
       </c>
       <c r="C8" t="n">
-        <v>11.02419380999647</v>
+        <v>0.9934428847544361</v>
       </c>
       <c r="D8" t="n">
-        <v>10.73304772286091</v>
+        <v>1.063856799161013</v>
       </c>
       <c r="E8" t="n">
-        <v>11.02419380999647</v>
+        <v>0.9218954481653792</v>
       </c>
       <c r="F8" t="n">
-        <v>11.02419380999647</v>
+        <v>0.7415740344976345</v>
       </c>
       <c r="G8" t="n">
-        <v>10.89587323286687</v>
+        <v>1.00805035623954</v>
       </c>
       <c r="H8" t="n">
-        <v>10.75790584951492</v>
+        <v>1.009485049718039</v>
       </c>
       <c r="I8" t="n">
-        <v>11.02419380999647</v>
+        <v>0.9998969990854797</v>
       </c>
       <c r="J8" t="n">
-        <v>10.88458112790753</v>
+        <v>1.009536582513106</v>
       </c>
       <c r="K8" t="n">
-        <v>10.98175509754009</v>
+        <v>0.7424004454422634</v>
       </c>
       <c r="L8" t="n">
-        <v>10.74354619513948</v>
+        <v>1.283389339564579</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.168568656287407</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.389622200542007</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.399210115877522</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.655777455643224</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.389622094380893</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.397775557696068</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.399210251175724</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.389622200542007</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.399210251175723</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.260153825183472</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.399210251175723</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>11.17843731941751</v>
+      </c>
+      <c r="C10" t="n">
+        <v>11.02419380999647</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10.73304772286091</v>
+      </c>
+      <c r="E10" t="n">
+        <v>11.02419380999647</v>
+      </c>
+      <c r="F10" t="n">
+        <v>11.02419380999647</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.89587323286687</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10.75790584951493</v>
+      </c>
+      <c r="I10" t="n">
+        <v>11.02419380999647</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10.88458112790754</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10.98175509754009</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10.74354619513949</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>4.585458166074485</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4.636778752275627</v>
-      </c>
-      <c r="D9" t="n">
-        <v>4.404054314990704</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.636778752275627</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.636778752275627</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.47044562428855</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4.414172732951736</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.636778752275627</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.465721762693612</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.505338584903287</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4.408336045832102</v>
+      <c r="B11" t="n">
+        <v>4.585458166074488</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.636778752275629</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.404054314990708</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.636778752275629</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.636778752275629</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.470445624288552</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.414172732951745</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.636778752275629</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.465721762693613</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.505338584903289</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.408336045832106</v>
       </c>
     </row>
   </sheetData>
@@ -7175,7 +8535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7243,321 +8603,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.37328106632741</v>
+        <v>4.690927305928101</v>
       </c>
       <c r="C2" t="n">
-        <v>10.84053620914785</v>
+        <v>4.853774221961496</v>
       </c>
       <c r="D2" t="n">
-        <v>42.421236092125</v>
+        <v>4.71794423165459</v>
       </c>
       <c r="E2" t="n">
-        <v>10.84053620914785</v>
+        <v>4.853774221961496</v>
       </c>
       <c r="F2" t="n">
-        <v>10.84053620914785</v>
+        <v>4.853774221961496</v>
       </c>
       <c r="G2" t="n">
-        <v>30.25665620235305</v>
+        <v>4.699025686150819</v>
       </c>
       <c r="H2" t="n">
-        <v>66.19441548357777</v>
+        <v>4.740564490796634</v>
       </c>
       <c r="I2" t="n">
-        <v>10.84053620914785</v>
+        <v>4.853774221961496</v>
       </c>
       <c r="J2" t="n">
-        <v>40.4877711599062</v>
+        <v>4.711129204563415</v>
       </c>
       <c r="K2" t="n">
-        <v>20.48700408658032</v>
+        <v>4.692013350230343</v>
       </c>
       <c r="L2" t="n">
-        <v>19.82344641934541</v>
+        <v>4.7226756139542</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6470159839199962</v>
+        <v>11.01213487679657</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6084459063002691</v>
+        <v>11.18748089262026</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6470159839199962</v>
+        <v>11.01213487679657</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6148090900021765</v>
+        <v>11.18748089262026</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6148090900021748</v>
+        <v>11.18748089262026</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6447910617593202</v>
+        <v>11.00855020141487</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6470159839199962</v>
+        <v>11.01213487679657</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6324192092338276</v>
+        <v>11.18748089262026</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6470159839199962</v>
+        <v>11.01213487679657</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6470159839199962</v>
+        <v>11.01213487679657</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6470159839199962</v>
+        <v>11.01213487679657</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7712031010940449</v>
+        <v>19.37328106632738</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7231059761614467</v>
+        <v>10.84053620914782</v>
       </c>
       <c r="D4" t="n">
-        <v>0.810735299117866</v>
+        <v>42.42123609212501</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7109243000661767</v>
+        <v>10.84053620914782</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7544960664927352</v>
+        <v>10.84053620914782</v>
       </c>
       <c r="G4" t="n">
-        <v>1.19743402083263</v>
+        <v>30.25665620235307</v>
       </c>
       <c r="H4" t="n">
-        <v>1.25616067954946</v>
+        <v>66.19441548357776</v>
       </c>
       <c r="I4" t="n">
-        <v>1.185062168307132</v>
+        <v>10.84053620914782</v>
       </c>
       <c r="J4" t="n">
-        <v>1.226977875394524</v>
+        <v>40.48777115990617</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7670867855937624</v>
+        <v>20.48700408658034</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7856859286769959</v>
+        <v>19.82344641934554</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.168105819657791</v>
+        <v>0.6470159839199928</v>
       </c>
       <c r="C5" t="n">
-        <v>1.153509044971628</v>
+        <v>0.6084459063002677</v>
       </c>
       <c r="D5" t="n">
-        <v>1.166070109441767</v>
+        <v>0.6470159839199928</v>
       </c>
       <c r="E5" t="n">
-        <v>1.15149172282825</v>
+        <v>0.6148090900021757</v>
       </c>
       <c r="F5" t="n">
-        <v>1.15149172282825</v>
+        <v>0.6148090900021758</v>
       </c>
       <c r="G5" t="n">
-        <v>1.165880897497126</v>
+        <v>0.6447910617593228</v>
       </c>
       <c r="H5" t="n">
-        <v>1.168105819657791</v>
+        <v>0.6470159839199928</v>
       </c>
       <c r="I5" t="n">
-        <v>1.153509044971628</v>
+        <v>0.6324192092338269</v>
       </c>
       <c r="J5" t="n">
-        <v>1.168105819657791</v>
+        <v>0.6470159839199928</v>
       </c>
       <c r="K5" t="n">
-        <v>1.168105819657791</v>
+        <v>0.6470159839199928</v>
       </c>
       <c r="L5" t="n">
-        <v>1.168105819657791</v>
+        <v>0.6470159839199928</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.393713811386737</v>
+        <v>0.7712031010940407</v>
       </c>
       <c r="C6" t="n">
-        <v>1.974135903903104</v>
+        <v>0.7231059761614406</v>
       </c>
       <c r="D6" t="n">
-        <v>2.111194392126584</v>
+        <v>0.8107352991178641</v>
       </c>
       <c r="E6" t="n">
-        <v>1.810970669073845</v>
+        <v>0.710924300066121</v>
       </c>
       <c r="F6" t="n">
-        <v>1.397965049270314</v>
+        <v>0.7544960664927327</v>
       </c>
       <c r="G6" t="n">
-        <v>1.985746320413793</v>
+        <v>1.197434020832629</v>
       </c>
       <c r="H6" t="n">
-        <v>1.987971242575058</v>
+        <v>1.256160679549451</v>
       </c>
       <c r="I6" t="n">
-        <v>1.973374467888288</v>
+        <v>1.18506216830713</v>
       </c>
       <c r="J6" t="n">
-        <v>1.988088030810461</v>
+        <v>1.22697787539452</v>
       </c>
       <c r="K6" t="n">
-        <v>1.382675174538974</v>
+        <v>0.7670867855937378</v>
       </c>
       <c r="L6" t="n">
-        <v>2.608722820105098</v>
+        <v>0.7856859286769887</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.539719858353155</v>
+        <v>1.168105819657793</v>
       </c>
       <c r="C7" t="n">
-        <v>3.100709494501666</v>
+        <v>1.153509044971628</v>
       </c>
       <c r="D7" t="n">
-        <v>3.115306309422195</v>
+        <v>1.166070109441768</v>
       </c>
       <c r="E7" t="n">
-        <v>3.764922779380629</v>
+        <v>1.15149172282825</v>
       </c>
       <c r="F7" t="n">
-        <v>3.100708482348062</v>
+        <v>1.15149172282825</v>
       </c>
       <c r="G7" t="n">
-        <v>3.113081347027162</v>
+        <v>1.165880897497124</v>
       </c>
       <c r="H7" t="n">
-        <v>3.115306269187837</v>
+        <v>1.168105819657793</v>
       </c>
       <c r="I7" t="n">
-        <v>3.100709494501666</v>
+        <v>1.153509044971628</v>
       </c>
       <c r="J7" t="n">
-        <v>3.115306269187837</v>
+        <v>1.168105819657793</v>
       </c>
       <c r="K7" t="n">
-        <v>2.781809259170401</v>
+        <v>1.168105819657793</v>
       </c>
       <c r="L7" t="n">
-        <v>3.115306269187837</v>
+        <v>1.168105819657793</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.56457362224661</v>
+        <v>1.39371381138674</v>
       </c>
       <c r="C8" t="n">
-        <v>10.94107356799109</v>
+        <v>1.974135903903104</v>
       </c>
       <c r="D8" t="n">
-        <v>9.998858450586546</v>
+        <v>2.111194392126583</v>
       </c>
       <c r="E8" t="n">
-        <v>10.94107356799109</v>
+        <v>1.810970669073846</v>
       </c>
       <c r="F8" t="n">
-        <v>10.94107356799109</v>
+        <v>1.397965049270313</v>
       </c>
       <c r="G8" t="n">
-        <v>10.31952667573078</v>
+        <v>1.98574632041379</v>
       </c>
       <c r="H8" t="n">
-        <v>9.552667022578651</v>
+        <v>1.987971242575056</v>
       </c>
       <c r="I8" t="n">
-        <v>10.94107356799109</v>
+        <v>1.973374467888292</v>
       </c>
       <c r="J8" t="n">
-        <v>10.14805536877187</v>
+        <v>1.98808803081046</v>
       </c>
       <c r="K8" t="n">
-        <v>10.54233195661484</v>
+        <v>1.382675174538972</v>
       </c>
       <c r="L8" t="n">
-        <v>9.916532291816559</v>
+        <v>2.608722820105099</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.539719858353154</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.10070949450167</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.115306309422196</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.764922779380632</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.10070848234806</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.11308134702716</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.115306269187833</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.10070949450167</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.115306269187833</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.781809259170401</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.115306269187833</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10.56457362224661</v>
+      </c>
+      <c r="C10" t="n">
+        <v>10.94107356799109</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.998858450586543</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.94107356799109</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10.94107356799109</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.31952667573078</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.552667022578651</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.94107356799109</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10.14805536877186</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10.54233195661483</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.91653229181656</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>4.487285508814779</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4.741658104001672</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>4.487285508814775</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.741658104001673</v>
+      </c>
+      <c r="D11" t="n">
         <v>4.256900228608655</v>
       </c>
-      <c r="E9" t="n">
-        <v>4.741658104001672</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.741658104001672</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.385517786176867</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4.076501966079401</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.741658104001672</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.317970274754165</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.478251524374579</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4.509270471368746</v>
+      <c r="E11" t="n">
+        <v>4.741658104001673</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.741658104001673</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.385517786176865</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.076501966079396</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.741658104001673</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.317970274754166</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.47825152437458</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.509270471368739</v>
       </c>
     </row>
   </sheetData>
@@ -7571,7 +9011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7639,320 +9079,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.849829020526768</v>
+        <v>4.544974031964355</v>
       </c>
       <c r="C2" t="n">
-        <v>4.51916168281678</v>
+        <v>4.74034024130932</v>
       </c>
       <c r="D2" t="n">
-        <v>27.51775242415582</v>
+        <v>4.5829492886343</v>
       </c>
       <c r="E2" t="n">
-        <v>4.51916168281678</v>
+        <v>4.74034024130932</v>
       </c>
       <c r="F2" t="n">
-        <v>4.51916168281678</v>
+        <v>4.74034024130932</v>
       </c>
       <c r="G2" t="n">
-        <v>9.363727158020659</v>
+        <v>4.557542843215005</v>
       </c>
       <c r="H2" t="n">
-        <v>2.33397639077475</v>
+        <v>4.549843186206677</v>
       </c>
       <c r="I2" t="n">
-        <v>4.51916168281678</v>
+        <v>4.74034024130932</v>
       </c>
       <c r="J2" t="n">
-        <v>16.24387449588982</v>
+        <v>4.565479716505935</v>
       </c>
       <c r="K2" t="n">
-        <v>6.509815903212308</v>
+        <v>4.555475605708552</v>
       </c>
       <c r="L2" t="n">
-        <v>31.2359880270873</v>
+        <v>4.551603137853534</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5365834264660156</v>
+        <v>10.8891623990505</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5051201848818467</v>
+        <v>11.07968326713231</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5365834264660156</v>
+        <v>10.8891623990505</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5092709917577856</v>
+        <v>11.07968326713231</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5092709917577855</v>
+        <v>11.07968326713231</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5348619965774993</v>
+        <v>10.88795529831341</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5365834264660156</v>
+        <v>10.8891623990505</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5251837615778218</v>
+        <v>11.07968326713231</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5365834264660156</v>
+        <v>10.8891623990505</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5365834264660156</v>
+        <v>10.8891623990505</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5365834264660156</v>
+        <v>10.8891623990505</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.860578336767583</v>
+        <v>-1.849829020526775</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5641220116151326</v>
+        <v>4.51916168281677</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6317223486354903</v>
+        <v>27.51775242415579</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5572402585464131</v>
+        <v>4.51916168281677</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5759478298094884</v>
+        <v>4.51916168281677</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8588569068790701</v>
+        <v>9.363727158020669</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9013627012467298</v>
+        <v>2.333976390774746</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8491786718793829</v>
+        <v>4.51916168281677</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6027141512073013</v>
+        <v>16.24387449588985</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5877637145287339</v>
+        <v>6.509815903212309</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5977159082974512</v>
+        <v>31.23598802708725</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.921828622566736</v>
+        <v>0.5365834264660202</v>
       </c>
       <c r="C5" t="n">
-        <v>0.910428957678533</v>
+        <v>0.5051201848818474</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9199346851126612</v>
+        <v>0.5365834264660202</v>
       </c>
       <c r="E5" t="n">
-        <v>0.906419347477859</v>
+        <v>0.5092709917577855</v>
       </c>
       <c r="F5" t="n">
-        <v>0.906419347477859</v>
+        <v>0.5092709917577855</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9201071926782192</v>
+        <v>0.534861996577503</v>
       </c>
       <c r="H5" t="n">
-        <v>0.921828622566736</v>
+        <v>0.5365834264660202</v>
       </c>
       <c r="I5" t="n">
-        <v>0.910428957678533</v>
+        <v>0.5251837615778228</v>
       </c>
       <c r="J5" t="n">
-        <v>0.921828622566736</v>
+        <v>0.5365834264660202</v>
       </c>
       <c r="K5" t="n">
-        <v>0.921828622566736</v>
+        <v>0.5365834264660202</v>
       </c>
       <c r="L5" t="n">
-        <v>0.921828622566736</v>
+        <v>0.5365834264660202</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.041938750688289</v>
+        <v>0.860578336767584</v>
       </c>
       <c r="C6" t="n">
-        <v>1.435121026793415</v>
+        <v>0.5641220116150715</v>
       </c>
       <c r="D6" t="n">
-        <v>1.53205577492988</v>
+        <v>0.6317223486354913</v>
       </c>
       <c r="E6" t="n">
-        <v>1.323722775809473</v>
+        <v>0.5572402585464141</v>
       </c>
       <c r="F6" t="n">
-        <v>1.042144726995557</v>
+        <v>0.5759478298094887</v>
       </c>
       <c r="G6" t="n">
-        <v>1.446159574316738</v>
+        <v>0.8588569068790676</v>
       </c>
       <c r="H6" t="n">
-        <v>1.447881004206163</v>
+        <v>0.9013627012467259</v>
       </c>
       <c r="I6" t="n">
-        <v>1.436481339317049</v>
+        <v>0.8491786718793876</v>
       </c>
       <c r="J6" t="n">
-        <v>1.447960783377617</v>
+        <v>0.6027141512072997</v>
       </c>
       <c r="K6" t="n">
-        <v>1.034398164923792</v>
+        <v>0.5877637145287271</v>
       </c>
       <c r="L6" t="n">
-        <v>1.871921632248573</v>
+        <v>0.5977159082974629</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.71425388642655</v>
+        <v>0.9218286225667365</v>
       </c>
       <c r="C7" t="n">
-        <v>2.065473902764845</v>
+        <v>0.9104289576785326</v>
       </c>
       <c r="D7" t="n">
-        <v>2.076873860254869</v>
+        <v>0.9199346851126637</v>
       </c>
       <c r="E7" t="n">
-        <v>2.483929446546524</v>
+        <v>0.9064193474778603</v>
       </c>
       <c r="F7" t="n">
-        <v>2.06547378750059</v>
+        <v>0.9064193474778603</v>
       </c>
       <c r="G7" t="n">
-        <v>2.075152137764517</v>
+        <v>0.9201071926782138</v>
       </c>
       <c r="H7" t="n">
-        <v>2.076873567653036</v>
+        <v>0.9218286225667365</v>
       </c>
       <c r="I7" t="n">
-        <v>2.065473902764845</v>
+        <v>0.9104289576785326</v>
       </c>
       <c r="J7" t="n">
-        <v>2.076873567653036</v>
+        <v>0.9218286225667365</v>
       </c>
       <c r="K7" t="n">
-        <v>1.866770423300216</v>
+        <v>0.9218286225667365</v>
       </c>
       <c r="L7" t="n">
-        <v>2.076873567653036</v>
+        <v>0.9218286225667365</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.95095278085726</v>
+        <v>1.04193875068829</v>
       </c>
       <c r="C8" t="n">
-        <v>10.97624451745756</v>
+        <v>1.435121026793413</v>
       </c>
       <c r="D8" t="n">
-        <v>10.15539364925888</v>
+        <v>1.532055774929889</v>
       </c>
       <c r="E8" t="n">
-        <v>10.97624451745756</v>
+        <v>1.323722775809473</v>
       </c>
       <c r="F8" t="n">
-        <v>10.97624451745756</v>
+        <v>1.042144726995561</v>
       </c>
       <c r="G8" t="n">
-        <v>10.66212344211597</v>
+        <v>1.446159574316735</v>
       </c>
       <c r="H8" t="n">
-        <v>10.84968071290202</v>
+        <v>1.447881004206163</v>
       </c>
       <c r="I8" t="n">
-        <v>10.97624451745756</v>
+        <v>1.436481339317057</v>
       </c>
       <c r="J8" t="n">
-        <v>10.5240761969105</v>
+        <v>1.447960783377618</v>
       </c>
       <c r="K8" t="n">
-        <v>10.73101435080554</v>
+        <v>1.03439816492379</v>
       </c>
       <c r="L8" t="n">
-        <v>10.22455513049952</v>
+        <v>1.871921632248567</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.714253886426544</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.065473902764841</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.076873860254862</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.483929446546519</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.065473787500587</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.075152137764518</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.076873567653038</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.065473902764841</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.076873567653038</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.866770423300214</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.076873567653038</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10.95095278085727</v>
+      </c>
+      <c r="C10" t="n">
+        <v>10.97624451745756</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10.15539364925889</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.97624451745756</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10.97624451745756</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.66212344211596</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10.84968071290203</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.97624451745756</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10.5240761969105</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10.73101435080554</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10.22455513049952</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>4.573088852600695</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4.693275280567573</v>
-      </c>
-      <c r="D9" t="n">
-        <v>4.249082169096853</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.693275280567573</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.693275280567573</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.454788628961736</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4.53187889318845</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.693275280567573</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.399364331071542</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.483517739769168</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="B11" t="n">
+        <v>4.573088852600697</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.693275280567574</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.249082169096855</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.693275280567574</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.693275280567574</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.454788628961741</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.531878893188454</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.693275280567574</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.399364331071546</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.483517739769171</v>
+      </c>
+      <c r="L11" t="n">
         <v>4.27773573701611</v>
       </c>
     </row>
